--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85334FEA-CBC0-403C-8AEA-41066A1D0368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B87028-D17F-4E68-95C7-CFC112385F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -67,20 +67,6 @@
     <t>結合テスト</t>
     <rPh sb="0" eb="2">
       <t>ケツゴウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にて
-名前(性)　欄</t>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -144,6 +130,103 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>カンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面
+名前(性)　欄</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「さとう」と入力（ひらがな）
+→”確認する”押下</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Sato」と入力（アルファベット）
+→”確認する”押下</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面
+名前(名)　欄</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「太郎」と入力（漢字）
+→”確認する”押下</t>
+    <rPh sb="1" eb="3">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「たろう」と入力（ひらがな）
+→”確認する”押下</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「タロウ」と入力（カタカナ）
+→”確認する”押下</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Taro」と入力（アルファベット）
+→”確認する”押下</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -218,7 +301,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -306,13 +389,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -331,41 +427,53 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B3C2FF-BF7D-4386-AA89-D980D04CF618}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="25.58203125" customWidth="1"/>
@@ -694,15 +802,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
@@ -727,200 +835,288 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="E3" s="15">
+        <v>45960</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="B4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="20">
+        <v>45960</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="G4" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17">
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="20">
         <v>45960</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="E6" s="20">
+        <v>45965</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="20">
+        <v>45965</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="20">
+        <v>45965</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="11">
-        <v>45960</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="D9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="20">
+        <v>45965</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="20">
+        <v>45965</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1"/>
@@ -951,6 +1147,11 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -975,15 +1176,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
@@ -1055,15 +1256,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B87028-D17F-4E68-95C7-CFC112385F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C41284D-4873-4F1E-BEF7-221D59192B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="35">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -54,13 +54,6 @@
   </si>
   <si>
     <t>環境</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>単体テスト</t>
-    <rPh sb="0" eb="2">
-      <t>タンタイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -134,20 +127,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録画面
-名前(性)　欄</t>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「さとう」と入力（ひらがな）
 →”確認する”押下</t>
     <rPh sb="6" eb="8">
@@ -170,23 +149,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録画面
-名前(名)　欄</t>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「太郎」と入力（漢字）
 →”確認する”押下</t>
     <rPh sb="1" eb="3">
@@ -226,6 +188,160 @@
       <t>カクニン</t>
     </rPh>
     <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前(性)　欄</t>
+    <rPh sb="6" eb="7">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前(名)　欄</t>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単体テスト（アカウント登録画面）</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>トウロクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（性）　欄</t>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（名）　欄</t>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄</t>
+    <rPh sb="7" eb="8">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="25" eb="27">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako-1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="26" eb="28">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako&amp;1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="26" eb="28">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ｈanako1234@yahoo.co.jp（Ｈ全角）
+→”確認する”押下</t>
+    <rPh sb="24" eb="26">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hanako1234@yahoo.co.jp（H半角）
+→”確認する”押下</t>
+    <rPh sb="24" eb="26">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako!1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="26" eb="28">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hanako１２３４@yahoo.co.jp（数字全角）
+→”確認する”押下</t>
+    <rPh sb="23" eb="25">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -408,11 +524,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -474,6 +587,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -789,373 +908,1457 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B3C2FF-BF7D-4386-AA89-D980D04CF618}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="B1:H139"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="25.58203125" customWidth="1"/>
-    <col min="2" max="2" width="30.58203125" customWidth="1"/>
-    <col min="3" max="3" width="45.58203125" customWidth="1"/>
-    <col min="4" max="4" width="15.58203125" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.58203125" customWidth="1"/>
-    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="1" max="1" width="33.58203125" customWidth="1"/>
+    <col min="2" max="2" width="25.58203125" customWidth="1"/>
+    <col min="3" max="3" width="33.58203125" customWidth="1"/>
+    <col min="4" max="4" width="45.58203125" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" customWidth="1"/>
+    <col min="6" max="6" width="20.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.58203125" customWidth="1"/>
+    <col min="8" max="8" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="3" t="s">
+    <row r="1" spans="2:8" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" spans="2:8" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="14">
+        <v>45960</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="19">
+        <v>45960</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="19">
+        <v>45960</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="D6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="15">
-        <v>45960</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="10" t="s">
+      <c r="D13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="D14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="D15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="20">
-        <v>45960</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="20">
-        <v>45960</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="20">
-        <v>45965</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="20">
-        <v>45965</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="20">
-        <v>45965</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="20">
-        <v>45965</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="20">
-        <v>45965</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+    </row>
+    <row r="88" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+    </row>
+    <row r="106" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+    </row>
+    <row r="122" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+    </row>
+    <row r="123" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+    </row>
+    <row r="124" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+    </row>
+    <row r="125" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+    </row>
+    <row r="128" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+    </row>
+    <row r="129" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+    </row>
+    <row r="130" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+    </row>
+    <row r="131" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+    </row>
+    <row r="133" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+    </row>
+    <row r="134" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+    </row>
+    <row r="135" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="136" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="137" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="138" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="139" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1170,42 +2373,42 @@
     <col min="1" max="1" width="25.58203125" customWidth="1"/>
     <col min="2" max="3" width="30.58203125" customWidth="1"/>
     <col min="4" max="4" width="15.58203125" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="30.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1250,42 +2453,42 @@
     <col min="1" max="1" width="25.58203125" customWidth="1"/>
     <col min="2" max="3" width="30.58203125" customWidth="1"/>
     <col min="4" max="4" width="15.58203125" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="30.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
     </row>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C41284D-4873-4F1E-BEF7-221D59192B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EF4120-1F53-4388-A3BD-7085F524B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="38">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -67,19 +67,6 @@
     <t>自身</t>
     <rPh sb="0" eb="2">
       <t>ジシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「指定されてる形式で～」というエラー表示</t>
-    <rPh sb="1" eb="3">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -343,6 +330,33 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力せず</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「このフィールドを入力してください。」というエラー</t>
+  </si>
+  <si>
+    <t>「このフィールドを入力してください。」というエラー</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「指定されてる形式で～」というエラー</t>
+    <rPh sb="1" eb="3">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケイシキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -512,9 +526,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -585,14 +597,14 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -908,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B3C2FF-BF7D-4386-AA89-D980D04CF618}">
-  <dimension ref="B1:H139"/>
+  <dimension ref="B1:H144"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="33.58203125" customWidth="1"/>
@@ -923,7 +935,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B1" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -957,36 +969,28 @@
     </row>
     <row r="3" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="14">
-        <v>45960</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>12</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>8</v>
@@ -995,67 +999,67 @@
         <v>45960</v>
       </c>
       <c r="G4" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="22" t="s">
         <v>11</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="19">
         <v>45960</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="19">
-        <v>45965</v>
+        <v>45960</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="7" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="7" t="s">
-        <v>22</v>
+      <c r="B7" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
@@ -1064,41 +1068,33 @@
         <v>45965</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="19">
-        <v>45965</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>12</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>9</v>
@@ -1110,18 +1106,18 @@
         <v>45965</v>
       </c>
       <c r="G9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>9</v>
@@ -1133,66 +1129,82 @@
         <v>45965</v>
       </c>
       <c r="G10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="19">
+        <v>45965</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
@@ -1201,13 +1213,13 @@
     </row>
     <row r="15" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
@@ -1216,10 +1228,10 @@
     </row>
     <row r="16" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>9</v>
@@ -1231,13 +1243,13 @@
     </row>
     <row r="17" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
@@ -1246,13 +1258,13 @@
     </row>
     <row r="18" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6"/>
@@ -1260,14 +1272,14 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>27</v>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="6"/>
@@ -1275,14 +1287,14 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>28</v>
+      <c r="B20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="6"/>
@@ -1290,14 +1302,14 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>29</v>
+      <c r="B21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="6"/>
@@ -1305,14 +1317,14 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>32</v>
+      <c r="B22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
@@ -1321,13 +1333,13 @@
     </row>
     <row r="23" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
@@ -1336,10 +1348,10 @@
     </row>
     <row r="24" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>26</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
@@ -1351,10 +1363,10 @@
     </row>
     <row r="25" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
@@ -1366,10 +1378,10 @@
     </row>
     <row r="26" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -1380,45 +1392,75 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="6"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="6"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="6"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="6"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E31" s="5"/>
       <c r="F31" s="6"/>
       <c r="G31" s="5"/>
@@ -2351,11 +2393,56 @@
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
     </row>
-    <row r="135" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="136" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="137" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="138" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="139" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="135" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+    </row>
+    <row r="136" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+    </row>
+    <row r="138" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+    </row>
+    <row r="139" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+    </row>
+    <row r="140" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="141" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="142" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="143" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="144" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EF4120-1F53-4388-A3BD-7085F524B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797572A1-3C40-42F4-8756-F6E6612DC222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="56">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -234,106 +234,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>hanako@yahoo.co.jp
-→”確認する”押下</t>
-    <rPh sb="21" eb="23">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hanako1234@yahoo.co.jp
-→”確認する”押下</t>
-    <rPh sb="25" eb="27">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hanako-1234@yahoo.co.jp
-→”確認する”押下</t>
-    <rPh sb="26" eb="28">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hanako&amp;1234@yahoo.co.jp
-→”確認する”押下</t>
-    <rPh sb="26" eb="28">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Ｈanako1234@yahoo.co.jp（Ｈ全角）
-→”確認する”押下</t>
-    <rPh sb="24" eb="26">
-      <t>ゼンカク</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Hanako1234@yahoo.co.jp（H半角）
-→”確認する”押下</t>
-    <rPh sb="24" eb="26">
-      <t>ハンカク</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hanako!1234@yahoo.co.jp
-→”確認する”押下</t>
-    <rPh sb="26" eb="28">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hanako１２３４@yahoo.co.jp（数字全角）
-→”確認する”押下</t>
-    <rPh sb="23" eb="25">
-      <t>スウジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ゼンカク</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>入力せず</t>
     <rPh sb="0" eb="2">
       <t>ニュウリョク</t>
@@ -357,6 +257,344 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="19" eb="21">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro-1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="24" eb="26">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Taro1234@yahoo.co.jp（T半角）
+→”確認する”押下</t>
+    <rPh sb="22" eb="24">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ｔaro1234@yahoo.co.jp（T全角）
+→”確認する”押下</t>
+    <rPh sb="22" eb="24">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro!1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="24" eb="26">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro&amp;1234@yahoo.co.jp
+→”確認する”押下</t>
+    <rPh sb="24" eb="26">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taro１２３４@yahoo.co.jp（数字全角）
+→”確認する”押下</t>
+    <rPh sb="21" eb="23">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「tarotaro」と入力
+→”確認する”押下</t>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「taro777」と入力
+→”確認する”押下</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「TaroTaro」と入力
+→”確認する”押下</t>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Ｔarotaro」と入力（Ｈ全角）
+→”確認する”押下</t>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「taro---」と入力
+→”確認する”押下</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「taro!」と入力
+→”確認する”押下</t>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「taro&amp;」と入力
+→”確認する”押下</t>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別 欄</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どちらか選択してください</t>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「男」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="2">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「女」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="2">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1234567」と入力
+→”確認する”押下</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「123ー4567」と入力
+→”確認する”押下</t>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「指定されてる形式で入力してください」というエラー</t>
+    <rPh sb="1" eb="3">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「１２３４５６７」と入力
+→”確認する”押下</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「１２３４５６」と入力（1桁足りず）
+→”確認する”押下</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -365,7 +603,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +653,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -536,7 +783,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -573,9 +820,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -584,9 +828,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -597,13 +838,28 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,35 +1176,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B3C2FF-BF7D-4386-AA89-D980D04CF618}">
-  <dimension ref="B1:H144"/>
+  <dimension ref="B1:H145"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="33.58203125" customWidth="1"/>
     <col min="2" max="2" width="25.58203125" customWidth="1"/>
-    <col min="3" max="3" width="33.58203125" customWidth="1"/>
+    <col min="3" max="3" width="37.58203125" style="25" customWidth="1"/>
     <col min="4" max="4" width="45.58203125" customWidth="1"/>
     <col min="5" max="5" width="15.58203125" customWidth="1"/>
     <col min="6" max="6" width="20.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.58203125" customWidth="1"/>
+    <col min="7" max="7" width="37.58203125" customWidth="1"/>
     <col min="8" max="8" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="2:8" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -971,37 +1227,37 @@
       <c r="B3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>34</v>
+      <c r="C3" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="17">
         <v>45960</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="19" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1009,22 +1265,22 @@
       <c r="B5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <v>45960</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1032,22 +1288,22 @@
       <c r="B6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <v>45960</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1055,22 +1311,22 @@
       <c r="B7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="23" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="17">
         <v>45965</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1078,22 +1334,22 @@
       <c r="B8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>34</v>
+      <c r="C8" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="19"/>
+      <c r="F8" s="17"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="18"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -1102,13 +1358,13 @@
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <v>45965</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1116,7 +1372,7 @@
       <c r="B10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -1125,13 +1381,13 @@
       <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="17">
         <v>45965</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1139,22 +1395,22 @@
       <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="23" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <v>45965</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1162,22 +1418,22 @@
       <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="23" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="17">
         <v>45965</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1185,26 +1441,26 @@
       <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>34</v>
+      <c r="C13" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="19"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="23" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
@@ -1215,11 +1471,11 @@
       <c r="B15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="23" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
@@ -1230,7 +1486,7 @@
       <c r="B16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -1245,11 +1501,11 @@
       <c r="B17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="23" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
@@ -1260,11 +1516,11 @@
       <c r="B18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>34</v>
+      <c r="C18" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6"/>
@@ -1275,11 +1531,11 @@
       <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="6"/>
@@ -1290,11 +1546,11 @@
       <c r="B20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="23" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="6"/>
@@ -1305,7 +1561,7 @@
       <c r="B21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="23" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1320,11 +1576,11 @@
       <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="23" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
@@ -1335,11 +1591,11 @@
       <c r="B23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>34</v>
+      <c r="C23" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
@@ -1350,8 +1606,8 @@
       <c r="B24" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>26</v>
+      <c r="C24" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
@@ -1365,8 +1621,8 @@
       <c r="B25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>27</v>
+      <c r="C25" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
@@ -1380,8 +1636,8 @@
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>28</v>
+      <c r="C26" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -1395,8 +1651,8 @@
       <c r="B27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>31</v>
+      <c r="C27" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>9</v>
@@ -1410,11 +1666,11 @@
       <c r="B28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="21" t="s">
-        <v>30</v>
+      <c r="C28" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="6"/>
@@ -1425,11 +1681,11 @@
       <c r="B29" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>32</v>
+      <c r="C29" s="24" t="s">
+        <v>36</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="6"/>
@@ -1440,11 +1696,11 @@
       <c r="B30" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="6"/>
@@ -1455,11 +1711,11 @@
       <c r="B31" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>33</v>
+      <c r="C31" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="6"/>
@@ -1467,135 +1723,225 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="E32" s="5"/>
       <c r="F32" s="6"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
     </row>
     <row r="34" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E36" s="5"/>
       <c r="F36" s="6"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E37" s="5"/>
       <c r="F37" s="6"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E39" s="5"/>
       <c r="F39" s="6"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="E40" s="5"/>
       <c r="F40" s="6"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E43" s="5"/>
       <c r="F43" s="6"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E44" s="5"/>
       <c r="F44" s="6"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
     <row r="46" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
       <c r="G46" s="5"/>
@@ -1603,7 +1949,7 @@
     </row>
     <row r="47" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="8"/>
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
@@ -1612,7 +1958,7 @@
     </row>
     <row r="48" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="8"/>
       <c r="E48" s="5"/>
       <c r="F48" s="6"/>
@@ -1621,7 +1967,7 @@
     </row>
     <row r="49" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
+      <c r="C49" s="18"/>
       <c r="D49" s="8"/>
       <c r="E49" s="5"/>
       <c r="F49" s="6"/>
@@ -1630,7 +1976,7 @@
     </row>
     <row r="50" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="8"/>
       <c r="E50" s="5"/>
       <c r="F50" s="6"/>
@@ -1639,7 +1985,7 @@
     </row>
     <row r="51" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="8"/>
       <c r="E51" s="5"/>
       <c r="F51" s="6"/>
@@ -1648,7 +1994,7 @@
     </row>
     <row r="52" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="8"/>
       <c r="E52" s="5"/>
       <c r="F52" s="6"/>
@@ -1657,7 +2003,7 @@
     </row>
     <row r="53" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="8"/>
       <c r="E53" s="5"/>
       <c r="F53" s="6"/>
@@ -1666,7 +2012,7 @@
     </row>
     <row r="54" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="8"/>
       <c r="E54" s="5"/>
       <c r="F54" s="6"/>
@@ -1675,7 +2021,7 @@
     </row>
     <row r="55" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
+      <c r="C55" s="18"/>
       <c r="D55" s="8"/>
       <c r="E55" s="5"/>
       <c r="F55" s="6"/>
@@ -1684,7 +2030,7 @@
     </row>
     <row r="56" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="8"/>
       <c r="E56" s="5"/>
       <c r="F56" s="6"/>
@@ -1693,7 +2039,7 @@
     </row>
     <row r="57" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
+      <c r="C57" s="18"/>
       <c r="D57" s="8"/>
       <c r="E57" s="5"/>
       <c r="F57" s="6"/>
@@ -1702,7 +2048,7 @@
     </row>
     <row r="58" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="8"/>
       <c r="E58" s="5"/>
       <c r="F58" s="6"/>
@@ -1711,7 +2057,7 @@
     </row>
     <row r="59" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
+      <c r="C59" s="18"/>
       <c r="D59" s="8"/>
       <c r="E59" s="5"/>
       <c r="F59" s="6"/>
@@ -1720,7 +2066,7 @@
     </row>
     <row r="60" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
+      <c r="C60" s="18"/>
       <c r="D60" s="8"/>
       <c r="E60" s="5"/>
       <c r="F60" s="6"/>
@@ -1729,7 +2075,7 @@
     </row>
     <row r="61" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
+      <c r="C61" s="18"/>
       <c r="D61" s="8"/>
       <c r="E61" s="5"/>
       <c r="F61" s="6"/>
@@ -1738,7 +2084,7 @@
     </row>
     <row r="62" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
+      <c r="C62" s="18"/>
       <c r="D62" s="8"/>
       <c r="E62" s="5"/>
       <c r="F62" s="6"/>
@@ -1747,7 +2093,7 @@
     </row>
     <row r="63" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="8"/>
       <c r="E63" s="5"/>
       <c r="F63" s="6"/>
@@ -1756,7 +2102,7 @@
     </row>
     <row r="64" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
+      <c r="C64" s="18"/>
       <c r="D64" s="8"/>
       <c r="E64" s="5"/>
       <c r="F64" s="6"/>
@@ -1765,7 +2111,7 @@
     </row>
     <row r="65" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+      <c r="C65" s="18"/>
       <c r="D65" s="8"/>
       <c r="E65" s="5"/>
       <c r="F65" s="6"/>
@@ -1774,7 +2120,7 @@
     </row>
     <row r="66" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
+      <c r="C66" s="18"/>
       <c r="D66" s="8"/>
       <c r="E66" s="5"/>
       <c r="F66" s="6"/>
@@ -1783,7 +2129,7 @@
     </row>
     <row r="67" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="C67" s="18"/>
       <c r="D67" s="8"/>
       <c r="E67" s="5"/>
       <c r="F67" s="6"/>
@@ -1792,7 +2138,7 @@
     </row>
     <row r="68" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="C68" s="18"/>
       <c r="D68" s="8"/>
       <c r="E68" s="5"/>
       <c r="F68" s="6"/>
@@ -1801,7 +2147,7 @@
     </row>
     <row r="69" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="C69" s="18"/>
       <c r="D69" s="8"/>
       <c r="E69" s="5"/>
       <c r="F69" s="6"/>
@@ -1810,7 +2156,7 @@
     </row>
     <row r="70" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
+      <c r="C70" s="18"/>
       <c r="D70" s="8"/>
       <c r="E70" s="5"/>
       <c r="F70" s="6"/>
@@ -1819,7 +2165,7 @@
     </row>
     <row r="71" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
+      <c r="C71" s="18"/>
       <c r="D71" s="8"/>
       <c r="E71" s="5"/>
       <c r="F71" s="6"/>
@@ -1828,7 +2174,7 @@
     </row>
     <row r="72" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
+      <c r="C72" s="18"/>
       <c r="D72" s="8"/>
       <c r="E72" s="5"/>
       <c r="F72" s="6"/>
@@ -1837,7 +2183,7 @@
     </row>
     <row r="73" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
+      <c r="C73" s="18"/>
       <c r="D73" s="8"/>
       <c r="E73" s="5"/>
       <c r="F73" s="6"/>
@@ -1846,7 +2192,7 @@
     </row>
     <row r="74" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
+      <c r="C74" s="18"/>
       <c r="D74" s="8"/>
       <c r="E74" s="5"/>
       <c r="F74" s="6"/>
@@ -1855,7 +2201,7 @@
     </row>
     <row r="75" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
+      <c r="C75" s="18"/>
       <c r="D75" s="8"/>
       <c r="E75" s="5"/>
       <c r="F75" s="6"/>
@@ -1864,7 +2210,7 @@
     </row>
     <row r="76" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
+      <c r="C76" s="18"/>
       <c r="D76" s="8"/>
       <c r="E76" s="5"/>
       <c r="F76" s="6"/>
@@ -1873,7 +2219,7 @@
     </row>
     <row r="77" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
+      <c r="C77" s="18"/>
       <c r="D77" s="8"/>
       <c r="E77" s="5"/>
       <c r="F77" s="6"/>
@@ -1882,7 +2228,7 @@
     </row>
     <row r="78" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
+      <c r="C78" s="18"/>
       <c r="D78" s="8"/>
       <c r="E78" s="5"/>
       <c r="F78" s="6"/>
@@ -1891,7 +2237,7 @@
     </row>
     <row r="79" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
+      <c r="C79" s="18"/>
       <c r="D79" s="8"/>
       <c r="E79" s="5"/>
       <c r="F79" s="6"/>
@@ -1900,7 +2246,7 @@
     </row>
     <row r="80" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
+      <c r="C80" s="18"/>
       <c r="D80" s="8"/>
       <c r="E80" s="5"/>
       <c r="F80" s="6"/>
@@ -1909,7 +2255,7 @@
     </row>
     <row r="81" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
+      <c r="C81" s="18"/>
       <c r="D81" s="8"/>
       <c r="E81" s="5"/>
       <c r="F81" s="6"/>
@@ -1918,7 +2264,7 @@
     </row>
     <row r="82" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
+      <c r="C82" s="18"/>
       <c r="D82" s="8"/>
       <c r="E82" s="5"/>
       <c r="F82" s="6"/>
@@ -1927,7 +2273,7 @@
     </row>
     <row r="83" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
+      <c r="C83" s="18"/>
       <c r="D83" s="8"/>
       <c r="E83" s="5"/>
       <c r="F83" s="6"/>
@@ -1936,7 +2282,7 @@
     </row>
     <row r="84" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
+      <c r="C84" s="18"/>
       <c r="D84" s="8"/>
       <c r="E84" s="5"/>
       <c r="F84" s="6"/>
@@ -1945,7 +2291,7 @@
     </row>
     <row r="85" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
+      <c r="C85" s="18"/>
       <c r="D85" s="8"/>
       <c r="E85" s="5"/>
       <c r="F85" s="6"/>
@@ -1954,7 +2300,7 @@
     </row>
     <row r="86" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
+      <c r="C86" s="18"/>
       <c r="D86" s="8"/>
       <c r="E86" s="5"/>
       <c r="F86" s="6"/>
@@ -1963,7 +2309,7 @@
     </row>
     <row r="87" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
+      <c r="C87" s="18"/>
       <c r="D87" s="8"/>
       <c r="E87" s="5"/>
       <c r="F87" s="6"/>
@@ -1972,7 +2318,7 @@
     </row>
     <row r="88" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
+      <c r="C88" s="18"/>
       <c r="D88" s="8"/>
       <c r="E88" s="5"/>
       <c r="F88" s="6"/>
@@ -1981,7 +2327,7 @@
     </row>
     <row r="89" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
+      <c r="C89" s="18"/>
       <c r="D89" s="8"/>
       <c r="E89" s="5"/>
       <c r="F89" s="6"/>
@@ -1990,7 +2336,7 @@
     </row>
     <row r="90" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
+      <c r="C90" s="18"/>
       <c r="D90" s="8"/>
       <c r="E90" s="5"/>
       <c r="F90" s="6"/>
@@ -1999,7 +2345,7 @@
     </row>
     <row r="91" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
+      <c r="C91" s="18"/>
       <c r="D91" s="8"/>
       <c r="E91" s="5"/>
       <c r="F91" s="6"/>
@@ -2008,7 +2354,7 @@
     </row>
     <row r="92" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
+      <c r="C92" s="18"/>
       <c r="D92" s="8"/>
       <c r="E92" s="5"/>
       <c r="F92" s="6"/>
@@ -2017,7 +2363,7 @@
     </row>
     <row r="93" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
+      <c r="C93" s="18"/>
       <c r="D93" s="8"/>
       <c r="E93" s="5"/>
       <c r="F93" s="6"/>
@@ -2026,7 +2372,7 @@
     </row>
     <row r="94" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
+      <c r="C94" s="18"/>
       <c r="D94" s="8"/>
       <c r="E94" s="5"/>
       <c r="F94" s="6"/>
@@ -2035,7 +2381,7 @@
     </row>
     <row r="95" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
+      <c r="C95" s="18"/>
       <c r="D95" s="8"/>
       <c r="E95" s="5"/>
       <c r="F95" s="6"/>
@@ -2044,7 +2390,7 @@
     </row>
     <row r="96" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
+      <c r="C96" s="18"/>
       <c r="D96" s="8"/>
       <c r="E96" s="5"/>
       <c r="F96" s="6"/>
@@ -2053,7 +2399,7 @@
     </row>
     <row r="97" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
+      <c r="C97" s="18"/>
       <c r="D97" s="8"/>
       <c r="E97" s="5"/>
       <c r="F97" s="6"/>
@@ -2062,7 +2408,7 @@
     </row>
     <row r="98" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
+      <c r="C98" s="18"/>
       <c r="D98" s="8"/>
       <c r="E98" s="5"/>
       <c r="F98" s="6"/>
@@ -2071,7 +2417,7 @@
     </row>
     <row r="99" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
+      <c r="C99" s="18"/>
       <c r="D99" s="8"/>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
@@ -2080,7 +2426,7 @@
     </row>
     <row r="100" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
+      <c r="C100" s="18"/>
       <c r="D100" s="8"/>
       <c r="E100" s="5"/>
       <c r="F100" s="6"/>
@@ -2089,7 +2435,7 @@
     </row>
     <row r="101" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
+      <c r="C101" s="18"/>
       <c r="D101" s="8"/>
       <c r="E101" s="5"/>
       <c r="F101" s="6"/>
@@ -2098,7 +2444,7 @@
     </row>
     <row r="102" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
+      <c r="C102" s="18"/>
       <c r="D102" s="8"/>
       <c r="E102" s="5"/>
       <c r="F102" s="6"/>
@@ -2107,7 +2453,7 @@
     </row>
     <row r="103" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
+      <c r="C103" s="18"/>
       <c r="D103" s="8"/>
       <c r="E103" s="5"/>
       <c r="F103" s="6"/>
@@ -2116,7 +2462,7 @@
     </row>
     <row r="104" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
+      <c r="C104" s="18"/>
       <c r="D104" s="8"/>
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
@@ -2125,7 +2471,7 @@
     </row>
     <row r="105" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
+      <c r="C105" s="18"/>
       <c r="D105" s="8"/>
       <c r="E105" s="5"/>
       <c r="F105" s="6"/>
@@ -2134,7 +2480,7 @@
     </row>
     <row r="106" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
+      <c r="C106" s="18"/>
       <c r="D106" s="8"/>
       <c r="E106" s="5"/>
       <c r="F106" s="6"/>
@@ -2143,7 +2489,7 @@
     </row>
     <row r="107" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
+      <c r="C107" s="18"/>
       <c r="D107" s="8"/>
       <c r="E107" s="5"/>
       <c r="F107" s="6"/>
@@ -2152,7 +2498,7 @@
     </row>
     <row r="108" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
+      <c r="C108" s="18"/>
       <c r="D108" s="8"/>
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
@@ -2161,7 +2507,7 @@
     </row>
     <row r="109" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
+      <c r="C109" s="18"/>
       <c r="D109" s="8"/>
       <c r="E109" s="5"/>
       <c r="F109" s="6"/>
@@ -2170,7 +2516,7 @@
     </row>
     <row r="110" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
+      <c r="C110" s="18"/>
       <c r="D110" s="8"/>
       <c r="E110" s="5"/>
       <c r="F110" s="6"/>
@@ -2179,7 +2525,7 @@
     </row>
     <row r="111" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
+      <c r="C111" s="18"/>
       <c r="D111" s="8"/>
       <c r="E111" s="5"/>
       <c r="F111" s="6"/>
@@ -2188,7 +2534,7 @@
     </row>
     <row r="112" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
+      <c r="C112" s="18"/>
       <c r="D112" s="8"/>
       <c r="E112" s="5"/>
       <c r="F112" s="6"/>
@@ -2197,7 +2543,7 @@
     </row>
     <row r="113" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
+      <c r="C113" s="18"/>
       <c r="D113" s="8"/>
       <c r="E113" s="5"/>
       <c r="F113" s="6"/>
@@ -2206,7 +2552,7 @@
     </row>
     <row r="114" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
+      <c r="C114" s="18"/>
       <c r="D114" s="8"/>
       <c r="E114" s="5"/>
       <c r="F114" s="6"/>
@@ -2215,7 +2561,7 @@
     </row>
     <row r="115" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
+      <c r="C115" s="18"/>
       <c r="D115" s="8"/>
       <c r="E115" s="5"/>
       <c r="F115" s="6"/>
@@ -2224,7 +2570,7 @@
     </row>
     <row r="116" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
+      <c r="C116" s="18"/>
       <c r="D116" s="8"/>
       <c r="E116" s="5"/>
       <c r="F116" s="6"/>
@@ -2233,7 +2579,7 @@
     </row>
     <row r="117" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
+      <c r="C117" s="18"/>
       <c r="D117" s="8"/>
       <c r="E117" s="5"/>
       <c r="F117" s="6"/>
@@ -2242,7 +2588,7 @@
     </row>
     <row r="118" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
+      <c r="C118" s="18"/>
       <c r="D118" s="8"/>
       <c r="E118" s="5"/>
       <c r="F118" s="6"/>
@@ -2251,7 +2597,7 @@
     </row>
     <row r="119" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
+      <c r="C119" s="18"/>
       <c r="D119" s="8"/>
       <c r="E119" s="5"/>
       <c r="F119" s="6"/>
@@ -2260,7 +2606,7 @@
     </row>
     <row r="120" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
+      <c r="C120" s="18"/>
       <c r="D120" s="8"/>
       <c r="E120" s="5"/>
       <c r="F120" s="6"/>
@@ -2269,7 +2615,7 @@
     </row>
     <row r="121" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
+      <c r="C121" s="18"/>
       <c r="D121" s="8"/>
       <c r="E121" s="5"/>
       <c r="F121" s="6"/>
@@ -2278,7 +2624,7 @@
     </row>
     <row r="122" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
+      <c r="C122" s="18"/>
       <c r="D122" s="8"/>
       <c r="E122" s="5"/>
       <c r="F122" s="6"/>
@@ -2287,7 +2633,7 @@
     </row>
     <row r="123" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
+      <c r="C123" s="18"/>
       <c r="D123" s="8"/>
       <c r="E123" s="5"/>
       <c r="F123" s="6"/>
@@ -2296,7 +2642,7 @@
     </row>
     <row r="124" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
+      <c r="C124" s="18"/>
       <c r="D124" s="8"/>
       <c r="E124" s="5"/>
       <c r="F124" s="6"/>
@@ -2305,7 +2651,7 @@
     </row>
     <row r="125" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
+      <c r="C125" s="18"/>
       <c r="D125" s="8"/>
       <c r="E125" s="5"/>
       <c r="F125" s="6"/>
@@ -2314,7 +2660,7 @@
     </row>
     <row r="126" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
+      <c r="C126" s="18"/>
       <c r="D126" s="8"/>
       <c r="E126" s="5"/>
       <c r="F126" s="6"/>
@@ -2323,7 +2669,7 @@
     </row>
     <row r="127" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
+      <c r="C127" s="18"/>
       <c r="D127" s="8"/>
       <c r="E127" s="5"/>
       <c r="F127" s="6"/>
@@ -2332,7 +2678,7 @@
     </row>
     <row r="128" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
+      <c r="C128" s="18"/>
       <c r="D128" s="8"/>
       <c r="E128" s="5"/>
       <c r="F128" s="6"/>
@@ -2341,7 +2687,7 @@
     </row>
     <row r="129" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
+      <c r="C129" s="18"/>
       <c r="D129" s="8"/>
       <c r="E129" s="5"/>
       <c r="F129" s="6"/>
@@ -2350,7 +2696,7 @@
     </row>
     <row r="130" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
+      <c r="C130" s="18"/>
       <c r="D130" s="8"/>
       <c r="E130" s="5"/>
       <c r="F130" s="6"/>
@@ -2359,7 +2705,7 @@
     </row>
     <row r="131" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
+      <c r="C131" s="18"/>
       <c r="D131" s="8"/>
       <c r="E131" s="5"/>
       <c r="F131" s="6"/>
@@ -2368,7 +2714,7 @@
     </row>
     <row r="132" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
+      <c r="C132" s="18"/>
       <c r="D132" s="8"/>
       <c r="E132" s="5"/>
       <c r="F132" s="6"/>
@@ -2377,7 +2723,7 @@
     </row>
     <row r="133" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
+      <c r="C133" s="18"/>
       <c r="D133" s="8"/>
       <c r="E133" s="5"/>
       <c r="F133" s="6"/>
@@ -2386,7 +2732,7 @@
     </row>
     <row r="134" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
+      <c r="C134" s="18"/>
       <c r="D134" s="8"/>
       <c r="E134" s="5"/>
       <c r="F134" s="6"/>
@@ -2395,7 +2741,7 @@
     </row>
     <row r="135" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
+      <c r="C135" s="18"/>
       <c r="D135" s="8"/>
       <c r="E135" s="5"/>
       <c r="F135" s="6"/>
@@ -2404,7 +2750,7 @@
     </row>
     <row r="136" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
+      <c r="C136" s="18"/>
       <c r="D136" s="8"/>
       <c r="E136" s="5"/>
       <c r="F136" s="6"/>
@@ -2413,7 +2759,7 @@
     </row>
     <row r="137" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
+      <c r="C137" s="18"/>
       <c r="D137" s="8"/>
       <c r="E137" s="5"/>
       <c r="F137" s="6"/>
@@ -2422,7 +2768,7 @@
     </row>
     <row r="138" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
+      <c r="C138" s="18"/>
       <c r="D138" s="8"/>
       <c r="E138" s="5"/>
       <c r="F138" s="6"/>
@@ -2431,18 +2777,27 @@
     </row>
     <row r="139" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
+      <c r="C139" s="18"/>
       <c r="D139" s="8"/>
       <c r="E139" s="5"/>
       <c r="F139" s="6"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
     </row>
-    <row r="140" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="140" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="8"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+    </row>
     <row r="141" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="142" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="143" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="144" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="145" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
@@ -2466,15 +2821,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -2546,15 +2901,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797572A1-3C40-42F4-8756-F6E6612DC222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BFF0C5-6E71-44D0-A6EF-791BE168C9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="72">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -197,16 +197,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>単体テスト（アカウント登録画面）</t>
-    <rPh sb="0" eb="2">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>トウロクガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カナ（性）　欄</t>
     <rPh sb="3" eb="4">
       <t>セイ</t>
@@ -476,17 +466,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>どちらか選択してください</t>
+    <t>「男」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="2">
+      <t>オトコ</t>
+    </rPh>
     <rPh sb="4" eb="6">
       <t>センタク</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「男」を選択
+    <rPh sb="9" eb="11">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「女」を選択
 →”確認する”押下</t>
     <rPh sb="1" eb="2">
-      <t>オトコ</t>
+      <t>オンナ</t>
     </rPh>
     <rPh sb="4" eb="6">
       <t>センタク</t>
@@ -496,30 +496,6 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「女」を選択
-→”確認する”押下</t>
-    <rPh sb="1" eb="2">
-      <t>オンナ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>郵便番号</t>
-    <rPh sb="0" eb="4">
-      <t>ユウビンバンゴウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -594,6 +570,276 @@
       <t>カクニン</t>
     </rPh>
     <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都道府県 欄</t>
+    <rPh sb="0" eb="4">
+      <t>トドウフケン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「どちらか選択してください」というエラー</t>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「選択してください」というエラー</t>
+    <rPh sb="1" eb="3">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「北海道」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>ホッカイドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「埼玉県」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>サイタマケン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「東京都」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>トウキョウト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村 欄</t>
+    <rPh sb="0" eb="2">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チョウソン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市横浜」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨコハマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「つくばみらい市」と入力
+→”確認する”押下</t>
+    <rPh sb="7" eb="8">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「南アルプス市」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="2">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「NewYork」と入力
+→”確認する”押下</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単体テスト</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録機能</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市1丁目」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウメ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市　３丁目」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウメ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市！」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市（1丁目）」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウメ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -678,7 +924,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -777,13 +1023,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -826,9 +1116,6 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -856,11 +1143,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1176,1634 +1484,1940 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B3C2FF-BF7D-4386-AA89-D980D04CF618}">
-  <dimension ref="B1:H145"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:J146"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="33.58203125" customWidth="1"/>
-    <col min="2" max="2" width="25.58203125" customWidth="1"/>
-    <col min="3" max="3" width="37.58203125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="45.58203125" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" customWidth="1"/>
-    <col min="6" max="6" width="20.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="37.58203125" customWidth="1"/>
-    <col min="8" max="8" width="15.58203125" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="2:8" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="28"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="16">
+        <v>45960</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="28"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="16">
+        <v>45960</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="28"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="16">
+        <v>45960</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="28"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="G7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="17">
-        <v>45960</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="H7" s="16">
+        <v>45965</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="J7" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="17">
-        <v>45960</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="17">
-        <v>45960</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="17">
-        <v>45965</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="28"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="17"/>
+      <c r="E8" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="7" t="s">
+      <c r="I8" s="5"/>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="28"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="17">
+      <c r="H9" s="16">
         <v>45965</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="J9" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="28"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="E10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="17">
+      <c r="H10" s="16">
         <v>45965</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="J10" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="28"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="E11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="17">
+      <c r="H11" s="16">
         <v>45965</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="J11" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="28"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="E12" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="17">
+      <c r="H12" s="16">
         <v>45965</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="J12" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="17"/>
+    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="28"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="7" t="s">
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="28"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="28"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="28"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="28"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="28"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="E18" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="28"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="28"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="28"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="28"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="28"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="28"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="28"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="28"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="28"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="28"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="28"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="28"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="28"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="28"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="E32" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="28"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="E33" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="28"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="E34" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="28"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="E35" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>42</v>
-      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="28"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
+      <c r="E36" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>43</v>
-      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="28"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6"/>
+      <c r="E37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="28"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
+      <c r="E38" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>45</v>
-      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="28"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
+      <c r="E39" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="8" t="s">
+      <c r="H39" s="6"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="28"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="28"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="F41" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="28"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="28"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="28"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="28"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="28"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="28"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="28"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="28"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="28"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="28"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-    </row>
-    <row r="41" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="8" t="s">
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="28"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="8" t="s">
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="28"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="8" t="s">
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="28"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="8"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="8"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="8"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="8"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="8"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="8"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-    </row>
-    <row r="53" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="8"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="8"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="8"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="28"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-    </row>
-    <row r="56" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="8"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="28"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-    </row>
-    <row r="57" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="8"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="28"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-    </row>
-    <row r="58" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="8"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="28"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-    </row>
-    <row r="59" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="8"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="28"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-    </row>
-    <row r="60" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="8"/>
-      <c r="C60" s="18"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="28"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-    </row>
-    <row r="61" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="8"/>
-      <c r="C61" s="18"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="28"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="8"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-    </row>
-    <row r="62" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="8"/>
-      <c r="C62" s="18"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="28"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-    </row>
-    <row r="63" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="8"/>
-      <c r="C63" s="18"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="28"/>
+      <c r="C63" s="30"/>
       <c r="D63" s="8"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="8"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="8"/>
-      <c r="C64" s="18"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="28"/>
+      <c r="C64" s="30"/>
       <c r="D64" s="8"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="6"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-    </row>
-    <row r="65" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="8"/>
-      <c r="C65" s="18"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="28"/>
+      <c r="C65" s="30"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="6"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="8"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-    </row>
-    <row r="66" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="8"/>
-      <c r="C66" s="18"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+    </row>
+    <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="28"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="8"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="6"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-    </row>
-    <row r="67" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="8"/>
-      <c r="C67" s="18"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+    </row>
+    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="28"/>
       <c r="D67" s="8"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="6"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="8"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-    </row>
-    <row r="68" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="8"/>
-      <c r="C68" s="18"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+    </row>
+    <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="28"/>
       <c r="D68" s="8"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="6"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-    </row>
-    <row r="69" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="8"/>
-      <c r="C69" s="18"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+    </row>
+    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="28"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="8"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-    </row>
-    <row r="70" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="8"/>
-      <c r="C70" s="18"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+    </row>
+    <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="28"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="6"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-    </row>
-    <row r="71" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="8"/>
-      <c r="C71" s="18"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+    </row>
+    <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="28"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="8"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="8"/>
-      <c r="C72" s="18"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="28"/>
       <c r="D72" s="8"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="8"/>
-      <c r="C73" s="18"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="28"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="8"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-    </row>
-    <row r="74" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="8"/>
-      <c r="C74" s="18"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="28"/>
       <c r="D74" s="8"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="8"/>
-      <c r="C75" s="18"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="28"/>
       <c r="D75" s="8"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="8"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="8"/>
-      <c r="C76" s="18"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="28"/>
       <c r="D76" s="8"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-    </row>
-    <row r="77" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="8"/>
-      <c r="C77" s="18"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="28"/>
       <c r="D77" s="8"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="6"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="8"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-    </row>
-    <row r="78" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="8"/>
-      <c r="C78" s="18"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="28"/>
       <c r="D78" s="8"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="8"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-    </row>
-    <row r="79" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="8"/>
-      <c r="C79" s="18"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="28"/>
       <c r="D79" s="8"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="6"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="8"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-    </row>
-    <row r="80" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="8"/>
-      <c r="C80" s="18"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="28"/>
       <c r="D80" s="8"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="8"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-    </row>
-    <row r="81" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="8"/>
-      <c r="C81" s="18"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="28"/>
       <c r="D81" s="8"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="8"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-    </row>
-    <row r="82" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="8"/>
-      <c r="C82" s="18"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="28"/>
       <c r="D82" s="8"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="8"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
-    </row>
-    <row r="83" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="8"/>
-      <c r="C83" s="18"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="28"/>
       <c r="D83" s="8"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="8"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-    </row>
-    <row r="84" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="8"/>
-      <c r="C84" s="18"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="28"/>
       <c r="D84" s="8"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="6"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="8"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-    </row>
-    <row r="85" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="8"/>
-      <c r="C85" s="18"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="28"/>
       <c r="D85" s="8"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="8"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-    </row>
-    <row r="86" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="8"/>
-      <c r="C86" s="18"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="28"/>
       <c r="D86" s="8"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="6"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="8"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="8"/>
-      <c r="C87" s="18"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="28"/>
       <c r="D87" s="8"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="8"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-    </row>
-    <row r="88" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="8"/>
-      <c r="C88" s="18"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="28"/>
       <c r="D88" s="8"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="8"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-    </row>
-    <row r="89" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="8"/>
-      <c r="C89" s="18"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="28"/>
       <c r="D89" s="8"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="6"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="8"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-    </row>
-    <row r="90" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="8"/>
-      <c r="C90" s="18"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="28"/>
       <c r="D90" s="8"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="8"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-    </row>
-    <row r="91" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="8"/>
-      <c r="C91" s="18"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="28"/>
       <c r="D91" s="8"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="8"/>
       <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-    </row>
-    <row r="92" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="8"/>
-      <c r="C92" s="18"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="28"/>
       <c r="D92" s="8"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="8"/>
       <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-    </row>
-    <row r="93" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="8"/>
-      <c r="C93" s="18"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="28"/>
       <c r="D93" s="8"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="8"/>
       <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-    </row>
-    <row r="94" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="8"/>
-      <c r="C94" s="18"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="28"/>
       <c r="D94" s="8"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="E94" s="17"/>
+      <c r="F94" s="8"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-    </row>
-    <row r="95" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="8"/>
-      <c r="C95" s="18"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="28"/>
       <c r="D95" s="8"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="6"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="8"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-    </row>
-    <row r="96" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="8"/>
-      <c r="C96" s="18"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="28"/>
       <c r="D96" s="8"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="8"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-    </row>
-    <row r="97" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="8"/>
-      <c r="C97" s="18"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="28"/>
       <c r="D97" s="8"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="6"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="8"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-    </row>
-    <row r="98" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="8"/>
-      <c r="C98" s="18"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="28"/>
       <c r="D98" s="8"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="6"/>
+      <c r="E98" s="17"/>
+      <c r="F98" s="8"/>
       <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-    </row>
-    <row r="99" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="8"/>
-      <c r="C99" s="18"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="28"/>
       <c r="D99" s="8"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="6"/>
+      <c r="E99" s="17"/>
+      <c r="F99" s="8"/>
       <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-    </row>
-    <row r="100" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="8"/>
-      <c r="C100" s="18"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="28"/>
       <c r="D100" s="8"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="6"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="8"/>
       <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-    </row>
-    <row r="101" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="8"/>
-      <c r="C101" s="18"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="28"/>
       <c r="D101" s="8"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="6"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="8"/>
       <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-    </row>
-    <row r="102" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="8"/>
-      <c r="C102" s="18"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="28"/>
       <c r="D102" s="8"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="6"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="8"/>
       <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
-    </row>
-    <row r="103" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="8"/>
-      <c r="C103" s="18"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+    </row>
+    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="28"/>
       <c r="D103" s="8"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="6"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="8"/>
       <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-    </row>
-    <row r="104" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="8"/>
-      <c r="C104" s="18"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+    </row>
+    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="28"/>
       <c r="D104" s="8"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="6"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="8"/>
       <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-    </row>
-    <row r="105" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="8"/>
-      <c r="C105" s="18"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+    </row>
+    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="28"/>
       <c r="D105" s="8"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="6"/>
+      <c r="E105" s="17"/>
+      <c r="F105" s="8"/>
       <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-    </row>
-    <row r="106" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="8"/>
-      <c r="C106" s="18"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+    </row>
+    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="28"/>
       <c r="D106" s="8"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="6"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="8"/>
       <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-    </row>
-    <row r="107" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="8"/>
-      <c r="C107" s="18"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+    </row>
+    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="28"/>
       <c r="D107" s="8"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="6"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="8"/>
       <c r="G107" s="5"/>
-      <c r="H107" s="5"/>
-    </row>
-    <row r="108" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="8"/>
-      <c r="C108" s="18"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+    </row>
+    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="28"/>
       <c r="D108" s="8"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="6"/>
+      <c r="E108" s="17"/>
+      <c r="F108" s="8"/>
       <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
-    </row>
-    <row r="109" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="8"/>
-      <c r="C109" s="18"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+    </row>
+    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="28"/>
       <c r="D109" s="8"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="6"/>
+      <c r="E109" s="17"/>
+      <c r="F109" s="8"/>
       <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
-    </row>
-    <row r="110" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="8"/>
-      <c r="C110" s="18"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+    </row>
+    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="28"/>
       <c r="D110" s="8"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="6"/>
+      <c r="E110" s="17"/>
+      <c r="F110" s="8"/>
       <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
-    </row>
-    <row r="111" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="8"/>
-      <c r="C111" s="18"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+    </row>
+    <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="28"/>
       <c r="D111" s="8"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="6"/>
+      <c r="E111" s="17"/>
+      <c r="F111" s="8"/>
       <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
-    </row>
-    <row r="112" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="8"/>
-      <c r="C112" s="18"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+    </row>
+    <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="28"/>
       <c r="D112" s="8"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="6"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="8"/>
       <c r="G112" s="5"/>
-      <c r="H112" s="5"/>
-    </row>
-    <row r="113" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="8"/>
-      <c r="C113" s="18"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+    </row>
+    <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="28"/>
       <c r="D113" s="8"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="6"/>
+      <c r="E113" s="17"/>
+      <c r="F113" s="8"/>
       <c r="G113" s="5"/>
-      <c r="H113" s="5"/>
-    </row>
-    <row r="114" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="8"/>
-      <c r="C114" s="18"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+    </row>
+    <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="28"/>
       <c r="D114" s="8"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="6"/>
+      <c r="E114" s="17"/>
+      <c r="F114" s="8"/>
       <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-    </row>
-    <row r="115" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="8"/>
-      <c r="C115" s="18"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+    </row>
+    <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="28"/>
       <c r="D115" s="8"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="6"/>
+      <c r="E115" s="17"/>
+      <c r="F115" s="8"/>
       <c r="G115" s="5"/>
-      <c r="H115" s="5"/>
-    </row>
-    <row r="116" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="8"/>
-      <c r="C116" s="18"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+    </row>
+    <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="28"/>
       <c r="D116" s="8"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="6"/>
+      <c r="E116" s="17"/>
+      <c r="F116" s="8"/>
       <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
-    </row>
-    <row r="117" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="8"/>
-      <c r="C117" s="18"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+    </row>
+    <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="28"/>
       <c r="D117" s="8"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="6"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="8"/>
       <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
-    </row>
-    <row r="118" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="8"/>
-      <c r="C118" s="18"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+    </row>
+    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="28"/>
       <c r="D118" s="8"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="6"/>
+      <c r="E118" s="17"/>
+      <c r="F118" s="8"/>
       <c r="G118" s="5"/>
-      <c r="H118" s="5"/>
-    </row>
-    <row r="119" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="8"/>
-      <c r="C119" s="18"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+    </row>
+    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="28"/>
       <c r="D119" s="8"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="6"/>
+      <c r="E119" s="17"/>
+      <c r="F119" s="8"/>
       <c r="G119" s="5"/>
-      <c r="H119" s="5"/>
-    </row>
-    <row r="120" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="8"/>
-      <c r="C120" s="18"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+    </row>
+    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="28"/>
       <c r="D120" s="8"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="6"/>
+      <c r="E120" s="17"/>
+      <c r="F120" s="8"/>
       <c r="G120" s="5"/>
-      <c r="H120" s="5"/>
-    </row>
-    <row r="121" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="8"/>
-      <c r="C121" s="18"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+    </row>
+    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="28"/>
       <c r="D121" s="8"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="6"/>
+      <c r="E121" s="17"/>
+      <c r="F121" s="8"/>
       <c r="G121" s="5"/>
-      <c r="H121" s="5"/>
-    </row>
-    <row r="122" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="8"/>
-      <c r="C122" s="18"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+    </row>
+    <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="28"/>
       <c r="D122" s="8"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="6"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="8"/>
       <c r="G122" s="5"/>
-      <c r="H122" s="5"/>
-    </row>
-    <row r="123" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="8"/>
-      <c r="C123" s="18"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+    </row>
+    <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="28"/>
       <c r="D123" s="8"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="6"/>
+      <c r="E123" s="17"/>
+      <c r="F123" s="8"/>
       <c r="G123" s="5"/>
-      <c r="H123" s="5"/>
-    </row>
-    <row r="124" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="8"/>
-      <c r="C124" s="18"/>
+      <c r="H123" s="6"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+    </row>
+    <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="28"/>
       <c r="D124" s="8"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="6"/>
+      <c r="E124" s="17"/>
+      <c r="F124" s="8"/>
       <c r="G124" s="5"/>
-      <c r="H124" s="5"/>
-    </row>
-    <row r="125" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="8"/>
-      <c r="C125" s="18"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+    </row>
+    <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="28"/>
       <c r="D125" s="8"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="6"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="8"/>
       <c r="G125" s="5"/>
-      <c r="H125" s="5"/>
-    </row>
-    <row r="126" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="8"/>
-      <c r="C126" s="18"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+    </row>
+    <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="28"/>
       <c r="D126" s="8"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="6"/>
+      <c r="E126" s="17"/>
+      <c r="F126" s="8"/>
       <c r="G126" s="5"/>
-      <c r="H126" s="5"/>
-    </row>
-    <row r="127" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="8"/>
-      <c r="C127" s="18"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+    </row>
+    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="28"/>
       <c r="D127" s="8"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="6"/>
+      <c r="E127" s="17"/>
+      <c r="F127" s="8"/>
       <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
-    </row>
-    <row r="128" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="8"/>
-      <c r="C128" s="18"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+    </row>
+    <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" s="28"/>
       <c r="D128" s="8"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="6"/>
+      <c r="E128" s="17"/>
+      <c r="F128" s="8"/>
       <c r="G128" s="5"/>
-      <c r="H128" s="5"/>
-    </row>
-    <row r="129" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B129" s="8"/>
-      <c r="C129" s="18"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+    </row>
+    <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" s="28"/>
       <c r="D129" s="8"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="6"/>
+      <c r="E129" s="17"/>
+      <c r="F129" s="8"/>
       <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
-    </row>
-    <row r="130" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="8"/>
-      <c r="C130" s="18"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5"/>
+    </row>
+    <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" s="28"/>
       <c r="D130" s="8"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="6"/>
+      <c r="E130" s="17"/>
+      <c r="F130" s="8"/>
       <c r="G130" s="5"/>
-      <c r="H130" s="5"/>
-    </row>
-    <row r="131" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B131" s="8"/>
-      <c r="C131" s="18"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+    </row>
+    <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="28"/>
       <c r="D131" s="8"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="6"/>
+      <c r="E131" s="17"/>
+      <c r="F131" s="8"/>
       <c r="G131" s="5"/>
-      <c r="H131" s="5"/>
-    </row>
-    <row r="132" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B132" s="8"/>
-      <c r="C132" s="18"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+    </row>
+    <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="28"/>
       <c r="D132" s="8"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="6"/>
+      <c r="E132" s="17"/>
+      <c r="F132" s="8"/>
       <c r="G132" s="5"/>
-      <c r="H132" s="5"/>
-    </row>
-    <row r="133" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="8"/>
-      <c r="C133" s="18"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5"/>
+    </row>
+    <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" s="28"/>
       <c r="D133" s="8"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="6"/>
+      <c r="E133" s="17"/>
+      <c r="F133" s="8"/>
       <c r="G133" s="5"/>
-      <c r="H133" s="5"/>
-    </row>
-    <row r="134" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="8"/>
-      <c r="C134" s="18"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5"/>
+    </row>
+    <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" s="28"/>
       <c r="D134" s="8"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="6"/>
+      <c r="E134" s="17"/>
+      <c r="F134" s="8"/>
       <c r="G134" s="5"/>
-      <c r="H134" s="5"/>
-    </row>
-    <row r="135" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="8"/>
-      <c r="C135" s="18"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5"/>
+    </row>
+    <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" s="28"/>
       <c r="D135" s="8"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="6"/>
+      <c r="E135" s="17"/>
+      <c r="F135" s="8"/>
       <c r="G135" s="5"/>
-      <c r="H135" s="5"/>
-    </row>
-    <row r="136" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="8"/>
-      <c r="C136" s="18"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+    </row>
+    <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="28"/>
       <c r="D136" s="8"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="6"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="8"/>
       <c r="G136" s="5"/>
-      <c r="H136" s="5"/>
-    </row>
-    <row r="137" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="8"/>
-      <c r="C137" s="18"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5"/>
+    </row>
+    <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" s="28"/>
       <c r="D137" s="8"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="6"/>
+      <c r="E137" s="17"/>
+      <c r="F137" s="8"/>
       <c r="G137" s="5"/>
-      <c r="H137" s="5"/>
-    </row>
-    <row r="138" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="8"/>
-      <c r="C138" s="18"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+    </row>
+    <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="28"/>
       <c r="D138" s="8"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="6"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="8"/>
       <c r="G138" s="5"/>
-      <c r="H138" s="5"/>
-    </row>
-    <row r="139" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B139" s="8"/>
-      <c r="C139" s="18"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+    </row>
+    <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="28"/>
       <c r="D139" s="8"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="6"/>
+      <c r="E139" s="17"/>
+      <c r="F139" s="8"/>
       <c r="G139" s="5"/>
-      <c r="H139" s="5"/>
-    </row>
-    <row r="140" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="8"/>
-      <c r="C140" s="18"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+    </row>
+    <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="28"/>
       <c r="D140" s="8"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="6"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="8"/>
       <c r="G140" s="5"/>
-      <c r="H140" s="5"/>
-    </row>
-    <row r="141" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="142" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="143" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="144" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+    </row>
+    <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" s="29"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+    </row>
+    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="145" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="146" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:H1"/>
+  <mergeCells count="4">
+    <mergeCell ref="C3:C66"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:B141"/>
+    <mergeCell ref="B1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="14" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2821,15 +3435,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -2901,15 +3515,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BFF0C5-6E71-44D0-A6EF-791BE168C9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC4770D-DF6F-4514-8638-53D60C6E16AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="86">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -788,31 +788,179 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「鎌倉市　３丁目」と入力
+    <t>「鎌倉市！」と入力
 →”確認する”押下</t>
     <rPh sb="1" eb="4">
       <t>カマクラシ</t>
     </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市（1丁目）」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
     <rPh sb="6" eb="8">
       <t>チョウメ</t>
     </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地 欄</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「123」と入力
+→”確認する”押下</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1-2-34」と入力
+→”確認する”押下</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1の2の34」と入力
+→”確認する”押下</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1～2～34」と入力
+→”確認する”押下</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1-2＠」と入力
+→”確認する”押下</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「1＆2」と入力
+→”確認する”押下</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「鎌倉市　３丁目」と入力（スペースあり）
+→”確認する”押下</t>
+    <rPh sb="1" eb="4">
+      <t>カマクラシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウメ</t>
+    </rPh>
     <rPh sb="10" eb="12">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「鎌倉市！」と入力
-→”確認する”押下</t>
-    <rPh sb="1" eb="4">
-      <t>カマクラシ</t>
-    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「一の二」と入力
+→”確認する”押下</t>
+    <rPh sb="1" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「イチのニ」と入力
+→”確認する”押下</t>
     <rPh sb="7" eb="9">
       <t>ニュウリョク</t>
     </rPh>
@@ -825,21 +973,73 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「鎌倉市（1丁目）」と入力
+    <t>「ハッピーマンション　102」と入力
+→”確認する”押下</t>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Happyマンション　102」と入力
+→”確認する”押下</t>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント権限 欄</t>
+    <rPh sb="5" eb="7">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「一般」を選択
+→”確認する”押下</t>
+    <rPh sb="1" eb="3">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「管理者」を選択
 →”確認する”押下</t>
     <rPh sb="1" eb="4">
-      <t>カマクラシ</t>
+      <t>カンリシャ</t>
     </rPh>
     <rPh sb="6" eb="8">
-      <t>チョウメ</t>
+      <t>センタク</t>
     </rPh>
     <rPh sb="11" eb="13">
-      <t>ニュウリョク</t>
+      <t>カクニン</t>
     </rPh>
     <rPh sb="16" eb="18">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1487,7 +1687,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J146"/>
+  <dimension ref="B1:J153"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -2515,7 +2715,7 @@
         <v>60</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>9</v>
@@ -2532,7 +2732,7 @@
         <v>60</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>28</v>
@@ -2549,7 +2749,7 @@
         <v>60</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -2579,9 +2779,15 @@
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="28"/>
       <c r="C60" s="30"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="8"/>
+      <c r="D60" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="6"/>
       <c r="I60" s="5"/>
@@ -2590,9 +2796,15 @@
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="28"/>
       <c r="C61" s="30"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="8"/>
+      <c r="D61" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G61" s="5"/>
       <c r="H61" s="6"/>
       <c r="I61" s="5"/>
@@ -2601,9 +2813,15 @@
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="28"/>
       <c r="C62" s="30"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="8"/>
+      <c r="D62" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G62" s="5"/>
       <c r="H62" s="6"/>
       <c r="I62" s="5"/>
@@ -2612,9 +2830,15 @@
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="28"/>
       <c r="C63" s="30"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="8"/>
+      <c r="D63" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="6"/>
       <c r="I63" s="5"/>
@@ -2623,9 +2847,15 @@
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="28"/>
       <c r="C64" s="30"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="8"/>
+      <c r="D64" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="6"/>
       <c r="I64" s="5"/>
@@ -2634,9 +2864,15 @@
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="28"/>
       <c r="C65" s="30"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="8"/>
+      <c r="D65" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G65" s="5"/>
       <c r="H65" s="6"/>
       <c r="I65" s="5"/>
@@ -2644,10 +2880,16 @@
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="28"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="8"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G66" s="5"/>
       <c r="H66" s="6"/>
       <c r="I66" s="5"/>
@@ -2655,9 +2897,16 @@
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="28"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="8"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G67" s="5"/>
       <c r="H67" s="6"/>
       <c r="I67" s="5"/>
@@ -2665,9 +2914,16 @@
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="28"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="8"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G68" s="5"/>
       <c r="H68" s="6"/>
       <c r="I68" s="5"/>
@@ -2675,9 +2931,16 @@
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="28"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="8"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
       <c r="I69" s="5"/>
@@ -2685,9 +2948,16 @@
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="28"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="8"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G70" s="5"/>
       <c r="H70" s="6"/>
       <c r="I70" s="5"/>
@@ -2695,9 +2965,16 @@
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="28"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="8"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G71" s="5"/>
       <c r="H71" s="6"/>
       <c r="I71" s="5"/>
@@ -2705,9 +2982,16 @@
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="28"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="8"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
       <c r="I72" s="5"/>
@@ -2715,6 +2999,7 @@
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="28"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="8"/>
       <c r="E73" s="17"/>
       <c r="F73" s="8"/>
@@ -3394,7 +3679,7 @@
       <c r="J140" s="5"/>
     </row>
     <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="29"/>
+      <c r="B141" s="28"/>
       <c r="D141" s="8"/>
       <c r="E141" s="17"/>
       <c r="F141" s="8"/>
@@ -3403,21 +3688,91 @@
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
     </row>
-    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="145" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="146" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B142" s="28"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+    </row>
+    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" s="28"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+    </row>
+    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B144" s="28"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="6"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+    </row>
+    <row r="145" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" s="28"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="6"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+    </row>
+    <row r="146" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B146" s="28"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="17"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+    </row>
+    <row r="147" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" s="28"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="17"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+    </row>
+    <row r="148" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B148" s="29"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="17"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+    </row>
+    <row r="149" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="150" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="151" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="152" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="153" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C3:C66"/>
+    <mergeCell ref="C3:C73"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B141"/>
+    <mergeCell ref="B3:B148"/>
     <mergeCell ref="B1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="14" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="13" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC4770D-DF6F-4514-8638-53D60C6E16AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8522A6A1-6CD5-4ECD-8D16-B836EB7A2745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -1124,7 +1124,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1267,13 +1267,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1356,6 +1369,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1687,7 +1709,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J153"/>
+  <dimension ref="B1:J93"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -1740,10 +1762,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="33" t="s">
         <v>66</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -1761,8 +1783,8 @@
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="28"/>
-      <c r="C4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
@@ -1786,8 +1808,8 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="28"/>
-      <c r="C5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
@@ -1811,8 +1833,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="28"/>
-      <c r="C6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="9" t="s">
         <v>20</v>
       </c>
@@ -1836,8 +1858,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="28"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
@@ -1861,8 +1883,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="28"/>
-      <c r="C8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
@@ -1878,8 +1900,8 @@
       <c r="J8" s="15"/>
     </row>
     <row r="9" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="28"/>
-      <c r="C9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
@@ -1903,8 +1925,8 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="28"/>
-      <c r="C10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
@@ -1928,8 +1950,8 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="28"/>
-      <c r="C11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
@@ -1953,8 +1975,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="28"/>
-      <c r="C12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
@@ -1978,8 +2000,8 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="28"/>
-      <c r="C13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
@@ -1995,8 +2017,8 @@
       <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="28"/>
-      <c r="C14" s="30"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="7" t="s">
         <v>22</v>
       </c>
@@ -2012,8 +2034,8 @@
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="28"/>
-      <c r="C15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="7" t="s">
         <v>22</v>
       </c>
@@ -2029,8 +2051,8 @@
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="28"/>
-      <c r="C16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
@@ -2046,8 +2068,8 @@
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="28"/>
-      <c r="C17" s="30"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="7" t="s">
         <v>22</v>
       </c>
@@ -2063,8 +2085,8 @@
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="28"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="7" t="s">
         <v>23</v>
       </c>
@@ -2080,8 +2102,8 @@
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="28"/>
-      <c r="C19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="33"/>
       <c r="D19" s="7" t="s">
         <v>23</v>
       </c>
@@ -2097,8 +2119,8 @@
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="28"/>
-      <c r="C20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="33"/>
       <c r="D20" s="7" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2136,8 @@
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="28"/>
-      <c r="C21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="33"/>
       <c r="D21" s="7" t="s">
         <v>23</v>
       </c>
@@ -2131,8 +2153,8 @@
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="28"/>
-      <c r="C22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="33"/>
       <c r="D22" s="7" t="s">
         <v>23</v>
       </c>
@@ -2148,8 +2170,8 @@
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="28"/>
-      <c r="C23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="33"/>
       <c r="D23" s="8" t="s">
         <v>24</v>
       </c>
@@ -2165,8 +2187,8 @@
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="28"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="33"/>
       <c r="D24" s="8" t="s">
         <v>24</v>
       </c>
@@ -2182,8 +2204,8 @@
       <c r="J24" s="5"/>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="28"/>
-      <c r="C25" s="30"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="33"/>
       <c r="D25" s="8" t="s">
         <v>24</v>
       </c>
@@ -2199,8 +2221,8 @@
       <c r="J25" s="5"/>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="28"/>
-      <c r="C26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="33"/>
       <c r="D26" s="8" t="s">
         <v>24</v>
       </c>
@@ -2216,8 +2238,8 @@
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="28"/>
-      <c r="C27" s="30"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="33"/>
       <c r="D27" s="8" t="s">
         <v>24</v>
       </c>
@@ -2233,8 +2255,8 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="28"/>
-      <c r="C28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="33"/>
       <c r="D28" s="8" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2272,8 @@
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="28"/>
-      <c r="C29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="33"/>
       <c r="D29" s="8" t="s">
         <v>24</v>
       </c>
@@ -2267,8 +2289,8 @@
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="28"/>
-      <c r="C30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="33"/>
       <c r="D30" s="8" t="s">
         <v>24</v>
       </c>
@@ -2284,8 +2306,8 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="28"/>
-      <c r="C31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="33"/>
       <c r="D31" s="8" t="s">
         <v>24</v>
       </c>
@@ -2301,8 +2323,8 @@
       <c r="J31" s="5"/>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="28"/>
-      <c r="C32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="33"/>
       <c r="D32" s="8" t="s">
         <v>29</v>
       </c>
@@ -2318,8 +2340,8 @@
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="28"/>
-      <c r="C33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="33"/>
       <c r="D33" s="8" t="s">
         <v>29</v>
       </c>
@@ -2335,8 +2357,8 @@
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="28"/>
-      <c r="C34" s="30"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="33"/>
       <c r="D34" s="8" t="s">
         <v>29</v>
       </c>
@@ -2352,8 +2374,8 @@
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="28"/>
-      <c r="C35" s="30"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="33"/>
       <c r="D35" s="8" t="s">
         <v>29</v>
       </c>
@@ -2369,8 +2391,8 @@
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="28"/>
-      <c r="C36" s="30"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="33"/>
       <c r="D36" s="8" t="s">
         <v>29</v>
       </c>
@@ -2386,8 +2408,8 @@
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="28"/>
-      <c r="C37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="33"/>
       <c r="D37" s="8" t="s">
         <v>29</v>
       </c>
@@ -2403,8 +2425,8 @@
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="28"/>
-      <c r="C38" s="30"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="33"/>
       <c r="D38" s="8" t="s">
         <v>29</v>
       </c>
@@ -2420,8 +2442,8 @@
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="28"/>
-      <c r="C39" s="30"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="33"/>
       <c r="D39" s="8" t="s">
         <v>29</v>
       </c>
@@ -2437,8 +2459,8 @@
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="28"/>
-      <c r="C40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="33"/>
       <c r="D40" s="8" t="s">
         <v>45</v>
       </c>
@@ -2454,8 +2476,8 @@
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="28"/>
-      <c r="C41" s="30"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="33"/>
       <c r="D41" s="8" t="s">
         <v>45</v>
       </c>
@@ -2471,8 +2493,8 @@
       <c r="J41" s="5"/>
     </row>
     <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="28"/>
-      <c r="C42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="33"/>
       <c r="D42" s="8" t="s">
         <v>45</v>
       </c>
@@ -2488,8 +2510,8 @@
       <c r="J42" s="5"/>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="28"/>
-      <c r="C43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="33"/>
       <c r="D43" s="8" t="s">
         <v>54</v>
       </c>
@@ -2505,8 +2527,8 @@
       <c r="J43" s="5"/>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="28"/>
-      <c r="C44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="33"/>
       <c r="D44" s="8" t="s">
         <v>54</v>
       </c>
@@ -2522,8 +2544,8 @@
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="28"/>
-      <c r="C45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="33"/>
       <c r="D45" s="8" t="s">
         <v>54</v>
       </c>
@@ -2539,8 +2561,8 @@
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="28"/>
-      <c r="C46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="33"/>
       <c r="D46" s="8" t="s">
         <v>54</v>
       </c>
@@ -2556,8 +2578,8 @@
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="28"/>
-      <c r="C47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="33"/>
       <c r="D47" s="8" t="s">
         <v>53</v>
       </c>
@@ -2573,8 +2595,8 @@
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="28"/>
-      <c r="C48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="33"/>
       <c r="D48" s="8" t="s">
         <v>53</v>
       </c>
@@ -2590,8 +2612,8 @@
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="28"/>
-      <c r="C49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="33"/>
       <c r="D49" s="8" t="s">
         <v>53</v>
       </c>
@@ -2607,8 +2629,8 @@
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="28"/>
-      <c r="C50" s="30"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="33"/>
       <c r="D50" s="8" t="s">
         <v>53</v>
       </c>
@@ -2624,8 +2646,8 @@
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="28"/>
-      <c r="C51" s="30"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="33"/>
       <c r="D51" s="8" t="s">
         <v>60</v>
       </c>
@@ -2641,8 +2663,8 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="28"/>
-      <c r="C52" s="30"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="33"/>
       <c r="D52" s="8" t="s">
         <v>60</v>
       </c>
@@ -2658,8 +2680,8 @@
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="28"/>
-      <c r="C53" s="30"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="33"/>
       <c r="D53" s="8" t="s">
         <v>60</v>
       </c>
@@ -2675,8 +2697,8 @@
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="28"/>
-      <c r="C54" s="30"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="33"/>
       <c r="D54" s="8" t="s">
         <v>60</v>
       </c>
@@ -2692,8 +2714,8 @@
       <c r="J54" s="5"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="28"/>
-      <c r="C55" s="30"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="33"/>
       <c r="D55" s="8" t="s">
         <v>60</v>
       </c>
@@ -2709,8 +2731,8 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="28"/>
-      <c r="C56" s="30"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="33"/>
       <c r="D56" s="8" t="s">
         <v>60</v>
       </c>
@@ -2726,8 +2748,8 @@
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="28"/>
-      <c r="C57" s="30"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="33"/>
       <c r="D57" s="8" t="s">
         <v>60</v>
       </c>
@@ -2743,8 +2765,8 @@
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="28"/>
-      <c r="C58" s="30"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="33"/>
       <c r="D58" s="8" t="s">
         <v>60</v>
       </c>
@@ -2760,8 +2782,8 @@
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="28"/>
-      <c r="C59" s="30"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="33"/>
       <c r="D59" s="8" t="s">
         <v>60</v>
       </c>
@@ -2777,8 +2799,8 @@
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="28"/>
-      <c r="C60" s="30"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="33"/>
       <c r="D60" s="8" t="s">
         <v>71</v>
       </c>
@@ -2794,8 +2816,8 @@
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="28"/>
-      <c r="C61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="33"/>
       <c r="D61" s="8" t="s">
         <v>71</v>
       </c>
@@ -2811,8 +2833,8 @@
       <c r="J61" s="5"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="28"/>
-      <c r="C62" s="30"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="33"/>
       <c r="D62" s="8" t="s">
         <v>71</v>
       </c>
@@ -2828,8 +2850,8 @@
       <c r="J62" s="5"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="28"/>
-      <c r="C63" s="30"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="33"/>
       <c r="D63" s="8" t="s">
         <v>71</v>
       </c>
@@ -2845,8 +2867,8 @@
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="28"/>
-      <c r="C64" s="30"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="33"/>
       <c r="D64" s="8" t="s">
         <v>71</v>
       </c>
@@ -2862,8 +2884,8 @@
       <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="28"/>
-      <c r="C65" s="30"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="33"/>
       <c r="D65" s="8" t="s">
         <v>71</v>
       </c>
@@ -2879,8 +2901,8 @@
       <c r="J65" s="5"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="28"/>
-      <c r="C66" s="30"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="33"/>
       <c r="D66" s="8" t="s">
         <v>71</v>
       </c>
@@ -2896,8 +2918,8 @@
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="28"/>
-      <c r="C67" s="30"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="33"/>
       <c r="D67" s="8" t="s">
         <v>71</v>
       </c>
@@ -2913,8 +2935,8 @@
       <c r="J67" s="5"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="28"/>
-      <c r="C68" s="30"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="33"/>
       <c r="D68" s="8" t="s">
         <v>71</v>
       </c>
@@ -2930,8 +2952,8 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="28"/>
-      <c r="C69" s="30"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="33"/>
       <c r="D69" s="8" t="s">
         <v>71</v>
       </c>
@@ -2947,8 +2969,8 @@
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="28"/>
-      <c r="C70" s="30"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="33"/>
       <c r="D70" s="8" t="s">
         <v>71</v>
       </c>
@@ -2964,8 +2986,8 @@
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="28"/>
-      <c r="C71" s="30"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="33"/>
       <c r="D71" s="8" t="s">
         <v>83</v>
       </c>
@@ -2981,8 +3003,8 @@
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="28"/>
-      <c r="C72" s="30"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="33"/>
       <c r="D72" s="8" t="s">
         <v>83</v>
       </c>
@@ -2998,8 +3020,8 @@
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="28"/>
-      <c r="C73" s="31"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="34"/>
       <c r="D73" s="8"/>
       <c r="E73" s="17"/>
       <c r="F73" s="8"/>
@@ -3009,7 +3031,8 @@
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="28"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="28"/>
       <c r="D74" s="8"/>
       <c r="E74" s="17"/>
       <c r="F74" s="8"/>
@@ -3019,7 +3042,8 @@
       <c r="J74" s="5"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="28"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="8"/>
       <c r="E75" s="17"/>
       <c r="F75" s="8"/>
@@ -3029,7 +3053,8 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="28"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="8"/>
       <c r="E76" s="17"/>
       <c r="F76" s="8"/>
@@ -3039,7 +3064,8 @@
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="28"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="8"/>
       <c r="E77" s="17"/>
       <c r="F77" s="8"/>
@@ -3049,7 +3075,8 @@
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="28"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="8"/>
       <c r="E78" s="17"/>
       <c r="F78" s="8"/>
@@ -3059,7 +3086,8 @@
       <c r="J78" s="5"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="28"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="8"/>
       <c r="E79" s="17"/>
       <c r="F79" s="8"/>
@@ -3069,7 +3097,8 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="28"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="8"/>
       <c r="E80" s="17"/>
       <c r="F80" s="8"/>
@@ -3079,7 +3108,8 @@
       <c r="J80" s="5"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="28"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="8"/>
       <c r="E81" s="17"/>
       <c r="F81" s="8"/>
@@ -3089,7 +3119,8 @@
       <c r="J81" s="5"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="28"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="8"/>
       <c r="E82" s="17"/>
       <c r="F82" s="8"/>
@@ -3099,7 +3130,8 @@
       <c r="J82" s="5"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="28"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="8"/>
       <c r="E83" s="17"/>
       <c r="F83" s="8"/>
@@ -3109,7 +3141,8 @@
       <c r="J83" s="5"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="28"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="8"/>
       <c r="E84" s="17"/>
       <c r="F84" s="8"/>
@@ -3119,7 +3152,8 @@
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="28"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="29"/>
       <c r="D85" s="8"/>
       <c r="E85" s="17"/>
       <c r="F85" s="8"/>
@@ -3129,7 +3163,8 @@
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="28"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="8"/>
       <c r="E86" s="17"/>
       <c r="F86" s="8"/>
@@ -3139,7 +3174,8 @@
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="28"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="8"/>
       <c r="E87" s="17"/>
       <c r="F87" s="8"/>
@@ -3149,7 +3185,8 @@
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="28"/>
+      <c r="B88" s="31"/>
+      <c r="C88" s="29"/>
       <c r="D88" s="8"/>
       <c r="E88" s="17"/>
       <c r="F88" s="8"/>
@@ -3159,7 +3196,8 @@
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="28"/>
+      <c r="B89" s="32"/>
+      <c r="C89" s="30"/>
       <c r="D89" s="8"/>
       <c r="E89" s="17"/>
       <c r="F89" s="8"/>
@@ -3168,611 +3206,21 @@
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
     </row>
-    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="28"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-    </row>
-    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="28"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-    </row>
-    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="28"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-    </row>
-    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="28"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-    </row>
-    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="28"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-    </row>
-    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="28"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-    </row>
-    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="28"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="17"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-    </row>
-    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="28"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
-    </row>
-    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="28"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="17"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-    </row>
-    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="28"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-    </row>
-    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="28"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-    </row>
-    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="28"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-    </row>
-    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="28"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-    </row>
-    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="28"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="17"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-    </row>
-    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="28"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="17"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-    </row>
-    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="28"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="17"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-    </row>
-    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="28"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-    </row>
-    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="28"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="17"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="5"/>
-      <c r="J107" s="5"/>
-    </row>
-    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="28"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="17"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="5"/>
-    </row>
-    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="28"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="17"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
-    </row>
-    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="28"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="17"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
-    </row>
-    <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="28"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="17"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-    </row>
-    <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="28"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="17"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-    </row>
-    <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="28"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="17"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="5"/>
-    </row>
-    <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="28"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-    </row>
-    <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="28"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="17"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="5"/>
-    </row>
-    <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="28"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="17"/>
-      <c r="F116" s="8"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
-    </row>
-    <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="28"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="17"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
-    </row>
-    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="28"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="17"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="5"/>
-    </row>
-    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="28"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
-    </row>
-    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="28"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="17"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="5"/>
-      <c r="J120" s="5"/>
-    </row>
-    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="28"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="5"/>
-      <c r="J121" s="5"/>
-    </row>
-    <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="28"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="5"/>
-      <c r="J122" s="5"/>
-    </row>
-    <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="28"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="5"/>
-      <c r="J123" s="5"/>
-    </row>
-    <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="28"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="17"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="5"/>
-      <c r="J124" s="5"/>
-    </row>
-    <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="28"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="5"/>
-      <c r="J125" s="5"/>
-    </row>
-    <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="28"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="17"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="5"/>
-      <c r="J126" s="5"/>
-    </row>
-    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="28"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="5"/>
-      <c r="J127" s="5"/>
-    </row>
-    <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="28"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="5"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="5"/>
-      <c r="J128" s="5"/>
-    </row>
-    <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B129" s="28"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="17"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="5"/>
-    </row>
-    <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="28"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="17"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="5"/>
-      <c r="J130" s="5"/>
-    </row>
-    <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B131" s="28"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="17"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="5"/>
-      <c r="J131" s="5"/>
-    </row>
-    <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B132" s="28"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="17"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="5"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="5"/>
-      <c r="J132" s="5"/>
-    </row>
-    <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="28"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="17"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="5"/>
-    </row>
-    <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="28"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="17"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="5"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="5"/>
-      <c r="J134" s="5"/>
-    </row>
-    <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="28"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="17"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="5"/>
-    </row>
-    <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="28"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="17"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="5"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="5"/>
-    </row>
-    <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="28"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="17"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="5"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="5"/>
-      <c r="J137" s="5"/>
-    </row>
-    <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="28"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="17"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="5"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="5"/>
-      <c r="J138" s="5"/>
-    </row>
-    <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B139" s="28"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="17"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="5"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="5"/>
-      <c r="J139" s="5"/>
-    </row>
-    <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="28"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="17"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="5"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="5"/>
-    </row>
-    <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="28"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="5"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="5"/>
-      <c r="J141" s="5"/>
-    </row>
-    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B142" s="28"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="5"/>
-      <c r="J142" s="5"/>
-    </row>
-    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B143" s="28"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="5"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="5"/>
-      <c r="J143" s="5"/>
-    </row>
-    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B144" s="28"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="5"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="5"/>
-      <c r="J144" s="5"/>
-    </row>
-    <row r="145" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="28"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="5"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
-    </row>
-    <row r="146" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B146" s="28"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="17"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="5"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
-    </row>
-    <row r="147" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B147" s="28"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="8"/>
-      <c r="G147" s="5"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="5"/>
-    </row>
-    <row r="148" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B148" s="29"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="8"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="5"/>
-    </row>
-    <row r="149" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="150" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="151" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="152" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="153" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C3:C73"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B148"/>
+    <mergeCell ref="B3:B89"/>
     <mergeCell ref="B1:J1"/>
+    <mergeCell ref="C74:C89"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="13" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8522A6A1-6CD5-4ECD-8D16-B836EB7A2745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C82AD48-5B18-4DA9-B551-18265C8628DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="106">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1041,6 +1041,385 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「漢字のみ」もしくは「ひらがなのみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「カタカナのみ」もしくは「英字のみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「指定されてる形式で～」というエラー</t>
+  </si>
+  <si>
+    <t>名前（性）欄に「漢字とひらがな」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「漢字orひらがなとカタカナor英字」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「カタカナと英字」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字のみ」もしくは「ひらがなのみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「カタカナのみ」もしくは「英字のみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字とひらがな」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字orひらがなとカタカナor英字」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「カタカナと英字」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（性）欄に「カタカナのみ」入力</t>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字のみ」「ひらがなのみ」「英字のみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「カタカナと漢字orひらがなor英字」で入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「数字」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「記号」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「数字」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「記号」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「漢字　漢字」「漢字　ひらがな」「ひらがな　漢字」「ひらがな　ひらがな」と間にスペースを挟む</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ハサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（性）欄に「カタカナ　カタカナ」と間にスペースを挟む</t>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1116,12 +1495,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -1286,7 +1677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1329,9 +1720,6 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1341,36 +1729,93 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1380,17 +1825,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1709,13 +2151,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J93"/>
+  <dimension ref="B1:J121"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="3" width="10.58203125" customWidth="1"/>
     <col min="4" max="4" width="25.58203125" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="20" customWidth="1"/>
     <col min="6" max="6" width="45.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
     <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
@@ -1724,25 +2166,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="19" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1762,16 +2204,16 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="38" t="s">
         <v>66</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1783,587 +2225,587 @@
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="31"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="25">
         <v>45960</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="31"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="25">
         <v>45960</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="31"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="25">
         <v>45960</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="31"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="25">
         <v>45965</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="31"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>25</v>
+      <c r="B8" s="43"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="16"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="15"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="31"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>16</v>
+      <c r="B9" s="43"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="16">
-        <v>45965</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>11</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="31"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>17</v>
+      <c r="B10" s="43"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="43"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="43"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="43"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="43"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="43"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="43"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="43"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H17" s="34">
         <v>45965</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I17" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J17" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="31"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="7" t="s">
+    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="43"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E18" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="34">
+        <v>45965</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="43"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F19" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G19" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H19" s="34">
         <v>45965</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I19" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J19" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="31"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="7" t="s">
+    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="43"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E20" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G20" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H20" s="34">
         <v>45965</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I20" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J20" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="31"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="31"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="31"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="31"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="31"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="31"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="31"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="31"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-    </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="31"/>
-      <c r="C21" s="33"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>92</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
+      <c r="H21" s="15"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="J21" s="14"/>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="31"/>
-      <c r="C22" s="33"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>93</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="43"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="43"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="43"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="43"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="43"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="43"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="43"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="43"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="31"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="31"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="8" t="s">
+      <c r="G30" s="33"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+    </row>
+    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="43"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="33"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+    </row>
+    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="43"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="31"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="31"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="31"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="31"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="8" t="s">
+      <c r="G32" s="33"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+    </row>
+    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="43"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="31"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-    </row>
-    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="31"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-    </row>
-    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="31"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-    </row>
-    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="31"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-    </row>
-    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="31"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
     </row>
     <row r="34" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="31"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>39</v>
+      <c r="B34" s="43"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>9</v>
@@ -2374,16 +2816,16 @@
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="31"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>40</v>
+      <c r="B35" s="43"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>98</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="6"/>
@@ -2391,13 +2833,13 @@
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="31"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>41</v>
+      <c r="B36" s="43"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2408,16 +2850,16 @@
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="31"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>42</v>
+      <c r="B37" s="43"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="6"/>
@@ -2425,16 +2867,16 @@
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="31"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>43</v>
+      <c r="B38" s="43"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="6"/>
@@ -2442,16 +2884,16 @@
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="31"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>44</v>
+      <c r="B39" s="43"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="6"/>
@@ -2459,16 +2901,16 @@
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="31"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="17" t="s">
+      <c r="B40" s="43"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="6"/>
@@ -2476,182 +2918,182 @@
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="31"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="8" t="s">
+      <c r="B41" s="43"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="33"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+    </row>
+    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="43"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="33"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+    </row>
+    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="43"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-    </row>
-    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="31"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="8" t="s">
+      <c r="G43" s="33"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+    </row>
+    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="43"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="33"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+    </row>
+    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="43"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-    </row>
-    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="31"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-    </row>
-    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="31"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-    </row>
-    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="31"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="31"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>52</v>
+      <c r="B46" s="43"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>98</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="31"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>25</v>
+      <c r="B47" s="43"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="G47" s="50"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="31"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>57</v>
+      <c r="B48" s="43"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="G48" s="50"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="50"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="31"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>58</v>
+      <c r="B49" s="43"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="G49" s="50"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="31"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>59</v>
+      <c r="B50" s="43"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="G50" s="50"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="50"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="31"/>
-      <c r="C51" s="33"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="38"/>
       <c r="D51" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F51" s="8" t="s">
@@ -2663,13 +3105,13 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="31"/>
-      <c r="C52" s="33"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="38"/>
       <c r="D52" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>61</v>
+        <v>24</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>9</v>
@@ -2680,13 +3122,13 @@
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="31"/>
-      <c r="C53" s="33"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="38"/>
       <c r="D53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>62</v>
+        <v>24</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>9</v>
@@ -2697,13 +3139,13 @@
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="31"/>
-      <c r="C54" s="33"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="38"/>
       <c r="D54" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>63</v>
+        <v>24</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>9</v>
@@ -2714,13 +3156,13 @@
       <c r="J54" s="5"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="31"/>
-      <c r="C55" s="33"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="38"/>
       <c r="D55" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>68</v>
+        <v>24</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>9</v>
@@ -2731,16 +3173,16 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="31"/>
-      <c r="C56" s="33"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="38"/>
       <c r="D56" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>78</v>
+        <v>24</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="6"/>
@@ -2748,13 +3190,13 @@
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="31"/>
-      <c r="C57" s="33"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="38"/>
       <c r="D57" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>69</v>
+        <v>24</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>28</v>
@@ -2765,13 +3207,13 @@
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="31"/>
-      <c r="C58" s="33"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="38"/>
       <c r="D58" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -2782,13 +3224,13 @@
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="31"/>
-      <c r="C59" s="33"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="38"/>
       <c r="D59" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>64</v>
+        <v>24</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>28</v>
@@ -2799,12 +3241,12 @@
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="31"/>
-      <c r="C60" s="33"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="38"/>
       <c r="D60" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="16" t="s">
         <v>25</v>
       </c>
       <c r="F60" s="8" t="s">
@@ -2816,13 +3258,13 @@
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="31"/>
-      <c r="C61" s="33"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="38"/>
       <c r="D61" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>72</v>
+        <v>29</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>9</v>
@@ -2833,13 +3275,13 @@
       <c r="J61" s="5"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="31"/>
-      <c r="C62" s="33"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="38"/>
       <c r="D62" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>73</v>
+        <v>29</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>9</v>
@@ -2850,13 +3292,13 @@
       <c r="J62" s="5"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="31"/>
-      <c r="C63" s="33"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="38"/>
       <c r="D63" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>74</v>
+        <v>29</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>9</v>
@@ -2867,16 +3309,16 @@
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="31"/>
-      <c r="C64" s="33"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="38"/>
       <c r="D64" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>79</v>
+        <v>29</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="6"/>
@@ -2884,16 +3326,16 @@
       <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="31"/>
-      <c r="C65" s="33"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="38"/>
       <c r="D65" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>80</v>
+        <v>29</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="6"/>
@@ -2901,16 +3343,16 @@
       <c r="J65" s="5"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="31"/>
-      <c r="C66" s="33"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="38"/>
       <c r="D66" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>81</v>
+        <v>29</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="6"/>
@@ -2918,13 +3360,13 @@
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="31"/>
-      <c r="C67" s="33"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="38"/>
       <c r="D67" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>82</v>
+        <v>29</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>28</v>
@@ -2935,16 +3377,16 @@
       <c r="J67" s="5"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="31"/>
-      <c r="C68" s="33"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="38"/>
       <c r="D68" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>75</v>
+        <v>45</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="6"/>
@@ -2952,16 +3394,16 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="31"/>
-      <c r="C69" s="33"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="38"/>
       <c r="D69" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
@@ -2969,16 +3411,16 @@
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="31"/>
-      <c r="C70" s="33"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="38"/>
       <c r="D70" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E70" s="22" t="s">
-        <v>76</v>
+        <v>45</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="6"/>
@@ -2986,13 +3428,13 @@
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="31"/>
-      <c r="C71" s="33"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="38"/>
       <c r="D71" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E71" s="22" t="s">
-        <v>84</v>
+        <v>54</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>9</v>
@@ -3003,16 +3445,16 @@
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="31"/>
-      <c r="C72" s="33"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="38"/>
       <c r="D72" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>85</v>
+        <v>54</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
@@ -3020,203 +3462,679 @@
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="31"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="8"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="6"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="31"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G74" s="5"/>
       <c r="H74" s="6"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="31"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="8"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="6"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="31"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="8"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G76" s="5"/>
       <c r="H76" s="6"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="31"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="8"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G77" s="5"/>
       <c r="H77" s="6"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="31"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="8"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G78" s="5"/>
       <c r="H78" s="6"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="31"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="8"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="31"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="8"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="6"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="31"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="8"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G81" s="5"/>
       <c r="H81" s="6"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="31"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="8"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="31"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="8"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="31"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="8"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="31"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="8"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="6"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="31"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="8"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="6"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="31"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="8"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="31"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="8"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="6"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="32"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="8"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G89" s="5"/>
       <c r="H89" s="6"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
     </row>
-    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="43"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" s="5"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="43"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="43"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E92" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="43"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="43"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="43"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="43"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="43"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="43"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="5"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="43"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="43"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="43"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="43"/>
+      <c r="C102" s="46"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+    </row>
+    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="43"/>
+      <c r="C103" s="47"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+    </row>
+    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="43"/>
+      <c r="C104" s="47"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+    </row>
+    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="43"/>
+      <c r="C105" s="47"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+    </row>
+    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="43"/>
+      <c r="C106" s="47"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+    </row>
+    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="43"/>
+      <c r="C107" s="47"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+    </row>
+    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="43"/>
+      <c r="C108" s="47"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+    </row>
+    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="43"/>
+      <c r="C109" s="47"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+    </row>
+    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="43"/>
+      <c r="C110" s="47"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+    </row>
+    <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="43"/>
+      <c r="C111" s="47"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+    </row>
+    <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="43"/>
+      <c r="C112" s="47"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+    </row>
+    <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="43"/>
+      <c r="C113" s="47"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+    </row>
+    <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="43"/>
+      <c r="C114" s="47"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+    </row>
+    <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="43"/>
+      <c r="C115" s="47"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+    </row>
+    <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="43"/>
+      <c r="C116" s="47"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+    </row>
+    <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="44"/>
+      <c r="C117" s="48"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+    </row>
+    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C73"/>
+    <mergeCell ref="C3:C101"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B89"/>
+    <mergeCell ref="B3:B117"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C74:C89"/>
+    <mergeCell ref="C102:C117"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3238,15 +4156,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -3318,15 +4236,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C82AD48-5B18-4DA9-B551-18265C8628DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97427227-E2B3-47F2-A496-8172325ED156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="121">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1045,44 +1045,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名前（性）欄に「漢字のみ」もしくは「ひらがなのみ」入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前（性）欄に「カタカナのみ」もしくは「英字のみ」入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「指定されてる形式で～」というエラー</t>
   </si>
   <si>
@@ -1105,85 +1067,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名前（性）欄に「漢字orひらがなとカタカナor英字」で入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前（性）欄に「カタカナと英字」で入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前（名）欄に「漢字のみ」もしくは「ひらがなのみ」入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前（名）欄に「カタカナのみ」もしくは「英字のみ」入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>名前（名）欄に「漢字とひらがな」で入力</t>
     <rPh sb="0" eb="2">
       <t>ナマエ</t>
@@ -1203,47 +1086,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名前（名）欄に「漢字orひらがなとカタカナor英字」で入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前（名）欄に「カタカナと英字」で入力</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カナ（性）欄に「カタカナのみ」入力</t>
     <rPh sb="3" eb="4">
       <t>セイ</t>
@@ -1419,6 +1261,331 @@
       <t>アイダ</t>
     </rPh>
     <rPh sb="26" eb="27">
+      <t>ハサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※これ以外の名前ならテストできない</t>
+  </si>
+  <si>
+    <t>※これ以外の名前ならテストできない</t>
+    <rPh sb="3" eb="5">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※これ以外の名前ならテストできない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に11字以上の文字数を入力</t>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10字までしか入力できない</t>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字　漢字」「漢字　ひらがな」「ひらがな　漢字」「ひらがな　ひらがな」と間にスペースを挟む</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ハサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に11字以上の文字数を入力</t>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（性）欄に11字以上の文字数を入力</t>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（名）欄に11字以上の文字数を入力</t>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「漢字のみ」「ひらがなのみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（性）欄に「カタカナのみ」「英字のみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「漢字のみ」「ひらがなのみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「カタカナのみ」「英字のみ」入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英字のみ＠　～」「半角数字のみ＠　～」を入力</t>
+    <rPh sb="10" eb="14">
+      <t>ハンカクエイジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英数字のみ＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「全角英字のみ＠　～」「全角数字のみ＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「ひらがなのみ＠　～」「カタカナのみ＠　～」「漢字のみ＠　～」を入力</t>
+    <rPh sb="41" eb="43">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「記号のみ（ハイフン・＠のみ除く）＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に101字以上の文字数を入力</t>
+    <rPh sb="12" eb="13">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>100字までしか入力できない</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「ハイフンのみ＠　～」「＠のみ＠　～」を入力</t>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英数字＋（どこかに－（ハイフン）・＠あり）＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英字のみ＠　～」「半角数字のみ＠　～」（どこか間にスペースを挟む）を入力</t>
+    <rPh sb="35" eb="36">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
       <t>ハサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1677,7 +1844,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1792,6 +1959,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1825,7 +1995,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -2151,7 +2324,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J121"/>
+  <dimension ref="B1:K130"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -2165,25 +2338,25 @@
     <col min="10" max="10" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-    </row>
-    <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="40" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+    </row>
+    <row r="2" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="E2" s="17" t="s">
         <v>1</v>
       </c>
@@ -2203,11 +2376,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="43" t="s">
+    <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="39" t="s">
         <v>66</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -2224,9 +2397,9 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="43"/>
-      <c r="C4" s="38"/>
+    <row r="4" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="44"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="21" t="s">
         <v>20</v>
       </c>
@@ -2248,10 +2421,13 @@
       <c r="J4" s="26" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="43"/>
-      <c r="C5" s="38"/>
+      <c r="K4" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="44"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="21" t="s">
         <v>20</v>
       </c>
@@ -2273,10 +2449,13 @@
       <c r="J5" s="24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="43"/>
-      <c r="C6" s="38"/>
+      <c r="K5" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="44"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="21" t="s">
         <v>20</v>
       </c>
@@ -2298,10 +2477,13 @@
       <c r="J6" s="24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="43"/>
-      <c r="C7" s="38"/>
+      <c r="K6" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="44"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
@@ -2323,15 +2505,18 @@
       <c r="J7" s="24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="43"/>
-      <c r="C8" s="38"/>
+      <c r="K7" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="44"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>9</v>
@@ -2341,31 +2526,31 @@
       <c r="I8" s="5"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="43"/>
-      <c r="C9" s="38"/>
+    <row r="9" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="44"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="15"/>
       <c r="I9" s="5"/>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="43"/>
-      <c r="C10" s="38"/>
+    <row r="10" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="44"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>9</v>
@@ -2375,60 +2560,60 @@
       <c r="I10" s="5"/>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="43"/>
-      <c r="C11" s="38"/>
+    <row r="11" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="44"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="15"/>
       <c r="I11" s="5"/>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="43"/>
-      <c r="C12" s="38"/>
+    <row r="12" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="44"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="15"/>
       <c r="I12" s="5"/>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="43"/>
-      <c r="C13" s="38"/>
+    <row r="13" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="44"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="15"/>
       <c r="I13" s="5"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="43"/>
-      <c r="C14" s="38"/>
+    <row r="14" spans="2:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="44"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
@@ -2436,55 +2621,66 @@
         <v>101</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="15"/>
       <c r="I14" s="5"/>
       <c r="J14" s="14"/>
     </row>
-    <row r="15" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="43"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="9" t="s">
-        <v>20</v>
+    <row r="15" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="44"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="15"/>
       <c r="I15" s="5"/>
       <c r="J15" s="14"/>
     </row>
-    <row r="16" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="43"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="7" t="s">
+    <row r="16" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="44"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="43"/>
-      <c r="C17" s="38"/>
+      <c r="E16" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="34">
+        <v>45965</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="44"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="31" t="s">
-        <v>16</v>
+      <c r="E17" s="36" t="s">
+        <v>17</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>9</v>
@@ -2501,18 +2697,21 @@
       <c r="J17" s="35" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="43"/>
-      <c r="C18" s="38"/>
+      <c r="K17" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="44"/>
+      <c r="C18" s="39"/>
       <c r="D18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="36" t="s">
-        <v>17</v>
+      <c r="E18" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G18" s="33" t="s">
         <v>8</v>
@@ -2526,15 +2725,18 @@
       <c r="J18" s="35" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="43"/>
-      <c r="C19" s="38"/>
+      <c r="K18" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="44"/>
+      <c r="C19" s="39"/>
       <c r="D19" s="30" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" s="32" t="s">
         <v>28</v>
@@ -2551,69 +2753,64 @@
       <c r="J19" s="35" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="43"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="30" t="s">
+      <c r="K19" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="44"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="34">
-        <v>45965</v>
-      </c>
-      <c r="I20" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="43"/>
-      <c r="C21" s="38"/>
+      <c r="E20" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="44"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="15"/>
       <c r="I21" s="5"/>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="43"/>
-      <c r="C22" s="38"/>
+    <row r="22" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="44"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="15"/>
       <c r="I22" s="5"/>
       <c r="J22" s="14"/>
     </row>
-    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="43"/>
-      <c r="C23" s="38"/>
+    <row r="23" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="44"/>
+      <c r="C23" s="39"/>
       <c r="D23" s="7" t="s">
         <v>21</v>
       </c>
@@ -2621,16 +2818,16 @@
         <v>94</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="15"/>
       <c r="I23" s="5"/>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="43"/>
-      <c r="C24" s="38"/>
+    <row r="24" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="44"/>
+      <c r="C24" s="39"/>
       <c r="D24" s="7" t="s">
         <v>21</v>
       </c>
@@ -2638,123 +2835,132 @@
         <v>95</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="15"/>
       <c r="I24" s="5"/>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="43"/>
-      <c r="C25" s="38"/>
+    <row r="25" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="44"/>
+      <c r="C25" s="39"/>
       <c r="D25" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="15"/>
       <c r="I25" s="5"/>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="43"/>
-      <c r="C26" s="38"/>
+    <row r="26" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="44"/>
+      <c r="C26" s="39"/>
       <c r="D26" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="15"/>
       <c r="I26" s="5"/>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="43"/>
-      <c r="C27" s="38"/>
+    <row r="27" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="44"/>
+      <c r="C27" s="39"/>
       <c r="D27" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="15"/>
       <c r="I27" s="5"/>
       <c r="J27" s="14"/>
     </row>
-    <row r="28" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="43"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="14"/>
-    </row>
-    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="43"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="7" t="s">
+    <row r="28" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="44"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="14"/>
-    </row>
-    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="43"/>
-      <c r="C30" s="38"/>
+      <c r="E28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="33"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="44"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="33"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="44"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G30" s="33"/>
       <c r="H30" s="37"/>
       <c r="I30" s="33"/>
       <c r="J30" s="33"/>
-    </row>
-    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="43"/>
-      <c r="C31" s="38"/>
+      <c r="K30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="44"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" s="32" t="s">
         <v>28</v>
@@ -2763,168 +2969,174 @@
       <c r="H31" s="37"/>
       <c r="I31" s="33"/>
       <c r="J31" s="33"/>
-    </row>
-    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="43"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="30" t="s">
+      <c r="K31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="44"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="32" t="s">
+      <c r="E32" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-    </row>
-    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="43"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="30" t="s">
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="44"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="32" t="s">
+      <c r="E33" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="33"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-    </row>
-    <row r="34" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="43"/>
-      <c r="C34" s="38"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="44"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="6"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="43"/>
-      <c r="C35" s="38"/>
+    <row r="35" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="44"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="6"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="43"/>
-      <c r="C36" s="38"/>
+    <row r="36" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="44"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="6"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="43"/>
-      <c r="C37" s="38"/>
+    <row r="37" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="44"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="6"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="43"/>
-      <c r="C38" s="38"/>
+    <row r="38" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="44"/>
+      <c r="C38" s="39"/>
       <c r="D38" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="6"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
-    <row r="39" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="43"/>
-      <c r="C39" s="38"/>
+    <row r="39" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="44"/>
+      <c r="C39" s="39"/>
       <c r="D39" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="6"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="43"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="7" t="s">
+    <row r="40" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="44"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-    </row>
-    <row r="41" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="43"/>
-      <c r="C41" s="38"/>
+      <c r="E40" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="33"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="44"/>
+      <c r="C41" s="39"/>
       <c r="D41" s="30" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" s="32" t="s">
         <v>28</v>
@@ -2933,163 +3145,172 @@
       <c r="H41" s="37"/>
       <c r="I41" s="33"/>
       <c r="J41" s="33"/>
-    </row>
-    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="43"/>
-      <c r="C42" s="38"/>
+      <c r="K41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="44"/>
+      <c r="C42" s="39"/>
       <c r="D42" s="30" t="s">
         <v>23</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F42" s="32" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G42" s="33"/>
       <c r="H42" s="37"/>
       <c r="I42" s="33"/>
       <c r="J42" s="33"/>
-    </row>
-    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="43"/>
-      <c r="C43" s="38"/>
+      <c r="K42" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="44"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="30" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G43" s="33"/>
       <c r="H43" s="37"/>
       <c r="I43" s="33"/>
       <c r="J43" s="33"/>
-    </row>
-    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="43"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="30" t="s">
+      <c r="K43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="44"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="32" t="s">
+      <c r="E44" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="44"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G44" s="33"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-    </row>
-    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="43"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="49" t="s">
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="44"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="50"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-    </row>
-    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="43"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="49" t="s">
-        <v>23</v>
-      </c>
       <c r="E46" s="19" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="50"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
-    </row>
-    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="43"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="49" t="s">
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="44"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47" s="50"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-    </row>
-    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="43"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="44"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E48" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="44"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="44"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G48" s="50"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="50"/>
-      <c r="J48" s="50"/>
-    </row>
-    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="43"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="50"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-    </row>
-    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="43"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G50" s="50"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="50"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="43"/>
-      <c r="C51" s="38"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="39"/>
       <c r="D51" s="8" t="s">
         <v>24</v>
       </c>
@@ -3105,305 +3326,305 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="43"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="8" t="s">
+      <c r="B52" s="44"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="43"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="8" t="s">
+      <c r="B53" s="44"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="43"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="8" t="s">
+      <c r="B54" s="44"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="37"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="43"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="8" t="s">
+      <c r="B55" s="44"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="37"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="43"/>
-      <c r="C56" s="38"/>
-      <c r="D56" s="8" t="s">
+      <c r="B56" s="44"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="43"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="8" t="s">
+      <c r="B57" s="44"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="43"/>
-      <c r="C58" s="38"/>
-      <c r="D58" s="8" t="s">
+      <c r="B58" s="44"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="43"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="8" t="s">
+      <c r="B59" s="44"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F59" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="43"/>
-      <c r="C60" s="38"/>
-      <c r="D60" s="8" t="s">
+      <c r="B60" s="44"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G60" s="52"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+    </row>
+    <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="44"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="52"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
+    </row>
+    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="44"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="52"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="52"/>
+      <c r="J62" s="52"/>
+    </row>
+    <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="44"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="52"/>
+      <c r="H63" s="53"/>
+      <c r="I63" s="52"/>
+      <c r="J63" s="52"/>
+    </row>
+    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="44"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="52"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="52"/>
+      <c r="J64" s="52"/>
+    </row>
+    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="44"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="52"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="52"/>
+    </row>
+    <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="44"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="52"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="52"/>
+      <c r="J66" s="52"/>
+    </row>
+    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="44"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F67" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="52"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="52"/>
+      <c r="J67" s="52"/>
+    </row>
+    <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="44"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="52"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="52"/>
+      <c r="J68" s="52"/>
+    </row>
+    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="44"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E60" s="16" t="s">
+      <c r="E69" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F69" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-    </row>
-    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="43"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-    </row>
-    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="43"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-    </row>
-    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="43"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-    </row>
-    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="43"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64" s="5"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-    </row>
-    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="43"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-    </row>
-    <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="43"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="5"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-    </row>
-    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="43"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67" s="5"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-    </row>
-    <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="43"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G68" s="5"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-    </row>
-    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="43"/>
-      <c r="C69" s="38"/>
-      <c r="D69" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
@@ -3411,13 +3632,13 @@
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="43"/>
-      <c r="C70" s="38"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="39"/>
       <c r="D70" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>9</v>
@@ -3428,13 +3649,13 @@
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="43"/>
-      <c r="C71" s="38"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="39"/>
       <c r="D71" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>9</v>
@@ -3445,16 +3666,16 @@
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="43"/>
-      <c r="C72" s="38"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="39"/>
       <c r="D72" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
@@ -3462,13 +3683,13 @@
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="43"/>
-      <c r="C73" s="38"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="39"/>
       <c r="D73" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>28</v>
@@ -3479,13 +3700,13 @@
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="43"/>
-      <c r="C74" s="38"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="39"/>
       <c r="D74" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3496,16 +3717,16 @@
       <c r="J74" s="5"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="43"/>
-      <c r="C75" s="38"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="39"/>
       <c r="D75" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="6"/>
@@ -3513,16 +3734,16 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="43"/>
-      <c r="C76" s="38"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="39"/>
       <c r="D76" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>57</v>
+        <v>29</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="6"/>
@@ -3530,16 +3751,16 @@
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="43"/>
-      <c r="C77" s="38"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="39"/>
       <c r="D77" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="6"/>
@@ -3547,13 +3768,13 @@
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="43"/>
-      <c r="C78" s="38"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="39"/>
       <c r="D78" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>9</v>
@@ -3564,16 +3785,16 @@
       <c r="J78" s="5"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="43"/>
-      <c r="C79" s="38"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="39"/>
       <c r="D79" s="8" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
@@ -3581,13 +3802,13 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="43"/>
-      <c r="C80" s="38"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="39"/>
       <c r="D80" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>9</v>
@@ -3598,16 +3819,16 @@
       <c r="J80" s="5"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="43"/>
-      <c r="C81" s="38"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="39"/>
       <c r="D81" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="6"/>
@@ -3615,16 +3836,16 @@
       <c r="J81" s="5"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="43"/>
-      <c r="C82" s="38"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="39"/>
       <c r="D82" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
@@ -3632,16 +3853,16 @@
       <c r="J82" s="5"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="43"/>
-      <c r="C83" s="38"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="39"/>
       <c r="D83" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
@@ -3649,16 +3870,16 @@
       <c r="J83" s="5"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="43"/>
-      <c r="C84" s="38"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="39"/>
       <c r="D84" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>78</v>
+        <v>53</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
@@ -3666,16 +3887,16 @@
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="43"/>
-      <c r="C85" s="38"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="39"/>
       <c r="D85" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="6"/>
@@ -3683,16 +3904,16 @@
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="43"/>
-      <c r="C86" s="38"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="39"/>
       <c r="D86" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="6"/>
@@ -3700,16 +3921,16 @@
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="43"/>
-      <c r="C87" s="38"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="39"/>
       <c r="D87" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
@@ -3717,10 +3938,10 @@
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="43"/>
-      <c r="C88" s="38"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="39"/>
       <c r="D88" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>25</v>
@@ -3734,13 +3955,13 @@
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="43"/>
-      <c r="C89" s="38"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="39"/>
       <c r="D89" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>9</v>
@@ -3751,13 +3972,13 @@
       <c r="J89" s="5"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="43"/>
-      <c r="C90" s="38"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="39"/>
       <c r="D90" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>9</v>
@@ -3768,13 +3989,13 @@
       <c r="J90" s="5"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="43"/>
-      <c r="C91" s="38"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="39"/>
       <c r="D91" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>9</v>
@@ -3785,13 +4006,13 @@
       <c r="J91" s="5"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="43"/>
-      <c r="C92" s="38"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="39"/>
       <c r="D92" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>9</v>
@@ -3802,13 +4023,13 @@
       <c r="J92" s="5"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="43"/>
-      <c r="C93" s="38"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="39"/>
       <c r="D93" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>9</v>
@@ -3819,16 +4040,16 @@
       <c r="J93" s="5"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="43"/>
-      <c r="C94" s="38"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="39"/>
       <c r="D94" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="6"/>
@@ -3836,13 +4057,13 @@
       <c r="J94" s="5"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="43"/>
-      <c r="C95" s="38"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="39"/>
       <c r="D95" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>28</v>
@@ -3853,13 +4074,13 @@
       <c r="J95" s="5"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="43"/>
-      <c r="C96" s="38"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="39"/>
       <c r="D96" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3870,16 +4091,16 @@
       <c r="J96" s="5"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="43"/>
-      <c r="C97" s="38"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="39"/>
       <c r="D97" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="6"/>
@@ -3887,16 +4108,16 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="43"/>
-      <c r="C98" s="38"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="39"/>
       <c r="D98" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="6"/>
@@ -3904,13 +4125,13 @@
       <c r="J98" s="5"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="43"/>
-      <c r="C99" s="38"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="39"/>
       <c r="D99" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>9</v>
@@ -3921,13 +4142,13 @@
       <c r="J99" s="5"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="43"/>
-      <c r="C100" s="38"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="39"/>
       <c r="D100" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>9</v>
@@ -3938,107 +4159,161 @@
       <c r="J100" s="5"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="43"/>
+      <c r="B101" s="44"/>
       <c r="C101" s="39"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="8"/>
+      <c r="D101" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G101" s="5"/>
       <c r="H101" s="6"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="43"/>
-      <c r="C102" s="46"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="8"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G102" s="5"/>
       <c r="H102" s="6"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="43"/>
-      <c r="C103" s="47"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="8"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G103" s="5"/>
       <c r="H103" s="6"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="43"/>
-      <c r="C104" s="47"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="16"/>
-      <c r="F104" s="8"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G104" s="5"/>
       <c r="H104" s="6"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
     </row>
     <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="43"/>
-      <c r="C105" s="47"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="16"/>
-      <c r="F105" s="8"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G105" s="5"/>
       <c r="H105" s="6"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
     </row>
     <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="43"/>
-      <c r="C106" s="47"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="16"/>
-      <c r="F106" s="8"/>
+      <c r="B106" s="44"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G106" s="5"/>
       <c r="H106" s="6"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
     </row>
     <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="43"/>
-      <c r="C107" s="47"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="16"/>
-      <c r="F107" s="8"/>
+      <c r="B107" s="44"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G107" s="5"/>
       <c r="H107" s="6"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
     </row>
     <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="43"/>
-      <c r="C108" s="47"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="8"/>
+      <c r="B108" s="44"/>
+      <c r="C108" s="39"/>
+      <c r="D108" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G108" s="5"/>
       <c r="H108" s="6"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
     </row>
     <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="43"/>
-      <c r="C109" s="47"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="16"/>
-      <c r="F109" s="8"/>
+      <c r="B109" s="44"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G109" s="5"/>
       <c r="H109" s="6"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
     </row>
     <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="43"/>
-      <c r="C110" s="47"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="40"/>
       <c r="D110" s="8"/>
       <c r="E110" s="16"/>
       <c r="F110" s="8"/>
@@ -4048,7 +4323,7 @@
       <c r="J110" s="5"/>
     </row>
     <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="43"/>
+      <c r="B111" s="44"/>
       <c r="C111" s="47"/>
       <c r="D111" s="8"/>
       <c r="E111" s="16"/>
@@ -4059,8 +4334,8 @@
       <c r="J111" s="5"/>
     </row>
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="43"/>
-      <c r="C112" s="47"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="48"/>
       <c r="D112" s="8"/>
       <c r="E112" s="16"/>
       <c r="F112" s="8"/>
@@ -4070,8 +4345,8 @@
       <c r="J112" s="5"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="43"/>
-      <c r="C113" s="47"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="48"/>
       <c r="D113" s="8"/>
       <c r="E113" s="16"/>
       <c r="F113" s="8"/>
@@ -4081,8 +4356,8 @@
       <c r="J113" s="5"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="43"/>
-      <c r="C114" s="47"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="8"/>
       <c r="E114" s="16"/>
       <c r="F114" s="8"/>
@@ -4092,8 +4367,8 @@
       <c r="J114" s="5"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="43"/>
-      <c r="C115" s="47"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="8"/>
       <c r="E115" s="16"/>
       <c r="F115" s="8"/>
@@ -4103,8 +4378,8 @@
       <c r="J115" s="5"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="43"/>
-      <c r="C116" s="47"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="48"/>
       <c r="D116" s="8"/>
       <c r="E116" s="16"/>
       <c r="F116" s="8"/>
@@ -4124,17 +4399,116 @@
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
     </row>
-    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="44"/>
+      <c r="C118" s="48"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="16"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+    </row>
+    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="44"/>
+      <c r="C119" s="48"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="16"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+    </row>
+    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="44"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="16"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+    </row>
+    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="44"/>
+      <c r="C121" s="48"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+    </row>
+    <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="44"/>
+      <c r="C122" s="48"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="16"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+    </row>
+    <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="44"/>
+      <c r="C123" s="48"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="6"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+    </row>
+    <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="44"/>
+      <c r="C124" s="48"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+    </row>
+    <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="44"/>
+      <c r="C125" s="48"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+    </row>
+    <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="45"/>
+      <c r="C126" s="49"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+    </row>
+    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="129" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="130" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C101"/>
+    <mergeCell ref="C3:C110"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B117"/>
+    <mergeCell ref="B3:B126"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C102:C117"/>
+    <mergeCell ref="C111:C126"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4156,15 +4530,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -4236,15 +4610,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97427227-E2B3-47F2-A496-8172325ED156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A390F15-D43B-4D06-BDE0-A70DCD89D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="129">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1519,19 +1519,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレス欄に「記号のみ（ハイフン・＠のみ除く）＠　～」を入力</t>
-    <rPh sb="10" eb="12">
-      <t>キゴウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メールアドレス欄に101字以上の文字数を入力</t>
     <rPh sb="12" eb="13">
       <t>ジ</t>
@@ -1581,12 +1568,138 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレス欄に「半角英字のみ＠　～」「半角数字のみ＠　～」（どこか間にスペースを挟む）を入力</t>
+    <t>パスワード欄に「半角英字のみ」「半角数字のみ」のパスワードを入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ハンカクエイジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に11字以上の文字数を入力</t>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「半角英数字のみ」のパスワードを入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>エイスウジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「全角英字のみ」「全角数字のみ」のパスワードを入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そもそも入力ができない。（入力形式が切り替わらない）</t>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ニュウリョクケイシキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「ひらがなのみ＠　～」「カタカナのみ＠　～」「漢字のみ＠　～」を入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「記号」を入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英数字＋どこかに記号あり（ハイフン・＠除く）＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「スペース」を入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英字のみ＠　～」「半角数字のみ＠　～」（どこか間にスペースを入力）</t>
     <rPh sb="35" eb="36">
       <t>アイダ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ハサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1844,7 +1957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1878,9 +1991,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2006,6 +2116,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2324,13 +2440,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K130"/>
+  <dimension ref="B1:K137"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="3" width="10.58203125" customWidth="1"/>
     <col min="4" max="4" width="25.58203125" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="19" customWidth="1"/>
     <col min="6" max="6" width="45.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
     <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
@@ -2339,25 +2455,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -2377,609 +2493,609 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="38" t="s">
         <v>66</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
     </row>
     <row r="4" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="44"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="21" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="24">
         <v>45960</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="37" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="44"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="21" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <v>45960</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="37" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="44"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="21" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="24">
         <v>45960</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="K6" s="37" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="44"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="21" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <v>45965</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="37" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="44"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>107</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="14"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="14"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="44"/>
-      <c r="C9" s="39"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>108</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="14"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="44"/>
-      <c r="C10" s="39"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>87</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="15"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="14"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="44"/>
-      <c r="C11" s="39"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>92</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="14"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="44"/>
-      <c r="C12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="15"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="14"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="44"/>
-      <c r="C13" s="39"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>96</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="14"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="2:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="44"/>
-      <c r="C14" s="39"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>101</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="15"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="14"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="44"/>
-      <c r="C15" s="39"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="14"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="44"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="30" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <v>45965</v>
       </c>
-      <c r="I16" s="33" t="s">
+      <c r="I16" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="37" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="44"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="30" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="33">
         <v>45965</v>
       </c>
-      <c r="I17" s="33" t="s">
+      <c r="I17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="38" t="s">
+      <c r="K17" s="37" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="44"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="30" t="s">
+      <c r="B18" s="43"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="33">
         <v>45965</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="35" t="s">
+      <c r="J18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="37" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="44"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="30" t="s">
+      <c r="B19" s="43"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="33">
         <v>45965</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="37" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="44"/>
-      <c r="C20" s="39"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>109</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="15"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="44"/>
-      <c r="C21" s="39"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
         <v>110</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="15"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="44"/>
-      <c r="C22" s="39"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>88</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="44"/>
-      <c r="C23" s="39"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="14"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="44"/>
-      <c r="C24" s="39"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="14"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="44"/>
-      <c r="C25" s="39"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="18" t="s">
         <v>103</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="15"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="14"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="44"/>
-      <c r="C26" s="39"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>104</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="15"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="14"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="44"/>
-      <c r="C27" s="39"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="15"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="14"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="44"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="30" t="s">
+      <c r="B28" s="43"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
       <c r="K28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="44"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="30" t="s">
+      <c r="B29" s="43"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="33"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
       <c r="K29" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="44"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="30" t="s">
+      <c r="B30" s="43"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
       <c r="K30" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="44"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="30" t="s">
+      <c r="B31" s="43"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="31" t="s">
+      <c r="E31" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="33"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
       <c r="K31" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="44"/>
-      <c r="C32" s="39"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F32" s="8" t="s">
@@ -2991,12 +3107,12 @@
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="44"/>
-      <c r="C33" s="39"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="18" t="s">
         <v>90</v>
       </c>
       <c r="F33" s="8" t="s">
@@ -3008,12 +3124,12 @@
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="44"/>
-      <c r="C34" s="39"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="38"/>
       <c r="D34" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F34" s="8" t="s">
@@ -3025,12 +3141,12 @@
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="44"/>
-      <c r="C35" s="39"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="18" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="8" t="s">
@@ -3042,12 +3158,12 @@
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="44"/>
-      <c r="C36" s="39"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="18" t="s">
         <v>95</v>
       </c>
       <c r="F36" s="8" t="s">
@@ -3059,12 +3175,12 @@
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="44"/>
-      <c r="C37" s="39"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="18" t="s">
         <v>97</v>
       </c>
       <c r="F37" s="8" t="s">
@@ -3076,12 +3192,12 @@
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="44"/>
-      <c r="C38" s="39"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="18" t="s">
         <v>105</v>
       </c>
       <c r="F38" s="8" t="s">
@@ -3093,12 +3209,12 @@
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="44"/>
-      <c r="C39" s="39"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="38"/>
       <c r="D39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="8" t="s">
@@ -3110,92 +3226,92 @@
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="44"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="30" t="s">
+      <c r="B40" s="43"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="33"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
       <c r="K40" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="44"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="30" t="s">
+      <c r="B41" s="43"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="31" t="s">
+      <c r="E41" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="F41" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="33"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
       <c r="K41" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="44"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="30" t="s">
+      <c r="B42" s="43"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="F42" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G42" s="33"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
       <c r="K42" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="44"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="30" t="s">
+      <c r="B43" s="43"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="31" t="s">
+      <c r="E43" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="32" t="s">
+      <c r="F43" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="33"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
       <c r="K43" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="44"/>
-      <c r="C44" s="39"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="38"/>
       <c r="D44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F44" s="8" t="s">
@@ -3207,12 +3323,12 @@
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="44"/>
-      <c r="C45" s="39"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="38"/>
       <c r="D45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="18" t="s">
         <v>90</v>
       </c>
       <c r="F45" s="8" t="s">
@@ -3224,12 +3340,12 @@
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="44"/>
-      <c r="C46" s="39"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="38"/>
       <c r="D46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F46" s="8" t="s">
@@ -3241,12 +3357,12 @@
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="44"/>
-      <c r="C47" s="39"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="38"/>
       <c r="D47" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="18" t="s">
         <v>94</v>
       </c>
       <c r="F47" s="8" t="s">
@@ -3258,12 +3374,12 @@
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="44"/>
-      <c r="C48" s="39"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="38"/>
       <c r="D48" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="18" t="s">
         <v>95</v>
       </c>
       <c r="F48" s="8" t="s">
@@ -3275,12 +3391,12 @@
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="44"/>
-      <c r="C49" s="39"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="38"/>
       <c r="D49" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="18" t="s">
         <v>97</v>
       </c>
       <c r="F49" s="8" t="s">
@@ -3292,12 +3408,12 @@
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="44"/>
-      <c r="C50" s="39"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="38"/>
       <c r="D50" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="18" t="s">
         <v>106</v>
       </c>
       <c r="F50" s="8" t="s">
@@ -3309,12 +3425,12 @@
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="44"/>
-      <c r="C51" s="39"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="38"/>
       <c r="D51" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F51" s="8" t="s">
@@ -3326,301 +3442,301 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="44"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="32" t="s">
+      <c r="B52" s="43"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E52" s="31" t="s">
+      <c r="E52" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F52" s="32" t="s">
+      <c r="F52" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G52" s="33"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="33"/>
-      <c r="J52" s="33"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="44"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="32" t="s">
+      <c r="B53" s="43"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="31" t="s">
+      <c r="E53" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="32" t="s">
+      <c r="F53" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="33"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="44"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="32" t="s">
+      <c r="B54" s="43"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="32" t="s">
+      <c r="F54" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="33"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="44"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="32" t="s">
+      <c r="B55" s="43"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="31" t="s">
+      <c r="E55" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F55" s="32" t="s">
+      <c r="F55" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="33"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="44"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="32" t="s">
+      <c r="B56" s="43"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F56" s="32" t="s">
+      <c r="F56" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="33"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="33"/>
-      <c r="J56" s="33"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="44"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="32" t="s">
+      <c r="B57" s="43"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F57" s="32" t="s">
+      <c r="F57" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="33"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="44"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="32" t="s">
+      <c r="B58" s="43"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="31" t="s">
+      <c r="E58" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="32" t="s">
+      <c r="F58" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="33"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="33"/>
-      <c r="J58" s="33"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="44"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="32" t="s">
+      <c r="B59" s="43"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="31" t="s">
+      <c r="E59" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="32" t="s">
+      <c r="F59" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G59" s="33"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="44"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="50" t="s">
+      <c r="B60" s="43"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="G60" s="51"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="51"/>
+      <c r="J60" s="51"/>
+    </row>
+    <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="43"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F61" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="51"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="51"/>
+      <c r="J61" s="51"/>
+    </row>
+    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="43"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F62" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="51"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="51"/>
+      <c r="J62" s="51"/>
+    </row>
+    <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="43"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="51"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="51"/>
+      <c r="J63" s="51"/>
+    </row>
+    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="43"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="51"/>
+      <c r="H64" s="52"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="51"/>
+    </row>
+    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="43"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="G60" s="52"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="52"/>
-    </row>
-    <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="44"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="50" t="s">
+      <c r="F65" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="51"/>
+      <c r="H65" s="52"/>
+      <c r="I65" s="51"/>
+      <c r="J65" s="51"/>
+    </row>
+    <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="43"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="E61" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="F61" s="50" t="s">
+      <c r="E66" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="F66" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G61" s="52"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="52"/>
-      <c r="J61" s="52"/>
-    </row>
-    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="44"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="50" t="s">
+      <c r="G66" s="51"/>
+      <c r="H66" s="52"/>
+      <c r="I66" s="51"/>
+      <c r="J66" s="51"/>
+    </row>
+    <row r="67" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="43"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="F62" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62" s="52"/>
-      <c r="H62" s="53"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-    </row>
-    <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="44"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="50" t="s">
+      <c r="E67" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="51"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="51"/>
+    </row>
+    <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="43"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="E63" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="F63" s="50" t="s">
+      <c r="E68" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G63" s="52"/>
-      <c r="H63" s="53"/>
-      <c r="I63" s="52"/>
-      <c r="J63" s="52"/>
-    </row>
-    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="44"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64" s="52"/>
-      <c r="H64" s="53"/>
-      <c r="I64" s="52"/>
-      <c r="J64" s="52"/>
-    </row>
-    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="44"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="G65" s="52"/>
-      <c r="H65" s="53"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="52"/>
-    </row>
-    <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="44"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="F66" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="G66" s="52"/>
-      <c r="H66" s="53"/>
-      <c r="I66" s="52"/>
-      <c r="J66" s="52"/>
-    </row>
-    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="44"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="F67" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67" s="52"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="52"/>
-      <c r="J67" s="52"/>
-    </row>
-    <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="44"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F68" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="G68" s="52"/>
-      <c r="H68" s="53"/>
-      <c r="I68" s="52"/>
-      <c r="J68" s="52"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="52"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="51"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="44"/>
-      <c r="C69" s="39"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="38"/>
       <c r="D69" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="E69" s="15" t="s">
         <v>25</v>
       </c>
       <c r="F69" s="8" t="s">
@@ -3632,254 +3748,254 @@
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="44"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="8" t="s">
+      <c r="B70" s="43"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="44"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="8" t="s">
+      <c r="B71" s="43"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="44"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="8" t="s">
+      <c r="B72" s="43"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="44"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="8" t="s">
+      <c r="B73" s="43"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="44"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="8" t="s">
+      <c r="B74" s="43"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="32"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="44"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="8" t="s">
+      <c r="B75" s="43"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="44"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="8" t="s">
+      <c r="B76" s="43"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="32"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="44"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="8" t="s">
+      <c r="B77" s="43"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G77" s="51"/>
+      <c r="H77" s="52"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51"/>
+    </row>
+    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="43"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="F78" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="51"/>
+      <c r="H78" s="52"/>
+      <c r="I78" s="51"/>
+      <c r="J78" s="51"/>
+    </row>
+    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="43"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="51"/>
+      <c r="J79" s="51"/>
+    </row>
+    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="43"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="F80" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="51"/>
+      <c r="J80" s="51"/>
+    </row>
+    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="43"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="F81" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
+      <c r="I81" s="51"/>
+      <c r="J81" s="51"/>
+    </row>
+    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="43"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="F82" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="51"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51"/>
+    </row>
+    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="43"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F83" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="51"/>
+      <c r="H83" s="52"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
+    </row>
+    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="43"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E77" s="16" t="s">
+      <c r="E84" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F84" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-    </row>
-    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="44"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G78" s="5"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-    </row>
-    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="44"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-    </row>
-    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="44"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
-    </row>
-    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="44"/>
-      <c r="C81" s="39"/>
-      <c r="D81" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-    </row>
-    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="44"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
-    </row>
-    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="44"/>
-      <c r="C83" s="39"/>
-      <c r="D83" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83" s="5"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
-    </row>
-    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="44"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E84" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
@@ -3887,13 +4003,13 @@
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="44"/>
-      <c r="C85" s="39"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="38"/>
       <c r="D85" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>9</v>
@@ -3904,13 +4020,13 @@
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="44"/>
-      <c r="C86" s="39"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="38"/>
       <c r="D86" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>9</v>
@@ -3921,13 +4037,13 @@
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="44"/>
-      <c r="C87" s="39"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="38"/>
       <c r="D87" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>9</v>
@@ -3938,16 +4054,16 @@
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="44"/>
-      <c r="C88" s="39"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="38"/>
       <c r="D88" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="6"/>
@@ -3955,16 +4071,16 @@
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="44"/>
-      <c r="C89" s="39"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="38"/>
       <c r="D89" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="6"/>
@@ -3972,16 +4088,16 @@
       <c r="J89" s="5"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="44"/>
-      <c r="C90" s="39"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="38"/>
       <c r="D90" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="6"/>
@@ -3989,16 +4105,16 @@
       <c r="J90" s="5"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="44"/>
-      <c r="C91" s="39"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="38"/>
       <c r="D91" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>63</v>
+        <v>53</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="6"/>
@@ -4006,13 +4122,13 @@
       <c r="J91" s="5"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="44"/>
-      <c r="C92" s="39"/>
+      <c r="B92" s="43"/>
+      <c r="C92" s="38"/>
       <c r="D92" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E92" s="19" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>9</v>
@@ -4023,13 +4139,13 @@
       <c r="J92" s="5"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="44"/>
-      <c r="C93" s="39"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="38"/>
       <c r="D93" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>78</v>
+        <v>53</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>9</v>
@@ -4040,16 +4156,16 @@
       <c r="J93" s="5"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="44"/>
-      <c r="C94" s="39"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="38"/>
       <c r="D94" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>69</v>
+        <v>53</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>59</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="6"/>
@@ -4057,16 +4173,16 @@
       <c r="J94" s="5"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="44"/>
-      <c r="C95" s="39"/>
+      <c r="B95" s="43"/>
+      <c r="C95" s="38"/>
       <c r="D95" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E95" s="19" t="s">
-        <v>70</v>
+      <c r="E95" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="6"/>
@@ -4074,16 +4190,16 @@
       <c r="J95" s="5"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="44"/>
-      <c r="C96" s="39"/>
+      <c r="B96" s="43"/>
+      <c r="C96" s="38"/>
       <c r="D96" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E96" s="19" t="s">
-        <v>64</v>
+      <c r="E96" s="18" t="s">
+        <v>61</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="6"/>
@@ -4091,16 +4207,16 @@
       <c r="J96" s="5"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="44"/>
-      <c r="C97" s="39"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="38"/>
       <c r="D97" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E97" s="19" t="s">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="6"/>
@@ -4108,13 +4224,13 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="44"/>
-      <c r="C98" s="39"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="38"/>
       <c r="D98" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E98" s="19" t="s">
-        <v>72</v>
+        <v>60</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>63</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>9</v>
@@ -4125,13 +4241,13 @@
       <c r="J98" s="5"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="44"/>
-      <c r="C99" s="39"/>
+      <c r="B99" s="43"/>
+      <c r="C99" s="38"/>
       <c r="D99" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>73</v>
+        <v>60</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>9</v>
@@ -4142,13 +4258,13 @@
       <c r="J99" s="5"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="44"/>
-      <c r="C100" s="39"/>
+      <c r="B100" s="43"/>
+      <c r="C100" s="38"/>
       <c r="D100" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E100" s="19" t="s">
-        <v>74</v>
+        <v>60</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>9</v>
@@ -4159,16 +4275,16 @@
       <c r="J100" s="5"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="44"/>
-      <c r="C101" s="39"/>
+      <c r="B101" s="43"/>
+      <c r="C101" s="38"/>
       <c r="D101" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E101" s="19" t="s">
-        <v>79</v>
+        <v>60</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>69</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="6"/>
@@ -4176,16 +4292,16 @@
       <c r="J101" s="5"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="44"/>
-      <c r="C102" s="39"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="38"/>
       <c r="D102" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E102" s="19" t="s">
-        <v>80</v>
+        <v>60</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="6"/>
@@ -4193,16 +4309,16 @@
       <c r="J102" s="5"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="44"/>
-      <c r="C103" s="39"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="38"/>
       <c r="D103" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>81</v>
+        <v>60</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="6"/>
@@ -4210,16 +4326,16 @@
       <c r="J103" s="5"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="44"/>
-      <c r="C104" s="39"/>
+      <c r="B104" s="43"/>
+      <c r="C104" s="38"/>
       <c r="D104" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E104" s="19" t="s">
-        <v>82</v>
+      <c r="E104" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="6"/>
@@ -4227,16 +4343,16 @@
       <c r="J104" s="5"/>
     </row>
     <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="44"/>
-      <c r="C105" s="39"/>
+      <c r="B105" s="43"/>
+      <c r="C105" s="38"/>
       <c r="D105" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E105" s="19" t="s">
-        <v>75</v>
+      <c r="E105" s="18" t="s">
+        <v>72</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="6"/>
@@ -4244,16 +4360,16 @@
       <c r="J105" s="5"/>
     </row>
     <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="44"/>
-      <c r="C106" s="39"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="38"/>
       <c r="D106" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E106" s="19" t="s">
-        <v>77</v>
+      <c r="E106" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="6"/>
@@ -4261,16 +4377,16 @@
       <c r="J106" s="5"/>
     </row>
     <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="44"/>
-      <c r="C107" s="39"/>
+      <c r="B107" s="43"/>
+      <c r="C107" s="38"/>
       <c r="D107" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E107" s="19" t="s">
-        <v>76</v>
+      <c r="E107" s="18" t="s">
+        <v>74</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="6"/>
@@ -4278,13 +4394,13 @@
       <c r="J107" s="5"/>
     </row>
     <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="44"/>
-      <c r="C108" s="39"/>
+      <c r="B108" s="43"/>
+      <c r="C108" s="38"/>
       <c r="D108" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E108" s="19" t="s">
-        <v>84</v>
+        <v>71</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>9</v>
@@ -4295,13 +4411,13 @@
       <c r="J108" s="5"/>
     </row>
     <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="44"/>
-      <c r="C109" s="39"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="38"/>
       <c r="D109" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E109" s="19" t="s">
-        <v>85</v>
+        <v>71</v>
+      </c>
+      <c r="E109" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>9</v>
@@ -4312,87 +4428,129 @@
       <c r="J109" s="5"/>
     </row>
     <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="44"/>
-      <c r="C110" s="40"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="8"/>
+      <c r="B110" s="43"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E110" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G110" s="5"/>
       <c r="H110" s="6"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
     </row>
     <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="44"/>
-      <c r="C111" s="47"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="8"/>
+      <c r="B111" s="43"/>
+      <c r="C111" s="38"/>
+      <c r="D111" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E111" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G111" s="5"/>
       <c r="H111" s="6"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
     </row>
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="44"/>
-      <c r="C112" s="48"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="8"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E112" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G112" s="5"/>
       <c r="H112" s="6"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="44"/>
-      <c r="C113" s="48"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="8"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G113" s="5"/>
       <c r="H113" s="6"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="44"/>
-      <c r="C114" s="48"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="8"/>
+      <c r="B114" s="43"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E114" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G114" s="5"/>
       <c r="H114" s="6"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="44"/>
-      <c r="C115" s="48"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="8"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="38"/>
+      <c r="D115" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E115" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G115" s="5"/>
       <c r="H115" s="6"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="44"/>
-      <c r="C116" s="48"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="16"/>
-      <c r="F116" s="8"/>
+      <c r="B116" s="43"/>
+      <c r="C116" s="38"/>
+      <c r="D116" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G116" s="5"/>
       <c r="H116" s="6"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="44"/>
-      <c r="C117" s="48"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="39"/>
       <c r="D117" s="8"/>
-      <c r="E117" s="16"/>
+      <c r="E117" s="15"/>
       <c r="F117" s="8"/>
       <c r="G117" s="5"/>
       <c r="H117" s="6"/>
@@ -4400,10 +4558,10 @@
       <c r="J117" s="5"/>
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="44"/>
-      <c r="C118" s="48"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="46"/>
       <c r="D118" s="8"/>
-      <c r="E118" s="16"/>
+      <c r="E118" s="15"/>
       <c r="F118" s="8"/>
       <c r="G118" s="5"/>
       <c r="H118" s="6"/>
@@ -4411,10 +4569,10 @@
       <c r="J118" s="5"/>
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="44"/>
-      <c r="C119" s="48"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="47"/>
       <c r="D119" s="8"/>
-      <c r="E119" s="16"/>
+      <c r="E119" s="15"/>
       <c r="F119" s="8"/>
       <c r="G119" s="5"/>
       <c r="H119" s="6"/>
@@ -4422,10 +4580,10 @@
       <c r="J119" s="5"/>
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="44"/>
-      <c r="C120" s="48"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="47"/>
       <c r="D120" s="8"/>
-      <c r="E120" s="16"/>
+      <c r="E120" s="15"/>
       <c r="F120" s="8"/>
       <c r="G120" s="5"/>
       <c r="H120" s="6"/>
@@ -4433,10 +4591,10 @@
       <c r="J120" s="5"/>
     </row>
     <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="44"/>
-      <c r="C121" s="48"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="47"/>
       <c r="D121" s="8"/>
-      <c r="E121" s="16"/>
+      <c r="E121" s="15"/>
       <c r="F121" s="8"/>
       <c r="G121" s="5"/>
       <c r="H121" s="6"/>
@@ -4444,10 +4602,10 @@
       <c r="J121" s="5"/>
     </row>
     <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="44"/>
-      <c r="C122" s="48"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="47"/>
       <c r="D122" s="8"/>
-      <c r="E122" s="16"/>
+      <c r="E122" s="15"/>
       <c r="F122" s="8"/>
       <c r="G122" s="5"/>
       <c r="H122" s="6"/>
@@ -4455,10 +4613,10 @@
       <c r="J122" s="5"/>
     </row>
     <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="44"/>
-      <c r="C123" s="48"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="47"/>
       <c r="D123" s="8"/>
-      <c r="E123" s="16"/>
+      <c r="E123" s="15"/>
       <c r="F123" s="8"/>
       <c r="G123" s="5"/>
       <c r="H123" s="6"/>
@@ -4466,10 +4624,10 @@
       <c r="J123" s="5"/>
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="44"/>
-      <c r="C124" s="48"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="47"/>
       <c r="D124" s="8"/>
-      <c r="E124" s="16"/>
+      <c r="E124" s="15"/>
       <c r="F124" s="8"/>
       <c r="G124" s="5"/>
       <c r="H124" s="6"/>
@@ -4477,10 +4635,10 @@
       <c r="J124" s="5"/>
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="44"/>
-      <c r="C125" s="48"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="47"/>
       <c r="D125" s="8"/>
-      <c r="E125" s="16"/>
+      <c r="E125" s="15"/>
       <c r="F125" s="8"/>
       <c r="G125" s="5"/>
       <c r="H125" s="6"/>
@@ -4488,27 +4646,104 @@
       <c r="J125" s="5"/>
     </row>
     <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="45"/>
-      <c r="C126" s="49"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="47"/>
       <c r="D126" s="8"/>
-      <c r="E126" s="16"/>
+      <c r="E126" s="15"/>
       <c r="F126" s="8"/>
       <c r="G126" s="5"/>
       <c r="H126" s="6"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
     </row>
-    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="129" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="130" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="43"/>
+      <c r="C127" s="47"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+    </row>
+    <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" s="43"/>
+      <c r="C128" s="47"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+    </row>
+    <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" s="43"/>
+      <c r="C129" s="47"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="15"/>
+      <c r="F129" s="8"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5"/>
+    </row>
+    <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" s="43"/>
+      <c r="C130" s="47"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="15"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+    </row>
+    <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="43"/>
+      <c r="C131" s="47"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+    </row>
+    <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="43"/>
+      <c r="C132" s="47"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="15"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5"/>
+    </row>
+    <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" s="44"/>
+      <c r="C133" s="48"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="8"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5"/>
+    </row>
+    <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C110"/>
+    <mergeCell ref="C3:C117"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B126"/>
+    <mergeCell ref="B3:B133"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C111:C126"/>
+    <mergeCell ref="C118:C133"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4530,15 +4765,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -4610,15 +4845,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A390F15-D43B-4D06-BDE0-A70DCD89D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18799461-6F4B-4FDF-A260-517C06156460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="136">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1568,19 +1568,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パスワード欄に「半角英字のみ」「半角数字のみ」のパスワードを入力</t>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>ハンカクエイジ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>パスワード欄に11字以上の文字数を入力</t>
     <rPh sb="9" eb="10">
       <t>ジ</t>
@@ -1597,41 +1584,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パスワード欄に「半角英数字のみ」のパスワードを入力</t>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンカク</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>エイスウジ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パスワード欄に「全角英字のみ」「全角数字のみ」のパスワードを入力</t>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゼンカク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ゼンカク</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>そもそも入力ができない。（入力形式が切り替わらない）</t>
     <rPh sb="4" eb="6">
       <t>ニュウリョク</t>
@@ -1700,6 +1652,151 @@
     <t>メールアドレス欄に「半角英字のみ＠　～」「半角数字のみ＠　～」（どこか間にスペースを入力）</t>
     <rPh sb="35" eb="36">
       <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「半角英字のみ」「半角数字のみ」入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ハンカクエイジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「半角英数字のみ」入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>エイスウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に「全角英字のみ」「全角数字のみ」入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「このフィールドを入力してください。」というエラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１～６桁もしくは８桁以上入力</t>
+    <rPh sb="3" eb="4">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ケタイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄に「ひらがなのみ」「カタカナのみ」「漢字のみ」「英字のみ」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>エイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄に「半角数字のみ」入力</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ハンカクスウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄に「全角数字のみ」入力</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄に「記号（ハイフン含む）」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄に「半角数字のみ（間にスペースを入力）」入力</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ハンカクスウジ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2440,7 +2537,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K137"/>
+  <dimension ref="B1:K144"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -3703,7 +3800,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F67" s="49" t="s">
         <v>28</v>
@@ -3720,7 +3817,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F68" s="49" t="s">
         <v>28</v>
@@ -3740,7 +3837,7 @@
         <v>25</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
@@ -3873,7 +3970,7 @@
         <v>29</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>102</v>
@@ -3890,7 +3987,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="54" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F78" s="49" t="s">
         <v>9</v>
@@ -3907,7 +4004,7 @@
         <v>29</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F79" s="49" t="s">
         <v>9</v>
@@ -3924,10 +4021,10 @@
         <v>29</v>
       </c>
       <c r="E80" s="54" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F80" s="49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G80" s="51"/>
       <c r="H80" s="52"/>
@@ -3941,10 +4038,10 @@
         <v>29</v>
       </c>
       <c r="E81" s="54" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F81" s="49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G81" s="51"/>
       <c r="H81" s="52"/>
@@ -3958,7 +4055,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F82" s="49" t="s">
         <v>28</v>
@@ -3975,7 +4072,7 @@
         <v>29</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F83" s="49" t="s">
         <v>28</v>
@@ -4039,201 +4136,201 @@
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="43"/>
       <c r="C87" s="38"/>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="F87" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G87" s="5"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="32"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="43"/>
       <c r="C88" s="38"/>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E88" s="18" t="s">
+      <c r="E88" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="8" t="s">
+      <c r="F88" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G88" s="5"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="32"/>
+      <c r="J88" s="32"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="43"/>
       <c r="C89" s="38"/>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="F89" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G89" s="5"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="32"/>
+      <c r="J89" s="32"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="43"/>
       <c r="C90" s="38"/>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="E90" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F90" s="8" t="s">
+      <c r="F90" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G90" s="5"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="36"/>
+      <c r="I90" s="32"/>
+      <c r="J90" s="32"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="43"/>
       <c r="C91" s="38"/>
-      <c r="D91" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E91" s="15" t="s">
+      <c r="D91" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E91" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F91" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G91" s="5"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
+      <c r="F91" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="G91" s="51"/>
+      <c r="H91" s="52"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="51"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="43"/>
       <c r="C92" s="38"/>
-      <c r="D92" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E92" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
+      <c r="D92" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E92" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F92" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" s="51"/>
+      <c r="H92" s="52"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="51"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="43"/>
       <c r="C93" s="38"/>
-      <c r="D93" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="F93" s="8" t="s">
+      <c r="D93" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E93" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="F93" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="43"/>
       <c r="C94" s="38"/>
-      <c r="D94" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
+      <c r="D94" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E94" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F94" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="51"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="51"/>
+      <c r="J94" s="51"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="43"/>
       <c r="C95" s="38"/>
-      <c r="D95" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
+      <c r="D95" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E95" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="F95" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="51"/>
+      <c r="H95" s="52"/>
+      <c r="I95" s="51"/>
+      <c r="J95" s="51"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="43"/>
       <c r="C96" s="38"/>
-      <c r="D96" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
+      <c r="D96" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E96" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F96" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="51"/>
+      <c r="H96" s="52"/>
+      <c r="I96" s="51"/>
+      <c r="J96" s="51"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="43"/>
       <c r="C97" s="38"/>
-      <c r="D97" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
+      <c r="D97" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E97" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F97" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="51"/>
+      <c r="H97" s="52"/>
+      <c r="I97" s="51"/>
+      <c r="J97" s="51"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="43"/>
       <c r="C98" s="38"/>
       <c r="D98" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>63</v>
+        <v>53</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="6"/>
@@ -4244,10 +4341,10 @@
       <c r="B99" s="43"/>
       <c r="C99" s="38"/>
       <c r="D99" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>9</v>
@@ -4261,10 +4358,10 @@
       <c r="B100" s="43"/>
       <c r="C100" s="38"/>
       <c r="D100" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>9</v>
@@ -4278,13 +4375,13 @@
       <c r="B101" s="43"/>
       <c r="C101" s="38"/>
       <c r="D101" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="6"/>
@@ -4298,10 +4395,10 @@
         <v>60</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="6"/>
@@ -4315,10 +4412,10 @@
         <v>60</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="6"/>
@@ -4329,13 +4426,13 @@
       <c r="B104" s="43"/>
       <c r="C104" s="38"/>
       <c r="D104" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="6"/>
@@ -4346,10 +4443,10 @@
       <c r="B105" s="43"/>
       <c r="C105" s="38"/>
       <c r="D105" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>9</v>
@@ -4363,10 +4460,10 @@
       <c r="B106" s="43"/>
       <c r="C106" s="38"/>
       <c r="D106" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>9</v>
@@ -4380,10 +4477,10 @@
       <c r="B107" s="43"/>
       <c r="C107" s="38"/>
       <c r="D107" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>9</v>
@@ -4397,13 +4494,13 @@
       <c r="B108" s="43"/>
       <c r="C108" s="38"/>
       <c r="D108" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="6"/>
@@ -4414,13 +4511,13 @@
       <c r="B109" s="43"/>
       <c r="C109" s="38"/>
       <c r="D109" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="6"/>
@@ -4431,13 +4528,13 @@
       <c r="B110" s="43"/>
       <c r="C110" s="38"/>
       <c r="D110" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="6"/>
@@ -4451,10 +4548,10 @@
         <v>71</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="6"/>
@@ -4468,10 +4565,10 @@
         <v>71</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="6"/>
@@ -4485,10 +4582,10 @@
         <v>71</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="6"/>
@@ -4502,10 +4599,10 @@
         <v>71</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="6"/>
@@ -4516,10 +4613,10 @@
       <c r="B115" s="43"/>
       <c r="C115" s="38"/>
       <c r="D115" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>9</v>
@@ -4533,10 +4630,10 @@
       <c r="B116" s="43"/>
       <c r="C116" s="38"/>
       <c r="D116" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>9</v>
@@ -4548,10 +4645,16 @@
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="43"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="8"/>
+      <c r="C117" s="38"/>
+      <c r="D117" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E117" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G117" s="5"/>
       <c r="H117" s="6"/>
       <c r="I117" s="5"/>
@@ -4559,10 +4662,16 @@
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="43"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="8"/>
+      <c r="C118" s="38"/>
+      <c r="D118" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E118" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G118" s="5"/>
       <c r="H118" s="6"/>
       <c r="I118" s="5"/>
@@ -4570,10 +4679,16 @@
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="43"/>
-      <c r="C119" s="47"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="8"/>
+      <c r="C119" s="38"/>
+      <c r="D119" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E119" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G119" s="5"/>
       <c r="H119" s="6"/>
       <c r="I119" s="5"/>
@@ -4581,10 +4696,16 @@
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="43"/>
-      <c r="C120" s="47"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="8"/>
+      <c r="C120" s="38"/>
+      <c r="D120" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E120" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G120" s="5"/>
       <c r="H120" s="6"/>
       <c r="I120" s="5"/>
@@ -4592,10 +4713,16 @@
     </row>
     <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="43"/>
-      <c r="C121" s="47"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="8"/>
+      <c r="C121" s="38"/>
+      <c r="D121" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E121" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G121" s="5"/>
       <c r="H121" s="6"/>
       <c r="I121" s="5"/>
@@ -4603,10 +4730,16 @@
     </row>
     <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="43"/>
-      <c r="C122" s="47"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="8"/>
+      <c r="C122" s="38"/>
+      <c r="D122" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G122" s="5"/>
       <c r="H122" s="6"/>
       <c r="I122" s="5"/>
@@ -4614,10 +4747,16 @@
     </row>
     <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" s="43"/>
-      <c r="C123" s="47"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="8"/>
+      <c r="C123" s="38"/>
+      <c r="D123" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G123" s="5"/>
       <c r="H123" s="6"/>
       <c r="I123" s="5"/>
@@ -4625,7 +4764,7 @@
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="43"/>
-      <c r="C124" s="47"/>
+      <c r="C124" s="39"/>
       <c r="D124" s="8"/>
       <c r="E124" s="15"/>
       <c r="F124" s="8"/>
@@ -4636,7 +4775,7 @@
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="43"/>
-      <c r="C125" s="47"/>
+      <c r="C125" s="46"/>
       <c r="D125" s="8"/>
       <c r="E125" s="15"/>
       <c r="F125" s="8"/>
@@ -4723,8 +4862,8 @@
       <c r="J132" s="5"/>
     </row>
     <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="44"/>
-      <c r="C133" s="48"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="47"/>
       <c r="D133" s="8"/>
       <c r="E133" s="15"/>
       <c r="F133" s="8"/>
@@ -4733,17 +4872,94 @@
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
     </row>
-    <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" s="43"/>
+      <c r="C134" s="47"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="15"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5"/>
+    </row>
+    <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" s="43"/>
+      <c r="C135" s="47"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+    </row>
+    <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="43"/>
+      <c r="C136" s="47"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5"/>
+    </row>
+    <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" s="43"/>
+      <c r="C137" s="47"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+    </row>
+    <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="43"/>
+      <c r="C138" s="47"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+    </row>
+    <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="43"/>
+      <c r="C139" s="47"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="15"/>
+      <c r="F139" s="8"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+    </row>
+    <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="44"/>
+      <c r="C140" s="48"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+    </row>
+    <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C117"/>
+    <mergeCell ref="C3:C124"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B133"/>
+    <mergeCell ref="B3:B140"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C118:C133"/>
+    <mergeCell ref="C125:C140"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18799461-6F4B-4FDF-A260-517C06156460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E792AC-63EF-4667-B1D6-863FC298887E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="139">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -602,13 +602,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「選択してください」というエラー</t>
-    <rPh sb="1" eb="3">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「北海道」を選択
 →”確認する”押下</t>
     <rPh sb="1" eb="4">
@@ -1797,6 +1790,37 @@
     </rPh>
     <rPh sb="26" eb="28">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択せず</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択せず</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「リストの項目を選択してください。」というエラー</t>
+    <rPh sb="5" eb="7">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プルダウンより選択する</t>
+    <rPh sb="7" eb="9">
+      <t>センタク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2537,7 +2561,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K144"/>
+  <dimension ref="B1:K145"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -2553,7 +2577,7 @@
   <sheetData>
     <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B1" s="45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
@@ -2591,10 +2615,10 @@
     </row>
     <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>20</v>
@@ -2635,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2663,7 +2687,7 @@
         <v>11</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2691,7 +2715,7 @@
         <v>11</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2719,7 +2743,7 @@
         <v>11</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2729,7 +2753,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>9</v>
@@ -2746,10 +2770,10 @@
         <v>20</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="14"/>
@@ -2763,7 +2787,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>9</v>
@@ -2780,10 +2804,10 @@
         <v>20</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="14"/>
@@ -2797,10 +2821,10 @@
         <v>20</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="14"/>
@@ -2814,10 +2838,10 @@
         <v>20</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="14"/>
@@ -2831,10 +2855,10 @@
         <v>20</v>
       </c>
       <c r="E14" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="14"/>
@@ -2883,7 +2907,7 @@
         <v>11</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2911,7 +2935,7 @@
         <v>11</v>
       </c>
       <c r="K17" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2939,7 +2963,7 @@
         <v>11</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2967,7 +2991,7 @@
         <v>11</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2977,7 +3001,7 @@
         <v>21</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>9</v>
@@ -2994,10 +3018,10 @@
         <v>21</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="14"/>
@@ -3011,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>9</v>
@@ -3028,10 +3052,10 @@
         <v>21</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="14"/>
@@ -3045,10 +3069,10 @@
         <v>21</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="14"/>
@@ -3062,10 +3086,10 @@
         <v>21</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="14"/>
@@ -3079,10 +3103,10 @@
         <v>21</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="14"/>
@@ -3123,7 +3147,7 @@
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
       <c r="K28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3143,7 +3167,7 @@
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
       <c r="K29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3163,7 +3187,7 @@
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
       <c r="K30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3183,7 +3207,7 @@
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
       <c r="K31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3193,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>9</v>
@@ -3210,7 +3234,7 @@
         <v>22</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>28</v>
@@ -3227,7 +3251,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -3244,10 +3268,10 @@
         <v>22</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="6"/>
@@ -3261,10 +3285,10 @@
         <v>22</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="6"/>
@@ -3278,10 +3302,10 @@
         <v>22</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="6"/>
@@ -3295,10 +3319,10 @@
         <v>22</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="6"/>
@@ -3339,7 +3363,7 @@
       <c r="I40" s="32"/>
       <c r="J40" s="32"/>
       <c r="K40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3359,7 +3383,7 @@
       <c r="I41" s="32"/>
       <c r="J41" s="32"/>
       <c r="K41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3379,7 +3403,7 @@
       <c r="I42" s="32"/>
       <c r="J42" s="32"/>
       <c r="K42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3399,7 +3423,7 @@
       <c r="I43" s="32"/>
       <c r="J43" s="32"/>
       <c r="K43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3409,7 +3433,7 @@
         <v>23</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>9</v>
@@ -3426,7 +3450,7 @@
         <v>23</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>28</v>
@@ -3443,7 +3467,7 @@
         <v>23</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -3460,10 +3484,10 @@
         <v>23</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="6"/>
@@ -3477,10 +3501,10 @@
         <v>23</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="6"/>
@@ -3494,10 +3518,10 @@
         <v>23</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="6"/>
@@ -3511,10 +3535,10 @@
         <v>23</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="6"/>
@@ -3681,10 +3705,10 @@
         <v>24</v>
       </c>
       <c r="E60" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>116</v>
       </c>
       <c r="G60" s="51"/>
       <c r="H60" s="52"/>
@@ -3698,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F61" s="49" t="s">
         <v>9</v>
@@ -3715,7 +3739,7 @@
         <v>24</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="49" t="s">
         <v>9</v>
@@ -3732,7 +3756,7 @@
         <v>24</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F63" s="49" t="s">
         <v>28</v>
@@ -3749,7 +3773,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F64" s="49" t="s">
         <v>28</v>
@@ -3766,7 +3790,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F65" s="49" t="s">
         <v>9</v>
@@ -3783,7 +3807,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F66" s="49" t="s">
         <v>9</v>
@@ -3800,7 +3824,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F67" s="49" t="s">
         <v>28</v>
@@ -3817,7 +3841,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F68" s="49" t="s">
         <v>28</v>
@@ -3837,7 +3861,7 @@
         <v>25</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
@@ -3970,10 +3994,10 @@
         <v>29</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G77" s="51"/>
       <c r="H77" s="52"/>
@@ -3987,7 +4011,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F78" s="49" t="s">
         <v>9</v>
@@ -4004,7 +4028,7 @@
         <v>29</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F79" s="49" t="s">
         <v>9</v>
@@ -4021,10 +4045,10 @@
         <v>29</v>
       </c>
       <c r="E80" s="54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F80" s="49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G80" s="51"/>
       <c r="H80" s="52"/>
@@ -4038,10 +4062,10 @@
         <v>29</v>
       </c>
       <c r="E81" s="54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F81" s="49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G81" s="51"/>
       <c r="H81" s="52"/>
@@ -4055,7 +4079,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F82" s="49" t="s">
         <v>28</v>
@@ -4072,7 +4096,7 @@
         <v>29</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F83" s="49" t="s">
         <v>28</v>
@@ -4089,7 +4113,7 @@
         <v>45</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>55</v>
@@ -4211,7 +4235,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G91" s="51"/>
       <c r="H91" s="52"/>
@@ -4225,7 +4249,7 @@
         <v>54</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F92" s="49" t="s">
         <v>28</v>
@@ -4242,7 +4266,7 @@
         <v>54</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F93" s="49" t="s">
         <v>9</v>
@@ -4259,7 +4283,7 @@
         <v>54</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F94" s="49" t="s">
         <v>28</v>
@@ -4276,7 +4300,7 @@
         <v>54</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F95" s="49" t="s">
         <v>28</v>
@@ -4293,7 +4317,7 @@
         <v>54</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F96" s="49" t="s">
         <v>28</v>
@@ -4310,7 +4334,7 @@
         <v>54</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F97" s="49" t="s">
         <v>28</v>
@@ -4323,99 +4347,99 @@
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="43"/>
       <c r="C98" s="38"/>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E98" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="8" t="s">
+      <c r="E98" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="G98" s="5"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
+      <c r="F98" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G98" s="32"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="32"/>
+      <c r="J98" s="32"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="43"/>
       <c r="C99" s="38"/>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E99" s="18" t="s">
+      <c r="E99" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="F99" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="32"/>
+      <c r="J99" s="32"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="43"/>
       <c r="C100" s="38"/>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E100" s="18" t="s">
+      <c r="E100" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="32"/>
+      <c r="J100" s="32"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="43"/>
       <c r="C101" s="38"/>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="E101" s="18" t="s">
-        <v>59</v>
+      <c r="E101" s="50" t="s">
+        <v>135</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="G101" s="51"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="51"/>
+      <c r="J101" s="51"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="43"/>
       <c r="C102" s="38"/>
-      <c r="D102" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E102" s="18" t="s">
-        <v>25</v>
+      <c r="D102" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="50" t="s">
+        <v>138</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="G102" s="51"/>
+      <c r="H102" s="52"/>
+      <c r="I102" s="51"/>
+      <c r="J102" s="51"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="43"/>
       <c r="C103" s="38"/>
       <c r="D103" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="6"/>
@@ -4426,10 +4450,10 @@
       <c r="B104" s="43"/>
       <c r="C104" s="38"/>
       <c r="D104" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E104" s="18" t="s">
         <v>60</v>
-      </c>
-      <c r="E104" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>9</v>
@@ -4443,10 +4467,10 @@
       <c r="B105" s="43"/>
       <c r="C105" s="38"/>
       <c r="D105" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>9</v>
@@ -4460,10 +4484,10 @@
       <c r="B106" s="43"/>
       <c r="C106" s="38"/>
       <c r="D106" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>9</v>
@@ -4477,10 +4501,10 @@
       <c r="B107" s="43"/>
       <c r="C107" s="38"/>
       <c r="D107" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>9</v>
@@ -4494,13 +4518,13 @@
       <c r="B108" s="43"/>
       <c r="C108" s="38"/>
       <c r="D108" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="6"/>
@@ -4511,10 +4535,10 @@
       <c r="B109" s="43"/>
       <c r="C109" s="38"/>
       <c r="D109" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>28</v>
@@ -4528,10 +4552,10 @@
       <c r="B110" s="43"/>
       <c r="C110" s="38"/>
       <c r="D110" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4545,13 +4569,13 @@
       <c r="B111" s="43"/>
       <c r="C111" s="38"/>
       <c r="D111" s="8" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="6"/>
@@ -4562,13 +4586,13 @@
       <c r="B112" s="43"/>
       <c r="C112" s="38"/>
       <c r="D112" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="6"/>
@@ -4579,10 +4603,10 @@
       <c r="B113" s="43"/>
       <c r="C113" s="38"/>
       <c r="D113" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E113" s="18" t="s">
         <v>71</v>
-      </c>
-      <c r="E113" s="18" t="s">
-        <v>73</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>9</v>
@@ -4596,10 +4620,10 @@
       <c r="B114" s="43"/>
       <c r="C114" s="38"/>
       <c r="D114" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>9</v>
@@ -4613,10 +4637,10 @@
       <c r="B115" s="43"/>
       <c r="C115" s="38"/>
       <c r="D115" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>9</v>
@@ -4630,10 +4654,10 @@
       <c r="B116" s="43"/>
       <c r="C116" s="38"/>
       <c r="D116" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>9</v>
@@ -4647,10 +4671,10 @@
       <c r="B117" s="43"/>
       <c r="C117" s="38"/>
       <c r="D117" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>9</v>
@@ -4664,13 +4688,13 @@
       <c r="B118" s="43"/>
       <c r="C118" s="38"/>
       <c r="D118" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E118" s="18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="6"/>
@@ -4681,10 +4705,10 @@
       <c r="B119" s="43"/>
       <c r="C119" s="38"/>
       <c r="D119" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E119" s="18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>28</v>
@@ -4698,10 +4722,10 @@
       <c r="B120" s="43"/>
       <c r="C120" s="38"/>
       <c r="D120" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4715,7 +4739,7 @@
       <c r="B121" s="43"/>
       <c r="C121" s="38"/>
       <c r="D121" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E121" s="18" t="s">
         <v>76</v>
@@ -4732,13 +4756,13 @@
       <c r="B122" s="43"/>
       <c r="C122" s="38"/>
       <c r="D122" s="8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="6"/>
@@ -4749,10 +4773,10 @@
       <c r="B123" s="43"/>
       <c r="C123" s="38"/>
       <c r="D123" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E123" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="E123" s="18" t="s">
-        <v>85</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>9</v>
@@ -4764,10 +4788,16 @@
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="43"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="8"/>
+      <c r="C124" s="38"/>
+      <c r="D124" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E124" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G124" s="5"/>
       <c r="H124" s="6"/>
       <c r="I124" s="5"/>
@@ -4775,7 +4805,7 @@
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="43"/>
-      <c r="C125" s="46"/>
+      <c r="C125" s="39"/>
       <c r="D125" s="8"/>
       <c r="E125" s="15"/>
       <c r="F125" s="8"/>
@@ -4786,7 +4816,7 @@
     </row>
     <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" s="43"/>
-      <c r="C126" s="47"/>
+      <c r="C126" s="46"/>
       <c r="D126" s="8"/>
       <c r="E126" s="15"/>
       <c r="F126" s="8"/>
@@ -4939,8 +4969,8 @@
       <c r="J139" s="5"/>
     </row>
     <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="44"/>
-      <c r="C140" s="48"/>
+      <c r="B140" s="43"/>
+      <c r="C140" s="47"/>
       <c r="D140" s="8"/>
       <c r="E140" s="15"/>
       <c r="F140" s="8"/>
@@ -4949,17 +4979,28 @@
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
     </row>
-    <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" s="44"/>
+      <c r="C141" s="48"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+    </row>
     <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="145" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C124"/>
+    <mergeCell ref="C3:C125"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B140"/>
+    <mergeCell ref="B3:B141"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C125:C140"/>
+    <mergeCell ref="C126:C141"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E792AC-63EF-4667-B1D6-863FC298887E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8F45DA-4C66-4471-A97E-4980AB5AC634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="単体テスト" sheetId="1" r:id="rId1"/>
-    <sheet name="結合テスト" sheetId="2" r:id="rId2"/>
-    <sheet name="総合テスト" sheetId="3" r:id="rId3"/>
+    <sheet name="単体テスト（訂正前あり）" sheetId="1" r:id="rId1"/>
+    <sheet name="単体テスト (新)" sheetId="4" r:id="rId2"/>
+    <sheet name="結合テスト" sheetId="2" r:id="rId3"/>
+    <sheet name="総合テスト" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="149">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1821,6 +1822,139 @@
     <t>プルダウンより選択する</t>
     <rPh sb="7" eb="9">
       <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「ひらがなのみ」「カタカナのみ」「漢字のみ」「数字のみ」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「ひらがな＋カタカナor漢字or数字」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「ひらがな＋カタカナ＋漢字or数字」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「ひらがな＋カタカナ＋漢字＋数字」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「ハイフン（-、－）」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「英字のみ」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「記号（ハイフン（-、－）除く）」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村欄に「スペース（半角・全角）」を入力</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゼンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前（名）欄に「数字」「記号」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「ハイフンのみ＠　～」「＠ のみ＠　～」を入力</t>
+    <rPh sb="30" eb="32">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2193,6 +2327,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2237,12 +2377,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2561,7 +2695,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K145"/>
+  <dimension ref="B1:K153"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -2576,24 +2710,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
     </row>
     <row r="2" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="16" t="s">
         <v>1</v>
       </c>
@@ -2614,10 +2748,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="40" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -2635,8 +2769,8 @@
       <c r="J3" s="11"/>
     </row>
     <row r="4" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="43"/>
-      <c r="C4" s="38"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="20" t="s">
         <v>20</v>
       </c>
@@ -2663,8 +2797,8 @@
       </c>
     </row>
     <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="43"/>
-      <c r="C5" s="38"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
@@ -2691,8 +2825,8 @@
       </c>
     </row>
     <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="43"/>
-      <c r="C6" s="38"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="20" t="s">
         <v>20</v>
       </c>
@@ -2719,8 +2853,8 @@
       </c>
     </row>
     <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="43"/>
-      <c r="C7" s="38"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="20" t="s">
         <v>20</v>
       </c>
@@ -2747,8 +2881,8 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="43"/>
-      <c r="C8" s="38"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="9" t="s">
         <v>20</v>
       </c>
@@ -2764,8 +2898,8 @@
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="43"/>
-      <c r="C9" s="38"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="40"/>
       <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
@@ -2781,8 +2915,8 @@
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="43"/>
-      <c r="C10" s="38"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="9" t="s">
         <v>20</v>
       </c>
@@ -2798,8 +2932,8 @@
       <c r="J10" s="13"/>
     </row>
     <row r="11" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="43"/>
-      <c r="C11" s="38"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2949,8 @@
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="43"/>
-      <c r="C12" s="38"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
@@ -2832,8 +2966,8 @@
       <c r="J12" s="13"/>
     </row>
     <row r="13" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="43"/>
-      <c r="C13" s="38"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="9" t="s">
         <v>20</v>
       </c>
@@ -2849,8 +2983,8 @@
       <c r="J13" s="13"/>
     </row>
     <row r="14" spans="2:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="43"/>
-      <c r="C14" s="38"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
@@ -2866,8 +3000,8 @@
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="43"/>
-      <c r="C15" s="38"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
@@ -2883,8 +3017,8 @@
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="43"/>
-      <c r="C16" s="38"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="29" t="s">
         <v>21</v>
       </c>
@@ -2911,8 +3045,8 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="43"/>
-      <c r="C17" s="38"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="29" t="s">
         <v>21</v>
       </c>
@@ -2939,8 +3073,8 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="43"/>
-      <c r="C18" s="38"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="29" t="s">
         <v>21</v>
       </c>
@@ -2967,8 +3101,8 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="43"/>
-      <c r="C19" s="38"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="29" t="s">
         <v>21</v>
       </c>
@@ -2995,8 +3129,8 @@
       </c>
     </row>
     <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="43"/>
-      <c r="C20" s="38"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
@@ -3012,8 +3146,8 @@
       <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="43"/>
-      <c r="C21" s="38"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="7" t="s">
         <v>21</v>
       </c>
@@ -3029,8 +3163,8 @@
       <c r="J21" s="13"/>
     </row>
     <row r="22" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="43"/>
-      <c r="C22" s="38"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="7" t="s">
         <v>21</v>
       </c>
@@ -3046,8 +3180,8 @@
       <c r="J22" s="13"/>
     </row>
     <row r="23" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="43"/>
-      <c r="C23" s="38"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="7" t="s">
         <v>21</v>
       </c>
@@ -3063,8 +3197,8 @@
       <c r="J23" s="13"/>
     </row>
     <row r="24" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="43"/>
-      <c r="C24" s="38"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="7" t="s">
         <v>21</v>
       </c>
@@ -3080,8 +3214,8 @@
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="43"/>
-      <c r="C25" s="38"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="7" t="s">
         <v>21</v>
       </c>
@@ -3097,8 +3231,8 @@
       <c r="J25" s="13"/>
     </row>
     <row r="26" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="43"/>
-      <c r="C26" s="38"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="7" t="s">
         <v>21</v>
       </c>
@@ -3114,8 +3248,8 @@
       <c r="J26" s="13"/>
     </row>
     <row r="27" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="43"/>
-      <c r="C27" s="38"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="7" t="s">
         <v>22</v>
       </c>
@@ -3131,8 +3265,8 @@
       <c r="J27" s="13"/>
     </row>
     <row r="28" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="43"/>
-      <c r="C28" s="38"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="29" t="s">
         <v>22</v>
       </c>
@@ -3151,8 +3285,8 @@
       </c>
     </row>
     <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="43"/>
-      <c r="C29" s="38"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="29" t="s">
         <v>22</v>
       </c>
@@ -3171,8 +3305,8 @@
       </c>
     </row>
     <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="43"/>
-      <c r="C30" s="38"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="29" t="s">
         <v>22</v>
       </c>
@@ -3191,8 +3325,8 @@
       </c>
     </row>
     <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="43"/>
-      <c r="C31" s="38"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="29" t="s">
         <v>22</v>
       </c>
@@ -3211,8 +3345,8 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="43"/>
-      <c r="C32" s="38"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="7" t="s">
         <v>22</v>
       </c>
@@ -3228,8 +3362,8 @@
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="43"/>
-      <c r="C33" s="38"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="7" t="s">
         <v>22</v>
       </c>
@@ -3245,8 +3379,8 @@
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="43"/>
-      <c r="C34" s="38"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="7" t="s">
         <v>22</v>
       </c>
@@ -3262,8 +3396,8 @@
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="43"/>
-      <c r="C35" s="38"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="7" t="s">
         <v>22</v>
       </c>
@@ -3279,8 +3413,8 @@
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="43"/>
-      <c r="C36" s="38"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="7" t="s">
         <v>22</v>
       </c>
@@ -3296,8 +3430,8 @@
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="43"/>
-      <c r="C37" s="38"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="7" t="s">
         <v>22</v>
       </c>
@@ -3313,8 +3447,8 @@
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="43"/>
-      <c r="C38" s="38"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="7" t="s">
         <v>22</v>
       </c>
@@ -3330,8 +3464,8 @@
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="43"/>
-      <c r="C39" s="38"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="7" t="s">
         <v>23</v>
       </c>
@@ -3347,8 +3481,8 @@
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="43"/>
-      <c r="C40" s="38"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="29" t="s">
         <v>23</v>
       </c>
@@ -3367,8 +3501,8 @@
       </c>
     </row>
     <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="43"/>
-      <c r="C41" s="38"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="40"/>
       <c r="D41" s="29" t="s">
         <v>23</v>
       </c>
@@ -3387,8 +3521,8 @@
       </c>
     </row>
     <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="43"/>
-      <c r="C42" s="38"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="40"/>
       <c r="D42" s="29" t="s">
         <v>23</v>
       </c>
@@ -3407,8 +3541,8 @@
       </c>
     </row>
     <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="43"/>
-      <c r="C43" s="38"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="40"/>
       <c r="D43" s="29" t="s">
         <v>23</v>
       </c>
@@ -3427,8 +3561,8 @@
       </c>
     </row>
     <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="43"/>
-      <c r="C44" s="38"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="40"/>
       <c r="D44" s="7" t="s">
         <v>23</v>
       </c>
@@ -3444,8 +3578,8 @@
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="43"/>
-      <c r="C45" s="38"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="40"/>
       <c r="D45" s="7" t="s">
         <v>23</v>
       </c>
@@ -3461,8 +3595,8 @@
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="43"/>
-      <c r="C46" s="38"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="40"/>
       <c r="D46" s="7" t="s">
         <v>23</v>
       </c>
@@ -3478,8 +3612,8 @@
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="43"/>
-      <c r="C47" s="38"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="40"/>
       <c r="D47" s="7" t="s">
         <v>23</v>
       </c>
@@ -3495,8 +3629,8 @@
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="43"/>
-      <c r="C48" s="38"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="40"/>
       <c r="D48" s="7" t="s">
         <v>23</v>
       </c>
@@ -3512,8 +3646,8 @@
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="43"/>
-      <c r="C49" s="38"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="40"/>
       <c r="D49" s="7" t="s">
         <v>23</v>
       </c>
@@ -3529,8 +3663,8 @@
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="43"/>
-      <c r="C50" s="38"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="40"/>
       <c r="D50" s="7" t="s">
         <v>23</v>
       </c>
@@ -3546,8 +3680,8 @@
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="43"/>
-      <c r="C51" s="38"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="40"/>
       <c r="D51" s="8" t="s">
         <v>24</v>
       </c>
@@ -3563,8 +3697,8 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="43"/>
-      <c r="C52" s="38"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="40"/>
       <c r="D52" s="31" t="s">
         <v>24</v>
       </c>
@@ -3580,8 +3714,8 @@
       <c r="J52" s="32"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="43"/>
-      <c r="C53" s="38"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="40"/>
       <c r="D53" s="31" t="s">
         <v>24</v>
       </c>
@@ -3597,8 +3731,8 @@
       <c r="J53" s="32"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="43"/>
-      <c r="C54" s="38"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="40"/>
       <c r="D54" s="31" t="s">
         <v>24</v>
       </c>
@@ -3614,8 +3748,8 @@
       <c r="J54" s="32"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="43"/>
-      <c r="C55" s="38"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="40"/>
       <c r="D55" s="31" t="s">
         <v>24</v>
       </c>
@@ -3631,8 +3765,8 @@
       <c r="J55" s="32"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="43"/>
-      <c r="C56" s="38"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="40"/>
       <c r="D56" s="31" t="s">
         <v>24</v>
       </c>
@@ -3648,8 +3782,8 @@
       <c r="J56" s="32"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="43"/>
-      <c r="C57" s="38"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="40"/>
       <c r="D57" s="31" t="s">
         <v>24</v>
       </c>
@@ -3665,8 +3799,8 @@
       <c r="J57" s="32"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="43"/>
-      <c r="C58" s="38"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="40"/>
       <c r="D58" s="31" t="s">
         <v>24</v>
       </c>
@@ -3682,8 +3816,8 @@
       <c r="J58" s="32"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="43"/>
-      <c r="C59" s="38"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="40"/>
       <c r="D59" s="31" t="s">
         <v>24</v>
       </c>
@@ -3699,9 +3833,9 @@
       <c r="J59" s="32"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="43"/>
-      <c r="C60" s="38"/>
-      <c r="D60" s="49" t="s">
+      <c r="B60" s="45"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="18" t="s">
@@ -3710,150 +3844,150 @@
       <c r="F60" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G60" s="51"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="51"/>
-      <c r="J60" s="51"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
     </row>
     <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="43"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="49" t="s">
+      <c r="B61" s="45"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E61" s="50" t="s">
+      <c r="E61" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F61" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G61" s="51"/>
-      <c r="H61" s="52"/>
-      <c r="I61" s="51"/>
-      <c r="J61" s="51"/>
+      <c r="F61" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="43"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="49" t="s">
+      <c r="B62" s="45"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="50" t="s">
+      <c r="E62" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F62" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62" s="51"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
+      <c r="F62" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
     </row>
     <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="43"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="49" t="s">
+      <c r="B63" s="45"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E63" s="50" t="s">
+      <c r="E63" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F63" s="49" t="s">
+      <c r="F63" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G63" s="51"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="43"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="49" t="s">
+      <c r="B64" s="45"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E64" s="50" t="s">
+      <c r="E64" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F64" s="49" t="s">
+      <c r="F64" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G64" s="51"/>
-      <c r="H64" s="52"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="51"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="43"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="49" t="s">
+      <c r="B65" s="45"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="50" t="s">
+      <c r="E65" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F65" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G65" s="51"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="51"/>
+      <c r="F65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
     </row>
     <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="43"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="49" t="s">
+      <c r="B66" s="45"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E66" s="50" t="s">
+      <c r="E66" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F66" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G66" s="51"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="51"/>
+      <c r="F66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
     </row>
     <row r="67" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="43"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="49" t="s">
+      <c r="B67" s="45"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E67" s="50" t="s">
+      <c r="E67" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F67" s="49" t="s">
+      <c r="F67" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G67" s="51"/>
-      <c r="H67" s="52"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="51"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
     </row>
     <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="43"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="49" t="s">
+      <c r="B68" s="45"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="50" t="s">
+      <c r="E68" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F68" s="49" t="s">
+      <c r="F68" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G68" s="51"/>
-      <c r="H68" s="52"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="51"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="43"/>
-      <c r="C69" s="38"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="40"/>
       <c r="D69" s="8" t="s">
         <v>29</v>
       </c>
@@ -3869,12 +4003,12 @@
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="43"/>
-      <c r="C70" s="38"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="40"/>
       <c r="D70" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E70" s="53" t="s">
+      <c r="E70" s="38" t="s">
         <v>38</v>
       </c>
       <c r="F70" s="31" t="s">
@@ -3886,12 +4020,12 @@
       <c r="J70" s="32"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="43"/>
-      <c r="C71" s="38"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="40"/>
       <c r="D71" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E71" s="53" t="s">
+      <c r="E71" s="38" t="s">
         <v>39</v>
       </c>
       <c r="F71" s="31" t="s">
@@ -3903,12 +4037,12 @@
       <c r="J71" s="32"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="43"/>
-      <c r="C72" s="38"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="40"/>
       <c r="D72" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E72" s="53" t="s">
+      <c r="E72" s="38" t="s">
         <v>40</v>
       </c>
       <c r="F72" s="31" t="s">
@@ -3920,12 +4054,12 @@
       <c r="J72" s="32"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="43"/>
-      <c r="C73" s="38"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="40"/>
       <c r="D73" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E73" s="53" t="s">
+      <c r="E73" s="38" t="s">
         <v>41</v>
       </c>
       <c r="F73" s="31" t="s">
@@ -3937,12 +4071,12 @@
       <c r="J73" s="32"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="43"/>
-      <c r="C74" s="38"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="40"/>
       <c r="D74" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="53" t="s">
+      <c r="E74" s="38" t="s">
         <v>42</v>
       </c>
       <c r="F74" s="31" t="s">
@@ -3954,12 +4088,12 @@
       <c r="J74" s="32"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="43"/>
-      <c r="C75" s="38"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="40"/>
       <c r="D75" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E75" s="53" t="s">
+      <c r="E75" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F75" s="31" t="s">
@@ -3971,12 +4105,12 @@
       <c r="J75" s="32"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="43"/>
-      <c r="C76" s="38"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="40"/>
       <c r="D76" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E76" s="53" t="s">
+      <c r="E76" s="38" t="s">
         <v>44</v>
       </c>
       <c r="F76" s="31" t="s">
@@ -3988,9 +4122,9 @@
       <c r="J76" s="32"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="43"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="49" t="s">
+      <c r="B77" s="45"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E77" s="18" t="s">
@@ -3999,116 +4133,116 @@
       <c r="F77" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G77" s="51"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="51"/>
-      <c r="J77" s="51"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="43"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="49" t="s">
+      <c r="B78" s="45"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E78" s="54" t="s">
+      <c r="E78" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="F78" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G78" s="51"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="51"/>
-      <c r="J78" s="51"/>
+      <c r="F78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="43"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="49" t="s">
+      <c r="B79" s="45"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E79" s="54" t="s">
+      <c r="E79" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="F79" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G79" s="51"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="51"/>
+      <c r="F79" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="5"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="43"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="49" t="s">
+      <c r="B80" s="45"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E80" s="54" t="s">
+      <c r="E80" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="F80" s="49" t="s">
+      <c r="F80" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G80" s="51"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="51"/>
-      <c r="J80" s="51"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="43"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="49" t="s">
+      <c r="B81" s="45"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E81" s="54" t="s">
+      <c r="E81" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="F81" s="49" t="s">
+      <c r="F81" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G81" s="51"/>
-      <c r="H81" s="52"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="43"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="49" t="s">
+      <c r="B82" s="45"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E82" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F82" s="49" t="s">
+      <c r="F82" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G82" s="51"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="51"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="43"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="49" t="s">
+      <c r="B83" s="45"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E83" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F83" s="49" t="s">
+      <c r="F83" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G83" s="51"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="51"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="43"/>
-      <c r="C84" s="38"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="40"/>
       <c r="D84" s="8" t="s">
         <v>45</v>
       </c>
@@ -4124,8 +4258,8 @@
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="43"/>
-      <c r="C85" s="38"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="40"/>
       <c r="D85" s="8" t="s">
         <v>45</v>
       </c>
@@ -4141,8 +4275,8 @@
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="43"/>
-      <c r="C86" s="38"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="40"/>
       <c r="D86" s="8" t="s">
         <v>45</v>
       </c>
@@ -4158,8 +4292,8 @@
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="43"/>
-      <c r="C87" s="38"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="40"/>
       <c r="D87" s="31" t="s">
         <v>54</v>
       </c>
@@ -4175,8 +4309,8 @@
       <c r="J87" s="32"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="43"/>
-      <c r="C88" s="38"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="40"/>
       <c r="D88" s="31" t="s">
         <v>54</v>
       </c>
@@ -4192,8 +4326,8 @@
       <c r="J88" s="32"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="43"/>
-      <c r="C89" s="38"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="40"/>
       <c r="D89" s="31" t="s">
         <v>54</v>
       </c>
@@ -4209,8 +4343,8 @@
       <c r="J89" s="32"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="43"/>
-      <c r="C90" s="38"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="40"/>
       <c r="D90" s="31" t="s">
         <v>54</v>
       </c>
@@ -4226,127 +4360,127 @@
       <c r="J90" s="32"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="43"/>
-      <c r="C91" s="38"/>
-      <c r="D91" s="49" t="s">
+      <c r="B91" s="45"/>
+      <c r="C91" s="40"/>
+      <c r="D91" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E91" s="50" t="s">
+      <c r="E91" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F91" s="49" t="s">
+      <c r="F91" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="G91" s="51"/>
-      <c r="H91" s="52"/>
-      <c r="I91" s="51"/>
-      <c r="J91" s="51"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="43"/>
-      <c r="C92" s="38"/>
-      <c r="D92" s="49" t="s">
+      <c r="B92" s="45"/>
+      <c r="C92" s="40"/>
+      <c r="D92" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E92" s="50" t="s">
+      <c r="E92" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F92" s="49" t="s">
+      <c r="F92" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G92" s="51"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="51"/>
-      <c r="J92" s="51"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="43"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="49" t="s">
+      <c r="B93" s="45"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E93" s="50" t="s">
+      <c r="E93" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F93" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G93" s="51"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="51"/>
+      <c r="F93" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="43"/>
-      <c r="C94" s="38"/>
-      <c r="D94" s="49" t="s">
+      <c r="B94" s="45"/>
+      <c r="C94" s="40"/>
+      <c r="D94" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E94" s="50" t="s">
+      <c r="E94" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F94" s="49" t="s">
+      <c r="F94" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G94" s="51"/>
-      <c r="H94" s="52"/>
-      <c r="I94" s="51"/>
-      <c r="J94" s="51"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="43"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="49" t="s">
+      <c r="B95" s="45"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E95" s="50" t="s">
+      <c r="E95" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F95" s="49" t="s">
+      <c r="F95" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G95" s="51"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="51"/>
-      <c r="J95" s="51"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="43"/>
-      <c r="C96" s="38"/>
-      <c r="D96" s="49" t="s">
+      <c r="B96" s="45"/>
+      <c r="C96" s="40"/>
+      <c r="D96" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E96" s="50" t="s">
+      <c r="E96" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F96" s="49" t="s">
+      <c r="F96" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G96" s="51"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="51"/>
-      <c r="J96" s="51"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="43"/>
-      <c r="C97" s="38"/>
-      <c r="D97" s="49" t="s">
+      <c r="B97" s="45"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E97" s="50" t="s">
+      <c r="E97" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F97" s="49" t="s">
+      <c r="F97" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G97" s="51"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="51"/>
-      <c r="J97" s="51"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="43"/>
-      <c r="C98" s="38"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="40"/>
       <c r="D98" s="31" t="s">
         <v>53</v>
       </c>
@@ -4362,8 +4496,8 @@
       <c r="J98" s="32"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="43"/>
-      <c r="C99" s="38"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="40"/>
       <c r="D99" s="31" t="s">
         <v>53</v>
       </c>
@@ -4379,8 +4513,8 @@
       <c r="J99" s="32"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="43"/>
-      <c r="C100" s="38"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="40"/>
       <c r="D100" s="31" t="s">
         <v>53</v>
       </c>
@@ -4396,339 +4530,339 @@
       <c r="J100" s="32"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="43"/>
-      <c r="C101" s="38"/>
-      <c r="D101" s="49" t="s">
+      <c r="B101" s="45"/>
+      <c r="C101" s="40"/>
+      <c r="D101" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E101" s="50" t="s">
+      <c r="E101" s="18" t="s">
         <v>135</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G101" s="51"/>
-      <c r="H101" s="52"/>
-      <c r="I101" s="51"/>
-      <c r="J101" s="51"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="43"/>
-      <c r="C102" s="38"/>
-      <c r="D102" s="49" t="s">
+      <c r="B102" s="45"/>
+      <c r="C102" s="40"/>
+      <c r="D102" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E102" s="50" t="s">
+      <c r="E102" s="18" t="s">
         <v>138</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G102" s="51"/>
-      <c r="H102" s="52"/>
-      <c r="I102" s="51"/>
-      <c r="J102" s="51"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="43"/>
-      <c r="C103" s="38"/>
-      <c r="D103" s="8" t="s">
+      <c r="B103" s="45"/>
+      <c r="C103" s="40"/>
+      <c r="D103" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E103" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="F103" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="54"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="53"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="43"/>
-      <c r="C104" s="38"/>
-      <c r="D104" s="8" t="s">
+      <c r="B104" s="45"/>
+      <c r="C104" s="40"/>
+      <c r="D104" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E104" s="18" t="s">
+      <c r="E104" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F104" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
+      <c r="F104" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G104" s="32"/>
+      <c r="H104" s="36"/>
+      <c r="I104" s="32"/>
+      <c r="J104" s="32"/>
     </row>
     <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="43"/>
-      <c r="C105" s="38"/>
-      <c r="D105" s="8" t="s">
+      <c r="B105" s="45"/>
+      <c r="C105" s="40"/>
+      <c r="D105" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E105" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F105" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
+      <c r="F105" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105" s="32"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="32"/>
+      <c r="J105" s="32"/>
     </row>
     <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="43"/>
-      <c r="C106" s="38"/>
-      <c r="D106" s="8" t="s">
+      <c r="B106" s="45"/>
+      <c r="C106" s="40"/>
+      <c r="D106" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E106" s="18" t="s">
+      <c r="E106" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="F106" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
+      <c r="F106" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G106" s="32"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="32"/>
+      <c r="J106" s="32"/>
     </row>
     <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="43"/>
-      <c r="C107" s="38"/>
-      <c r="D107" s="8" t="s">
+      <c r="B107" s="45"/>
+      <c r="C107" s="40"/>
+      <c r="D107" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="18" t="s">
+      <c r="E107" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="F107" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G107" s="5"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="5"/>
-      <c r="J107" s="5"/>
+      <c r="F107" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G107" s="32"/>
+      <c r="H107" s="36"/>
+      <c r="I107" s="32"/>
+      <c r="J107" s="32"/>
     </row>
     <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="43"/>
-      <c r="C108" s="38"/>
-      <c r="D108" s="8" t="s">
+      <c r="B108" s="45"/>
+      <c r="C108" s="40"/>
+      <c r="D108" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E108" s="18" t="s">
+      <c r="E108" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="F108" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G108" s="5"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="5"/>
+      <c r="F108" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G108" s="32"/>
+      <c r="H108" s="36"/>
+      <c r="I108" s="32"/>
+      <c r="J108" s="32"/>
     </row>
     <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="43"/>
-      <c r="C109" s="38"/>
-      <c r="D109" s="8" t="s">
+      <c r="B109" s="45"/>
+      <c r="C109" s="40"/>
+      <c r="D109" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E109" s="18" t="s">
+      <c r="E109" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G109" s="5"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
+      <c r="G109" s="32"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="32"/>
+      <c r="J109" s="32"/>
     </row>
     <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="43"/>
-      <c r="C110" s="38"/>
-      <c r="D110" s="8" t="s">
+      <c r="B110" s="45"/>
+      <c r="C110" s="40"/>
+      <c r="D110" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E110" s="18" t="s">
+      <c r="E110" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G110" s="5"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="32"/>
+      <c r="J110" s="32"/>
     </row>
     <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="43"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="8" t="s">
+      <c r="B111" s="45"/>
+      <c r="C111" s="40"/>
+      <c r="D111" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E111" s="18" t="s">
+      <c r="E111" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="G111" s="5"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
+      <c r="G111" s="32"/>
+      <c r="H111" s="36"/>
+      <c r="I111" s="32"/>
+      <c r="J111" s="32"/>
     </row>
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="43"/>
-      <c r="C112" s="38"/>
-      <c r="D112" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E112" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G112" s="5"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
+      <c r="B112" s="45"/>
+      <c r="C112" s="40"/>
+      <c r="D112" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E112" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F112" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G112" s="53"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="53"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="43"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E113" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G113" s="5"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="5"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="40"/>
+      <c r="D113" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="F113" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" s="53"/>
+      <c r="H113" s="54"/>
+      <c r="I113" s="53"/>
+      <c r="J113" s="53"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="43"/>
-      <c r="C114" s="38"/>
-      <c r="D114" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E114" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G114" s="5"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="40"/>
+      <c r="D114" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E114" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="F114" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G114" s="53"/>
+      <c r="H114" s="54"/>
+      <c r="I114" s="53"/>
+      <c r="J114" s="53"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="43"/>
-      <c r="C115" s="38"/>
-      <c r="D115" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E115" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G115" s="5"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="5"/>
+      <c r="B115" s="45"/>
+      <c r="C115" s="40"/>
+      <c r="D115" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E115" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="F115" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G115" s="53"/>
+      <c r="H115" s="54"/>
+      <c r="I115" s="53"/>
+      <c r="J115" s="53"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="43"/>
-      <c r="C116" s="38"/>
-      <c r="D116" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E116" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G116" s="5"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="40"/>
+      <c r="D116" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E116" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="F116" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G116" s="53"/>
+      <c r="H116" s="54"/>
+      <c r="I116" s="53"/>
+      <c r="J116" s="53"/>
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="43"/>
-      <c r="C117" s="38"/>
-      <c r="D117" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G117" s="5"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="40"/>
+      <c r="D117" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E117" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="F117" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G117" s="53"/>
+      <c r="H117" s="54"/>
+      <c r="I117" s="53"/>
+      <c r="J117" s="53"/>
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="43"/>
-      <c r="C118" s="38"/>
-      <c r="D118" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E118" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G118" s="5"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="5"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="40"/>
+      <c r="D118" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E118" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="F118" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="53"/>
+      <c r="H118" s="54"/>
+      <c r="I118" s="53"/>
+      <c r="J118" s="53"/>
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="43"/>
-      <c r="C119" s="38"/>
-      <c r="D119" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E119" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G119" s="5"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
+      <c r="B119" s="45"/>
+      <c r="C119" s="40"/>
+      <c r="D119" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E119" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F119" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="53"/>
+      <c r="H119" s="54"/>
+      <c r="I119" s="53"/>
+      <c r="J119" s="53"/>
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="43"/>
-      <c r="C120" s="38"/>
+      <c r="B120" s="45"/>
+      <c r="C120" s="40"/>
       <c r="D120" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="6"/>
@@ -4736,16 +4870,16 @@
       <c r="J120" s="5"/>
     </row>
     <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="43"/>
-      <c r="C121" s="38"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="40"/>
       <c r="D121" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E121" s="18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="6"/>
@@ -4753,16 +4887,16 @@
       <c r="J121" s="5"/>
     </row>
     <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="43"/>
-      <c r="C122" s="38"/>
+      <c r="B122" s="45"/>
+      <c r="C122" s="40"/>
       <c r="D122" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="6"/>
@@ -4770,13 +4904,13 @@
       <c r="J122" s="5"/>
     </row>
     <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="43"/>
-      <c r="C123" s="38"/>
+      <c r="B123" s="45"/>
+      <c r="C123" s="40"/>
       <c r="D123" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>9</v>
@@ -4787,13 +4921,13 @@
       <c r="J123" s="5"/>
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="43"/>
-      <c r="C124" s="38"/>
+      <c r="B124" s="45"/>
+      <c r="C124" s="40"/>
       <c r="D124" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>9</v>
@@ -4804,96 +4938,144 @@
       <c r="J124" s="5"/>
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="43"/>
-      <c r="C125" s="39"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="8"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="40"/>
+      <c r="D125" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E125" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G125" s="5"/>
       <c r="H125" s="6"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
     </row>
     <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="43"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="8"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="40"/>
+      <c r="D126" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G126" s="5"/>
       <c r="H126" s="6"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
     </row>
     <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="43"/>
-      <c r="C127" s="47"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="8"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="40"/>
+      <c r="D127" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E127" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G127" s="5"/>
       <c r="H127" s="6"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
     </row>
     <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="43"/>
-      <c r="C128" s="47"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="8"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="40"/>
+      <c r="D128" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E128" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G128" s="5"/>
       <c r="H128" s="6"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
     </row>
     <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B129" s="43"/>
-      <c r="C129" s="47"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="8"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="40"/>
+      <c r="D129" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E129" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G129" s="5"/>
       <c r="H129" s="6"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
     </row>
     <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="43"/>
-      <c r="C130" s="47"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="8"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="40"/>
+      <c r="D130" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G130" s="5"/>
       <c r="H130" s="6"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
     </row>
     <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B131" s="43"/>
-      <c r="C131" s="47"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="8"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="40"/>
+      <c r="D131" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E131" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G131" s="5"/>
       <c r="H131" s="6"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
     </row>
     <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B132" s="43"/>
-      <c r="C132" s="47"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="8"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="40"/>
+      <c r="D132" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E132" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G132" s="5"/>
       <c r="H132" s="6"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
     </row>
     <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="43"/>
-      <c r="C133" s="47"/>
+      <c r="B133" s="45"/>
+      <c r="C133" s="41"/>
       <c r="D133" s="8"/>
       <c r="E133" s="15"/>
       <c r="F133" s="8"/>
@@ -4903,8 +5085,8 @@
       <c r="J133" s="5"/>
     </row>
     <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="43"/>
-      <c r="C134" s="47"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="48"/>
       <c r="D134" s="8"/>
       <c r="E134" s="15"/>
       <c r="F134" s="8"/>
@@ -4914,8 +5096,8 @@
       <c r="J134" s="5"/>
     </row>
     <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="43"/>
-      <c r="C135" s="47"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="49"/>
       <c r="D135" s="8"/>
       <c r="E135" s="15"/>
       <c r="F135" s="8"/>
@@ -4925,8 +5107,8 @@
       <c r="J135" s="5"/>
     </row>
     <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="43"/>
-      <c r="C136" s="47"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="49"/>
       <c r="D136" s="8"/>
       <c r="E136" s="15"/>
       <c r="F136" s="8"/>
@@ -4936,8 +5118,8 @@
       <c r="J136" s="5"/>
     </row>
     <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="43"/>
-      <c r="C137" s="47"/>
+      <c r="B137" s="45"/>
+      <c r="C137" s="49"/>
       <c r="D137" s="8"/>
       <c r="E137" s="15"/>
       <c r="F137" s="8"/>
@@ -4947,8 +5129,8 @@
       <c r="J137" s="5"/>
     </row>
     <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="43"/>
-      <c r="C138" s="47"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="49"/>
       <c r="D138" s="8"/>
       <c r="E138" s="15"/>
       <c r="F138" s="8"/>
@@ -4958,8 +5140,8 @@
       <c r="J138" s="5"/>
     </row>
     <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B139" s="43"/>
-      <c r="C139" s="47"/>
+      <c r="B139" s="45"/>
+      <c r="C139" s="49"/>
       <c r="D139" s="8"/>
       <c r="E139" s="15"/>
       <c r="F139" s="8"/>
@@ -4969,8 +5151,8 @@
       <c r="J139" s="5"/>
     </row>
     <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="43"/>
-      <c r="C140" s="47"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="49"/>
       <c r="D140" s="8"/>
       <c r="E140" s="15"/>
       <c r="F140" s="8"/>
@@ -4980,8 +5162,8 @@
       <c r="J140" s="5"/>
     </row>
     <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="44"/>
-      <c r="C141" s="48"/>
+      <c r="B141" s="45"/>
+      <c r="C141" s="49"/>
       <c r="D141" s="8"/>
       <c r="E141" s="15"/>
       <c r="F141" s="8"/>
@@ -4990,17 +5172,105 @@
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
     </row>
-    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="145" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B142" s="45"/>
+      <c r="C142" s="49"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+    </row>
+    <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" s="45"/>
+      <c r="C143" s="49"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="15"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+    </row>
+    <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B144" s="45"/>
+      <c r="C144" s="49"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="15"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="6"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+    </row>
+    <row r="145" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" s="45"/>
+      <c r="C145" s="49"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="15"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="6"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+    </row>
+    <row r="146" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B146" s="45"/>
+      <c r="C146" s="49"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="15"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+    </row>
+    <row r="147" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" s="45"/>
+      <c r="C147" s="49"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="15"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+    </row>
+    <row r="148" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B148" s="45"/>
+      <c r="C148" s="49"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="15"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+    </row>
+    <row r="149" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B149" s="46"/>
+      <c r="C149" s="50"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="15"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+    </row>
+    <row r="150" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="151" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="152" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="153" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C3:C125"/>
+    <mergeCell ref="C3:C133"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B141"/>
+    <mergeCell ref="B3:B149"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C126:C141"/>
+    <mergeCell ref="C134:C149"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5009,6 +5279,1660 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A2056B-5BAF-4B6A-8EF5-CB29DB5A4449}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:J105"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+    </row>
+    <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="45"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="45"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="45"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="45"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="45"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="45"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="45"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="45"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="45"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="45"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="45"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="45"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="45"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="45"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="45"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="45"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="45"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="45"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="45"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="45"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="45"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="45"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="45"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="45"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="45"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="45"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="45"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="45"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="45"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="45"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="45"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="45"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="45"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="45"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="45"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="45"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="45"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="45"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="45"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="45"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="45"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="45"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="45"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="45"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="45"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="45"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="45"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="45"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="45"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="45"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="45"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="45"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="45"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="45"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="45"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="45"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E62" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="53"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+    </row>
+    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="45"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G63" s="53"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="53"/>
+    </row>
+    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="45"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="53"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+    </row>
+    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="45"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="53"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+    </row>
+    <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="45"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="F66" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="53"/>
+      <c r="H66" s="54"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+    </row>
+    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="45"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="F67" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="53"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="53"/>
+    </row>
+    <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="45"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="F68" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="53"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+    </row>
+    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="45"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="53"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+    </row>
+    <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="45"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="53"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="53"/>
+    </row>
+    <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="45"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="45"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="45"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="45"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="45"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="45"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" s="5"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="45"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="45"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="45"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="5"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="45"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="5"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="45"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G81" s="5"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="45"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="45"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="45"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" s="5"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="45"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="45"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="45"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="45"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="45"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="45"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="45"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="45"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="45"/>
+      <c r="C93" s="49"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="45"/>
+      <c r="C94" s="49"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="45"/>
+      <c r="C95" s="49"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="45"/>
+      <c r="C96" s="49"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="45"/>
+      <c r="C97" s="49"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="45"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="45"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="45"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="46"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:B101"/>
+    <mergeCell ref="C3:C85"/>
+    <mergeCell ref="C86:C101"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6583BB8-6EF5-4B62-9DAB-61388D01CFF1}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -5022,15 +6946,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
@@ -5088,7 +7012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1192EA3-D33B-4233-8044-AC21C5911A0F}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -5102,15 +7026,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8F45DA-4C66-4471-A97E-4980AB5AC634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F5E0E5-67E9-4C33-B014-27C8D95A6F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="149">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -5283,7 +5283,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J105"/>
+  <dimension ref="B1:J102"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -6515,9 +6515,15 @@
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="45"/>
       <c r="C72" s="40"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="8"/>
+      <c r="D72" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
       <c r="I72" s="5"/>
@@ -6530,10 +6536,10 @@
         <v>70</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="6"/>
@@ -6547,7 +6553,7 @@
         <v>70</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>9</v>
@@ -6564,7 +6570,7 @@
         <v>70</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>9</v>
@@ -6581,7 +6587,7 @@
         <v>70</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>9</v>
@@ -6598,7 +6604,7 @@
         <v>70</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>9</v>
@@ -6615,10 +6621,10 @@
         <v>70</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="6"/>
@@ -6632,10 +6638,10 @@
         <v>70</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
@@ -6646,13 +6652,13 @@
       <c r="B80" s="45"/>
       <c r="C80" s="40"/>
       <c r="D80" s="8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="6"/>
@@ -6663,13 +6669,13 @@
       <c r="B81" s="45"/>
       <c r="C81" s="40"/>
       <c r="D81" s="8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="6"/>
@@ -6678,16 +6684,10 @@
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="45"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="C82" s="41"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="8"/>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
@@ -6695,16 +6695,10 @@
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="45"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="C83" s="48"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="8"/>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
@@ -6712,16 +6706,10 @@
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="45"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="C84" s="49"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="8"/>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
@@ -6729,7 +6717,7 @@
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="45"/>
-      <c r="C85" s="41"/>
+      <c r="C85" s="49"/>
       <c r="D85" s="8"/>
       <c r="E85" s="15"/>
       <c r="F85" s="8"/>
@@ -6740,7 +6728,7 @@
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="45"/>
-      <c r="C86" s="48"/>
+      <c r="C86" s="49"/>
       <c r="D86" s="8"/>
       <c r="E86" s="15"/>
       <c r="F86" s="8"/>
@@ -6871,8 +6859,8 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="45"/>
-      <c r="C98" s="49"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="50"/>
       <c r="D98" s="8"/>
       <c r="E98" s="15"/>
       <c r="F98" s="8"/>
@@ -6881,50 +6869,17 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
     </row>
-    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="45"/>
-      <c r="C99" s="49"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-    </row>
-    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="45"/>
-      <c r="C100" s="49"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-    </row>
-    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="46"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B101"/>
-    <mergeCell ref="C3:C85"/>
-    <mergeCell ref="C86:C101"/>
+    <mergeCell ref="B3:B98"/>
+    <mergeCell ref="C3:C82"/>
+    <mergeCell ref="C83:C98"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F5E0E5-67E9-4C33-B014-27C8D95A6F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAB5AF1-4A92-4FB7-BCC0-EA195B9CD099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="154">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1955,6 +1955,68 @@
     <t>メールアドレス欄に「ハイフンのみ＠　～」「＠ のみ＠　～」を入力</t>
     <rPh sb="30" eb="32">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「確認する」ボタン</t>
+    <rPh sb="1" eb="3">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未入力項目にて「このフィールドを入力してください。」というエラー</t>
+    <rPh sb="0" eb="3">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて入力した状態で「確認する」押下</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未入力項目ある状態で「確認する」押下</t>
+    <rPh sb="0" eb="3">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アカウント登録確認画面」へ遷移</t>
+    <rPh sb="6" eb="12">
+      <t>トウロクカクニンガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5283,7 +5345,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J102"/>
+  <dimension ref="B1:J110"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -6684,10 +6746,16 @@
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="45"/>
-      <c r="C82" s="41"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="8"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F82" s="39" t="s">
+        <v>150</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
@@ -6695,10 +6763,16 @@
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="45"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="8"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F83" s="39" t="s">
+        <v>153</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
@@ -6706,9 +6780,9 @@
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="45"/>
-      <c r="C84" s="49"/>
+      <c r="C84" s="41"/>
       <c r="D84" s="8"/>
-      <c r="E84" s="15"/>
+      <c r="E84" s="18"/>
       <c r="F84" s="8"/>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
@@ -6717,7 +6791,7 @@
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="45"/>
-      <c r="C85" s="49"/>
+      <c r="C85" s="48"/>
       <c r="D85" s="8"/>
       <c r="E85" s="15"/>
       <c r="F85" s="8"/>
@@ -6859,8 +6933,8 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="46"/>
-      <c r="C98" s="50"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="49"/>
       <c r="D98" s="8"/>
       <c r="E98" s="15"/>
       <c r="F98" s="8"/>
@@ -6869,17 +6943,105 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
     </row>
-    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="45"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="45"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="45"/>
+      <c r="C101" s="49"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="45"/>
+      <c r="C102" s="49"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+    </row>
+    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="45"/>
+      <c r="C103" s="49"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+    </row>
+    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="45"/>
+      <c r="C104" s="49"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+    </row>
+    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="45"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+    </row>
+    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="46"/>
+      <c r="C106" s="50"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+    </row>
+    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B98"/>
-    <mergeCell ref="C3:C82"/>
-    <mergeCell ref="C83:C98"/>
+    <mergeCell ref="B3:B106"/>
+    <mergeCell ref="C3:C84"/>
+    <mergeCell ref="C85:C106"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAB5AF1-4A92-4FB7-BCC0-EA195B9CD099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA5F8D1-76AD-4289-9F71-1AECFA126736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="167">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2016,6 +2016,169 @@
       <t>トウロクカクニンガメン</t>
     </rPh>
     <rPh sb="14" eb="16">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力した文字が●で表示される</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄に正しい形式（エラーのない形）で入力</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「前に戻る」ボタン</t>
+    <rPh sb="1" eb="2">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「登録する」ボタン</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「前に戻る」押下</t>
+    <rPh sb="1" eb="2">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「登録する」押下</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示された入力内容を維持したまま「アカウント登録画面」に戻ることができる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アカウント登録完了画面」へ遷移</t>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「TOPページへ戻る」ボタン</t>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「TOPページへ戻る」押下</t>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アカウント登録画面」へ遷移</t>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2112,7 +2275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2268,13 +2431,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2439,6 +2626,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5345,7 +5547,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J110"/>
+  <dimension ref="B1:J98"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -5398,7 +5600,7 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="59" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -6204,13 +6406,13 @@
       <c r="B50" s="45"/>
       <c r="C50" s="40"/>
       <c r="D50" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>135</v>
+        <v>29</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>156</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="6"/>
@@ -6223,11 +6425,11 @@
       <c r="D51" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E51" s="18" t="s">
-        <v>46</v>
+      <c r="E51" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="6"/>
@@ -6241,7 +6443,7 @@
         <v>45</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>9</v>
@@ -6255,13 +6457,13 @@
       <c r="B53" s="45"/>
       <c r="C53" s="40"/>
       <c r="D53" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="6"/>
@@ -6275,10 +6477,10 @@
         <v>54</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="6"/>
@@ -6292,10 +6494,10 @@
         <v>54</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="6"/>
@@ -6309,10 +6511,10 @@
         <v>54</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="6"/>
@@ -6326,7 +6528,7 @@
         <v>54</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>28</v>
@@ -6343,7 +6545,7 @@
         <v>54</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -6360,7 +6562,7 @@
         <v>54</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>28</v>
@@ -6374,13 +6576,13 @@
       <c r="B60" s="45"/>
       <c r="C60" s="40"/>
       <c r="D60" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="6"/>
@@ -6394,10 +6596,10 @@
         <v>53</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="6"/>
@@ -6407,19 +6609,19 @@
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="45"/>
       <c r="C62" s="40"/>
-      <c r="D62" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="E62" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="53"/>
-      <c r="H62" s="54"/>
-      <c r="I62" s="53"/>
-      <c r="J62" s="53"/>
+      <c r="D62" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="45"/>
@@ -6428,10 +6630,10 @@
         <v>59</v>
       </c>
       <c r="E63" s="52" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G63" s="53"/>
       <c r="H63" s="54"/>
@@ -6445,10 +6647,10 @@
         <v>59</v>
       </c>
       <c r="E64" s="52" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G64" s="53"/>
       <c r="H64" s="54"/>
@@ -6462,10 +6664,10 @@
         <v>59</v>
       </c>
       <c r="E65" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G65" s="53"/>
       <c r="H65" s="54"/>
@@ -6479,7 +6681,7 @@
         <v>59</v>
       </c>
       <c r="E66" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F66" s="51" t="s">
         <v>9</v>
@@ -6496,7 +6698,7 @@
         <v>59</v>
       </c>
       <c r="E67" s="52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F67" s="51" t="s">
         <v>9</v>
@@ -6513,7 +6715,7 @@
         <v>59</v>
       </c>
       <c r="E68" s="52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F68" s="51" t="s">
         <v>9</v>
@@ -6530,10 +6732,10 @@
         <v>59</v>
       </c>
       <c r="E69" s="52" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F69" s="51" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G69" s="53"/>
       <c r="H69" s="54"/>
@@ -6547,10 +6749,10 @@
         <v>59</v>
       </c>
       <c r="E70" s="52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F70" s="51" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G70" s="53"/>
       <c r="H70" s="54"/>
@@ -6560,19 +6762,19 @@
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="45"/>
       <c r="C71" s="40"/>
-      <c r="D71" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
+      <c r="D71" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="53"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="45"/>
@@ -6581,10 +6783,10 @@
         <v>70</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
@@ -6598,10 +6800,10 @@
         <v>70</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="6"/>
@@ -6615,10 +6817,10 @@
         <v>70</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="6"/>
@@ -6632,7 +6834,7 @@
         <v>70</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>9</v>
@@ -6649,7 +6851,7 @@
         <v>70</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>9</v>
@@ -6666,7 +6868,7 @@
         <v>70</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>9</v>
@@ -6683,10 +6885,10 @@
         <v>70</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="6"/>
@@ -6700,10 +6902,10 @@
         <v>70</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
@@ -6714,10 +6916,10 @@
       <c r="B80" s="45"/>
       <c r="C80" s="40"/>
       <c r="D80" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>9</v>
@@ -6734,7 +6936,7 @@
         <v>82</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>9</v>
@@ -6748,13 +6950,13 @@
       <c r="B82" s="45"/>
       <c r="C82" s="40"/>
       <c r="D82" s="8" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F82" s="39" t="s">
-        <v>150</v>
+        <v>84</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
@@ -6768,10 +6970,10 @@
         <v>149</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
@@ -6780,10 +6982,16 @@
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="45"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="8"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>153</v>
+      </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
@@ -6791,9 +6999,9 @@
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="45"/>
-      <c r="C85" s="48"/>
+      <c r="C85" s="41"/>
       <c r="D85" s="8"/>
-      <c r="E85" s="15"/>
+      <c r="E85" s="18"/>
       <c r="F85" s="8"/>
       <c r="G85" s="5"/>
       <c r="H85" s="6"/>
@@ -6802,10 +7010,18 @@
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="45"/>
-      <c r="C86" s="49"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="8"/>
+      <c r="C86" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F86" s="39" t="s">
+        <v>161</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="6"/>
       <c r="I86" s="5"/>
@@ -6813,10 +7029,16 @@
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="45"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="8"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
       <c r="I87" s="5"/>
@@ -6824,10 +7046,10 @@
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="45"/>
-      <c r="C88" s="49"/>
+      <c r="C88" s="57"/>
       <c r="D88" s="8"/>
       <c r="E88" s="15"/>
-      <c r="F88" s="8"/>
+      <c r="F88" s="39"/>
       <c r="G88" s="5"/>
       <c r="H88" s="6"/>
       <c r="I88" s="5"/>
@@ -6835,10 +7057,10 @@
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="45"/>
-      <c r="C89" s="49"/>
+      <c r="C89" s="57"/>
       <c r="D89" s="8"/>
       <c r="E89" s="15"/>
-      <c r="F89" s="8"/>
+      <c r="F89" s="39"/>
       <c r="G89" s="5"/>
       <c r="H89" s="6"/>
       <c r="I89" s="5"/>
@@ -6846,7 +7068,7 @@
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="45"/>
-      <c r="C90" s="49"/>
+      <c r="C90" s="57"/>
       <c r="D90" s="8"/>
       <c r="E90" s="15"/>
       <c r="F90" s="8"/>
@@ -6857,7 +7079,7 @@
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="45"/>
-      <c r="C91" s="49"/>
+      <c r="C91" s="57"/>
       <c r="D91" s="8"/>
       <c r="E91" s="15"/>
       <c r="F91" s="8"/>
@@ -6868,7 +7090,7 @@
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="45"/>
-      <c r="C92" s="49"/>
+      <c r="C92" s="58"/>
       <c r="D92" s="8"/>
       <c r="E92" s="15"/>
       <c r="F92" s="8"/>
@@ -6879,10 +7101,18 @@
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="45"/>
-      <c r="C93" s="49"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="8"/>
+      <c r="C93" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="G93" s="5"/>
       <c r="H93" s="6"/>
       <c r="I93" s="5"/>
@@ -6890,7 +7120,7 @@
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="45"/>
-      <c r="C94" s="49"/>
+      <c r="C94" s="45"/>
       <c r="D94" s="8"/>
       <c r="E94" s="15"/>
       <c r="F94" s="8"/>
@@ -6901,7 +7131,7 @@
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="45"/>
-      <c r="C95" s="49"/>
+      <c r="C95" s="45"/>
       <c r="D95" s="8"/>
       <c r="E95" s="15"/>
       <c r="F95" s="8"/>
@@ -6912,7 +7142,7 @@
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="45"/>
-      <c r="C96" s="49"/>
+      <c r="C96" s="45"/>
       <c r="D96" s="8"/>
       <c r="E96" s="15"/>
       <c r="F96" s="8"/>
@@ -6923,7 +7153,7 @@
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="45"/>
-      <c r="C97" s="49"/>
+      <c r="C97" s="45"/>
       <c r="D97" s="8"/>
       <c r="E97" s="15"/>
       <c r="F97" s="8"/>
@@ -6933,8 +7163,8 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="45"/>
-      <c r="C98" s="49"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="46"/>
       <c r="D98" s="8"/>
       <c r="E98" s="15"/>
       <c r="F98" s="8"/>
@@ -6943,105 +7173,14 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
     </row>
-    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="45"/>
-      <c r="C99" s="49"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-    </row>
-    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="45"/>
-      <c r="C100" s="49"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-    </row>
-    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="45"/>
-      <c r="C101" s="49"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-    </row>
-    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="45"/>
-      <c r="C102" s="49"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-    </row>
-    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="45"/>
-      <c r="C103" s="49"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-    </row>
-    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="45"/>
-      <c r="C104" s="49"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-    </row>
-    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="45"/>
-      <c r="C105" s="49"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="15"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-    </row>
-    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="46"/>
-      <c r="C106" s="50"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="15"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-    </row>
-    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B106"/>
-    <mergeCell ref="C3:C84"/>
-    <mergeCell ref="C85:C106"/>
+    <mergeCell ref="C3:C85"/>
+    <mergeCell ref="C86:C92"/>
+    <mergeCell ref="B3:B98"/>
+    <mergeCell ref="C93:C98"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA5F8D1-76AD-4289-9F71-1AECFA126736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E958FD1A-F8C9-4272-8644-9F80216FEBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="168">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2182,6 +2182,9 @@
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PC/chrome</t>
   </si>
 </sst>
 </file>
@@ -5615,10 +5618,18 @@
       <c r="F3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="12">
+        <v>45973</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="45"/>
@@ -5632,10 +5643,18 @@
       <c r="F4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="13"/>
+      <c r="G4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="45"/>
@@ -5649,10 +5668,18 @@
       <c r="F5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="13"/>
+      <c r="G5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="45"/>
@@ -5666,10 +5693,18 @@
       <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="13"/>
+      <c r="G6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="45"/>
@@ -5683,10 +5718,18 @@
       <c r="F7" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="13"/>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="45"/>
@@ -5700,10 +5743,18 @@
       <c r="F8" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="13"/>
+      <c r="G8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="45"/>
@@ -5717,10 +5768,18 @@
       <c r="F9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="13"/>
+      <c r="G9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="45"/>
@@ -5734,10 +5793,18 @@
       <c r="F10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="13"/>
+      <c r="G10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="45"/>
@@ -5751,10 +5818,18 @@
       <c r="F11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="13"/>
+      <c r="G11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="45"/>
@@ -5768,10 +5843,18 @@
       <c r="F12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="13"/>
+      <c r="G12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="45"/>
@@ -5785,10 +5868,18 @@
       <c r="F13" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="13"/>
+      <c r="G13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="45"/>
@@ -5802,10 +5893,18 @@
       <c r="F14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="13"/>
+      <c r="G14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="45"/>
@@ -5819,10 +5918,18 @@
       <c r="F15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="13"/>
+      <c r="G15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="45"/>
@@ -5836,10 +5943,18 @@
       <c r="F16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="13"/>
+      <c r="G16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="45"/>
@@ -5853,10 +5968,18 @@
       <c r="F17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="13"/>
+      <c r="G17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="14">
+        <v>45973</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="45"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E958FD1A-F8C9-4272-8644-9F80216FEBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618C8FE7-2AD9-4F54-9C2C-A4192A3CD8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="単体テスト（訂正前あり）" sheetId="1" r:id="rId1"/>
     <sheet name="単体テスト (新)" sheetId="4" r:id="rId2"/>
     <sheet name="結合テスト" sheetId="2" r:id="rId3"/>
-    <sheet name="総合テスト" sheetId="3" r:id="rId4"/>
+    <sheet name="総合テスト" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="173">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -1952,13 +1952,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレス欄に「ハイフンのみ＠　～」「＠ のみ＠　～」を入力</t>
-    <rPh sb="30" eb="32">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「確認する」ボタン</t>
     <rPh sb="1" eb="3">
       <t>カクニン</t>
@@ -2185,13 +2178,85 @@
   </si>
   <si>
     <t>PC/chrome</t>
+  </si>
+  <si>
+    <t>自身</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「ハイフン（半角）のみ＠　～」「＠ （半角）のみ＠　～」を入力</t>
+    <rPh sb="15" eb="17">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「ハイフン（全角）のみ＠　～」「＠ （全角）のみ＠　～」を入力</t>
+    <rPh sb="15" eb="17">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ゼンカク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄に「半角英数字＋（どこかに-（半角ハイフン）・＠（半角）あり）＠　～」を入力</t>
+    <rPh sb="10" eb="12">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総合テスト</t>
+    <rPh sb="0" eb="2">
+      <t>ソウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスとしての正しい形式でなくても入力できてしまう</t>
+    <rPh sb="11" eb="12">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2251,6 +2316,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -2464,7 +2537,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2618,21 +2691,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2644,6 +2702,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4833,19 +4903,19 @@
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="45"/>
       <c r="C103" s="40"/>
-      <c r="D103" s="51" t="s">
+      <c r="D103" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E103" s="52" t="s">
+      <c r="E103" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F103" s="51" t="s">
+      <c r="F103" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G103" s="53"/>
-      <c r="H103" s="54"/>
-      <c r="I103" s="53"/>
-      <c r="J103" s="53"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="45"/>
@@ -4986,138 +5056,138 @@
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="45"/>
       <c r="C112" s="40"/>
-      <c r="D112" s="51" t="s">
+      <c r="D112" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E112" s="52" t="s">
+      <c r="E112" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F112" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G112" s="53"/>
-      <c r="H112" s="54"/>
-      <c r="I112" s="53"/>
-      <c r="J112" s="53"/>
+      <c r="F112" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G112" s="5"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="45"/>
       <c r="C113" s="40"/>
-      <c r="D113" s="51" t="s">
+      <c r="D113" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E113" s="52" t="s">
+      <c r="E113" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F113" s="51" t="s">
+      <c r="F113" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G113" s="53"/>
-      <c r="H113" s="54"/>
-      <c r="I113" s="53"/>
-      <c r="J113" s="53"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="45"/>
       <c r="C114" s="40"/>
-      <c r="D114" s="51" t="s">
+      <c r="D114" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E114" s="52" t="s">
+      <c r="E114" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F114" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G114" s="53"/>
-      <c r="H114" s="54"/>
-      <c r="I114" s="53"/>
-      <c r="J114" s="53"/>
+      <c r="F114" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G114" s="5"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="45"/>
       <c r="C115" s="40"/>
-      <c r="D115" s="51" t="s">
+      <c r="D115" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E115" s="52" t="s">
+      <c r="E115" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F115" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G115" s="53"/>
-      <c r="H115" s="54"/>
-      <c r="I115" s="53"/>
-      <c r="J115" s="53"/>
+      <c r="F115" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G115" s="5"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="45"/>
       <c r="C116" s="40"/>
-      <c r="D116" s="51" t="s">
+      <c r="D116" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="52" t="s">
+      <c r="E116" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F116" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G116" s="53"/>
-      <c r="H116" s="54"/>
-      <c r="I116" s="53"/>
-      <c r="J116" s="53"/>
+      <c r="F116" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G116" s="5"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="45"/>
       <c r="C117" s="40"/>
-      <c r="D117" s="51" t="s">
+      <c r="D117" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E117" s="52" t="s">
+      <c r="E117" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F117" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G117" s="53"/>
-      <c r="H117" s="54"/>
-      <c r="I117" s="53"/>
-      <c r="J117" s="53"/>
+      <c r="F117" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G117" s="5"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="45"/>
       <c r="C118" s="40"/>
-      <c r="D118" s="51" t="s">
+      <c r="D118" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E118" s="52" t="s">
+      <c r="E118" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F118" s="51" t="s">
+      <c r="F118" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G118" s="53"/>
-      <c r="H118" s="54"/>
-      <c r="I118" s="53"/>
-      <c r="J118" s="53"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="45"/>
       <c r="C119" s="40"/>
-      <c r="D119" s="51" t="s">
+      <c r="D119" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E119" s="52" t="s">
+      <c r="E119" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F119" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="53"/>
-      <c r="H119" s="54"/>
-      <c r="I119" s="53"/>
-      <c r="J119" s="53"/>
+      <c r="F119" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="5"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="45"/>
@@ -5550,7 +5620,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J98"/>
+  <dimension ref="B1:J99"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -5603,7 +5673,7 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="54" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -5628,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5653,7 +5723,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5678,7 +5748,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5703,7 +5773,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5728,7 +5798,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5753,7 +5823,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -5778,7 +5848,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5803,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5828,7 +5898,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5853,7 +5923,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5878,7 +5948,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5903,7 +5973,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5928,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -5953,7 +6023,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5978,7 +6048,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5993,10 +6063,18 @@
       <c r="F18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="13"/>
+      <c r="G18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="45"/>
@@ -6010,10 +6088,18 @@
       <c r="F19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="G19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="45"/>
@@ -6027,10 +6113,18 @@
       <c r="F20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="45"/>
@@ -6044,10 +6138,18 @@
       <c r="F21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="45"/>
@@ -6061,10 +6163,18 @@
       <c r="F22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="45"/>
@@ -6078,10 +6188,18 @@
       <c r="F23" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="G23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="45"/>
@@ -6095,10 +6213,18 @@
       <c r="F24" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="G24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="45"/>
@@ -6112,10 +6238,18 @@
       <c r="F25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="G25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="45"/>
@@ -6129,10 +6263,18 @@
       <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="G26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="45"/>
@@ -6146,10 +6288,18 @@
       <c r="F27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="45"/>
@@ -6163,10 +6313,18 @@
       <c r="F28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="G28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="45"/>
@@ -6180,10 +6338,18 @@
       <c r="F29" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="G29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="45"/>
@@ -6197,10 +6363,18 @@
       <c r="F30" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="45"/>
@@ -6214,10 +6388,18 @@
       <c r="F31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="G31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="45"/>
@@ -6231,10 +6413,18 @@
       <c r="F32" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="G32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="45"/>
@@ -6248,10 +6438,18 @@
       <c r="F33" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="G33" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="45"/>
@@ -6265,10 +6463,18 @@
       <c r="F34" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="G34" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="45"/>
@@ -6282,10 +6488,18 @@
       <c r="F35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="G35" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="45"/>
@@ -6299,12 +6513,20 @@
       <c r="F36" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-    </row>
-    <row r="37" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H36" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="45"/>
       <c r="C37" s="40"/>
       <c r="D37" s="8" t="s">
@@ -6316,44 +6538,68 @@
       <c r="F37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-    </row>
-    <row r="38" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H37" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="45"/>
       <c r="C38" s="40"/>
       <c r="D38" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-    </row>
-    <row r="39" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G38" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H38" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="45"/>
       <c r="C39" s="40"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="45"/>
@@ -6362,15 +6608,23 @@
         <v>24</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="45"/>
@@ -6379,32 +6633,48 @@
         <v>24</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-    </row>
-    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H41" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="45"/>
       <c r="C42" s="40"/>
       <c r="D42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="45"/>
@@ -6412,11 +6682,11 @@
       <c r="D43" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="18" t="s">
-        <v>118</v>
+      <c r="E43" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="6"/>
@@ -6429,11 +6699,11 @@
       <c r="D44" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E44" s="39" t="s">
-        <v>125</v>
+      <c r="E44" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="6"/>
@@ -6447,7 +6717,7 @@
         <v>29</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>9</v>
@@ -6464,10 +6734,10 @@
         <v>29</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="6"/>
@@ -6481,7 +6751,7 @@
         <v>29</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>119</v>
@@ -6497,11 +6767,11 @@
       <c r="D48" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="18" t="s">
-        <v>121</v>
+      <c r="E48" s="39" t="s">
+        <v>120</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="6"/>
@@ -6515,7 +6785,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>28</v>
@@ -6532,10 +6802,10 @@
         <v>29</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="6"/>
@@ -6546,13 +6816,13 @@
       <c r="B51" s="45"/>
       <c r="C51" s="40"/>
       <c r="D51" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>135</v>
+        <v>29</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>155</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="6"/>
@@ -6565,11 +6835,11 @@
       <c r="D52" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="18" t="s">
-        <v>46</v>
+      <c r="E52" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="6"/>
@@ -6583,7 +6853,7 @@
         <v>45</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>9</v>
@@ -6597,13 +6867,13 @@
       <c r="B54" s="45"/>
       <c r="C54" s="40"/>
       <c r="D54" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="6"/>
@@ -6617,10 +6887,10 @@
         <v>54</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="6"/>
@@ -6634,10 +6904,10 @@
         <v>54</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="6"/>
@@ -6651,10 +6921,10 @@
         <v>54</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="6"/>
@@ -6668,7 +6938,7 @@
         <v>54</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6955,7 @@
         <v>54</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>28</v>
@@ -6702,7 +6972,7 @@
         <v>54</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -6716,13 +6986,13 @@
       <c r="B61" s="45"/>
       <c r="C61" s="40"/>
       <c r="D61" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="6"/>
@@ -6736,10 +7006,10 @@
         <v>53</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="6"/>
@@ -6749,167 +7019,167 @@
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="45"/>
       <c r="C63" s="40"/>
-      <c r="D63" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="E63" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="53"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="53"/>
-      <c r="J63" s="53"/>
+      <c r="D63" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="45"/>
       <c r="C64" s="40"/>
-      <c r="D64" s="51" t="s">
+      <c r="D64" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E64" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="F64" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" s="53"/>
-      <c r="H64" s="54"/>
-      <c r="I64" s="53"/>
-      <c r="J64" s="53"/>
+      <c r="E64" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="45"/>
       <c r="C65" s="40"/>
-      <c r="D65" s="51" t="s">
+      <c r="D65" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E65" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" s="53"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
+      <c r="E65" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="45"/>
       <c r="C66" s="40"/>
-      <c r="D66" s="51" t="s">
+      <c r="D66" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F66" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G66" s="53"/>
-      <c r="H66" s="54"/>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
+      <c r="E66" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="45"/>
       <c r="C67" s="40"/>
-      <c r="D67" s="51" t="s">
+      <c r="D67" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="F67" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G67" s="53"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="53"/>
-      <c r="J67" s="53"/>
+      <c r="E67" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="45"/>
       <c r="C68" s="40"/>
-      <c r="D68" s="51" t="s">
+      <c r="D68" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E68" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F68" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="53"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="53"/>
-      <c r="J68" s="53"/>
+      <c r="E68" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="45"/>
       <c r="C69" s="40"/>
-      <c r="D69" s="51" t="s">
+      <c r="D69" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E69" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="F69" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G69" s="53"/>
-      <c r="H69" s="54"/>
-      <c r="I69" s="53"/>
-      <c r="J69" s="53"/>
+      <c r="E69" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" s="5"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="45"/>
       <c r="C70" s="40"/>
-      <c r="D70" s="51" t="s">
+      <c r="D70" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E70" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="F70" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="G70" s="53"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="53"/>
-      <c r="J70" s="53"/>
+      <c r="E70" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="45"/>
       <c r="C71" s="40"/>
-      <c r="D71" s="51" t="s">
+      <c r="D71" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E71" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="F71" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" s="53"/>
-      <c r="H71" s="54"/>
-      <c r="I71" s="53"/>
-      <c r="J71" s="53"/>
+      <c r="E71" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="45"/>
       <c r="C72" s="40"/>
       <c r="D72" s="8" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
@@ -6923,10 +7193,10 @@
         <v>70</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="6"/>
@@ -6940,10 +7210,10 @@
         <v>70</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="6"/>
@@ -6957,10 +7227,10 @@
         <v>70</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="6"/>
@@ -6974,7 +7244,7 @@
         <v>70</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>9</v>
@@ -6991,7 +7261,7 @@
         <v>70</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>9</v>
@@ -7008,7 +7278,7 @@
         <v>70</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>9</v>
@@ -7025,10 +7295,10 @@
         <v>70</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
@@ -7042,10 +7312,10 @@
         <v>70</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="6"/>
@@ -7056,10 +7326,10 @@
       <c r="B81" s="45"/>
       <c r="C81" s="40"/>
       <c r="D81" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>9</v>
@@ -7076,7 +7346,7 @@
         <v>82</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>9</v>
@@ -7090,13 +7360,13 @@
       <c r="B83" s="45"/>
       <c r="C83" s="40"/>
       <c r="D83" s="8" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F83" s="39" t="s">
-        <v>150</v>
+        <v>84</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
@@ -7107,13 +7377,13 @@
       <c r="B84" s="45"/>
       <c r="C84" s="40"/>
       <c r="D84" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E84" s="18" t="s">
         <v>151</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
@@ -7122,10 +7392,16 @@
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="45"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="8"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F85" s="39" t="s">
+        <v>152</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="6"/>
       <c r="I85" s="5"/>
@@ -7133,18 +7409,10 @@
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="45"/>
-      <c r="C86" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F86" s="39" t="s">
-        <v>161</v>
-      </c>
+      <c r="C86" s="41"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="8"/>
       <c r="G86" s="5"/>
       <c r="H86" s="6"/>
       <c r="I86" s="5"/>
@@ -7152,15 +7420,17 @@
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="45"/>
-      <c r="C87" s="57"/>
+      <c r="C87" s="51" t="s">
+        <v>153</v>
+      </c>
       <c r="D87" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E87" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="F87" s="39" t="s">
         <v>160</v>
-      </c>
-      <c r="F87" s="39" t="s">
-        <v>162</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
@@ -7169,10 +7439,16 @@
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="45"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="39"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F88" s="39" t="s">
+        <v>161</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="6"/>
       <c r="I88" s="5"/>
@@ -7180,7 +7456,7 @@
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="45"/>
-      <c r="C89" s="57"/>
+      <c r="C89" s="52"/>
       <c r="D89" s="8"/>
       <c r="E89" s="15"/>
       <c r="F89" s="39"/>
@@ -7191,10 +7467,10 @@
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="45"/>
-      <c r="C90" s="57"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="8"/>
       <c r="E90" s="15"/>
-      <c r="F90" s="8"/>
+      <c r="F90" s="39"/>
       <c r="G90" s="5"/>
       <c r="H90" s="6"/>
       <c r="I90" s="5"/>
@@ -7202,7 +7478,7 @@
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="45"/>
-      <c r="C91" s="57"/>
+      <c r="C91" s="52"/>
       <c r="D91" s="8"/>
       <c r="E91" s="15"/>
       <c r="F91" s="8"/>
@@ -7213,7 +7489,7 @@
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="45"/>
-      <c r="C92" s="58"/>
+      <c r="C92" s="52"/>
       <c r="D92" s="8"/>
       <c r="E92" s="15"/>
       <c r="F92" s="8"/>
@@ -7224,18 +7500,10 @@
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="45"/>
-      <c r="C93" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E93" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>166</v>
-      </c>
+      <c r="C93" s="53"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="8"/>
       <c r="G93" s="5"/>
       <c r="H93" s="6"/>
       <c r="I93" s="5"/>
@@ -7243,10 +7511,18 @@
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="8"/>
+      <c r="C94" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="G94" s="5"/>
       <c r="H94" s="6"/>
       <c r="I94" s="5"/>
@@ -7286,8 +7562,8 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="46"/>
-      <c r="C98" s="46"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="45"/>
       <c r="D98" s="8"/>
       <c r="E98" s="15"/>
       <c r="F98" s="8"/>
@@ -7296,14 +7572,25 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
     </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="46"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C3:C85"/>
-    <mergeCell ref="C86:C92"/>
-    <mergeCell ref="B3:B98"/>
-    <mergeCell ref="C93:C98"/>
+    <mergeCell ref="C3:C86"/>
+    <mergeCell ref="C87:C93"/>
+    <mergeCell ref="B3:B99"/>
+    <mergeCell ref="C94:C99"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7392,81 +7679,1746 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1192EA3-D33B-4233-8044-AC21C5911A0F}">
-  <dimension ref="A1:G26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31F6E48-2FF7-40BE-9951-33BCA157813A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:J99"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="25.58203125" customWidth="1"/>
-    <col min="2" max="3" width="30.58203125" customWidth="1"/>
-    <col min="4" max="4" width="15.58203125" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.58203125" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-    </row>
-    <row r="2" spans="1:7" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="2:10" s="57" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+    </row>
+    <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="4" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="5" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="6" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="7" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="8" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="9" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="10" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="11" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="12" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="45"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="45"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="45"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="45"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="45"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="45"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="45"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="45"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="45"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="45"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="45"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="45"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="45"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="45"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="45"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="45"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="45"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="45"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="45"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="45"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="45"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="45"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="45"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="45"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="45"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="45"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="45"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="45"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="45"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="45"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="45"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="45"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="45"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="14"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="45"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="45"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="45"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="14"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="45"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="45"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="45"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="45"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="45"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="45"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="45"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="45"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="45"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="45"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="45"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="45"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="45"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="45"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="45"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="45"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="45"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="45"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="45"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="45"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="45"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="45"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="45"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+    </row>
+    <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="45"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+    </row>
+    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="45"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+    </row>
+    <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="45"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+    </row>
+    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="45"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" s="5"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+    </row>
+    <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="45"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+    </row>
+    <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="45"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="45"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" s="5"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="45"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="45"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="45"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="45"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" s="5"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="45"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="45"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="45"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="5"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="45"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="5"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="45"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="5"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="45"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="45"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="45"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="G84" s="5"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="45"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F85" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G85" s="5"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="45"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="45"/>
+      <c r="C87" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="G87" s="5"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="45"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F88" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G88" s="5"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="45"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="45"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="39"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="45"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="45"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="45"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="45"/>
+      <c r="C94" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="45"/>
+      <c r="C95" s="45"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="45"/>
+      <c r="C97" s="45"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="45"/>
+      <c r="C98" s="45"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="46"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="6">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:B99"/>
+    <mergeCell ref="C3:C86"/>
+    <mergeCell ref="C87:C93"/>
+    <mergeCell ref="C94:C99"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618C8FE7-2AD9-4F54-9C2C-A4192A3CD8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B773EEA-B5E6-48F1-8A5E-B8FF8206A329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="10170" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
   <sheets>
     <sheet name="単体テスト（訂正前あり）" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="175">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2249,6 +2249,17 @@
     <rPh sb="21" eb="23">
       <t>ニュウリョク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし　（「これらのオプションから選択してください」）</t>
+    <rPh sb="16" eb="18">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6688,9 +6699,15 @@
       <c r="F43" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="5"/>
+      <c r="G43" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J43" s="5"/>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6705,9 +6722,15 @@
       <c r="F44" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="5"/>
+      <c r="G44" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6722,9 +6745,15 @@
       <c r="F45" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5"/>
+      <c r="G45" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6739,9 +6768,15 @@
       <c r="F46" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5"/>
+      <c r="G46" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H46" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6756,9 +6791,15 @@
       <c r="F47" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="5"/>
+      <c r="G47" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6773,9 +6814,15 @@
       <c r="F48" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="5"/>
+      <c r="G48" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H48" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6790,9 +6837,15 @@
       <c r="F49" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="5"/>
+      <c r="G49" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6807,9 +6860,15 @@
       <c r="F50" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="5"/>
+      <c r="G50" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H50" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6824,9 +6883,15 @@
       <c r="F51" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="5"/>
+      <c r="G51" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6841,9 +6906,15 @@
       <c r="F52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="5"/>
+      <c r="G52" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H52" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I52" s="58" t="s">
+        <v>173</v>
+      </c>
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6858,9 +6929,15 @@
       <c r="F53" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="5"/>
+      <c r="G53" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6875,9 +6952,15 @@
       <c r="F54" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="5"/>
+      <c r="G54" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H54" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="J54" s="5"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B773EEA-B5E6-48F1-8A5E-B8FF8206A329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFAB989-379C-4821-851F-F840D92EB62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="10170" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="176">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2260,6 +2260,19 @@
   </si>
   <si>
     <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし（「リスト内の項目を選択してください。」）</t>
+    <rPh sb="7" eb="8">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センタク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6708,7 +6721,9 @@
       <c r="I43" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="5"/>
+      <c r="J43" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="45"/>
@@ -6731,7 +6746,9 @@
       <c r="I44" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="5"/>
+      <c r="J44" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="45"/>
@@ -6754,7 +6771,9 @@
       <c r="I45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J45" s="5"/>
+      <c r="J45" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="45"/>
@@ -6777,7 +6796,9 @@
       <c r="I46" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J46" s="5"/>
+      <c r="J46" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="45"/>
@@ -6800,7 +6821,9 @@
       <c r="I47" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="5"/>
+      <c r="J47" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="45"/>
@@ -6823,7 +6846,9 @@
       <c r="I48" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J48" s="5"/>
+      <c r="J48" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="45"/>
@@ -6846,7 +6871,9 @@
       <c r="I49" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J49" s="5"/>
+      <c r="J49" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="45"/>
@@ -6869,7 +6896,9 @@
       <c r="I50" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J50" s="5"/>
+      <c r="J50" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="45"/>
@@ -6892,7 +6921,9 @@
       <c r="I51" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J51" s="5"/>
+      <c r="J51" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="45"/>
@@ -6915,7 +6946,9 @@
       <c r="I52" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="J52" s="5"/>
+      <c r="J52" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="45"/>
@@ -6938,7 +6971,9 @@
       <c r="I53" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J53" s="5"/>
+      <c r="J53" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="45"/>
@@ -6961,7 +6996,9 @@
       <c r="I54" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J54" s="5"/>
+      <c r="J54" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="45"/>
@@ -6975,10 +7012,18 @@
       <c r="F55" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="G55" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="45"/>
@@ -6992,10 +7037,18 @@
       <c r="F56" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="G56" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="45"/>
@@ -7009,10 +7062,18 @@
       <c r="F57" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="G57" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H57" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="45"/>
@@ -7026,10 +7087,18 @@
       <c r="F58" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="G58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="45"/>
@@ -7043,10 +7112,18 @@
       <c r="F59" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="G59" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="45"/>
@@ -7060,10 +7137,18 @@
       <c r="F60" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="G60" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H60" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="45"/>
@@ -7077,10 +7162,18 @@
       <c r="F61" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="G61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H61" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="45"/>
@@ -7094,10 +7187,18 @@
       <c r="F62" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="G62" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H62" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I62" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="45"/>
@@ -7111,10 +7212,18 @@
       <c r="F63" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+      <c r="G63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H63" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I63" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="45"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFAB989-379C-4821-851F-F840D92EB62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA682A3F-A345-4CA8-AC25-51AE9918E277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="10170" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
   <sheets>
     <sheet name="単体テスト（訂正前あり）" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="189">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2272,6 +2272,185 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>＠２回以上でも可能となってしまう</t>
+    <rPh sb="2" eb="5">
+      <t>カイイジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村での数字の入力も可能となる
+（入力規制したほうがいいのでは）</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ニュウリョクキセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし　※総合テストに記載あり</t>
+    <rPh sb="4" eb="6">
+      <t>ソウゴウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村の入力においてハイフンは不要ではないか</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マンション名等で英字の入力が必要なケースもあるのではないか</t>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「ひらがなのみ」「カタカナのみ」「漢字のみ」「数字のみ」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「英字のみ」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「ひらがな＋カタカナor漢字or数字」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「ひらがな＋カタカナ＋漢字or数字」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「ひらがな＋カタカナ＋漢字＋数字」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「ハイフン（-、－）」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「記号（ハイフン（-、－）除く）」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地欄に「スペース（半角・全角）」を入力</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゼンカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2561,7 +2740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2738,6 +2917,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6594,7 +6785,7 @@
         <v>45974</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>166</v>
@@ -6644,7 +6835,7 @@
         <v>45974</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>166</v>
@@ -7237,10 +7428,18 @@
       <c r="F64" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G64" s="5"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+      <c r="G64" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H64" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I64" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="45"/>
@@ -7254,10 +7453,18 @@
       <c r="F65" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
+      <c r="G65" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H65" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="45"/>
@@ -7271,10 +7478,18 @@
       <c r="F66" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G66" s="5"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="G66" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H66" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="45"/>
@@ -7288,10 +7503,18 @@
       <c r="F67" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="5"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="G67" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="45"/>
@@ -7305,10 +7528,18 @@
       <c r="F68" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G68" s="5"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
+      <c r="G68" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H68" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="45"/>
@@ -7322,10 +7553,18 @@
       <c r="F69" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="G69" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H69" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="45"/>
@@ -7339,10 +7578,18 @@
       <c r="F70" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="G70" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H70" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="45"/>
@@ -7356,10 +7603,18 @@
       <c r="F71" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
+      <c r="G71" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="45"/>
@@ -7373,10 +7628,18 @@
       <c r="F72" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
+      <c r="G72" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H72" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="45"/>
@@ -7390,10 +7653,18 @@
       <c r="F73" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
+      <c r="G73" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H73" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="45"/>
@@ -7402,15 +7673,23 @@
         <v>70</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
+      <c r="G74" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H74" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="45"/>
@@ -7419,15 +7698,23 @@
         <v>70</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
+      <c r="G75" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H75" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="45"/>
@@ -7436,15 +7723,23 @@
         <v>70</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
+      <c r="G76" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H76" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="45"/>
@@ -7453,15 +7748,23 @@
         <v>70</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
+      <c r="G77" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H77" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="45"/>
@@ -7470,15 +7773,23 @@
         <v>70</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G78" s="5"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
+      <c r="G78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H78" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="45"/>
@@ -7487,15 +7798,23 @@
         <v>70</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
+      <c r="G79" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H79" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="45"/>
@@ -7504,15 +7823,23 @@
         <v>70</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
+      <c r="G80" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H80" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="45"/>
@@ -7521,15 +7848,23 @@
         <v>70</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
+      <c r="G81" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H81" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="45"/>
@@ -7543,10 +7878,18 @@
       <c r="F82" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
+      <c r="G82" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H82" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="45"/>
@@ -7560,10 +7903,18 @@
       <c r="F83" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G83" s="5"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
+      <c r="G83" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H83" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="45"/>
@@ -7577,10 +7928,18 @@
       <c r="F84" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="G84" s="5"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
+      <c r="G84" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H84" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="45"/>
@@ -7594,10 +7953,18 @@
       <c r="F85" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="G85" s="5"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="5"/>
+      <c r="G85" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H85" s="14">
+        <v>45974</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="45"/>
@@ -7625,9 +7992,9 @@
         <v>160</v>
       </c>
       <c r="G87" s="5"/>
-      <c r="H87" s="6"/>
+      <c r="H87" s="62"/>
       <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
+      <c r="J87" s="13"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="45"/>
@@ -7642,9 +8009,9 @@
         <v>161</v>
       </c>
       <c r="G88" s="5"/>
-      <c r="H88" s="6"/>
+      <c r="H88" s="62"/>
       <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
+      <c r="J88" s="13"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="45"/>
@@ -7716,7 +8083,7 @@
         <v>165</v>
       </c>
       <c r="G94" s="5"/>
-      <c r="H94" s="6"/>
+      <c r="H94" s="62"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
     </row>
@@ -7885,7 +8252,7 @@
     <col min="6" max="6" width="45.58203125" customWidth="1"/>
     <col min="7" max="7" width="15.58203125" customWidth="1"/>
     <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" style="60" customWidth="1"/>
     <col min="10" max="10" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7920,7 +8287,7 @@
       <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="59" t="s">
         <v>5</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -7943,11 +8310,9 @@
       <c r="F3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="G3" s="11"/>
       <c r="H3" s="12"/>
-      <c r="I3" s="11"/>
+      <c r="I3" s="17"/>
       <c r="J3" s="11"/>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7962,11 +8327,9 @@
       <c r="F4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="14"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="58"/>
       <c r="J4" s="13"/>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7981,11 +8344,9 @@
       <c r="F5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="14"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="58"/>
       <c r="J5" s="13"/>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8000,11 +8361,9 @@
       <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G6" s="5"/>
       <c r="H6" s="14"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="58"/>
       <c r="J6" s="13"/>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8019,11 +8378,9 @@
       <c r="F7" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="14"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="58"/>
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8038,11 +8395,9 @@
       <c r="F8" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="14"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="58"/>
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8057,11 +8412,9 @@
       <c r="F9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="58"/>
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8076,11 +8429,9 @@
       <c r="F10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="58"/>
       <c r="J10" s="13"/>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8095,11 +8446,9 @@
       <c r="F11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G11" s="5"/>
       <c r="H11" s="14"/>
-      <c r="I11" s="5"/>
+      <c r="I11" s="58"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8114,11 +8463,9 @@
       <c r="F12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="14"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="58"/>
       <c r="J12" s="13"/>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8133,11 +8480,9 @@
       <c r="F13" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G13" s="5"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="5"/>
+      <c r="I13" s="58"/>
       <c r="J13" s="13"/>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8152,11 +8497,9 @@
       <c r="F14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="14"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="58"/>
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8171,11 +8514,9 @@
       <c r="F15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G15" s="5"/>
       <c r="H15" s="14"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="58"/>
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8190,11 +8531,9 @@
       <c r="F16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G16" s="5"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="58"/>
       <c r="J16" s="13"/>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8209,11 +8548,9 @@
       <c r="F17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="14"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="58"/>
       <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8228,11 +8565,9 @@
       <c r="F18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G18" s="5"/>
       <c r="H18" s="14"/>
-      <c r="I18" s="5"/>
+      <c r="I18" s="58"/>
       <c r="J18" s="13"/>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8247,11 +8582,9 @@
       <c r="F19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="58"/>
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8266,11 +8599,9 @@
       <c r="F20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G20" s="5"/>
       <c r="H20" s="14"/>
-      <c r="I20" s="5"/>
+      <c r="I20" s="58"/>
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8285,11 +8616,9 @@
       <c r="F21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G21" s="5"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="58"/>
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8304,11 +8633,9 @@
       <c r="F22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G22" s="5"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="58"/>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8323,11 +8650,9 @@
       <c r="F23" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="5"/>
+      <c r="I23" s="58"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8342,11 +8667,9 @@
       <c r="F24" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G24" s="5"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="58"/>
       <c r="J24" s="5"/>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8361,11 +8684,9 @@
       <c r="F25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G25" s="5"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="58"/>
       <c r="J25" s="5"/>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8380,11 +8701,9 @@
       <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G26" s="5"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="58"/>
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8399,11 +8718,9 @@
       <c r="F27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G27" s="5"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="58"/>
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8418,11 +8735,9 @@
       <c r="F28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G28" s="5"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="58"/>
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8437,11 +8752,9 @@
       <c r="F29" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G29" s="5"/>
       <c r="H29" s="14"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="58"/>
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8456,11 +8769,9 @@
       <c r="F30" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G30" s="5"/>
       <c r="H30" s="14"/>
-      <c r="I30" s="5"/>
+      <c r="I30" s="58"/>
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8475,11 +8786,9 @@
       <c r="F31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G31" s="5"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="5"/>
+      <c r="I31" s="58"/>
       <c r="J31" s="5"/>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8494,11 +8803,9 @@
       <c r="F32" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="5"/>
+      <c r="I32" s="58"/>
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8513,11 +8820,9 @@
       <c r="F33" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G33" s="5"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="5"/>
+      <c r="I33" s="58"/>
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -8532,11 +8837,9 @@
       <c r="F34" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G34" s="5"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="5"/>
+      <c r="I34" s="58"/>
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8551,11 +8854,9 @@
       <c r="F35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G35" s="5"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="5"/>
+      <c r="I35" s="58"/>
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -8570,11 +8871,9 @@
       <c r="F36" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G36" s="5"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="5"/>
+      <c r="I36" s="58"/>
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8589,11 +8888,9 @@
       <c r="F37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G37" s="5"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="5"/>
+      <c r="I37" s="58"/>
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8608,9 +8905,7 @@
       <c r="F38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G38" s="5"/>
       <c r="H38" s="14"/>
       <c r="I38" s="58" t="s">
         <v>172</v>
@@ -8629,11 +8924,9 @@
       <c r="F39" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G39" s="5"/>
       <c r="H39" s="14"/>
-      <c r="I39" s="5"/>
+      <c r="I39" s="58"/>
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8648,11 +8941,11 @@
       <c r="F40" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G40" s="5"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="5"/>
+      <c r="I40" s="61" t="s">
+        <v>176</v>
+      </c>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8667,11 +8960,9 @@
       <c r="F41" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="5"/>
+      <c r="I41" s="58"/>
       <c r="J41" s="5"/>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -8686,11 +8977,9 @@
       <c r="F42" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="G42" s="5"/>
       <c r="H42" s="14"/>
-      <c r="I42" s="5"/>
+      <c r="I42" s="58"/>
       <c r="J42" s="5"/>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8707,7 +8996,7 @@
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="6"/>
-      <c r="I43" s="5"/>
+      <c r="I43" s="58"/>
       <c r="J43" s="5"/>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8724,7 +9013,7 @@
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="6"/>
-      <c r="I44" s="5"/>
+      <c r="I44" s="58"/>
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8741,7 +9030,7 @@
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="6"/>
-      <c r="I45" s="5"/>
+      <c r="I45" s="58"/>
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8758,7 +9047,7 @@
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="6"/>
-      <c r="I46" s="5"/>
+      <c r="I46" s="58"/>
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8775,7 +9064,7 @@
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="5"/>
+      <c r="I47" s="58"/>
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8792,7 +9081,7 @@
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="6"/>
-      <c r="I48" s="5"/>
+      <c r="I48" s="58"/>
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8809,7 +9098,7 @@
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="6"/>
-      <c r="I49" s="5"/>
+      <c r="I49" s="58"/>
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8826,7 +9115,7 @@
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="6"/>
-      <c r="I50" s="5"/>
+      <c r="I50" s="58"/>
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8843,7 +9132,7 @@
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="6"/>
-      <c r="I51" s="5"/>
+      <c r="I51" s="58"/>
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8860,7 +9149,7 @@
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="6"/>
-      <c r="I52" s="5"/>
+      <c r="I52" s="58"/>
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8877,7 +9166,7 @@
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="6"/>
-      <c r="I53" s="5"/>
+      <c r="I53" s="58"/>
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8894,7 +9183,7 @@
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="6"/>
-      <c r="I54" s="5"/>
+      <c r="I54" s="58"/>
       <c r="J54" s="5"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8911,7 +9200,7 @@
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="6"/>
-      <c r="I55" s="5"/>
+      <c r="I55" s="58"/>
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8928,7 +9217,7 @@
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="6"/>
-      <c r="I56" s="5"/>
+      <c r="I56" s="58"/>
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8945,7 +9234,7 @@
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="6"/>
-      <c r="I57" s="5"/>
+      <c r="I57" s="58"/>
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8962,7 +9251,7 @@
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="6"/>
-      <c r="I58" s="5"/>
+      <c r="I58" s="58"/>
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8979,7 +9268,7 @@
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="6"/>
-      <c r="I59" s="5"/>
+      <c r="I59" s="58"/>
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8996,7 +9285,7 @@
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="6"/>
-      <c r="I60" s="5"/>
+      <c r="I60" s="58"/>
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9013,7 +9302,7 @@
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="6"/>
-      <c r="I61" s="5"/>
+      <c r="I61" s="58"/>
       <c r="J61" s="5"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9030,7 +9319,7 @@
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="6"/>
-      <c r="I62" s="5"/>
+      <c r="I62" s="58"/>
       <c r="J62" s="5"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9047,7 +9336,7 @@
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="6"/>
-      <c r="I63" s="5"/>
+      <c r="I63" s="58"/>
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9064,7 +9353,7 @@
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="6"/>
-      <c r="I64" s="5"/>
+      <c r="I64" s="58"/>
       <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9081,7 +9370,9 @@
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="6"/>
-      <c r="I65" s="5"/>
+      <c r="I65" s="58" t="s">
+        <v>177</v>
+      </c>
       <c r="J65" s="5"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9098,7 +9389,7 @@
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="6"/>
-      <c r="I66" s="5"/>
+      <c r="I66" s="58"/>
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9115,7 +9406,9 @@
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="6"/>
-      <c r="I67" s="5"/>
+      <c r="I67" s="58" t="s">
+        <v>177</v>
+      </c>
       <c r="J67" s="5"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9132,7 +9425,9 @@
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="6"/>
-      <c r="I68" s="5"/>
+      <c r="I68" s="58" t="s">
+        <v>177</v>
+      </c>
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9149,7 +9444,9 @@
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
-      <c r="I69" s="5"/>
+      <c r="I69" s="58" t="s">
+        <v>177</v>
+      </c>
       <c r="J69" s="5"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9166,7 +9463,9 @@
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="6"/>
-      <c r="I70" s="5"/>
+      <c r="I70" s="58" t="s">
+        <v>179</v>
+      </c>
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9183,7 +9482,7 @@
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="6"/>
-      <c r="I71" s="5"/>
+      <c r="I71" s="58"/>
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9200,7 +9499,7 @@
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="6"/>
-      <c r="I72" s="5"/>
+      <c r="I72" s="58"/>
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9217,7 +9516,7 @@
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="6"/>
-      <c r="I73" s="5"/>
+      <c r="I73" s="58"/>
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9234,7 +9533,7 @@
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="6"/>
-      <c r="I74" s="5"/>
+      <c r="I74" s="58"/>
       <c r="J74" s="5"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9251,7 +9550,9 @@
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="6"/>
-      <c r="I75" s="5"/>
+      <c r="I75" s="58" t="s">
+        <v>180</v>
+      </c>
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9268,7 +9569,7 @@
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="6"/>
-      <c r="I76" s="5"/>
+      <c r="I76" s="58"/>
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9285,7 +9586,7 @@
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="6"/>
-      <c r="I77" s="5"/>
+      <c r="I77" s="58"/>
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9302,7 +9603,7 @@
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="6"/>
-      <c r="I78" s="5"/>
+      <c r="I78" s="58"/>
       <c r="J78" s="5"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9319,7 +9620,7 @@
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="6"/>
-      <c r="I79" s="5"/>
+      <c r="I79" s="58"/>
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9336,7 +9637,7 @@
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="6"/>
-      <c r="I80" s="5"/>
+      <c r="I80" s="58"/>
       <c r="J80" s="5"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9353,7 +9654,7 @@
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="6"/>
-      <c r="I81" s="5"/>
+      <c r="I81" s="58"/>
       <c r="J81" s="5"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9370,7 +9671,7 @@
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6"/>
-      <c r="I82" s="5"/>
+      <c r="I82" s="58"/>
       <c r="J82" s="5"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9387,7 +9688,7 @@
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="6"/>
-      <c r="I83" s="5"/>
+      <c r="I83" s="58"/>
       <c r="J83" s="5"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9404,7 +9705,7 @@
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="6"/>
-      <c r="I84" s="5"/>
+      <c r="I84" s="58"/>
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9421,7 +9722,7 @@
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="6"/>
-      <c r="I85" s="5"/>
+      <c r="I85" s="58"/>
       <c r="J85" s="5"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9432,7 +9733,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="5"/>
       <c r="H86" s="6"/>
-      <c r="I86" s="5"/>
+      <c r="I86" s="58"/>
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9451,7 +9752,7 @@
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
-      <c r="I87" s="5"/>
+      <c r="I87" s="58"/>
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9468,7 +9769,7 @@
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="6"/>
-      <c r="I88" s="5"/>
+      <c r="I88" s="58"/>
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9479,7 +9780,7 @@
       <c r="F89" s="39"/>
       <c r="G89" s="5"/>
       <c r="H89" s="6"/>
-      <c r="I89" s="5"/>
+      <c r="I89" s="58"/>
       <c r="J89" s="5"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9490,7 +9791,7 @@
       <c r="F90" s="39"/>
       <c r="G90" s="5"/>
       <c r="H90" s="6"/>
-      <c r="I90" s="5"/>
+      <c r="I90" s="58"/>
       <c r="J90" s="5"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9501,7 +9802,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="5"/>
       <c r="H91" s="6"/>
-      <c r="I91" s="5"/>
+      <c r="I91" s="58"/>
       <c r="J91" s="5"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9512,7 +9813,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="5"/>
       <c r="H92" s="6"/>
-      <c r="I92" s="5"/>
+      <c r="I92" s="58"/>
       <c r="J92" s="5"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9523,7 +9824,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="5"/>
       <c r="H93" s="6"/>
-      <c r="I93" s="5"/>
+      <c r="I93" s="58"/>
       <c r="J93" s="5"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9542,7 +9843,7 @@
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="6"/>
-      <c r="I94" s="5"/>
+      <c r="I94" s="58"/>
       <c r="J94" s="5"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9553,7 +9854,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="5"/>
       <c r="H95" s="6"/>
-      <c r="I95" s="5"/>
+      <c r="I95" s="58"/>
       <c r="J95" s="5"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9564,7 +9865,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="5"/>
       <c r="H96" s="6"/>
-      <c r="I96" s="5"/>
+      <c r="I96" s="58"/>
       <c r="J96" s="5"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9575,7 +9876,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="5"/>
       <c r="H97" s="6"/>
-      <c r="I97" s="5"/>
+      <c r="I97" s="58"/>
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9586,7 +9887,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="5"/>
       <c r="H98" s="6"/>
-      <c r="I98" s="5"/>
+      <c r="I98" s="58"/>
       <c r="J98" s="5"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9597,7 +9898,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="5"/>
       <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
+      <c r="I99" s="58"/>
       <c r="J99" s="5"/>
     </row>
   </sheetData>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA682A3F-A345-4CA8-AC25-51AE9918E277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525AD548-5B8E-4790-BF3A-A86C4790FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="191">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2181,6 +2181,9 @@
   </si>
   <si>
     <t>自身</t>
+  </si>
+  <si>
+    <t>自身</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2257,6 +2260,9 @@
       <t>センタク</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
   </si>
   <si>
     <t>なし</t>
@@ -6654,7 +6660,7 @@
         <v>115</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H33" s="14">
         <v>45974</v>
@@ -6679,7 +6685,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H34" s="14">
         <v>45974</v>
@@ -6704,7 +6710,7 @@
         <v>9</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H35" s="14">
         <v>45974</v>
@@ -6729,7 +6735,7 @@
         <v>28</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H36" s="14">
         <v>45974</v>
@@ -6754,7 +6760,7 @@
         <v>28</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H37" s="14">
         <v>45974</v>
@@ -6773,19 +6779,19 @@
         <v>24</v>
       </c>
       <c r="E38" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="H38" s="14">
         <v>45974</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>166</v>
@@ -6798,13 +6804,13 @@
         <v>24</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H39" s="14">
         <v>45974</v>
@@ -6823,19 +6829,19 @@
         <v>24</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H40" s="14">
         <v>45974</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>166</v>
@@ -6854,7 +6860,7 @@
         <v>28</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H41" s="14">
         <v>45974</v>
@@ -6879,7 +6885,7 @@
         <v>28</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H42" s="14">
         <v>45974</v>
@@ -6904,7 +6910,7 @@
         <v>128</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="14">
         <v>45974</v>
@@ -6929,7 +6935,7 @@
         <v>101</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H44" s="14">
         <v>45974</v>
@@ -6954,7 +6960,7 @@
         <v>9</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="14">
         <v>45974</v>
@@ -6979,7 +6985,7 @@
         <v>9</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="14">
         <v>45974</v>
@@ -7004,7 +7010,7 @@
         <v>119</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="14">
         <v>45974</v>
@@ -7029,7 +7035,7 @@
         <v>119</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="14">
         <v>45974</v>
@@ -7054,7 +7060,7 @@
         <v>28</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" s="14">
         <v>45974</v>
@@ -7079,7 +7085,7 @@
         <v>28</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="14">
         <v>45974</v>
@@ -7104,7 +7110,7 @@
         <v>154</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H51" s="14">
         <v>45974</v>
@@ -7129,13 +7135,13 @@
         <v>55</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H52" s="14">
         <v>45974</v>
       </c>
       <c r="I52" s="58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J52" s="13" t="s">
         <v>166</v>
@@ -7154,13 +7160,13 @@
         <v>9</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H53" s="14">
         <v>45974</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J53" s="13" t="s">
         <v>166</v>
@@ -7179,13 +7185,13 @@
         <v>9</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H54" s="14">
         <v>45974</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J54" s="13" t="s">
         <v>166</v>
@@ -7204,13 +7210,13 @@
         <v>128</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H55" s="14">
         <v>45974</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J55" s="13" t="s">
         <v>166</v>
@@ -7229,13 +7235,13 @@
         <v>28</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H56" s="14">
         <v>45974</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J56" s="13" t="s">
         <v>166</v>
@@ -7254,13 +7260,13 @@
         <v>9</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="14">
         <v>45974</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J57" s="13" t="s">
         <v>166</v>
@@ -7279,13 +7285,13 @@
         <v>28</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H58" s="14">
         <v>45974</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J58" s="13" t="s">
         <v>166</v>
@@ -7304,13 +7310,13 @@
         <v>28</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H59" s="14">
         <v>45974</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J59" s="13" t="s">
         <v>166</v>
@@ -7329,13 +7335,13 @@
         <v>28</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H60" s="14">
         <v>45974</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J60" s="13" t="s">
         <v>166</v>
@@ -7354,13 +7360,13 @@
         <v>28</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H61" s="14">
         <v>45974</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J61" s="13" t="s">
         <v>166</v>
@@ -7379,13 +7385,13 @@
         <v>137</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H62" s="14">
         <v>45974</v>
       </c>
       <c r="I62" s="58" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J62" s="13" t="s">
         <v>166</v>
@@ -7404,13 +7410,13 @@
         <v>9</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H63" s="14">
         <v>45974</v>
       </c>
       <c r="I63" s="58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J63" s="13" t="s">
         <v>166</v>
@@ -7429,13 +7435,13 @@
         <v>26</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H64" s="14">
         <v>45974</v>
       </c>
       <c r="I64" s="58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J64" s="13" t="s">
         <v>166</v>
@@ -7454,13 +7460,13 @@
         <v>9</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H65" s="14">
         <v>45974</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J65" s="13" t="s">
         <v>166</v>
@@ -7479,13 +7485,13 @@
         <v>28</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H66" s="14">
         <v>45974</v>
       </c>
       <c r="I66" s="58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J66" s="13" t="s">
         <v>166</v>
@@ -7504,13 +7510,13 @@
         <v>9</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H67" s="14">
         <v>45974</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J67" s="13" t="s">
         <v>166</v>
@@ -7529,13 +7535,13 @@
         <v>9</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H68" s="14">
         <v>45974</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J68" s="13" t="s">
         <v>166</v>
@@ -7554,13 +7560,13 @@
         <v>9</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H69" s="14">
         <v>45974</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J69" s="13" t="s">
         <v>166</v>
@@ -7579,13 +7585,13 @@
         <v>9</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H70" s="14">
         <v>45974</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J70" s="13" t="s">
         <v>166</v>
@@ -7604,13 +7610,13 @@
         <v>28</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H71" s="14">
         <v>45974</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J71" s="13" t="s">
         <v>166</v>
@@ -7629,13 +7635,13 @@
         <v>9</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H72" s="14">
         <v>45974</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J72" s="13" t="s">
         <v>166</v>
@@ -7654,13 +7660,13 @@
         <v>26</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H73" s="14">
         <v>45974</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J73" s="13" t="s">
         <v>166</v>
@@ -7673,19 +7679,19 @@
         <v>70</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H74" s="14">
         <v>45974</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J74" s="13" t="s">
         <v>166</v>
@@ -7698,19 +7704,19 @@
         <v>70</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H75" s="14">
         <v>45974</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J75" s="13" t="s">
         <v>166</v>
@@ -7723,19 +7729,19 @@
         <v>70</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H76" s="14">
         <v>45974</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J76" s="13" t="s">
         <v>166</v>
@@ -7748,19 +7754,19 @@
         <v>70</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H77" s="14">
         <v>45974</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J77" s="13" t="s">
         <v>166</v>
@@ -7773,19 +7779,19 @@
         <v>70</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H78" s="14">
         <v>45974</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J78" s="13" t="s">
         <v>166</v>
@@ -7798,19 +7804,19 @@
         <v>70</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H79" s="14">
         <v>45974</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J79" s="13" t="s">
         <v>166</v>
@@ -7823,19 +7829,19 @@
         <v>70</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H80" s="14">
         <v>45974</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J80" s="13" t="s">
         <v>166</v>
@@ -7848,19 +7854,19 @@
         <v>70</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H81" s="14">
         <v>45974</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J81" s="13" t="s">
         <v>166</v>
@@ -7879,13 +7885,13 @@
         <v>9</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H82" s="14">
         <v>45974</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J82" s="13" t="s">
         <v>166</v>
@@ -7904,13 +7910,13 @@
         <v>9</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H83" s="14">
         <v>45974</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J83" s="13" t="s">
         <v>166</v>
@@ -7929,13 +7935,13 @@
         <v>149</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H84" s="14">
         <v>45974</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J84" s="13" t="s">
         <v>166</v>
@@ -7954,13 +7960,13 @@
         <v>152</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H85" s="14">
         <v>45974</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J85" s="13" t="s">
         <v>166</v>
@@ -7991,10 +7997,18 @@
       <c r="F87" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="G87" s="5"/>
-      <c r="H87" s="62"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="13"/>
+      <c r="G87" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H87" s="62">
+        <v>45974</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="45"/>
@@ -8008,10 +8022,18 @@
       <c r="F88" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="G88" s="5"/>
-      <c r="H88" s="62"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="13"/>
+      <c r="G88" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H88" s="62">
+        <v>45974</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="45"/>
@@ -8082,10 +8104,18 @@
       <c r="F94" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="62"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
+      <c r="G94" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H94" s="62">
+        <v>45974</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J94" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="45"/>
@@ -8258,7 +8288,7 @@
   <sheetData>
     <row r="1" spans="2:10" s="57" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B1" s="56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="56"/>
@@ -8900,7 +8930,7 @@
         <v>24</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>9</v>
@@ -8908,7 +8938,7 @@
       <c r="G38" s="5"/>
       <c r="H38" s="14"/>
       <c r="I38" s="58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J38" s="5"/>
     </row>
@@ -8919,7 +8949,7 @@
         <v>24</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>28</v>
@@ -8936,7 +8966,7 @@
         <v>24</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>9</v>
@@ -8944,7 +8974,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="14"/>
       <c r="I40" s="61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J40" s="5"/>
     </row>
@@ -9371,7 +9401,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="6"/>
       <c r="I65" s="58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J65" s="5"/>
     </row>
@@ -9407,7 +9437,7 @@
       <c r="G67" s="5"/>
       <c r="H67" s="6"/>
       <c r="I67" s="58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J67" s="5"/>
     </row>
@@ -9426,7 +9456,7 @@
       <c r="G68" s="5"/>
       <c r="H68" s="6"/>
       <c r="I68" s="58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J68" s="5"/>
     </row>
@@ -9445,7 +9475,7 @@
       <c r="G69" s="5"/>
       <c r="H69" s="6"/>
       <c r="I69" s="58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J69" s="5"/>
     </row>
@@ -9464,7 +9494,7 @@
       <c r="G70" s="5"/>
       <c r="H70" s="6"/>
       <c r="I70" s="58" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J70" s="5"/>
     </row>
@@ -9551,7 +9581,7 @@
       <c r="G75" s="5"/>
       <c r="H75" s="6"/>
       <c r="I75" s="58" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J75" s="5"/>
     </row>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56A6C1-1497-4192-8EA6-891D979FB0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A8692E-8410-4423-8054-BC10FE5E5CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="215">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2482,9 +2482,6 @@
   </si>
   <si>
     <t>アカウント登録画面にてすべて入力後、「確認する」を押下</t>
-  </si>
-  <si>
-    <t>アカウント登録画面にてすべて入力後、「確認する」を押下</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
@@ -2503,167 +2500,351 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録画面にて「名前（性）欄」に入力した
+    <t>名前（名）欄</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（名）欄</t>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス欄</t>
+    <rPh sb="7" eb="8">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード欄</t>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都道府県 欄</t>
+    <rPh sb="0" eb="4">
+      <t>トドウフケン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便番号 欄</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別 欄</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市区町村 欄</t>
+    <rPh sb="0" eb="4">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「名前（性）欄」に入力した
 内容が表示されている</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
-    <rPh sb="12" eb="14">
+    <rPh sb="11" eb="13">
       <t>ナマエ</t>
     </rPh>
-    <rPh sb="15" eb="16">
+    <rPh sb="14" eb="15">
       <t>セイ</t>
     </rPh>
-    <rPh sb="17" eb="18">
+    <rPh sb="16" eb="17">
       <t>ラン</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="19" eb="21">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="25" eb="27">
+    <rPh sb="24" eb="26">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="27" eb="29">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名前（名）欄</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「名前（名）欄」に入力した
+    <t>アカウント登録画面で「名前（名）欄」に入力した
 内容が表示されている</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
-    <rPh sb="12" eb="14">
+    <rPh sb="11" eb="13">
       <t>ナマエ</t>
     </rPh>
-    <rPh sb="15" eb="16">
+    <rPh sb="14" eb="15">
       <t>ナ</t>
     </rPh>
-    <rPh sb="17" eb="18">
+    <rPh sb="16" eb="17">
       <t>ラン</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="19" eb="21">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="25" eb="27">
+    <rPh sb="24" eb="26">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="27" eb="29">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カナ（名）欄</t>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「カナ（名）欄」に入力した
+    <t>アカウント登録画面で「カナ（名）欄」に入力した
 内容が表示されている</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
-    <rPh sb="15" eb="16">
+    <rPh sb="14" eb="15">
       <t>ナ</t>
     </rPh>
-    <rPh sb="17" eb="18">
+    <rPh sb="16" eb="17">
       <t>ラン</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="19" eb="21">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="25" eb="27">
+    <rPh sb="24" eb="26">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="27" eb="29">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレス欄</t>
-  </si>
-  <si>
-    <t>メールアドレス欄</t>
-    <rPh sb="7" eb="8">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「メールアドレス欄」に入力した
-内容が表示されている</t>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「メールアドレス欄」に入力した
+    <t>アカウント登録画面で「メールアドレス欄」に入力した
 内容が表示されている</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
-    <rPh sb="19" eb="20">
+    <rPh sb="18" eb="19">
       <t>ラン</t>
     </rPh>
-    <rPh sb="22" eb="24">
+    <rPh sb="21" eb="23">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="27" eb="29">
+    <rPh sb="26" eb="28">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="29" eb="31">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パスワード欄</t>
-  </si>
-  <si>
-    <t>パスワード欄</t>
-    <rPh sb="5" eb="6">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「メールアドレス欄」に入力した
-文字数分が”●”表示されている</t>
-  </si>
-  <si>
-    <t>アカウント登録画面にて「メールアドレス欄」に入力した
+    <t>アカウント登録画面で「メールアドレス欄」に入力した
 文字数分が”●”表示されている</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
+    <rPh sb="18" eb="19">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>モジスウブン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「性別 欄」にて選択した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「郵便番号欄」に入力した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「都道府県 欄」にて選択した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>トドウフケン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「市区町村 欄」に入力した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>番地 欄</t>
+    <rPh sb="0" eb="2">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「番地 欄」に入力した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント権限 欄</t>
+    <rPh sb="5" eb="7">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面で「アカウント権限 欄」にて選択した
+内容が表示されている</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケンゲン</t>
+    </rPh>
     <rPh sb="19" eb="20">
       <t>ラン</t>
     </rPh>
-    <rPh sb="22" eb="24">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="27" eb="31">
-      <t>モジスウブン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
+    <rPh sb="23" eb="25">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -8472,7 +8653,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -8536,10 +8717,10 @@
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F3" s="78" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
@@ -8551,13 +8732,13 @@
       <c r="B4" s="65"/>
       <c r="C4" s="65"/>
       <c r="D4" s="67" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
@@ -8569,13 +8750,13 @@
       <c r="B5" s="65"/>
       <c r="C5" s="65"/>
       <c r="D5" s="67" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
@@ -8587,13 +8768,13 @@
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
       <c r="D6" s="67" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
@@ -8605,13 +8786,13 @@
       <c r="B7" s="65"/>
       <c r="C7" s="65"/>
       <c r="D7" s="67" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
@@ -8623,7 +8804,7 @@
       <c r="B8" s="65"/>
       <c r="C8" s="65"/>
       <c r="D8" s="67" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>193</v>
@@ -8640,9 +8821,15 @@
       <c r="A9" s="70"/>
       <c r="B9" s="65"/>
       <c r="C9" s="65"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="38"/>
+      <c r="D9" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>207</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
       <c r="I9" s="4"/>
@@ -8652,9 +8839,15 @@
       <c r="A10" s="70"/>
       <c r="B10" s="65"/>
       <c r="C10" s="65"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="38"/>
+      <c r="D10" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>208</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
@@ -8664,9 +8857,15 @@
       <c r="A11" s="70"/>
       <c r="B11" s="65"/>
       <c r="C11" s="65"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="38"/>
+      <c r="D11" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>209</v>
+      </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
       <c r="I11" s="4"/>
@@ -8676,9 +8875,15 @@
       <c r="A12" s="70"/>
       <c r="B12" s="65"/>
       <c r="C12" s="65"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="38"/>
+      <c r="D12" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>209</v>
+      </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
       <c r="I12" s="4"/>
@@ -8688,9 +8893,15 @@
       <c r="A13" s="70"/>
       <c r="B13" s="65"/>
       <c r="C13" s="65"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="38"/>
+      <c r="D13" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>212</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
       <c r="I13" s="4"/>
@@ -8701,13 +8912,13 @@
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
       <c r="D14" s="67" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -8718,9 +8929,15 @@
       <c r="A15" s="70"/>
       <c r="B15" s="65"/>
       <c r="C15" s="65"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="38"/>
+      <c r="D15" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>152</v>
+      </c>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
       <c r="I15" s="4"/>
@@ -8729,16 +8946,10 @@
     <row r="16" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="70"/>
       <c r="B16" s="65"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>195</v>
-      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="38"/>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
       <c r="I16" s="4"/>
@@ -8747,16 +8958,10 @@
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="70"/>
       <c r="B17" s="65"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>197</v>
-      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="38"/>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="4"/>
@@ -8767,13 +8972,13 @@
       <c r="B18" s="65"/>
       <c r="C18" s="72"/>
       <c r="D18" s="67" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
@@ -8785,13 +8990,13 @@
       <c r="B19" s="65"/>
       <c r="C19" s="72"/>
       <c r="D19" s="67" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="13"/>
@@ -8802,14 +9007,14 @@
       <c r="A20" s="70"/>
       <c r="B20" s="65"/>
       <c r="C20" s="72"/>
-      <c r="D20" s="68" t="s">
-        <v>201</v>
+      <c r="D20" s="67" t="s">
+        <v>195</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="13"/>
@@ -8820,14 +9025,14 @@
       <c r="A21" s="70"/>
       <c r="B21" s="65"/>
       <c r="C21" s="72"/>
-      <c r="D21" s="68" t="s">
-        <v>205</v>
+      <c r="D21" s="67" t="s">
+        <v>195</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="13"/>
@@ -8838,9 +9043,15 @@
       <c r="A22" s="70"/>
       <c r="B22" s="65"/>
       <c r="C22" s="72"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="38"/>
+      <c r="D22" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>205</v>
+      </c>
       <c r="G22" s="4"/>
       <c r="H22" s="13"/>
       <c r="I22" s="4"/>
@@ -8850,9 +9061,15 @@
       <c r="A23" s="70"/>
       <c r="B23" s="65"/>
       <c r="C23" s="72"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="38"/>
+      <c r="D23" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>206</v>
+      </c>
       <c r="G23" s="4"/>
       <c r="H23" s="13"/>
       <c r="I23" s="4"/>
@@ -8862,9 +9079,15 @@
       <c r="A24" s="70"/>
       <c r="B24" s="65"/>
       <c r="C24" s="72"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="38"/>
+      <c r="D24" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>207</v>
+      </c>
       <c r="G24" s="4"/>
       <c r="H24" s="13"/>
       <c r="I24" s="4"/>
@@ -8874,9 +9097,15 @@
       <c r="A25" s="70"/>
       <c r="B25" s="65"/>
       <c r="C25" s="72"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="38"/>
+      <c r="D25" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>208</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="13"/>
       <c r="I25" s="4"/>
@@ -8886,9 +9115,15 @@
       <c r="A26" s="70"/>
       <c r="B26" s="65"/>
       <c r="C26" s="72"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="38"/>
+      <c r="D26" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>209</v>
+      </c>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
       <c r="I26" s="4"/>
@@ -8898,9 +9133,15 @@
       <c r="A27" s="70"/>
       <c r="B27" s="65"/>
       <c r="C27" s="72"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="38"/>
+      <c r="D27" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>210</v>
+      </c>
       <c r="G27" s="4"/>
       <c r="H27" s="13"/>
       <c r="I27" s="4"/>
@@ -8910,9 +9151,15 @@
       <c r="A28" s="70"/>
       <c r="B28" s="65"/>
       <c r="C28" s="72"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="38"/>
+      <c r="D28" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>212</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="13"/>
       <c r="I28" s="4"/>
@@ -8922,9 +9169,15 @@
       <c r="A29" s="70"/>
       <c r="B29" s="65"/>
       <c r="C29" s="72"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="38"/>
+      <c r="D29" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>214</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="13"/>
       <c r="I29" s="4"/>
@@ -9042,7 +9295,7 @@
       <c r="A39" s="70"/>
       <c r="B39" s="65"/>
       <c r="C39" s="72"/>
-      <c r="D39" s="69"/>
+      <c r="D39" s="68"/>
       <c r="E39" s="17"/>
       <c r="F39" s="38"/>
       <c r="G39" s="4"/>
@@ -9054,7 +9307,7 @@
       <c r="A40" s="70"/>
       <c r="B40" s="65"/>
       <c r="C40" s="72"/>
-      <c r="D40" s="69"/>
+      <c r="D40" s="68"/>
       <c r="E40" s="17"/>
       <c r="F40" s="38"/>
       <c r="G40" s="4"/>
@@ -9175,7 +9428,7 @@
       <c r="B50" s="65"/>
       <c r="C50" s="72"/>
       <c r="D50" s="69"/>
-      <c r="E50" s="14"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="38"/>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
@@ -9199,7 +9452,7 @@
       <c r="B52" s="65"/>
       <c r="C52" s="72"/>
       <c r="D52" s="69"/>
-      <c r="E52" s="38"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="38"/>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -9211,7 +9464,7 @@
       <c r="B53" s="65"/>
       <c r="C53" s="72"/>
       <c r="D53" s="69"/>
-      <c r="E53" s="38"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="38"/>
       <c r="G53" s="4"/>
       <c r="H53" s="13"/>
@@ -9247,7 +9500,7 @@
       <c r="B56" s="65"/>
       <c r="C56" s="72"/>
       <c r="D56" s="69"/>
-      <c r="E56" s="17"/>
+      <c r="E56" s="38"/>
       <c r="F56" s="38"/>
       <c r="G56" s="4"/>
       <c r="H56" s="13"/>
@@ -9259,7 +9512,7 @@
       <c r="B57" s="65"/>
       <c r="C57" s="72"/>
       <c r="D57" s="69"/>
-      <c r="E57" s="17"/>
+      <c r="E57" s="38"/>
       <c r="F57" s="38"/>
       <c r="G57" s="4"/>
       <c r="H57" s="13"/>
@@ -9283,11 +9536,11 @@
       <c r="B59" s="65"/>
       <c r="C59" s="72"/>
       <c r="D59" s="69"/>
-      <c r="E59" s="14"/>
+      <c r="E59" s="17"/>
       <c r="F59" s="38"/>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
-      <c r="I59" s="40"/>
+      <c r="I59" s="4"/>
       <c r="J59" s="12"/>
     </row>
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9307,11 +9560,11 @@
       <c r="B61" s="65"/>
       <c r="C61" s="72"/>
       <c r="D61" s="69"/>
-      <c r="E61" s="17"/>
+      <c r="E61" s="14"/>
       <c r="F61" s="38"/>
       <c r="G61" s="4"/>
       <c r="H61" s="13"/>
-      <c r="I61" s="4"/>
+      <c r="I61" s="40"/>
       <c r="J61" s="12"/>
     </row>
     <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9407,7 +9660,7 @@
       <c r="F69" s="38"/>
       <c r="G69" s="4"/>
       <c r="H69" s="13"/>
-      <c r="I69" s="40"/>
+      <c r="I69" s="4"/>
       <c r="J69" s="12"/>
     </row>
     <row r="70" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9419,7 +9672,7 @@
       <c r="F70" s="38"/>
       <c r="G70" s="4"/>
       <c r="H70" s="13"/>
-      <c r="I70" s="40"/>
+      <c r="I70" s="4"/>
       <c r="J70" s="12"/>
     </row>
     <row r="71" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9443,7 +9696,7 @@
       <c r="F72" s="38"/>
       <c r="G72" s="4"/>
       <c r="H72" s="13"/>
-      <c r="I72" s="4"/>
+      <c r="I72" s="40"/>
       <c r="J72" s="12"/>
     </row>
     <row r="73" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9479,7 +9732,7 @@
       <c r="F75" s="38"/>
       <c r="G75" s="4"/>
       <c r="H75" s="13"/>
-      <c r="I75" s="4"/>
+      <c r="I75" s="40"/>
       <c r="J75" s="12"/>
     </row>
     <row r="76" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -9689,50 +9942,50 @@
     <row r="93" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="70"/>
       <c r="B93" s="65"/>
-      <c r="C93" s="73"/>
+      <c r="C93" s="72"/>
       <c r="D93" s="69"/>
       <c r="E93" s="17"/>
       <c r="F93" s="38"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="5"/>
+      <c r="H93" s="13"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="12"/>
     </row>
     <row r="94" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="70"/>
       <c r="B94" s="65"/>
-      <c r="C94" s="74"/>
+      <c r="C94" s="72"/>
       <c r="D94" s="69"/>
-      <c r="E94" s="14"/>
+      <c r="E94" s="17"/>
       <c r="F94" s="38"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="44"/>
+      <c r="H94" s="13"/>
       <c r="I94" s="4"/>
       <c r="J94" s="12"/>
     </row>
     <row r="95" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="70"/>
       <c r="B95" s="65"/>
-      <c r="C95" s="72"/>
+      <c r="C95" s="73"/>
       <c r="D95" s="69"/>
-      <c r="E95" s="14"/>
+      <c r="E95" s="17"/>
       <c r="F95" s="38"/>
       <c r="G95" s="4"/>
-      <c r="H95" s="44"/>
+      <c r="H95" s="5"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="12"/>
+      <c r="J95" s="4"/>
     </row>
     <row r="96" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="70"/>
       <c r="B96" s="65"/>
-      <c r="C96" s="72"/>
+      <c r="C96" s="74"/>
       <c r="D96" s="69"/>
       <c r="E96" s="14"/>
       <c r="F96" s="38"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="5"/>
+      <c r="H96" s="44"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="12"/>
     </row>
     <row r="97" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="70"/>
@@ -9742,9 +9995,9 @@
       <c r="E97" s="14"/>
       <c r="F97" s="38"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="5"/>
+      <c r="H97" s="44"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="12"/>
     </row>
     <row r="98" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="70"/>
@@ -9773,7 +10026,7 @@
     <row r="100" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="70"/>
       <c r="B100" s="65"/>
-      <c r="C100" s="73"/>
+      <c r="C100" s="72"/>
       <c r="D100" s="69"/>
       <c r="E100" s="14"/>
       <c r="F100" s="38"/>
@@ -9785,19 +10038,19 @@
     <row r="101" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="70"/>
       <c r="B101" s="65"/>
-      <c r="C101" s="75"/>
+      <c r="C101" s="72"/>
       <c r="D101" s="69"/>
       <c r="E101" s="14"/>
       <c r="F101" s="38"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="44"/>
+      <c r="H101" s="5"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="12"/>
+      <c r="J101" s="4"/>
     </row>
     <row r="102" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="70"/>
       <c r="B102" s="65"/>
-      <c r="C102" s="76"/>
+      <c r="C102" s="73"/>
       <c r="D102" s="69"/>
       <c r="E102" s="14"/>
       <c r="F102" s="38"/>
@@ -9809,14 +10062,14 @@
     <row r="103" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="70"/>
       <c r="B103" s="65"/>
-      <c r="C103" s="76"/>
+      <c r="C103" s="75"/>
       <c r="D103" s="69"/>
       <c r="E103" s="14"/>
       <c r="F103" s="38"/>
       <c r="G103" s="4"/>
-      <c r="H103" s="5"/>
+      <c r="H103" s="44"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
+      <c r="J103" s="12"/>
     </row>
     <row r="104" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="70"/>
@@ -9844,8 +10097,8 @@
     </row>
     <row r="106" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="70"/>
-      <c r="B106" s="66"/>
-      <c r="C106" s="77"/>
+      <c r="B106" s="65"/>
+      <c r="C106" s="76"/>
       <c r="D106" s="69"/>
       <c r="E106" s="14"/>
       <c r="F106" s="38"/>
@@ -9854,13 +10107,37 @@
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
     </row>
-    <row r="107" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="107" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="70"/>
+      <c r="B107" s="65"/>
+      <c r="C107" s="76"/>
+      <c r="D107" s="69"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="38"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+    </row>
+    <row r="108" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="70"/>
+      <c r="B108" s="66"/>
+      <c r="C108" s="77"/>
+      <c r="D108" s="69"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="38"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+    </row>
+    <row r="109" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B106"/>
-    <mergeCell ref="C3:C15"/>
+    <mergeCell ref="B3:B108"/>
+    <mergeCell ref="C3:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A8692E-8410-4423-8054-BC10FE5E5CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CE9D89-1CDA-49CB-9FC2-0E53E09657CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="224">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2847,6 +2847,96 @@
     <rPh sb="31" eb="33">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示内容確認後、「登録する」を押下</t>
+    <rPh sb="0" eb="7">
+      <t>ヒョウジナイヨウカクニンゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「family_name」カラムへ内容が登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「last_name」カラムへ内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面へ遷移し、「登録完了しました」表示</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「last_name_kana」カラムへ内容が登録されている</t>
+    <rPh sb="26" eb="28">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カナ（性）欄</t>
+    <rPh sb="3" eb="4">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「family_name_kana」カラムへ内容が登録されている</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3159,7 +3249,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3295,6 +3385,21 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -3331,6 +3436,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -3338,18 +3449,6 @@
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3361,41 +3460,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3729,24 +3804,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -3767,10 +3842,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="50" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -3788,8 +3863,8 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="50"/>
-      <c r="C4" s="45"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="19" t="s">
         <v>20</v>
       </c>
@@ -3816,8 +3891,8 @@
       </c>
     </row>
     <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="50"/>
-      <c r="C5" s="45"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="19" t="s">
         <v>20</v>
       </c>
@@ -3844,8 +3919,8 @@
       </c>
     </row>
     <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="50"/>
-      <c r="C6" s="45"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="19" t="s">
         <v>20</v>
       </c>
@@ -3872,8 +3947,8 @@
       </c>
     </row>
     <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="50"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
@@ -3900,8 +3975,8 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="50"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
@@ -3917,8 +3992,8 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="50"/>
-      <c r="C9" s="45"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
@@ -3934,8 +4009,8 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="50"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="8" t="s">
         <v>20</v>
       </c>
@@ -3951,8 +4026,8 @@
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="50"/>
-      <c r="C11" s="45"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
@@ -3968,8 +4043,8 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="50"/>
-      <c r="C12" s="45"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="8" t="s">
         <v>20</v>
       </c>
@@ -3985,8 +4060,8 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="50"/>
-      <c r="C13" s="45"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
@@ -4002,8 +4077,8 @@
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="50"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
@@ -4019,8 +4094,8 @@
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="50"/>
-      <c r="C15" s="45"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
@@ -4036,8 +4111,8 @@
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="50"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="28" t="s">
         <v>21</v>
       </c>
@@ -4064,8 +4139,8 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="50"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="28" t="s">
         <v>21</v>
       </c>
@@ -4092,8 +4167,8 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="50"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="28" t="s">
         <v>21</v>
       </c>
@@ -4120,8 +4195,8 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="50"/>
-      <c r="C19" s="45"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="28" t="s">
         <v>21</v>
       </c>
@@ -4148,8 +4223,8 @@
       </c>
     </row>
     <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="50"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="6" t="s">
         <v>21</v>
       </c>
@@ -4165,8 +4240,8 @@
       <c r="J20" s="12"/>
     </row>
     <row r="21" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="50"/>
-      <c r="C21" s="45"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="6" t="s">
         <v>21</v>
       </c>
@@ -4182,8 +4257,8 @@
       <c r="J21" s="12"/>
     </row>
     <row r="22" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="50"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="6" t="s">
         <v>21</v>
       </c>
@@ -4199,8 +4274,8 @@
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="50"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
@@ -4216,8 +4291,8 @@
       <c r="J23" s="12"/>
     </row>
     <row r="24" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="50"/>
-      <c r="C24" s="45"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
@@ -4233,8 +4308,8 @@
       <c r="J24" s="12"/>
     </row>
     <row r="25" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="50"/>
-      <c r="C25" s="45"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
@@ -4250,8 +4325,8 @@
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="50"/>
-      <c r="C26" s="45"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
@@ -4267,8 +4342,8 @@
       <c r="J26" s="12"/>
     </row>
     <row r="27" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="50"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="6" t="s">
         <v>22</v>
       </c>
@@ -4284,8 +4359,8 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="50"/>
-      <c r="C28" s="45"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="28" t="s">
         <v>22</v>
       </c>
@@ -4304,8 +4379,8 @@
       </c>
     </row>
     <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="50"/>
-      <c r="C29" s="45"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="28" t="s">
         <v>22</v>
       </c>
@@ -4324,8 +4399,8 @@
       </c>
     </row>
     <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="50"/>
-      <c r="C30" s="45"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="28" t="s">
         <v>22</v>
       </c>
@@ -4344,8 +4419,8 @@
       </c>
     </row>
     <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="50"/>
-      <c r="C31" s="45"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="28" t="s">
         <v>22</v>
       </c>
@@ -4364,8 +4439,8 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="50"/>
-      <c r="C32" s="45"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="50"/>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
@@ -4381,8 +4456,8 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="50"/>
-      <c r="C33" s="45"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
@@ -4398,8 +4473,8 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="50"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="50"/>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
@@ -4415,8 +4490,8 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="50"/>
-      <c r="C35" s="45"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="50"/>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
@@ -4432,8 +4507,8 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="50"/>
-      <c r="C36" s="45"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
@@ -4449,8 +4524,8 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="50"/>
-      <c r="C37" s="45"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="50"/>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
@@ -4466,8 +4541,8 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="50"/>
-      <c r="C38" s="45"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="50"/>
       <c r="D38" s="6" t="s">
         <v>22</v>
       </c>
@@ -4483,8 +4558,8 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="50"/>
-      <c r="C39" s="45"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="50"/>
       <c r="D39" s="6" t="s">
         <v>23</v>
       </c>
@@ -4500,8 +4575,8 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="50"/>
-      <c r="C40" s="45"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="50"/>
       <c r="D40" s="28" t="s">
         <v>23</v>
       </c>
@@ -4520,8 +4595,8 @@
       </c>
     </row>
     <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="50"/>
-      <c r="C41" s="45"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="50"/>
       <c r="D41" s="28" t="s">
         <v>23</v>
       </c>
@@ -4540,8 +4615,8 @@
       </c>
     </row>
     <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="50"/>
-      <c r="C42" s="45"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="50"/>
       <c r="D42" s="28" t="s">
         <v>23</v>
       </c>
@@ -4560,8 +4635,8 @@
       </c>
     </row>
     <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="50"/>
-      <c r="C43" s="45"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="50"/>
       <c r="D43" s="28" t="s">
         <v>23</v>
       </c>
@@ -4580,8 +4655,8 @@
       </c>
     </row>
     <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="50"/>
-      <c r="C44" s="45"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="6" t="s">
         <v>23</v>
       </c>
@@ -4597,8 +4672,8 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="50"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="6" t="s">
         <v>23</v>
       </c>
@@ -4614,8 +4689,8 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="50"/>
-      <c r="C46" s="45"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="6" t="s">
         <v>23</v>
       </c>
@@ -4631,8 +4706,8 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="50"/>
-      <c r="C47" s="45"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="50"/>
       <c r="D47" s="6" t="s">
         <v>23</v>
       </c>
@@ -4648,8 +4723,8 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="50"/>
-      <c r="C48" s="45"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="6" t="s">
         <v>23</v>
       </c>
@@ -4665,8 +4740,8 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="50"/>
-      <c r="C49" s="45"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="6" t="s">
         <v>23</v>
       </c>
@@ -4682,8 +4757,8 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="50"/>
-      <c r="C50" s="45"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="6" t="s">
         <v>23</v>
       </c>
@@ -4699,8 +4774,8 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="50"/>
-      <c r="C51" s="45"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="7" t="s">
         <v>24</v>
       </c>
@@ -4716,8 +4791,8 @@
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="50"/>
-      <c r="C52" s="45"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="30" t="s">
         <v>24</v>
       </c>
@@ -4733,8 +4808,8 @@
       <c r="J52" s="31"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="50"/>
-      <c r="C53" s="45"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="30" t="s">
         <v>24</v>
       </c>
@@ -4750,8 +4825,8 @@
       <c r="J53" s="31"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="50"/>
-      <c r="C54" s="45"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="50"/>
       <c r="D54" s="30" t="s">
         <v>24</v>
       </c>
@@ -4767,8 +4842,8 @@
       <c r="J54" s="31"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="50"/>
-      <c r="C55" s="45"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="50"/>
       <c r="D55" s="30" t="s">
         <v>24</v>
       </c>
@@ -4784,8 +4859,8 @@
       <c r="J55" s="31"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="50"/>
-      <c r="C56" s="45"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="50"/>
       <c r="D56" s="30" t="s">
         <v>24</v>
       </c>
@@ -4801,8 +4876,8 @@
       <c r="J56" s="31"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="50"/>
-      <c r="C57" s="45"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="50"/>
       <c r="D57" s="30" t="s">
         <v>24</v>
       </c>
@@ -4818,8 +4893,8 @@
       <c r="J57" s="31"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="50"/>
-      <c r="C58" s="45"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="50"/>
       <c r="D58" s="30" t="s">
         <v>24</v>
       </c>
@@ -4835,8 +4910,8 @@
       <c r="J58" s="31"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="50"/>
-      <c r="C59" s="45"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="50"/>
       <c r="D59" s="30" t="s">
         <v>24</v>
       </c>
@@ -4852,8 +4927,8 @@
       <c r="J59" s="31"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="50"/>
-      <c r="C60" s="45"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="50"/>
       <c r="D60" s="7" t="s">
         <v>24</v>
       </c>
@@ -4869,8 +4944,8 @@
       <c r="J60" s="4"/>
     </row>
     <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="50"/>
-      <c r="C61" s="45"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="50"/>
       <c r="D61" s="7" t="s">
         <v>24</v>
       </c>
@@ -4886,8 +4961,8 @@
       <c r="J61" s="4"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="50"/>
-      <c r="C62" s="45"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="50"/>
       <c r="D62" s="7" t="s">
         <v>24</v>
       </c>
@@ -4903,8 +4978,8 @@
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="50"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="50"/>
       <c r="D63" s="7" t="s">
         <v>24</v>
       </c>
@@ -4920,8 +4995,8 @@
       <c r="J63" s="4"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="50"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="50"/>
       <c r="D64" s="7" t="s">
         <v>24</v>
       </c>
@@ -4937,8 +5012,8 @@
       <c r="J64" s="4"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="50"/>
-      <c r="C65" s="45"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="50"/>
       <c r="D65" s="7" t="s">
         <v>24</v>
       </c>
@@ -4954,8 +5029,8 @@
       <c r="J65" s="4"/>
     </row>
     <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="50"/>
-      <c r="C66" s="45"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="50"/>
       <c r="D66" s="7" t="s">
         <v>24</v>
       </c>
@@ -4971,8 +5046,8 @@
       <c r="J66" s="4"/>
     </row>
     <row r="67" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="50"/>
-      <c r="C67" s="45"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="50"/>
       <c r="D67" s="7" t="s">
         <v>24</v>
       </c>
@@ -4988,8 +5063,8 @@
       <c r="J67" s="4"/>
     </row>
     <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="50"/>
-      <c r="C68" s="45"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="50"/>
       <c r="D68" s="7" t="s">
         <v>24</v>
       </c>
@@ -5005,8 +5080,8 @@
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="50"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="50"/>
       <c r="D69" s="7" t="s">
         <v>29</v>
       </c>
@@ -5022,8 +5097,8 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="50"/>
-      <c r="C70" s="45"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="50"/>
       <c r="D70" s="30" t="s">
         <v>29</v>
       </c>
@@ -5039,8 +5114,8 @@
       <c r="J70" s="31"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="50"/>
-      <c r="C71" s="45"/>
+      <c r="B71" s="55"/>
+      <c r="C71" s="50"/>
       <c r="D71" s="30" t="s">
         <v>29</v>
       </c>
@@ -5056,8 +5131,8 @@
       <c r="J71" s="31"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="50"/>
-      <c r="C72" s="45"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="50"/>
       <c r="D72" s="30" t="s">
         <v>29</v>
       </c>
@@ -5073,8 +5148,8 @@
       <c r="J72" s="31"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="50"/>
-      <c r="C73" s="45"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="50"/>
       <c r="D73" s="30" t="s">
         <v>29</v>
       </c>
@@ -5090,8 +5165,8 @@
       <c r="J73" s="31"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="50"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="50"/>
       <c r="D74" s="30" t="s">
         <v>29</v>
       </c>
@@ -5107,8 +5182,8 @@
       <c r="J74" s="31"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="50"/>
-      <c r="C75" s="45"/>
+      <c r="B75" s="55"/>
+      <c r="C75" s="50"/>
       <c r="D75" s="30" t="s">
         <v>29</v>
       </c>
@@ -5124,8 +5199,8 @@
       <c r="J75" s="31"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="50"/>
-      <c r="C76" s="45"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="50"/>
       <c r="D76" s="30" t="s">
         <v>29</v>
       </c>
@@ -5141,8 +5216,8 @@
       <c r="J76" s="31"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="50"/>
-      <c r="C77" s="45"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="50"/>
       <c r="D77" s="7" t="s">
         <v>29</v>
       </c>
@@ -5158,8 +5233,8 @@
       <c r="J77" s="4"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="50"/>
-      <c r="C78" s="45"/>
+      <c r="B78" s="55"/>
+      <c r="C78" s="50"/>
       <c r="D78" s="7" t="s">
         <v>29</v>
       </c>
@@ -5175,8 +5250,8 @@
       <c r="J78" s="4"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="50"/>
-      <c r="C79" s="45"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="50"/>
       <c r="D79" s="7" t="s">
         <v>29</v>
       </c>
@@ -5192,8 +5267,8 @@
       <c r="J79" s="4"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="50"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="7" t="s">
         <v>29</v>
       </c>
@@ -5209,8 +5284,8 @@
       <c r="J80" s="4"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="50"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="50"/>
       <c r="D81" s="7" t="s">
         <v>29</v>
       </c>
@@ -5226,8 +5301,8 @@
       <c r="J81" s="4"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="50"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="50"/>
       <c r="D82" s="7" t="s">
         <v>29</v>
       </c>
@@ -5243,8 +5318,8 @@
       <c r="J82" s="4"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="50"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="50"/>
       <c r="D83" s="7" t="s">
         <v>29</v>
       </c>
@@ -5260,8 +5335,8 @@
       <c r="J83" s="4"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="50"/>
-      <c r="C84" s="45"/>
+      <c r="B84" s="55"/>
+      <c r="C84" s="50"/>
       <c r="D84" s="7" t="s">
         <v>45</v>
       </c>
@@ -5277,8 +5352,8 @@
       <c r="J84" s="4"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="50"/>
-      <c r="C85" s="45"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="50"/>
       <c r="D85" s="7" t="s">
         <v>45</v>
       </c>
@@ -5294,8 +5369,8 @@
       <c r="J85" s="4"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="50"/>
-      <c r="C86" s="45"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="50"/>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
@@ -5311,8 +5386,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="50"/>
-      <c r="C87" s="45"/>
+      <c r="B87" s="55"/>
+      <c r="C87" s="50"/>
       <c r="D87" s="30" t="s">
         <v>54</v>
       </c>
@@ -5328,8 +5403,8 @@
       <c r="J87" s="31"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="50"/>
-      <c r="C88" s="45"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="50"/>
       <c r="D88" s="30" t="s">
         <v>54</v>
       </c>
@@ -5345,8 +5420,8 @@
       <c r="J88" s="31"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="50"/>
-      <c r="C89" s="45"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="50"/>
       <c r="D89" s="30" t="s">
         <v>54</v>
       </c>
@@ -5362,8 +5437,8 @@
       <c r="J89" s="31"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="50"/>
-      <c r="C90" s="45"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="50"/>
       <c r="D90" s="30" t="s">
         <v>54</v>
       </c>
@@ -5379,8 +5454,8 @@
       <c r="J90" s="31"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="50"/>
-      <c r="C91" s="45"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="50"/>
       <c r="D91" s="7" t="s">
         <v>54</v>
       </c>
@@ -5396,8 +5471,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="50"/>
-      <c r="C92" s="45"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="50"/>
       <c r="D92" s="7" t="s">
         <v>54</v>
       </c>
@@ -5413,8 +5488,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="50"/>
-      <c r="C93" s="45"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="50"/>
       <c r="D93" s="7" t="s">
         <v>54</v>
       </c>
@@ -5430,8 +5505,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="50"/>
-      <c r="C94" s="45"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="50"/>
       <c r="D94" s="7" t="s">
         <v>54</v>
       </c>
@@ -5447,8 +5522,8 @@
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="50"/>
-      <c r="C95" s="45"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="50"/>
       <c r="D95" s="7" t="s">
         <v>54</v>
       </c>
@@ -5464,8 +5539,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="50"/>
-      <c r="C96" s="45"/>
+      <c r="B96" s="55"/>
+      <c r="C96" s="50"/>
       <c r="D96" s="7" t="s">
         <v>54</v>
       </c>
@@ -5481,8 +5556,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="50"/>
-      <c r="C97" s="45"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="50"/>
       <c r="D97" s="7" t="s">
         <v>54</v>
       </c>
@@ -5498,8 +5573,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="50"/>
-      <c r="C98" s="45"/>
+      <c r="B98" s="55"/>
+      <c r="C98" s="50"/>
       <c r="D98" s="30" t="s">
         <v>53</v>
       </c>
@@ -5515,8 +5590,8 @@
       <c r="J98" s="31"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="50"/>
-      <c r="C99" s="45"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="50"/>
       <c r="D99" s="30" t="s">
         <v>53</v>
       </c>
@@ -5532,8 +5607,8 @@
       <c r="J99" s="31"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="50"/>
-      <c r="C100" s="45"/>
+      <c r="B100" s="55"/>
+      <c r="C100" s="50"/>
       <c r="D100" s="30" t="s">
         <v>53</v>
       </c>
@@ -5549,8 +5624,8 @@
       <c r="J100" s="31"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="50"/>
-      <c r="C101" s="45"/>
+      <c r="B101" s="55"/>
+      <c r="C101" s="50"/>
       <c r="D101" s="7" t="s">
         <v>53</v>
       </c>
@@ -5566,8 +5641,8 @@
       <c r="J101" s="4"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="50"/>
-      <c r="C102" s="45"/>
+      <c r="B102" s="55"/>
+      <c r="C102" s="50"/>
       <c r="D102" s="7" t="s">
         <v>53</v>
       </c>
@@ -5583,8 +5658,8 @@
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="50"/>
-      <c r="C103" s="45"/>
+      <c r="B103" s="55"/>
+      <c r="C103" s="50"/>
       <c r="D103" s="7" t="s">
         <v>59</v>
       </c>
@@ -5600,8 +5675,8 @@
       <c r="J103" s="4"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="50"/>
-      <c r="C104" s="45"/>
+      <c r="B104" s="55"/>
+      <c r="C104" s="50"/>
       <c r="D104" s="30" t="s">
         <v>59</v>
       </c>
@@ -5617,8 +5692,8 @@
       <c r="J104" s="31"/>
     </row>
     <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="50"/>
-      <c r="C105" s="45"/>
+      <c r="B105" s="55"/>
+      <c r="C105" s="50"/>
       <c r="D105" s="30" t="s">
         <v>59</v>
       </c>
@@ -5634,8 +5709,8 @@
       <c r="J105" s="31"/>
     </row>
     <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="50"/>
-      <c r="C106" s="45"/>
+      <c r="B106" s="55"/>
+      <c r="C106" s="50"/>
       <c r="D106" s="30" t="s">
         <v>59</v>
       </c>
@@ -5651,8 +5726,8 @@
       <c r="J106" s="31"/>
     </row>
     <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="50"/>
-      <c r="C107" s="45"/>
+      <c r="B107" s="55"/>
+      <c r="C107" s="50"/>
       <c r="D107" s="30" t="s">
         <v>59</v>
       </c>
@@ -5668,8 +5743,8 @@
       <c r="J107" s="31"/>
     </row>
     <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="50"/>
-      <c r="C108" s="45"/>
+      <c r="B108" s="55"/>
+      <c r="C108" s="50"/>
       <c r="D108" s="30" t="s">
         <v>59</v>
       </c>
@@ -5685,8 +5760,8 @@
       <c r="J108" s="31"/>
     </row>
     <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="50"/>
-      <c r="C109" s="45"/>
+      <c r="B109" s="55"/>
+      <c r="C109" s="50"/>
       <c r="D109" s="30" t="s">
         <v>59</v>
       </c>
@@ -5702,8 +5777,8 @@
       <c r="J109" s="31"/>
     </row>
     <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="50"/>
-      <c r="C110" s="45"/>
+      <c r="B110" s="55"/>
+      <c r="C110" s="50"/>
       <c r="D110" s="30" t="s">
         <v>59</v>
       </c>
@@ -5719,8 +5794,8 @@
       <c r="J110" s="31"/>
     </row>
     <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="50"/>
-      <c r="C111" s="45"/>
+      <c r="B111" s="55"/>
+      <c r="C111" s="50"/>
       <c r="D111" s="30" t="s">
         <v>59</v>
       </c>
@@ -5736,8 +5811,8 @@
       <c r="J111" s="31"/>
     </row>
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="50"/>
-      <c r="C112" s="45"/>
+      <c r="B112" s="55"/>
+      <c r="C112" s="50"/>
       <c r="D112" s="7" t="s">
         <v>59</v>
       </c>
@@ -5753,8 +5828,8 @@
       <c r="J112" s="4"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="50"/>
-      <c r="C113" s="45"/>
+      <c r="B113" s="55"/>
+      <c r="C113" s="50"/>
       <c r="D113" s="7" t="s">
         <v>59</v>
       </c>
@@ -5770,8 +5845,8 @@
       <c r="J113" s="4"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="50"/>
-      <c r="C114" s="45"/>
+      <c r="B114" s="55"/>
+      <c r="C114" s="50"/>
       <c r="D114" s="7" t="s">
         <v>59</v>
       </c>
@@ -5787,8 +5862,8 @@
       <c r="J114" s="4"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="50"/>
-      <c r="C115" s="45"/>
+      <c r="B115" s="55"/>
+      <c r="C115" s="50"/>
       <c r="D115" s="7" t="s">
         <v>59</v>
       </c>
@@ -5804,8 +5879,8 @@
       <c r="J115" s="4"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="50"/>
-      <c r="C116" s="45"/>
+      <c r="B116" s="55"/>
+      <c r="C116" s="50"/>
       <c r="D116" s="7" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5896,8 @@
       <c r="J116" s="4"/>
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="50"/>
-      <c r="C117" s="45"/>
+      <c r="B117" s="55"/>
+      <c r="C117" s="50"/>
       <c r="D117" s="7" t="s">
         <v>59</v>
       </c>
@@ -5838,8 +5913,8 @@
       <c r="J117" s="4"/>
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="50"/>
-      <c r="C118" s="45"/>
+      <c r="B118" s="55"/>
+      <c r="C118" s="50"/>
       <c r="D118" s="7" t="s">
         <v>59</v>
       </c>
@@ -5855,8 +5930,8 @@
       <c r="J118" s="4"/>
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="50"/>
-      <c r="C119" s="45"/>
+      <c r="B119" s="55"/>
+      <c r="C119" s="50"/>
       <c r="D119" s="7" t="s">
         <v>59</v>
       </c>
@@ -5872,8 +5947,8 @@
       <c r="J119" s="4"/>
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="50"/>
-      <c r="C120" s="45"/>
+      <c r="B120" s="55"/>
+      <c r="C120" s="50"/>
       <c r="D120" s="7" t="s">
         <v>70</v>
       </c>
@@ -5889,8 +5964,8 @@
       <c r="J120" s="4"/>
     </row>
     <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="50"/>
-      <c r="C121" s="45"/>
+      <c r="B121" s="55"/>
+      <c r="C121" s="50"/>
       <c r="D121" s="7" t="s">
         <v>70</v>
       </c>
@@ -5906,8 +5981,8 @@
       <c r="J121" s="4"/>
     </row>
     <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="50"/>
-      <c r="C122" s="45"/>
+      <c r="B122" s="55"/>
+      <c r="C122" s="50"/>
       <c r="D122" s="7" t="s">
         <v>70</v>
       </c>
@@ -5923,8 +5998,8 @@
       <c r="J122" s="4"/>
     </row>
     <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="50"/>
-      <c r="C123" s="45"/>
+      <c r="B123" s="55"/>
+      <c r="C123" s="50"/>
       <c r="D123" s="7" t="s">
         <v>70</v>
       </c>
@@ -5940,8 +6015,8 @@
       <c r="J123" s="4"/>
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="50"/>
-      <c r="C124" s="45"/>
+      <c r="B124" s="55"/>
+      <c r="C124" s="50"/>
       <c r="D124" s="7" t="s">
         <v>70</v>
       </c>
@@ -5957,8 +6032,8 @@
       <c r="J124" s="4"/>
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="50"/>
-      <c r="C125" s="45"/>
+      <c r="B125" s="55"/>
+      <c r="C125" s="50"/>
       <c r="D125" s="7" t="s">
         <v>70</v>
       </c>
@@ -5974,8 +6049,8 @@
       <c r="J125" s="4"/>
     </row>
     <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="50"/>
-      <c r="C126" s="45"/>
+      <c r="B126" s="55"/>
+      <c r="C126" s="50"/>
       <c r="D126" s="7" t="s">
         <v>70</v>
       </c>
@@ -5991,8 +6066,8 @@
       <c r="J126" s="4"/>
     </row>
     <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="50"/>
-      <c r="C127" s="45"/>
+      <c r="B127" s="55"/>
+      <c r="C127" s="50"/>
       <c r="D127" s="7" t="s">
         <v>70</v>
       </c>
@@ -6008,8 +6083,8 @@
       <c r="J127" s="4"/>
     </row>
     <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="50"/>
-      <c r="C128" s="45"/>
+      <c r="B128" s="55"/>
+      <c r="C128" s="50"/>
       <c r="D128" s="7" t="s">
         <v>70</v>
       </c>
@@ -6025,8 +6100,8 @@
       <c r="J128" s="4"/>
     </row>
     <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B129" s="50"/>
-      <c r="C129" s="45"/>
+      <c r="B129" s="55"/>
+      <c r="C129" s="50"/>
       <c r="D129" s="7" t="s">
         <v>70</v>
       </c>
@@ -6042,8 +6117,8 @@
       <c r="J129" s="4"/>
     </row>
     <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="50"/>
-      <c r="C130" s="45"/>
+      <c r="B130" s="55"/>
+      <c r="C130" s="50"/>
       <c r="D130" s="7" t="s">
         <v>70</v>
       </c>
@@ -6059,8 +6134,8 @@
       <c r="J130" s="4"/>
     </row>
     <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B131" s="50"/>
-      <c r="C131" s="45"/>
+      <c r="B131" s="55"/>
+      <c r="C131" s="50"/>
       <c r="D131" s="7" t="s">
         <v>82</v>
       </c>
@@ -6076,8 +6151,8 @@
       <c r="J131" s="4"/>
     </row>
     <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B132" s="50"/>
-      <c r="C132" s="45"/>
+      <c r="B132" s="55"/>
+      <c r="C132" s="50"/>
       <c r="D132" s="7" t="s">
         <v>82</v>
       </c>
@@ -6093,8 +6168,8 @@
       <c r="J132" s="4"/>
     </row>
     <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="50"/>
-      <c r="C133" s="46"/>
+      <c r="B133" s="55"/>
+      <c r="C133" s="51"/>
       <c r="D133" s="7"/>
       <c r="E133" s="14"/>
       <c r="F133" s="7"/>
@@ -6104,8 +6179,8 @@
       <c r="J133" s="4"/>
     </row>
     <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="50"/>
-      <c r="C134" s="53"/>
+      <c r="B134" s="55"/>
+      <c r="C134" s="58"/>
       <c r="D134" s="7"/>
       <c r="E134" s="14"/>
       <c r="F134" s="7"/>
@@ -6115,8 +6190,8 @@
       <c r="J134" s="4"/>
     </row>
     <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="50"/>
-      <c r="C135" s="54"/>
+      <c r="B135" s="55"/>
+      <c r="C135" s="59"/>
       <c r="D135" s="7"/>
       <c r="E135" s="14"/>
       <c r="F135" s="7"/>
@@ -6126,8 +6201,8 @@
       <c r="J135" s="4"/>
     </row>
     <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="50"/>
-      <c r="C136" s="54"/>
+      <c r="B136" s="55"/>
+      <c r="C136" s="59"/>
       <c r="D136" s="7"/>
       <c r="E136" s="14"/>
       <c r="F136" s="7"/>
@@ -6137,8 +6212,8 @@
       <c r="J136" s="4"/>
     </row>
     <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="50"/>
-      <c r="C137" s="54"/>
+      <c r="B137" s="55"/>
+      <c r="C137" s="59"/>
       <c r="D137" s="7"/>
       <c r="E137" s="14"/>
       <c r="F137" s="7"/>
@@ -6148,8 +6223,8 @@
       <c r="J137" s="4"/>
     </row>
     <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="50"/>
-      <c r="C138" s="54"/>
+      <c r="B138" s="55"/>
+      <c r="C138" s="59"/>
       <c r="D138" s="7"/>
       <c r="E138" s="14"/>
       <c r="F138" s="7"/>
@@ -6159,8 +6234,8 @@
       <c r="J138" s="4"/>
     </row>
     <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B139" s="50"/>
-      <c r="C139" s="54"/>
+      <c r="B139" s="55"/>
+      <c r="C139" s="59"/>
       <c r="D139" s="7"/>
       <c r="E139" s="14"/>
       <c r="F139" s="7"/>
@@ -6170,8 +6245,8 @@
       <c r="J139" s="4"/>
     </row>
     <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="50"/>
-      <c r="C140" s="54"/>
+      <c r="B140" s="55"/>
+      <c r="C140" s="59"/>
       <c r="D140" s="7"/>
       <c r="E140" s="14"/>
       <c r="F140" s="7"/>
@@ -6181,8 +6256,8 @@
       <c r="J140" s="4"/>
     </row>
     <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="50"/>
-      <c r="C141" s="54"/>
+      <c r="B141" s="55"/>
+      <c r="C141" s="59"/>
       <c r="D141" s="7"/>
       <c r="E141" s="14"/>
       <c r="F141" s="7"/>
@@ -6192,8 +6267,8 @@
       <c r="J141" s="4"/>
     </row>
     <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B142" s="50"/>
-      <c r="C142" s="54"/>
+      <c r="B142" s="55"/>
+      <c r="C142" s="59"/>
       <c r="D142" s="7"/>
       <c r="E142" s="14"/>
       <c r="F142" s="7"/>
@@ -6203,8 +6278,8 @@
       <c r="J142" s="4"/>
     </row>
     <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B143" s="50"/>
-      <c r="C143" s="54"/>
+      <c r="B143" s="55"/>
+      <c r="C143" s="59"/>
       <c r="D143" s="7"/>
       <c r="E143" s="14"/>
       <c r="F143" s="7"/>
@@ -6214,8 +6289,8 @@
       <c r="J143" s="4"/>
     </row>
     <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B144" s="50"/>
-      <c r="C144" s="54"/>
+      <c r="B144" s="55"/>
+      <c r="C144" s="59"/>
       <c r="D144" s="7"/>
       <c r="E144" s="14"/>
       <c r="F144" s="7"/>
@@ -6225,8 +6300,8 @@
       <c r="J144" s="4"/>
     </row>
     <row r="145" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="50"/>
-      <c r="C145" s="54"/>
+      <c r="B145" s="55"/>
+      <c r="C145" s="59"/>
       <c r="D145" s="7"/>
       <c r="E145" s="14"/>
       <c r="F145" s="7"/>
@@ -6236,8 +6311,8 @@
       <c r="J145" s="4"/>
     </row>
     <row r="146" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B146" s="50"/>
-      <c r="C146" s="54"/>
+      <c r="B146" s="55"/>
+      <c r="C146" s="59"/>
       <c r="D146" s="7"/>
       <c r="E146" s="14"/>
       <c r="F146" s="7"/>
@@ -6247,8 +6322,8 @@
       <c r="J146" s="4"/>
     </row>
     <row r="147" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B147" s="50"/>
-      <c r="C147" s="54"/>
+      <c r="B147" s="55"/>
+      <c r="C147" s="59"/>
       <c r="D147" s="7"/>
       <c r="E147" s="14"/>
       <c r="F147" s="7"/>
@@ -6258,8 +6333,8 @@
       <c r="J147" s="4"/>
     </row>
     <row r="148" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B148" s="50"/>
-      <c r="C148" s="54"/>
+      <c r="B148" s="55"/>
+      <c r="C148" s="59"/>
       <c r="D148" s="7"/>
       <c r="E148" s="14"/>
       <c r="F148" s="7"/>
@@ -6269,8 +6344,8 @@
       <c r="J148" s="4"/>
     </row>
     <row r="149" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B149" s="51"/>
-      <c r="C149" s="55"/>
+      <c r="B149" s="56"/>
+      <c r="C149" s="60"/>
       <c r="D149" s="7"/>
       <c r="E149" s="14"/>
       <c r="F149" s="7"/>
@@ -6317,24 +6392,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
     </row>
     <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -6355,13 +6430,13 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="67" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -6384,9 +6459,9 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="65"/>
+      <c r="B4" s="68"/>
       <c r="C4" s="62"/>
-      <c r="D4" s="67" t="s">
+      <c r="D4" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -6409,9 +6484,9 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="65"/>
+      <c r="B5" s="68"/>
       <c r="C5" s="62"/>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -6434,9 +6509,9 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="65"/>
+      <c r="B6" s="68"/>
       <c r="C6" s="62"/>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -6459,9 +6534,9 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="65"/>
+      <c r="B7" s="68"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -6484,9 +6559,9 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="65"/>
+      <c r="B8" s="68"/>
       <c r="C8" s="62"/>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -6509,9 +6584,9 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="65"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="62"/>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -6534,9 +6609,9 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="65"/>
+      <c r="B10" s="68"/>
       <c r="C10" s="62"/>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -6559,9 +6634,9 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="65"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="62"/>
-      <c r="D11" s="68" t="s">
+      <c r="D11" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -6584,9 +6659,9 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="65"/>
+      <c r="B12" s="68"/>
       <c r="C12" s="62"/>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -6609,9 +6684,9 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="65"/>
+      <c r="B13" s="68"/>
       <c r="C13" s="62"/>
-      <c r="D13" s="68" t="s">
+      <c r="D13" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -6634,9 +6709,9 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="65"/>
+      <c r="B14" s="68"/>
       <c r="C14" s="62"/>
-      <c r="D14" s="68" t="s">
+      <c r="D14" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -6659,9 +6734,9 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="65"/>
+      <c r="B15" s="68"/>
       <c r="C15" s="62"/>
-      <c r="D15" s="68" t="s">
+      <c r="D15" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -6684,9 +6759,9 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="65"/>
+      <c r="B16" s="68"/>
       <c r="C16" s="62"/>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -6709,9 +6784,9 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="65"/>
+      <c r="B17" s="68"/>
       <c r="C17" s="62"/>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -6734,9 +6809,9 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="65"/>
+      <c r="B18" s="68"/>
       <c r="C18" s="62"/>
-      <c r="D18" s="68" t="s">
+      <c r="D18" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -6759,9 +6834,9 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="65"/>
+      <c r="B19" s="68"/>
       <c r="C19" s="62"/>
-      <c r="D19" s="68" t="s">
+      <c r="D19" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -6784,9 +6859,9 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="65"/>
+      <c r="B20" s="68"/>
       <c r="C20" s="62"/>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -6809,9 +6884,9 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="65"/>
+      <c r="B21" s="68"/>
       <c r="C21" s="62"/>
-      <c r="D21" s="68" t="s">
+      <c r="D21" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -6834,9 +6909,9 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="65"/>
+      <c r="B22" s="68"/>
       <c r="C22" s="62"/>
-      <c r="D22" s="68" t="s">
+      <c r="D22" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -6859,9 +6934,9 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="65"/>
+      <c r="B23" s="68"/>
       <c r="C23" s="62"/>
-      <c r="D23" s="68" t="s">
+      <c r="D23" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -6884,9 +6959,9 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="65"/>
+      <c r="B24" s="68"/>
       <c r="C24" s="62"/>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -6909,9 +6984,9 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="65"/>
+      <c r="B25" s="68"/>
       <c r="C25" s="62"/>
-      <c r="D25" s="68" t="s">
+      <c r="D25" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -6934,9 +7009,9 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="65"/>
+      <c r="B26" s="68"/>
       <c r="C26" s="62"/>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -6959,9 +7034,9 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="65"/>
+      <c r="B27" s="68"/>
       <c r="C27" s="62"/>
-      <c r="D27" s="68" t="s">
+      <c r="D27" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -6984,9 +7059,9 @@
       </c>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="65"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="62"/>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -7009,9 +7084,9 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="65"/>
+      <c r="B29" s="68"/>
       <c r="C29" s="62"/>
-      <c r="D29" s="68" t="s">
+      <c r="D29" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -7034,9 +7109,9 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="65"/>
+      <c r="B30" s="68"/>
       <c r="C30" s="62"/>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -7059,9 +7134,9 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="65"/>
+      <c r="B31" s="68"/>
       <c r="C31" s="62"/>
-      <c r="D31" s="68" t="s">
+      <c r="D31" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -7084,9 +7159,9 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="65"/>
+      <c r="B32" s="68"/>
       <c r="C32" s="62"/>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -7109,9 +7184,9 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="65"/>
+      <c r="B33" s="68"/>
       <c r="C33" s="62"/>
-      <c r="D33" s="69" t="s">
+      <c r="D33" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="17" t="s">
@@ -7134,9 +7209,9 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="65"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="62"/>
-      <c r="D34" s="69" t="s">
+      <c r="D34" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -7159,9 +7234,9 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="65"/>
+      <c r="B35" s="68"/>
       <c r="C35" s="62"/>
-      <c r="D35" s="69" t="s">
+      <c r="D35" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E35" s="17" t="s">
@@ -7184,9 +7259,9 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="65"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="62"/>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="17" t="s">
@@ -7209,9 +7284,9 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="65"/>
+      <c r="B37" s="68"/>
       <c r="C37" s="62"/>
-      <c r="D37" s="69" t="s">
+      <c r="D37" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -7234,9 +7309,9 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="65"/>
+      <c r="B38" s="68"/>
       <c r="C38" s="62"/>
-      <c r="D38" s="69" t="s">
+      <c r="D38" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="17" t="s">
@@ -7259,9 +7334,9 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="65"/>
+      <c r="B39" s="68"/>
       <c r="C39" s="62"/>
-      <c r="D39" s="69" t="s">
+      <c r="D39" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="17" t="s">
@@ -7284,9 +7359,9 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="65"/>
+      <c r="B40" s="68"/>
       <c r="C40" s="62"/>
-      <c r="D40" s="69" t="s">
+      <c r="D40" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="17" t="s">
@@ -7309,9 +7384,9 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="65"/>
+      <c r="B41" s="68"/>
       <c r="C41" s="62"/>
-      <c r="D41" s="69" t="s">
+      <c r="D41" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="17" t="s">
@@ -7334,9 +7409,9 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="65"/>
+      <c r="B42" s="68"/>
       <c r="C42" s="62"/>
-      <c r="D42" s="69" t="s">
+      <c r="D42" s="47" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="17" t="s">
@@ -7359,9 +7434,9 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="65"/>
+      <c r="B43" s="68"/>
       <c r="C43" s="62"/>
-      <c r="D43" s="69" t="s">
+      <c r="D43" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E43" s="14" t="s">
@@ -7384,9 +7459,9 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="65"/>
+      <c r="B44" s="68"/>
       <c r="C44" s="62"/>
-      <c r="D44" s="69" t="s">
+      <c r="D44" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E44" s="17" t="s">
@@ -7409,9 +7484,9 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="65"/>
+      <c r="B45" s="68"/>
       <c r="C45" s="62"/>
-      <c r="D45" s="69" t="s">
+      <c r="D45" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E45" s="38" t="s">
@@ -7434,9 +7509,9 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="65"/>
+      <c r="B46" s="68"/>
       <c r="C46" s="62"/>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E46" s="38" t="s">
@@ -7459,9 +7534,9 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="65"/>
+      <c r="B47" s="68"/>
       <c r="C47" s="62"/>
-      <c r="D47" s="69" t="s">
+      <c r="D47" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E47" s="38" t="s">
@@ -7484,9 +7559,9 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="65"/>
+      <c r="B48" s="68"/>
       <c r="C48" s="62"/>
-      <c r="D48" s="69" t="s">
+      <c r="D48" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E48" s="38" t="s">
@@ -7509,9 +7584,9 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="65"/>
+      <c r="B49" s="68"/>
       <c r="C49" s="62"/>
-      <c r="D49" s="69" t="s">
+      <c r="D49" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E49" s="17" t="s">
@@ -7534,9 +7609,9 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="65"/>
+      <c r="B50" s="68"/>
       <c r="C50" s="62"/>
-      <c r="D50" s="69" t="s">
+      <c r="D50" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E50" s="17" t="s">
@@ -7559,9 +7634,9 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="65"/>
+      <c r="B51" s="68"/>
       <c r="C51" s="62"/>
-      <c r="D51" s="69" t="s">
+      <c r="D51" s="47" t="s">
         <v>29</v>
       </c>
       <c r="E51" s="17" t="s">
@@ -7584,9 +7659,9 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="65"/>
+      <c r="B52" s="68"/>
       <c r="C52" s="62"/>
-      <c r="D52" s="69" t="s">
+      <c r="D52" s="47" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="14" t="s">
@@ -7609,9 +7684,9 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="65"/>
+      <c r="B53" s="68"/>
       <c r="C53" s="62"/>
-      <c r="D53" s="69" t="s">
+      <c r="D53" s="47" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="17" t="s">
@@ -7634,9 +7709,9 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="65"/>
+      <c r="B54" s="68"/>
       <c r="C54" s="62"/>
-      <c r="D54" s="69" t="s">
+      <c r="D54" s="47" t="s">
         <v>45</v>
       </c>
       <c r="E54" s="17" t="s">
@@ -7659,9 +7734,9 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="65"/>
+      <c r="B55" s="68"/>
       <c r="C55" s="62"/>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E55" s="17" t="s">
@@ -7684,9 +7759,9 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="65"/>
+      <c r="B56" s="68"/>
       <c r="C56" s="62"/>
-      <c r="D56" s="69" t="s">
+      <c r="D56" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E56" s="17" t="s">
@@ -7709,9 +7784,9 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="65"/>
+      <c r="B57" s="68"/>
       <c r="C57" s="62"/>
-      <c r="D57" s="69" t="s">
+      <c r="D57" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="17" t="s">
@@ -7734,9 +7809,9 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="65"/>
+      <c r="B58" s="68"/>
       <c r="C58" s="62"/>
-      <c r="D58" s="69" t="s">
+      <c r="D58" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E58" s="17" t="s">
@@ -7759,9 +7834,9 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="65"/>
+      <c r="B59" s="68"/>
       <c r="C59" s="62"/>
-      <c r="D59" s="69" t="s">
+      <c r="D59" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E59" s="17" t="s">
@@ -7784,9 +7859,9 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="65"/>
+      <c r="B60" s="68"/>
       <c r="C60" s="62"/>
-      <c r="D60" s="69" t="s">
+      <c r="D60" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E60" s="17" t="s">
@@ -7809,9 +7884,9 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="65"/>
+      <c r="B61" s="68"/>
       <c r="C61" s="62"/>
-      <c r="D61" s="69" t="s">
+      <c r="D61" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E61" s="17" t="s">
@@ -7834,9 +7909,9 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="65"/>
+      <c r="B62" s="68"/>
       <c r="C62" s="62"/>
-      <c r="D62" s="69" t="s">
+      <c r="D62" s="47" t="s">
         <v>53</v>
       </c>
       <c r="E62" s="17" t="s">
@@ -7859,9 +7934,9 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="65"/>
+      <c r="B63" s="68"/>
       <c r="C63" s="62"/>
-      <c r="D63" s="69" t="s">
+      <c r="D63" s="47" t="s">
         <v>53</v>
       </c>
       <c r="E63" s="17" t="s">
@@ -7884,9 +7959,9 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="65"/>
+      <c r="B64" s="68"/>
       <c r="C64" s="62"/>
-      <c r="D64" s="69" t="s">
+      <c r="D64" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E64" s="17" t="s">
@@ -7909,9 +7984,9 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="65"/>
+      <c r="B65" s="68"/>
       <c r="C65" s="62"/>
-      <c r="D65" s="69" t="s">
+      <c r="D65" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E65" s="17" t="s">
@@ -7934,9 +8009,9 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="65"/>
+      <c r="B66" s="68"/>
       <c r="C66" s="62"/>
-      <c r="D66" s="69" t="s">
+      <c r="D66" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E66" s="17" t="s">
@@ -7959,9 +8034,9 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="65"/>
+      <c r="B67" s="68"/>
       <c r="C67" s="62"/>
-      <c r="D67" s="69" t="s">
+      <c r="D67" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E67" s="17" t="s">
@@ -7984,9 +8059,9 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="65"/>
+      <c r="B68" s="68"/>
       <c r="C68" s="62"/>
-      <c r="D68" s="69" t="s">
+      <c r="D68" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="17" t="s">
@@ -8009,9 +8084,9 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="65"/>
+      <c r="B69" s="68"/>
       <c r="C69" s="62"/>
-      <c r="D69" s="69" t="s">
+      <c r="D69" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E69" s="17" t="s">
@@ -8034,9 +8109,9 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="65"/>
+      <c r="B70" s="68"/>
       <c r="C70" s="62"/>
-      <c r="D70" s="69" t="s">
+      <c r="D70" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E70" s="17" t="s">
@@ -8059,9 +8134,9 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="65"/>
+      <c r="B71" s="68"/>
       <c r="C71" s="62"/>
-      <c r="D71" s="69" t="s">
+      <c r="D71" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E71" s="17" t="s">
@@ -8084,9 +8159,9 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="65"/>
+      <c r="B72" s="68"/>
       <c r="C72" s="62"/>
-      <c r="D72" s="69" t="s">
+      <c r="D72" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E72" s="17" t="s">
@@ -8109,9 +8184,9 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="65"/>
+      <c r="B73" s="68"/>
       <c r="C73" s="62"/>
-      <c r="D73" s="69" t="s">
+      <c r="D73" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E73" s="17" t="s">
@@ -8134,9 +8209,9 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="65"/>
+      <c r="B74" s="68"/>
       <c r="C74" s="62"/>
-      <c r="D74" s="69" t="s">
+      <c r="D74" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E74" s="17" t="s">
@@ -8159,9 +8234,9 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="65"/>
+      <c r="B75" s="68"/>
       <c r="C75" s="62"/>
-      <c r="D75" s="69" t="s">
+      <c r="D75" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E75" s="17" t="s">
@@ -8184,9 +8259,9 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="65"/>
+      <c r="B76" s="68"/>
       <c r="C76" s="62"/>
-      <c r="D76" s="69" t="s">
+      <c r="D76" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E76" s="17" t="s">
@@ -8209,9 +8284,9 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="65"/>
+      <c r="B77" s="68"/>
       <c r="C77" s="62"/>
-      <c r="D77" s="69" t="s">
+      <c r="D77" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E77" s="17" t="s">
@@ -8234,9 +8309,9 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="65"/>
+      <c r="B78" s="68"/>
       <c r="C78" s="62"/>
-      <c r="D78" s="69" t="s">
+      <c r="D78" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E78" s="17" t="s">
@@ -8259,9 +8334,9 @@
       </c>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="65"/>
+      <c r="B79" s="68"/>
       <c r="C79" s="62"/>
-      <c r="D79" s="69" t="s">
+      <c r="D79" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E79" s="17" t="s">
@@ -8284,9 +8359,9 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="65"/>
+      <c r="B80" s="68"/>
       <c r="C80" s="62"/>
-      <c r="D80" s="69" t="s">
+      <c r="D80" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E80" s="17" t="s">
@@ -8309,9 +8384,9 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="65"/>
+      <c r="B81" s="68"/>
       <c r="C81" s="62"/>
-      <c r="D81" s="69" t="s">
+      <c r="D81" s="47" t="s">
         <v>70</v>
       </c>
       <c r="E81" s="17" t="s">
@@ -8334,9 +8409,9 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="65"/>
+      <c r="B82" s="68"/>
       <c r="C82" s="62"/>
-      <c r="D82" s="69" t="s">
+      <c r="D82" s="47" t="s">
         <v>82</v>
       </c>
       <c r="E82" s="17" t="s">
@@ -8359,9 +8434,9 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="65"/>
+      <c r="B83" s="68"/>
       <c r="C83" s="62"/>
-      <c r="D83" s="69" t="s">
+      <c r="D83" s="47" t="s">
         <v>82</v>
       </c>
       <c r="E83" s="17" t="s">
@@ -8384,9 +8459,9 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="65"/>
+      <c r="B84" s="68"/>
       <c r="C84" s="62"/>
-      <c r="D84" s="69" t="s">
+      <c r="D84" s="47" t="s">
         <v>148</v>
       </c>
       <c r="E84" s="17" t="s">
@@ -8409,9 +8484,9 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="65"/>
+      <c r="B85" s="68"/>
       <c r="C85" s="62"/>
-      <c r="D85" s="69" t="s">
+      <c r="D85" s="47" t="s">
         <v>148</v>
       </c>
       <c r="E85" s="17" t="s">
@@ -8434,9 +8509,9 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="65"/>
+      <c r="B86" s="68"/>
       <c r="C86" s="63"/>
-      <c r="D86" s="69"/>
+      <c r="D86" s="47"/>
       <c r="E86" s="17"/>
       <c r="F86" s="7"/>
       <c r="G86" s="4"/>
@@ -8445,11 +8520,11 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="65"/>
-      <c r="C87" s="57" t="s">
+      <c r="B87" s="68"/>
+      <c r="C87" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="D87" s="69" t="s">
+      <c r="D87" s="47" t="s">
         <v>156</v>
       </c>
       <c r="E87" s="14" t="s">
@@ -8472,9 +8547,9 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="65"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="69" t="s">
+      <c r="B88" s="68"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="47" t="s">
         <v>157</v>
       </c>
       <c r="E88" s="14" t="s">
@@ -8497,9 +8572,9 @@
       </c>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="65"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="69"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="65"/>
+      <c r="D89" s="47"/>
       <c r="E89" s="14"/>
       <c r="F89" s="38"/>
       <c r="G89" s="4"/>
@@ -8508,9 +8583,9 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="65"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="69"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="65"/>
+      <c r="D90" s="47"/>
       <c r="E90" s="14"/>
       <c r="F90" s="38"/>
       <c r="G90" s="4"/>
@@ -8519,9 +8594,9 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="65"/>
-      <c r="C91" s="58"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="65"/>
+      <c r="D91" s="47"/>
       <c r="E91" s="14"/>
       <c r="F91" s="7"/>
       <c r="G91" s="4"/>
@@ -8530,9 +8605,9 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="65"/>
-      <c r="C92" s="58"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="65"/>
+      <c r="D92" s="47"/>
       <c r="E92" s="14"/>
       <c r="F92" s="7"/>
       <c r="G92" s="4"/>
@@ -8541,9 +8616,9 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="65"/>
-      <c r="C93" s="59"/>
-      <c r="D93" s="69"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="66"/>
+      <c r="D93" s="47"/>
       <c r="E93" s="14"/>
       <c r="F93" s="7"/>
       <c r="G93" s="4"/>
@@ -8552,11 +8627,11 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="65"/>
-      <c r="C94" s="61" t="s">
+      <c r="B94" s="68"/>
+      <c r="C94" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="D94" s="69" t="s">
+      <c r="D94" s="47" t="s">
         <v>163</v>
       </c>
       <c r="E94" s="14" t="s">
@@ -8579,9 +8654,9 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="65"/>
-      <c r="C95" s="50"/>
-      <c r="D95" s="69"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="47"/>
       <c r="E95" s="14"/>
       <c r="F95" s="7"/>
       <c r="G95" s="4"/>
@@ -8590,8 +8665,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="65"/>
-      <c r="C96" s="50"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="55"/>
       <c r="D96" s="7"/>
       <c r="E96" s="14"/>
       <c r="F96" s="7"/>
@@ -8601,8 +8676,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="65"/>
-      <c r="C97" s="50"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="55"/>
       <c r="D97" s="7"/>
       <c r="E97" s="14"/>
       <c r="F97" s="7"/>
@@ -8612,8 +8687,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="65"/>
-      <c r="C98" s="50"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="55"/>
       <c r="D98" s="7"/>
       <c r="E98" s="14"/>
       <c r="F98" s="7"/>
@@ -8623,8 +8698,8 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="66"/>
-      <c r="C99" s="51"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="56"/>
       <c r="D99" s="7"/>
       <c r="E99" s="14"/>
       <c r="F99" s="7"/>
@@ -8653,7 +8728,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -8668,24 +8743,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -8706,20 +8781,20 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="70"/>
+      <c r="A3" s="48"/>
       <c r="B3" s="71" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="45" t="s">
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="49" t="s">
         <v>202</v>
       </c>
       <c r="G3" s="10"/>
@@ -8728,10 +8803,10 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="70"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="67" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="45" t="s">
         <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -8746,10 +8821,10 @@
       <c r="J4" s="12"/>
     </row>
     <row r="5" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="70"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="67" t="s">
+      <c r="A5" s="48"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="45" t="s">
         <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -8764,10 +8839,10 @@
       <c r="J5" s="12"/>
     </row>
     <row r="6" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="70"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="67" t="s">
+      <c r="A6" s="48"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="45" t="s">
         <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -8782,10 +8857,10 @@
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="70"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="67" t="s">
+      <c r="A7" s="48"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="45" t="s">
         <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -8800,10 +8875,10 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="70"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="67" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="45" t="s">
         <v>197</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -8818,10 +8893,10 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="70"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="67" t="s">
+      <c r="A9" s="48"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="45" t="s">
         <v>200</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -8836,10 +8911,10 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="70"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="67" t="s">
+      <c r="A10" s="48"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="45" t="s">
         <v>199</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -8854,10 +8929,10 @@
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="70"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="67" t="s">
+      <c r="A11" s="48"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="45" t="s">
         <v>198</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -8872,10 +8947,10 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="70"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="67" t="s">
+      <c r="A12" s="48"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="45" t="s">
         <v>201</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -8890,10 +8965,10 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="70"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="67" t="s">
+      <c r="A13" s="48"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="45" t="s">
         <v>211</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -8908,10 +8983,10 @@
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="70"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67" t="s">
+      <c r="A14" s="48"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="45" t="s">
         <v>213</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -8926,10 +9001,10 @@
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="70"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="67" t="s">
+      <c r="A15" s="48"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="45" t="s">
         <v>148</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -8944,10 +9019,10 @@
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="70"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="67"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="45"/>
       <c r="E16" s="17"/>
       <c r="F16" s="38"/>
       <c r="G16" s="4"/>
@@ -8956,10 +9031,10 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="70"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="45"/>
       <c r="E17" s="17"/>
       <c r="F17" s="38"/>
       <c r="G17" s="4"/>
@@ -8968,10 +9043,12 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="70"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="67" t="s">
+      <c r="A18" s="48"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="45" t="s">
         <v>192</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -8986,10 +9063,10 @@
       <c r="J18" s="12"/>
     </row>
     <row r="19" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="70"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="67" t="s">
+      <c r="A19" s="48"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="45" t="s">
         <v>194</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -9004,10 +9081,10 @@
       <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="70"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="67" t="s">
+      <c r="A20" s="48"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="45" t="s">
         <v>195</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -9022,10 +9099,10 @@
       <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="70"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="67" t="s">
+      <c r="A21" s="48"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="45" t="s">
         <v>195</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -9040,10 +9117,10 @@
       <c r="J21" s="12"/>
     </row>
     <row r="22" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="70"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="68" t="s">
+      <c r="A22" s="48"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="46" t="s">
         <v>196</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -9058,10 +9135,10 @@
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="70"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="68" t="s">
+      <c r="A23" s="48"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="46" t="s">
         <v>197</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -9076,10 +9153,10 @@
       <c r="J23" s="12"/>
     </row>
     <row r="24" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="70"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="68" t="s">
+      <c r="A24" s="48"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="46" t="s">
         <v>200</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -9094,10 +9171,10 @@
       <c r="J24" s="12"/>
     </row>
     <row r="25" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="70"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="68" t="s">
+      <c r="A25" s="48"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="46" t="s">
         <v>199</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -9112,10 +9189,10 @@
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="70"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="68" t="s">
+      <c r="A26" s="48"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="46" t="s">
         <v>198</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -9130,10 +9207,10 @@
       <c r="J26" s="12"/>
     </row>
     <row r="27" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="70"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="68" t="s">
+      <c r="A27" s="48"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="46" t="s">
         <v>201</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -9148,10 +9225,10 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="70"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="68" t="s">
+      <c r="A28" s="48"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="46" t="s">
         <v>211</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -9166,10 +9243,10 @@
       <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="70"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="68" t="s">
+      <c r="A29" s="48"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="46" t="s">
         <v>213</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -9184,106 +9261,154 @@
       <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="70"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="38"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G30" s="4"/>
       <c r="H30" s="13"/>
       <c r="I30" s="4"/>
       <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="70"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="38"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>218</v>
+      </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
       <c r="I31" s="4"/>
       <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="70"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="38"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G32" s="4"/>
       <c r="H32" s="13"/>
       <c r="I32" s="4"/>
       <c r="J32" s="12"/>
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="70"/>
-      <c r="B33" s="65"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="38"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>219</v>
+      </c>
       <c r="G33" s="4"/>
       <c r="H33" s="13"/>
       <c r="I33" s="4"/>
       <c r="J33" s="12"/>
     </row>
     <row r="34" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="70"/>
-      <c r="B34" s="65"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="38"/>
+      <c r="A34" s="48"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G34" s="4"/>
       <c r="H34" s="13"/>
       <c r="I34" s="4"/>
       <c r="J34" s="12"/>
     </row>
     <row r="35" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="70"/>
-      <c r="B35" s="65"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="38"/>
+      <c r="A35" s="48"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>223</v>
+      </c>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
       <c r="I35" s="4"/>
       <c r="J35" s="12"/>
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="70"/>
-      <c r="B36" s="65"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="38"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
       <c r="I36" s="4"/>
       <c r="J36" s="12"/>
     </row>
     <row r="37" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="70"/>
-      <c r="B37" s="65"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="38"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>221</v>
+      </c>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
       <c r="I37" s="4"/>
       <c r="J37" s="12"/>
     </row>
     <row r="38" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="70"/>
-      <c r="B38" s="65"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="68"/>
+      <c r="A38" s="48"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="17"/>
       <c r="F38" s="38"/>
       <c r="G38" s="4"/>
@@ -9292,10 +9417,10 @@
       <c r="J38" s="12"/>
     </row>
     <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="70"/>
-      <c r="B39" s="65"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="68"/>
+      <c r="A39" s="48"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="46"/>
       <c r="E39" s="17"/>
       <c r="F39" s="38"/>
       <c r="G39" s="4"/>
@@ -9304,10 +9429,10 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="70"/>
-      <c r="B40" s="65"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="68"/>
+      <c r="A40" s="48"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="46"/>
       <c r="E40" s="17"/>
       <c r="F40" s="38"/>
       <c r="G40" s="4"/>
@@ -9316,10 +9441,10 @@
       <c r="J40" s="12"/>
     </row>
     <row r="41" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="70"/>
-      <c r="B41" s="65"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="69"/>
+      <c r="A41" s="48"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="46"/>
       <c r="E41" s="17"/>
       <c r="F41" s="38"/>
       <c r="G41" s="4"/>
@@ -9328,10 +9453,10 @@
       <c r="J41" s="12"/>
     </row>
     <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="70"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="69"/>
+      <c r="A42" s="48"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="46"/>
       <c r="E42" s="17"/>
       <c r="F42" s="38"/>
       <c r="G42" s="4"/>
@@ -9340,10 +9465,10 @@
       <c r="J42" s="12"/>
     </row>
     <row r="43" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="70"/>
-      <c r="B43" s="65"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="69"/>
+      <c r="A43" s="48"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="46"/>
       <c r="E43" s="17"/>
       <c r="F43" s="38"/>
       <c r="G43" s="4"/>
@@ -9352,10 +9477,10 @@
       <c r="J43" s="12"/>
     </row>
     <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="70"/>
-      <c r="B44" s="65"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="69"/>
+      <c r="A44" s="48"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="46"/>
       <c r="E44" s="17"/>
       <c r="F44" s="38"/>
       <c r="G44" s="4"/>
@@ -9364,10 +9489,10 @@
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="70"/>
-      <c r="B45" s="65"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="69"/>
+      <c r="A45" s="48"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="46"/>
       <c r="E45" s="17"/>
       <c r="F45" s="38"/>
       <c r="G45" s="4"/>
@@ -9376,10 +9501,10 @@
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="70"/>
-      <c r="B46" s="65"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="69"/>
+      <c r="A46" s="48"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="46"/>
       <c r="E46" s="17"/>
       <c r="F46" s="38"/>
       <c r="G46" s="4"/>
@@ -9388,10 +9513,10 @@
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="70"/>
-      <c r="B47" s="65"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="69"/>
+      <c r="A47" s="48"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="46"/>
       <c r="E47" s="17"/>
       <c r="F47" s="38"/>
       <c r="G47" s="4"/>
@@ -9400,22 +9525,28 @@
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="70"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="38"/>
+      <c r="A48" s="48"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>160</v>
+      </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
       <c r="I48" s="4"/>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="70"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="69"/>
+      <c r="A49" s="48"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="47"/>
       <c r="E49" s="17"/>
       <c r="F49" s="38"/>
       <c r="G49" s="4"/>
@@ -9424,10 +9555,10 @@
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="70"/>
-      <c r="B50" s="65"/>
-      <c r="C50" s="72"/>
-      <c r="D50" s="69"/>
+      <c r="A50" s="48"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="47"/>
       <c r="E50" s="17"/>
       <c r="F50" s="38"/>
       <c r="G50" s="4"/>
@@ -9436,10 +9567,12 @@
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="70"/>
-      <c r="B51" s="65"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="69"/>
+      <c r="A51" s="48"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" s="47"/>
       <c r="E51" s="17"/>
       <c r="F51" s="38"/>
       <c r="G51" s="4"/>
@@ -9448,11 +9581,11 @@
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="70"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="72"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="14"/>
+      <c r="A52" s="48"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="38"/>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -9460,684 +9593,110 @@
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="70"/>
-      <c r="B53" s="65"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="69"/>
-      <c r="E53" s="17"/>
+      <c r="A53" s="48"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="68"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="14"/>
       <c r="F53" s="38"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="13"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="12"/>
+      <c r="J53" s="4"/>
     </row>
     <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="70"/>
-      <c r="B54" s="65"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="69"/>
-      <c r="E54" s="38"/>
+      <c r="A54" s="48"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="14"/>
       <c r="F54" s="38"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="13"/>
+      <c r="H54" s="5"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="12"/>
+      <c r="J54" s="4"/>
     </row>
     <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="70"/>
-      <c r="B55" s="65"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="69"/>
-      <c r="E55" s="38"/>
+      <c r="A55" s="48"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="38"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="13"/>
+      <c r="H55" s="44"/>
       <c r="I55" s="4"/>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="70"/>
-      <c r="B56" s="65"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="69"/>
-      <c r="E56" s="38"/>
+      <c r="A56" s="48"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="14"/>
       <c r="F56" s="38"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="13"/>
+      <c r="H56" s="5"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="12"/>
+      <c r="J56" s="4"/>
     </row>
     <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="70"/>
-      <c r="B57" s="65"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="38"/>
+      <c r="A57" s="48"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="14"/>
       <c r="F57" s="38"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="13"/>
+      <c r="H57" s="5"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="12"/>
+      <c r="J57" s="4"/>
     </row>
     <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="70"/>
-      <c r="B58" s="65"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="17"/>
+      <c r="A58" s="48"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="14"/>
       <c r="F58" s="38"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="13"/>
+      <c r="H58" s="5"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="12"/>
+      <c r="J58" s="4"/>
     </row>
     <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="70"/>
-      <c r="B59" s="65"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="69"/>
-      <c r="E59" s="17"/>
+      <c r="A59" s="48"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="68"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="14"/>
       <c r="F59" s="38"/>
       <c r="G59" s="4"/>
-      <c r="H59" s="13"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="12"/>
+      <c r="J59" s="4"/>
     </row>
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="70"/>
-      <c r="B60" s="65"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="17"/>
+      <c r="A60" s="48"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="69"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="14"/>
       <c r="F60" s="38"/>
       <c r="G60" s="4"/>
-      <c r="H60" s="13"/>
+      <c r="H60" s="5"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="12"/>
-    </row>
-    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="70"/>
-      <c r="B61" s="65"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="12"/>
-    </row>
-    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="70"/>
-      <c r="B62" s="65"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="12"/>
-    </row>
-    <row r="63" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="70"/>
-      <c r="B63" s="65"/>
-      <c r="C63" s="72"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="12"/>
-    </row>
-    <row r="64" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="70"/>
-      <c r="B64" s="65"/>
-      <c r="C64" s="72"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="12"/>
-    </row>
-    <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="70"/>
-      <c r="B65" s="65"/>
-      <c r="C65" s="72"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="12"/>
-    </row>
-    <row r="66" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="70"/>
-      <c r="B66" s="65"/>
-      <c r="C66" s="72"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="12"/>
-    </row>
-    <row r="67" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="70"/>
-      <c r="B67" s="65"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="69"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="12"/>
-    </row>
-    <row r="68" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="70"/>
-      <c r="B68" s="65"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="69"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="12"/>
-    </row>
-    <row r="69" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="70"/>
-      <c r="B69" s="65"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="38"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="12"/>
-    </row>
-    <row r="70" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="70"/>
-      <c r="B70" s="65"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="69"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="12"/>
-    </row>
-    <row r="71" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="70"/>
-      <c r="B71" s="65"/>
-      <c r="C71" s="72"/>
-      <c r="D71" s="69"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="12"/>
-    </row>
-    <row r="72" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="70"/>
-      <c r="B72" s="65"/>
-      <c r="C72" s="72"/>
-      <c r="D72" s="69"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="40"/>
-      <c r="J72" s="12"/>
-    </row>
-    <row r="73" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="70"/>
-      <c r="B73" s="65"/>
-      <c r="C73" s="72"/>
-      <c r="D73" s="69"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="12"/>
-    </row>
-    <row r="74" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="70"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="72"/>
-      <c r="D74" s="69"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="12"/>
-    </row>
-    <row r="75" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="70"/>
-      <c r="B75" s="65"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="69"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="40"/>
-      <c r="J75" s="12"/>
-    </row>
-    <row r="76" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="70"/>
-      <c r="B76" s="65"/>
-      <c r="C76" s="72"/>
-      <c r="D76" s="69"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="12"/>
-    </row>
-    <row r="77" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="70"/>
-      <c r="B77" s="65"/>
-      <c r="C77" s="72"/>
-      <c r="D77" s="69"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="12"/>
-    </row>
-    <row r="78" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="70"/>
-      <c r="B78" s="65"/>
-      <c r="C78" s="72"/>
-      <c r="D78" s="69"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="12"/>
-    </row>
-    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="70"/>
-      <c r="B79" s="65"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="69"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="12"/>
-    </row>
-    <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="70"/>
-      <c r="B80" s="65"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="69"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="12"/>
-    </row>
-    <row r="81" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="70"/>
-      <c r="B81" s="65"/>
-      <c r="C81" s="72"/>
-      <c r="D81" s="69"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="12"/>
-    </row>
-    <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="70"/>
-      <c r="B82" s="65"/>
-      <c r="C82" s="72"/>
-      <c r="D82" s="69"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="12"/>
-    </row>
-    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="70"/>
-      <c r="B83" s="65"/>
-      <c r="C83" s="72"/>
-      <c r="D83" s="69"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="12"/>
-    </row>
-    <row r="84" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="70"/>
-      <c r="B84" s="65"/>
-      <c r="C84" s="72"/>
-      <c r="D84" s="69"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="12"/>
-    </row>
-    <row r="85" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="70"/>
-      <c r="B85" s="65"/>
-      <c r="C85" s="72"/>
-      <c r="D85" s="69"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="12"/>
-    </row>
-    <row r="86" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="70"/>
-      <c r="B86" s="65"/>
-      <c r="C86" s="72"/>
-      <c r="D86" s="69"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="12"/>
-    </row>
-    <row r="87" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="70"/>
-      <c r="B87" s="65"/>
-      <c r="C87" s="72"/>
-      <c r="D87" s="69"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="12"/>
-    </row>
-    <row r="88" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="70"/>
-      <c r="B88" s="65"/>
-      <c r="C88" s="72"/>
-      <c r="D88" s="69"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="38"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="12"/>
-    </row>
-    <row r="89" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="70"/>
-      <c r="B89" s="65"/>
-      <c r="C89" s="72"/>
-      <c r="D89" s="69"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="12"/>
-    </row>
-    <row r="90" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="70"/>
-      <c r="B90" s="65"/>
-      <c r="C90" s="72"/>
-      <c r="D90" s="69"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="38"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="12"/>
-    </row>
-    <row r="91" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="70"/>
-      <c r="B91" s="65"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="69"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="38"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="12"/>
-    </row>
-    <row r="92" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="70"/>
-      <c r="B92" s="65"/>
-      <c r="C92" s="72"/>
-      <c r="D92" s="69"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="38"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="12"/>
-    </row>
-    <row r="93" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="70"/>
-      <c r="B93" s="65"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="69"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="12"/>
-    </row>
-    <row r="94" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="70"/>
-      <c r="B94" s="65"/>
-      <c r="C94" s="72"/>
-      <c r="D94" s="69"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="12"/>
-    </row>
-    <row r="95" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="70"/>
-      <c r="B95" s="65"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="69"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="38"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="70"/>
-      <c r="B96" s="65"/>
-      <c r="C96" s="74"/>
-      <c r="D96" s="69"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="44"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="12"/>
-    </row>
-    <row r="97" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="70"/>
-      <c r="B97" s="65"/>
-      <c r="C97" s="72"/>
-      <c r="D97" s="69"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="44"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="12"/>
-    </row>
-    <row r="98" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="70"/>
-      <c r="B98" s="65"/>
-      <c r="C98" s="72"/>
-      <c r="D98" s="69"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="70"/>
-      <c r="B99" s="65"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="69"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="70"/>
-      <c r="B100" s="65"/>
-      <c r="C100" s="72"/>
-      <c r="D100" s="69"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="38"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-    </row>
-    <row r="101" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="70"/>
-      <c r="B101" s="65"/>
-      <c r="C101" s="72"/>
-      <c r="D101" s="69"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="38"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-    </row>
-    <row r="102" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="70"/>
-      <c r="B102" s="65"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="14"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-    </row>
-    <row r="103" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="70"/>
-      <c r="B103" s="65"/>
-      <c r="C103" s="75"/>
-      <c r="D103" s="69"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="38"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="44"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="12"/>
-    </row>
-    <row r="104" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="70"/>
-      <c r="B104" s="65"/>
-      <c r="C104" s="76"/>
-      <c r="D104" s="69"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="38"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-    </row>
-    <row r="105" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="70"/>
-      <c r="B105" s="65"/>
-      <c r="C105" s="76"/>
-      <c r="D105" s="69"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="38"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-    </row>
-    <row r="106" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="70"/>
-      <c r="B106" s="65"/>
-      <c r="C106" s="76"/>
-      <c r="D106" s="69"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="38"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-    </row>
-    <row r="107" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="70"/>
-      <c r="B107" s="65"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="69"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="38"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="5"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-    </row>
-    <row r="108" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="70"/>
-      <c r="B108" s="66"/>
-      <c r="C108" s="77"/>
-      <c r="D108" s="69"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="38"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="5"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-    </row>
-    <row r="109" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B108"/>
+    <mergeCell ref="B3:B60"/>
     <mergeCell ref="C3:C17"/>
+    <mergeCell ref="C18:C50"/>
+    <mergeCell ref="C51:C60"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10165,24 +9724,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="39" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="61" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
     </row>
     <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10203,10 +9762,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="50" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -10224,8 +9783,8 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="50"/>
-      <c r="C4" s="45"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="8" t="s">
         <v>20</v>
       </c>
@@ -10241,8 +9800,8 @@
       <c r="J4" s="12"/>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="50"/>
-      <c r="C5" s="45"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
@@ -10258,8 +9817,8 @@
       <c r="J5" s="12"/>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="50"/>
-      <c r="C6" s="45"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="8" t="s">
         <v>20</v>
       </c>
@@ -10275,8 +9834,8 @@
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="50"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
@@ -10292,8 +9851,8 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="50"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
@@ -10309,8 +9868,8 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="50"/>
-      <c r="C9" s="45"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
@@ -10326,8 +9885,8 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="50"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="8" t="s">
         <v>20</v>
       </c>
@@ -10343,8 +9902,8 @@
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="50"/>
-      <c r="C11" s="45"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
@@ -10360,8 +9919,8 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="50"/>
-      <c r="C12" s="45"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
@@ -10377,8 +9936,8 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="50"/>
-      <c r="C13" s="45"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
@@ -10394,8 +9953,8 @@
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="50"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="6" t="s">
         <v>21</v>
       </c>
@@ -10411,8 +9970,8 @@
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="50"/>
-      <c r="C15" s="45"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
@@ -10428,8 +9987,8 @@
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="50"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -10445,8 +10004,8 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="50"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="6" t="s">
         <v>21</v>
       </c>
@@ -10462,8 +10021,8 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="50"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
@@ -10479,8 +10038,8 @@
       <c r="J18" s="12"/>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="50"/>
-      <c r="C19" s="45"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="6" t="s">
         <v>22</v>
       </c>
@@ -10496,8 +10055,8 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="50"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="6" t="s">
         <v>22</v>
       </c>
@@ -10513,8 +10072,8 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="50"/>
-      <c r="C21" s="45"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
@@ -10530,8 +10089,8 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="50"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
@@ -10547,8 +10106,8 @@
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="50"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
@@ -10564,8 +10123,8 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="50"/>
-      <c r="C24" s="45"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="6" t="s">
         <v>22</v>
       </c>
@@ -10581,8 +10140,8 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="50"/>
-      <c r="C25" s="45"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="6" t="s">
         <v>23</v>
       </c>
@@ -10598,8 +10157,8 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="50"/>
-      <c r="C26" s="45"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="6" t="s">
         <v>23</v>
       </c>
@@ -10615,8 +10174,8 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="50"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="6" t="s">
         <v>23</v>
       </c>
@@ -10632,8 +10191,8 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="50"/>
-      <c r="C28" s="45"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="6" t="s">
         <v>23</v>
       </c>
@@ -10649,8 +10208,8 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="50"/>
-      <c r="C29" s="45"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="6" t="s">
         <v>23</v>
       </c>
@@ -10666,8 +10225,8 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="50"/>
-      <c r="C30" s="45"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="6" t="s">
         <v>23</v>
       </c>
@@ -10683,8 +10242,8 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="50"/>
-      <c r="C31" s="45"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="6" t="s">
         <v>23</v>
       </c>
@@ -10700,8 +10259,8 @@
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="50"/>
-      <c r="C32" s="45"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="50"/>
       <c r="D32" s="7" t="s">
         <v>24</v>
       </c>
@@ -10717,8 +10276,8 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="50"/>
-      <c r="C33" s="45"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="7" t="s">
         <v>24</v>
       </c>
@@ -10734,8 +10293,8 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="50"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="50"/>
       <c r="D34" s="7" t="s">
         <v>24</v>
       </c>
@@ -10751,8 +10310,8 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="50"/>
-      <c r="C35" s="45"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="50"/>
       <c r="D35" s="7" t="s">
         <v>24</v>
       </c>
@@ -10768,8 +10327,8 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="50"/>
-      <c r="C36" s="45"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="7" t="s">
         <v>24</v>
       </c>
@@ -10785,8 +10344,8 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="50"/>
-      <c r="C37" s="45"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="50"/>
       <c r="D37" s="7" t="s">
         <v>24</v>
       </c>
@@ -10802,8 +10361,8 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="50"/>
-      <c r="C38" s="45"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="50"/>
       <c r="D38" s="7" t="s">
         <v>24</v>
       </c>
@@ -10821,8 +10380,8 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="50"/>
-      <c r="C39" s="45"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="50"/>
       <c r="D39" s="7" t="s">
         <v>24</v>
       </c>
@@ -10838,8 +10397,8 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="50"/>
-      <c r="C40" s="45"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="50"/>
       <c r="D40" s="7" t="s">
         <v>24</v>
       </c>
@@ -10857,8 +10416,8 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="50"/>
-      <c r="C41" s="45"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="50"/>
       <c r="D41" s="7" t="s">
         <v>24</v>
       </c>
@@ -10874,8 +10433,8 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="50"/>
-      <c r="C42" s="45"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="50"/>
       <c r="D42" s="7" t="s">
         <v>24</v>
       </c>
@@ -10891,8 +10450,8 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="50"/>
-      <c r="C43" s="45"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="50"/>
       <c r="D43" s="7" t="s">
         <v>29</v>
       </c>
@@ -10908,8 +10467,8 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="50"/>
-      <c r="C44" s="45"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="7" t="s">
         <v>29</v>
       </c>
@@ -10925,8 +10484,8 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="50"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="7" t="s">
         <v>29</v>
       </c>
@@ -10942,8 +10501,8 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="50"/>
-      <c r="C46" s="45"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="7" t="s">
         <v>29</v>
       </c>
@@ -10959,8 +10518,8 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="50"/>
-      <c r="C47" s="45"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="50"/>
       <c r="D47" s="7" t="s">
         <v>29</v>
       </c>
@@ -10976,8 +10535,8 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="50"/>
-      <c r="C48" s="45"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="7" t="s">
         <v>29</v>
       </c>
@@ -10993,8 +10552,8 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="50"/>
-      <c r="C49" s="45"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="7" t="s">
         <v>29</v>
       </c>
@@ -11010,8 +10569,8 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="50"/>
-      <c r="C50" s="45"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="7" t="s">
         <v>29</v>
       </c>
@@ -11027,8 +10586,8 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="50"/>
-      <c r="C51" s="45"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="7" t="s">
         <v>29</v>
       </c>
@@ -11044,8 +10603,8 @@
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="50"/>
-      <c r="C52" s="45"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="7" t="s">
         <v>45</v>
       </c>
@@ -11061,8 +10620,8 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="50"/>
-      <c r="C53" s="45"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="7" t="s">
         <v>45</v>
       </c>
@@ -11078,8 +10637,8 @@
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="50"/>
-      <c r="C54" s="45"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="50"/>
       <c r="D54" s="7" t="s">
         <v>45</v>
       </c>
@@ -11095,8 +10654,8 @@
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="50"/>
-      <c r="C55" s="45"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="50"/>
       <c r="D55" s="7" t="s">
         <v>54</v>
       </c>
@@ -11112,8 +10671,8 @@
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="50"/>
-      <c r="C56" s="45"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="50"/>
       <c r="D56" s="7" t="s">
         <v>54</v>
       </c>
@@ -11129,8 +10688,8 @@
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="50"/>
-      <c r="C57" s="45"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="50"/>
       <c r="D57" s="7" t="s">
         <v>54</v>
       </c>
@@ -11146,8 +10705,8 @@
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="50"/>
-      <c r="C58" s="45"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="50"/>
       <c r="D58" s="7" t="s">
         <v>54</v>
       </c>
@@ -11163,8 +10722,8 @@
       <c r="J58" s="4"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="50"/>
-      <c r="C59" s="45"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="50"/>
       <c r="D59" s="7" t="s">
         <v>54</v>
       </c>
@@ -11180,8 +10739,8 @@
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="50"/>
-      <c r="C60" s="45"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="50"/>
       <c r="D60" s="7" t="s">
         <v>54</v>
       </c>
@@ -11197,8 +10756,8 @@
       <c r="J60" s="4"/>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="50"/>
-      <c r="C61" s="45"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="50"/>
       <c r="D61" s="7" t="s">
         <v>54</v>
       </c>
@@ -11214,8 +10773,8 @@
       <c r="J61" s="4"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="50"/>
-      <c r="C62" s="45"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="50"/>
       <c r="D62" s="7" t="s">
         <v>53</v>
       </c>
@@ -11231,8 +10790,8 @@
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="50"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="50"/>
       <c r="D63" s="7" t="s">
         <v>53</v>
       </c>
@@ -11248,8 +10807,8 @@
       <c r="J63" s="4"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="50"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="50"/>
       <c r="D64" s="7" t="s">
         <v>59</v>
       </c>
@@ -11265,8 +10824,8 @@
       <c r="J64" s="4"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="50"/>
-      <c r="C65" s="45"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="50"/>
       <c r="D65" s="7" t="s">
         <v>59</v>
       </c>
@@ -11284,8 +10843,8 @@
       <c r="J65" s="4"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="50"/>
-      <c r="C66" s="45"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="50"/>
       <c r="D66" s="7" t="s">
         <v>59</v>
       </c>
@@ -11301,8 +10860,8 @@
       <c r="J66" s="4"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="50"/>
-      <c r="C67" s="45"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="50"/>
       <c r="D67" s="7" t="s">
         <v>59</v>
       </c>
@@ -11320,8 +10879,8 @@
       <c r="J67" s="4"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="50"/>
-      <c r="C68" s="45"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="50"/>
       <c r="D68" s="7" t="s">
         <v>59</v>
       </c>
@@ -11339,8 +10898,8 @@
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="50"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="50"/>
       <c r="D69" s="7" t="s">
         <v>59</v>
       </c>
@@ -11358,8 +10917,8 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="50"/>
-      <c r="C70" s="45"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="50"/>
       <c r="D70" s="7" t="s">
         <v>59</v>
       </c>
@@ -11377,8 +10936,8 @@
       <c r="J70" s="4"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="50"/>
-      <c r="C71" s="45"/>
+      <c r="B71" s="55"/>
+      <c r="C71" s="50"/>
       <c r="D71" s="7" t="s">
         <v>59</v>
       </c>
@@ -11394,8 +10953,8 @@
       <c r="J71" s="4"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="50"/>
-      <c r="C72" s="45"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="50"/>
       <c r="D72" s="7" t="s">
         <v>59</v>
       </c>
@@ -11411,8 +10970,8 @@
       <c r="J72" s="4"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="50"/>
-      <c r="C73" s="45"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="50"/>
       <c r="D73" s="7" t="s">
         <v>70</v>
       </c>
@@ -11428,8 +10987,8 @@
       <c r="J73" s="4"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="50"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="50"/>
       <c r="D74" s="7" t="s">
         <v>70</v>
       </c>
@@ -11445,8 +11004,8 @@
       <c r="J74" s="4"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="50"/>
-      <c r="C75" s="45"/>
+      <c r="B75" s="55"/>
+      <c r="C75" s="50"/>
       <c r="D75" s="7" t="s">
         <v>70</v>
       </c>
@@ -11464,8 +11023,8 @@
       <c r="J75" s="4"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="50"/>
-      <c r="C76" s="45"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="50"/>
       <c r="D76" s="7" t="s">
         <v>70</v>
       </c>
@@ -11481,8 +11040,8 @@
       <c r="J76" s="4"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="50"/>
-      <c r="C77" s="45"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="50"/>
       <c r="D77" s="7" t="s">
         <v>70</v>
       </c>
@@ -11498,8 +11057,8 @@
       <c r="J77" s="4"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="50"/>
-      <c r="C78" s="45"/>
+      <c r="B78" s="55"/>
+      <c r="C78" s="50"/>
       <c r="D78" s="7" t="s">
         <v>70</v>
       </c>
@@ -11515,8 +11074,8 @@
       <c r="J78" s="4"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="50"/>
-      <c r="C79" s="45"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="50"/>
       <c r="D79" s="7" t="s">
         <v>70</v>
       </c>
@@ -11532,8 +11091,8 @@
       <c r="J79" s="4"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="50"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="7" t="s">
         <v>70</v>
       </c>
@@ -11549,8 +11108,8 @@
       <c r="J80" s="4"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="50"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="50"/>
       <c r="D81" s="7" t="s">
         <v>70</v>
       </c>
@@ -11566,8 +11125,8 @@
       <c r="J81" s="4"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="50"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="50"/>
       <c r="D82" s="7" t="s">
         <v>82</v>
       </c>
@@ -11583,8 +11142,8 @@
       <c r="J82" s="4"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="50"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="50"/>
       <c r="D83" s="7" t="s">
         <v>82</v>
       </c>
@@ -11600,8 +11159,8 @@
       <c r="J83" s="4"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="50"/>
-      <c r="C84" s="45"/>
+      <c r="B84" s="55"/>
+      <c r="C84" s="50"/>
       <c r="D84" s="7" t="s">
         <v>148</v>
       </c>
@@ -11617,8 +11176,8 @@
       <c r="J84" s="4"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="50"/>
-      <c r="C85" s="45"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="50"/>
       <c r="D85" s="7" t="s">
         <v>148</v>
       </c>
@@ -11634,8 +11193,8 @@
       <c r="J85" s="4"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="50"/>
-      <c r="C86" s="46"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="51"/>
       <c r="D86" s="7"/>
       <c r="E86" s="17"/>
       <c r="F86" s="7"/>
@@ -11645,8 +11204,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="50"/>
-      <c r="C87" s="57" t="s">
+      <c r="B87" s="55"/>
+      <c r="C87" s="64" t="s">
         <v>153</v>
       </c>
       <c r="D87" s="7" t="s">
@@ -11664,8 +11223,8 @@
       <c r="J87" s="4"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="50"/>
-      <c r="C88" s="58"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="65"/>
       <c r="D88" s="7" t="s">
         <v>157</v>
       </c>
@@ -11681,8 +11240,8 @@
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="50"/>
-      <c r="C89" s="58"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="65"/>
       <c r="D89" s="7"/>
       <c r="E89" s="14"/>
       <c r="F89" s="38"/>
@@ -11692,8 +11251,8 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="50"/>
-      <c r="C90" s="58"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="65"/>
       <c r="D90" s="7"/>
       <c r="E90" s="14"/>
       <c r="F90" s="38"/>
@@ -11703,8 +11262,8 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="50"/>
-      <c r="C91" s="58"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="65"/>
       <c r="D91" s="7"/>
       <c r="E91" s="14"/>
       <c r="F91" s="7"/>
@@ -11714,8 +11273,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="50"/>
-      <c r="C92" s="58"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="65"/>
       <c r="D92" s="7"/>
       <c r="E92" s="14"/>
       <c r="F92" s="7"/>
@@ -11725,8 +11284,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="50"/>
-      <c r="C93" s="59"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="66"/>
       <c r="D93" s="7"/>
       <c r="E93" s="14"/>
       <c r="F93" s="7"/>
@@ -11736,8 +11295,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="50"/>
-      <c r="C94" s="61" t="s">
+      <c r="B94" s="55"/>
+      <c r="C94" s="70" t="s">
         <v>162</v>
       </c>
       <c r="D94" s="7" t="s">
@@ -11755,8 +11314,8 @@
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="50"/>
-      <c r="C95" s="50"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="55"/>
       <c r="D95" s="7"/>
       <c r="E95" s="14"/>
       <c r="F95" s="7"/>
@@ -11766,8 +11325,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="50"/>
-      <c r="C96" s="50"/>
+      <c r="B96" s="55"/>
+      <c r="C96" s="55"/>
       <c r="D96" s="7"/>
       <c r="E96" s="14"/>
       <c r="F96" s="7"/>
@@ -11777,8 +11336,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="50"/>
-      <c r="C97" s="50"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
       <c r="D97" s="7"/>
       <c r="E97" s="14"/>
       <c r="F97" s="7"/>
@@ -11788,8 +11347,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="50"/>
-      <c r="C98" s="50"/>
+      <c r="B98" s="55"/>
+      <c r="C98" s="55"/>
       <c r="D98" s="7"/>
       <c r="E98" s="14"/>
       <c r="F98" s="7"/>
@@ -11799,8 +11358,8 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="56"/>
       <c r="D99" s="7"/>
       <c r="E99" s="14"/>
       <c r="F99" s="7"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CE9D89-1CDA-49CB-9FC2-0E53E09657CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA7F40F-90A6-445F-9792-A010C16F36E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="232">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2937,6 +2937,86 @@
   </si>
   <si>
     <t>データベース「family_name_kana」カラムへ内容が登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「mail」カラムへ内容が登録されている</t>
+    <rPh sb="16" eb="18">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「password」カラムへ内容が登録されている</t>
+    <rPh sb="20" eb="22">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムへ内容が登録されている</t>
+    <rPh sb="18" eb="20">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「postal_code」カラムへ内容が登録されている</t>
+    <rPh sb="23" eb="25">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「prefecture」カラムへ内容が登録されている</t>
+    <rPh sb="22" eb="24">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「address_1」カラムへ内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「address_2」カラムへ内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムへ内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8728,7 +8808,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9408,9 +9488,15 @@
       <c r="A38" s="48"/>
       <c r="B38" s="68"/>
       <c r="C38" s="68"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="38"/>
+      <c r="D38" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
       <c r="I38" s="4"/>
@@ -9420,9 +9506,15 @@
       <c r="A39" s="48"/>
       <c r="B39" s="68"/>
       <c r="C39" s="68"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="38"/>
+      <c r="D39" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>224</v>
+      </c>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
       <c r="I39" s="4"/>
@@ -9432,9 +9524,15 @@
       <c r="A40" s="48"/>
       <c r="B40" s="68"/>
       <c r="C40" s="68"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="38"/>
+      <c r="D40" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G40" s="4"/>
       <c r="H40" s="13"/>
       <c r="I40" s="4"/>
@@ -9444,9 +9542,15 @@
       <c r="A41" s="48"/>
       <c r="B41" s="68"/>
       <c r="C41" s="68"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="38"/>
+      <c r="D41" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>225</v>
+      </c>
       <c r="G41" s="4"/>
       <c r="H41" s="13"/>
       <c r="I41" s="4"/>
@@ -9456,9 +9560,15 @@
       <c r="A42" s="48"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="38"/>
+      <c r="D42" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G42" s="4"/>
       <c r="H42" s="13"/>
       <c r="I42" s="4"/>
@@ -9468,9 +9578,15 @@
       <c r="A43" s="48"/>
       <c r="B43" s="68"/>
       <c r="C43" s="68"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="38"/>
+      <c r="D43" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>226</v>
+      </c>
       <c r="G43" s="4"/>
       <c r="H43" s="13"/>
       <c r="I43" s="4"/>
@@ -9480,9 +9596,15 @@
       <c r="A44" s="48"/>
       <c r="B44" s="68"/>
       <c r="C44" s="68"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="38"/>
+      <c r="D44" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G44" s="4"/>
       <c r="H44" s="13"/>
       <c r="I44" s="4"/>
@@ -9492,9 +9614,15 @@
       <c r="A45" s="48"/>
       <c r="B45" s="68"/>
       <c r="C45" s="68"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="38"/>
+      <c r="D45" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>227</v>
+      </c>
       <c r="G45" s="4"/>
       <c r="H45" s="13"/>
       <c r="I45" s="4"/>
@@ -9504,9 +9632,15 @@
       <c r="A46" s="48"/>
       <c r="B46" s="68"/>
       <c r="C46" s="68"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="38"/>
+      <c r="D46" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G46" s="4"/>
       <c r="H46" s="13"/>
       <c r="I46" s="4"/>
@@ -9516,9 +9650,15 @@
       <c r="A47" s="48"/>
       <c r="B47" s="68"/>
       <c r="C47" s="68"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="38"/>
+      <c r="D47" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>228</v>
+      </c>
       <c r="G47" s="4"/>
       <c r="H47" s="13"/>
       <c r="I47" s="4"/>
@@ -9529,13 +9669,13 @@
       <c r="B48" s="68"/>
       <c r="C48" s="68"/>
       <c r="D48" s="46" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -9546,9 +9686,15 @@
       <c r="A49" s="48"/>
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="38"/>
+      <c r="D49" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>229</v>
+      </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
       <c r="I49" s="4"/>
@@ -9557,10 +9703,16 @@
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="48"/>
       <c r="B50" s="68"/>
-      <c r="C50" s="69"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="38"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
       <c r="I50" s="4"/>
@@ -9569,12 +9721,16 @@
     <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="48"/>
       <c r="B51" s="68"/>
-      <c r="C51" s="72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" s="47"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="38"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="G51" s="4"/>
       <c r="H51" s="13"/>
       <c r="I51" s="4"/>
@@ -9584,9 +9740,15 @@
       <c r="A52" s="48"/>
       <c r="B52" s="68"/>
       <c r="C52" s="68"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="38"/>
+      <c r="D52" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
       <c r="I52" s="4"/>
@@ -9596,35 +9758,47 @@
       <c r="A53" s="48"/>
       <c r="B53" s="68"/>
       <c r="C53" s="68"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="38"/>
+      <c r="D53" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>231</v>
+      </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="5"/>
+      <c r="H53" s="13"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
+      <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="48"/>
       <c r="B54" s="68"/>
       <c r="C54" s="68"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="14"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="38"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="5"/>
+      <c r="H54" s="13"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="48"/>
       <c r="B55" s="68"/>
       <c r="C55" s="68"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="38"/>
+      <c r="D55" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>160</v>
+      </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="44"/>
+      <c r="H55" s="13"/>
       <c r="I55" s="4"/>
       <c r="J55" s="12"/>
     </row>
@@ -9633,53 +9807,55 @@
       <c r="B56" s="68"/>
       <c r="C56" s="68"/>
       <c r="D56" s="47"/>
-      <c r="E56" s="14"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="38"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="5"/>
+      <c r="H56" s="13"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="48"/>
       <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
+      <c r="C57" s="69"/>
       <c r="D57" s="47"/>
-      <c r="E57" s="14"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="38"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="13"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="48"/>
       <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
+      <c r="C58" s="72" t="s">
+        <v>216</v>
+      </c>
       <c r="D58" s="47"/>
-      <c r="E58" s="14"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="38"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="5"/>
+      <c r="H58" s="13"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="48"/>
       <c r="B59" s="68"/>
       <c r="C59" s="68"/>
       <c r="D59" s="47"/>
-      <c r="E59" s="14"/>
+      <c r="E59" s="17"/>
       <c r="F59" s="38"/>
       <c r="G59" s="4"/>
-      <c r="H59" s="5"/>
+      <c r="H59" s="13"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="48"/>
-      <c r="B60" s="69"/>
-      <c r="C60" s="69"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="68"/>
       <c r="D60" s="47"/>
       <c r="E60" s="14"/>
       <c r="F60" s="38"/>
@@ -9688,15 +9864,99 @@
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="48"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="48"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="48"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="48"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="48"/>
+      <c r="B65" s="68"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="48"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="48"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B60"/>
+    <mergeCell ref="B3:B67"/>
     <mergeCell ref="C3:C17"/>
-    <mergeCell ref="C18:C50"/>
-    <mergeCell ref="C51:C60"/>
+    <mergeCell ref="C18:C57"/>
+    <mergeCell ref="C58:C67"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA7F40F-90A6-445F-9792-A010C16F36E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F3932E-6A00-4118-9466-EC45DFD0299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="240">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2960,16 +2960,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「gender」カラムへ内容が登録されている</t>
-    <rPh sb="18" eb="20">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データベース「postal_code」カラムへ内容が登録されている</t>
     <rPh sb="23" eb="25">
       <t>ナイヨウ</t>
@@ -3010,11 +3000,170 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「authority」カラムへ内容が登録されている</t>
-    <rPh sb="21" eb="23">
-      <t>ナイヨウ</t>
+    <t>前画面にて「登録する」を押下</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「登録する」ボタン</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面へ遷移し、エラーがなければ「登録完了しました」表示</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面へ遷移し、登録に不備のある場合「エラーが発生したためアカウント登録できません。」と表示</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>フビ</t>
     </rPh>
     <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録に不備のある場合「エラーが発生したためアカウント登録できません。」表示</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了or登録エラー表示</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>”男”を選択した場合、データベース「gender」カラムへ”０”が登録されている</t>
+    <rPh sb="1" eb="2">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>”女”を選択した場合、データベース「gender」カラムへ”１”が登録されている</t>
+    <rPh sb="1" eb="2">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>”一般”を選択した場合、データベース「authority」カラムへ”０”が登録されている</t>
+    <rPh sb="1" eb="3">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>”管理者”を選択した場合、データベース「authority」カラムへ”１”が登録されている</t>
+    <rPh sb="1" eb="4">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
       <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -8808,7 +8957,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9585,7 +9734,7 @@
         <v>217</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="13"/>
@@ -9597,13 +9746,13 @@
       <c r="B44" s="68"/>
       <c r="C44" s="68"/>
       <c r="D44" s="46" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="13"/>
@@ -9621,7 +9770,7 @@
         <v>217</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="13"/>
@@ -9633,13 +9782,13 @@
       <c r="B46" s="68"/>
       <c r="C46" s="68"/>
       <c r="D46" s="46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="13"/>
@@ -9657,7 +9806,7 @@
         <v>217</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="13"/>
@@ -9669,13 +9818,13 @@
       <c r="B48" s="68"/>
       <c r="C48" s="68"/>
       <c r="D48" s="46" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -9693,7 +9842,7 @@
         <v>217</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
@@ -9705,13 +9854,13 @@
       <c r="B50" s="68"/>
       <c r="C50" s="68"/>
       <c r="D50" s="46" t="s">
-        <v>70</v>
+        <v>201</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
@@ -9729,7 +9878,7 @@
         <v>217</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="13"/>
@@ -9741,13 +9890,13 @@
       <c r="B52" s="68"/>
       <c r="C52" s="68"/>
       <c r="D52" s="46" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -9765,7 +9914,7 @@
         <v>217</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="13"/>
@@ -9776,9 +9925,15 @@
       <c r="A54" s="48"/>
       <c r="B54" s="68"/>
       <c r="C54" s="68"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="38"/>
+      <c r="D54" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>238</v>
+      </c>
       <c r="G54" s="4"/>
       <c r="H54" s="13"/>
       <c r="I54" s="4"/>
@@ -9789,13 +9944,13 @@
       <c r="B55" s="68"/>
       <c r="C55" s="68"/>
       <c r="D55" s="46" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="13"/>
@@ -9806,7 +9961,7 @@
       <c r="A56" s="48"/>
       <c r="B56" s="68"/>
       <c r="C56" s="68"/>
-      <c r="D56" s="47"/>
+      <c r="D56" s="46"/>
       <c r="E56" s="17"/>
       <c r="F56" s="38"/>
       <c r="G56" s="4"/>
@@ -9817,10 +9972,16 @@
     <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="48"/>
       <c r="B57" s="68"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="38"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>160</v>
+      </c>
       <c r="G57" s="4"/>
       <c r="H57" s="13"/>
       <c r="I57" s="4"/>
@@ -9829,24 +9990,34 @@
     <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="48"/>
       <c r="B58" s="68"/>
-      <c r="C58" s="72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D58" s="47"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="38"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>232</v>
+      </c>
       <c r="G58" s="4"/>
       <c r="H58" s="13"/>
       <c r="I58" s="4"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="48"/>
       <c r="B59" s="68"/>
       <c r="C59" s="68"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="38"/>
+      <c r="D59" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
       <c r="I59" s="4"/>
@@ -9855,36 +10026,50 @@
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="48"/>
       <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
+      <c r="C60" s="69"/>
       <c r="D60" s="47"/>
-      <c r="E60" s="14"/>
+      <c r="E60" s="17"/>
       <c r="F60" s="38"/>
       <c r="G60" s="4"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="13"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="48"/>
       <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="38"/>
+      <c r="C61" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="D61" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>232</v>
+      </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="13"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" ht="33" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="48"/>
       <c r="B62" s="68"/>
       <c r="C62" s="68"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="38"/>
+      <c r="D62" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="44"/>
+      <c r="H62" s="13"/>
       <c r="I62" s="4"/>
       <c r="J62" s="12"/>
     </row>
@@ -9893,70 +10078,190 @@
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
       <c r="D63" s="47"/>
-      <c r="E63" s="14"/>
+      <c r="E63" s="17"/>
       <c r="F63" s="38"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="13"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
+      <c r="J63" s="12"/>
     </row>
     <row r="64" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="48"/>
       <c r="B64" s="68"/>
       <c r="C64" s="68"/>
       <c r="D64" s="47"/>
-      <c r="E64" s="14"/>
+      <c r="E64" s="17"/>
       <c r="F64" s="38"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="13"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
+      <c r="J64" s="12"/>
     </row>
     <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="48"/>
       <c r="B65" s="68"/>
       <c r="C65" s="68"/>
       <c r="D65" s="47"/>
-      <c r="E65" s="14"/>
+      <c r="E65" s="17"/>
       <c r="F65" s="38"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="5"/>
+      <c r="H65" s="13"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
+      <c r="J65" s="12"/>
     </row>
     <row r="66" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="48"/>
       <c r="B66" s="68"/>
       <c r="C66" s="68"/>
       <c r="D66" s="47"/>
-      <c r="E66" s="14"/>
+      <c r="E66" s="17"/>
       <c r="F66" s="38"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="13"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
+      <c r="J66" s="12"/>
     </row>
     <row r="67" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="48"/>
-      <c r="B67" s="69"/>
-      <c r="C67" s="69"/>
+      <c r="B67" s="68"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="47"/>
-      <c r="E67" s="14"/>
+      <c r="E67" s="17"/>
       <c r="F67" s="38"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="5"/>
+      <c r="H67" s="13"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="48"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="68"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="48"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="48"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="48"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="48"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="68"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="48"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="68"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="48"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="68"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="48"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="68"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="48"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="48"/>
+      <c r="B77" s="69"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B67"/>
+    <mergeCell ref="B3:B77"/>
     <mergeCell ref="C3:C17"/>
-    <mergeCell ref="C18:C57"/>
-    <mergeCell ref="C58:C67"/>
+    <mergeCell ref="C18:C60"/>
+    <mergeCell ref="C61:C77"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F3932E-6A00-4118-9466-EC45DFD0299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F30A8E-4AA6-4F85-9797-61C7906D7CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="261">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -3105,6 +3105,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>データベース「authority」カラムへ”０”が登録されている</t>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>”男”を選択した場合、データベース「gender」カラムへ”０”が登録されている</t>
     <rPh sb="1" eb="2">
       <t>オトコ</t>
@@ -3165,6 +3172,613 @@
     </rPh>
     <rPh sb="38" eb="40">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本画面にてすべて入力後、「確認する」を押下</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムへ”１”が登録されている</t>
+    <rPh sb="22" eb="24">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムへ”０”が登録されている</t>
+    <rPh sb="22" eb="24">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面にて”男”を選択→
+本画面にて「登録」を押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「名前（性）欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「名前（名）欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「カナ（性）欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「カナ（名）欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「メールアドレス欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「パスワード欄」に入力した文字数分”●”が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ホンガメン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>モジスウブン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面の「性別 欄」で選択した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「郵便番号 欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「市区町村 欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>シクチョウソン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面で「番地 欄」に入力した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面に遷移し、本画面の「アカウント権限 欄」で選択した内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムへ”1”が登録されている</t>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて入力（本項目にて”男”を選択）し、「確認する」を押下→
+アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて入力（本項目にて”女”を選択）し、「確認する」を押下→
+アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて入力（本項目にて”一般”を選択）し、「確認する」を押下→
+アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて入力（本項目にて”管理者”を選択）し、「確認する」を押下→
+アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8957,7 +9571,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9009,7 +9623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="48"/>
       <c r="B3" s="71" t="s">
         <v>66</v>
@@ -9021,17 +9635,17 @@
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
     </row>
-    <row r="4" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="48"/>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
@@ -9039,17 +9653,17 @@
         <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
       <c r="I4" s="4"/>
       <c r="J4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="48"/>
       <c r="B5" s="68"/>
       <c r="C5" s="68"/>
@@ -9057,17 +9671,17 @@
         <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
       <c r="I5" s="4"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="48"/>
       <c r="B6" s="68"/>
       <c r="C6" s="68"/>
@@ -9075,17 +9689,17 @@
         <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
       <c r="I6" s="4"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48"/>
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
@@ -9093,17 +9707,17 @@
         <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
       <c r="I7" s="4"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="48"/>
       <c r="B8" s="68"/>
       <c r="C8" s="68"/>
@@ -9111,10 +9725,10 @@
         <v>197</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
@@ -9129,46 +9743,46 @@
         <v>200</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
       <c r="I9" s="4"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
       <c r="B10" s="68"/>
       <c r="C10" s="68"/>
       <c r="D10" s="45" t="s">
-        <v>199</v>
+        <v>45</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
       <c r="B11" s="68"/>
       <c r="C11" s="68"/>
       <c r="D11" s="45" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
@@ -9180,13 +9794,13 @@
       <c r="B12" s="68"/>
       <c r="C12" s="68"/>
       <c r="D12" s="45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
@@ -9198,13 +9812,13 @@
       <c r="B13" s="68"/>
       <c r="C13" s="68"/>
       <c r="D13" s="45" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
@@ -9216,13 +9830,13 @@
       <c r="B14" s="68"/>
       <c r="C14" s="68"/>
       <c r="D14" s="45" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -9234,13 +9848,13 @@
       <c r="B15" s="68"/>
       <c r="C15" s="68"/>
       <c r="D15" s="45" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
@@ -9251,40 +9865,50 @@
       <c r="A16" s="48"/>
       <c r="B16" s="68"/>
       <c r="C16" s="68"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="38"/>
+      <c r="D16" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>255</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
       <c r="I16" s="4"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
       <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="38"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>236</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="4"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
       <c r="B18" s="68"/>
-      <c r="C18" s="72" t="s">
-        <v>215</v>
-      </c>
+      <c r="C18" s="68"/>
       <c r="D18" s="45" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
@@ -9295,15 +9919,9 @@
       <c r="A19" s="48"/>
       <c r="B19" s="68"/>
       <c r="C19" s="68"/>
-      <c r="D19" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>203</v>
-      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="4"/>
       <c r="H19" s="13"/>
       <c r="I19" s="4"/>
@@ -9314,13 +9932,13 @@
       <c r="B20" s="68"/>
       <c r="C20" s="68"/>
       <c r="D20" s="45" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="13"/>
@@ -9331,15 +9949,9 @@
       <c r="A21" s="48"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68"/>
-      <c r="D21" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>204</v>
-      </c>
+      <c r="D21" s="45"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="38"/>
       <c r="G21" s="4"/>
       <c r="H21" s="13"/>
       <c r="I21" s="4"/>
@@ -9348,16 +9960,10 @@
     <row r="22" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
       <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>205</v>
-      </c>
+      <c r="C22" s="69"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="38"/>
       <c r="G22" s="4"/>
       <c r="H22" s="13"/>
       <c r="I22" s="4"/>
@@ -9366,15 +9972,17 @@
     <row r="23" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
       <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="46" t="s">
-        <v>197</v>
+      <c r="C23" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>192</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="13"/>
@@ -9385,14 +9993,14 @@
       <c r="A24" s="48"/>
       <c r="B24" s="68"/>
       <c r="C24" s="68"/>
-      <c r="D24" s="46" t="s">
-        <v>200</v>
+      <c r="D24" s="45" t="s">
+        <v>194</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="13"/>
@@ -9403,14 +10011,14 @@
       <c r="A25" s="48"/>
       <c r="B25" s="68"/>
       <c r="C25" s="68"/>
-      <c r="D25" s="46" t="s">
-        <v>199</v>
+      <c r="D25" s="45" t="s">
+        <v>195</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="13"/>
@@ -9421,14 +10029,14 @@
       <c r="A26" s="48"/>
       <c r="B26" s="68"/>
       <c r="C26" s="68"/>
-      <c r="D26" s="46" t="s">
-        <v>198</v>
+      <c r="D26" s="45" t="s">
+        <v>195</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
@@ -9440,13 +10048,13 @@
       <c r="B27" s="68"/>
       <c r="C27" s="68"/>
       <c r="D27" s="46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="13"/>
@@ -9458,13 +10066,13 @@
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
       <c r="D28" s="46" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="13"/>
@@ -9476,13 +10084,13 @@
       <c r="B29" s="68"/>
       <c r="C29" s="68"/>
       <c r="D29" s="46" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>193</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="13"/>
@@ -9494,13 +10102,13 @@
       <c r="B30" s="68"/>
       <c r="C30" s="68"/>
       <c r="D30" s="46" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="13"/>
@@ -9512,13 +10120,13 @@
       <c r="B31" s="68"/>
       <c r="C31" s="68"/>
       <c r="D31" s="46" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
@@ -9530,13 +10138,13 @@
       <c r="B32" s="68"/>
       <c r="C32" s="68"/>
       <c r="D32" s="46" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="13"/>
@@ -9548,13 +10156,13 @@
       <c r="B33" s="68"/>
       <c r="C33" s="68"/>
       <c r="D33" s="46" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="13"/>
@@ -9566,13 +10174,13 @@
       <c r="B34" s="68"/>
       <c r="C34" s="68"/>
       <c r="D34" s="46" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="13"/>
@@ -9584,13 +10192,13 @@
       <c r="B35" s="68"/>
       <c r="C35" s="68"/>
       <c r="D35" s="46" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
@@ -9602,13 +10210,13 @@
       <c r="B36" s="68"/>
       <c r="C36" s="68"/>
       <c r="D36" s="46" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
@@ -9620,13 +10228,13 @@
       <c r="B37" s="68"/>
       <c r="C37" s="68"/>
       <c r="D37" s="46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
@@ -9638,13 +10246,13 @@
       <c r="B38" s="68"/>
       <c r="C38" s="68"/>
       <c r="D38" s="46" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
@@ -9656,13 +10264,13 @@
       <c r="B39" s="68"/>
       <c r="C39" s="68"/>
       <c r="D39" s="46" t="s">
-        <v>24</v>
+        <v>222</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
@@ -9674,13 +10282,13 @@
       <c r="B40" s="68"/>
       <c r="C40" s="68"/>
       <c r="D40" s="46" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="13"/>
@@ -9692,13 +10300,13 @@
       <c r="B41" s="68"/>
       <c r="C41" s="68"/>
       <c r="D41" s="46" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="13"/>
@@ -9710,13 +10318,13 @@
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
       <c r="D42" s="46" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="13"/>
@@ -9728,13 +10336,13 @@
       <c r="B43" s="68"/>
       <c r="C43" s="68"/>
       <c r="D43" s="46" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="13"/>
@@ -9746,13 +10354,13 @@
       <c r="B44" s="68"/>
       <c r="C44" s="68"/>
       <c r="D44" s="46" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="13"/>
@@ -9764,7 +10372,7 @@
       <c r="B45" s="68"/>
       <c r="C45" s="68"/>
       <c r="D45" s="46" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>217</v>
@@ -9782,13 +10390,13 @@
       <c r="B46" s="68"/>
       <c r="C46" s="68"/>
       <c r="D46" s="46" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="13"/>
@@ -9800,7 +10408,7 @@
       <c r="B47" s="68"/>
       <c r="C47" s="68"/>
       <c r="D47" s="46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>217</v>
@@ -9818,13 +10426,13 @@
       <c r="B48" s="68"/>
       <c r="C48" s="68"/>
       <c r="D48" s="46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -9836,13 +10444,13 @@
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
       <c r="D49" s="46" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
@@ -9854,13 +10462,13 @@
       <c r="B50" s="68"/>
       <c r="C50" s="68"/>
       <c r="D50" s="46" t="s">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
@@ -9872,13 +10480,13 @@
       <c r="B51" s="68"/>
       <c r="C51" s="68"/>
       <c r="D51" s="46" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="13"/>
@@ -9890,13 +10498,13 @@
       <c r="B52" s="68"/>
       <c r="C52" s="68"/>
       <c r="D52" s="46" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -9908,13 +10516,13 @@
       <c r="B53" s="68"/>
       <c r="C53" s="68"/>
       <c r="D53" s="46" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="13"/>
@@ -9926,13 +10534,13 @@
       <c r="B54" s="68"/>
       <c r="C54" s="68"/>
       <c r="D54" s="46" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="13"/>
@@ -9944,13 +10552,13 @@
       <c r="B55" s="68"/>
       <c r="C55" s="68"/>
       <c r="D55" s="46" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="13"/>
@@ -9961,9 +10569,15 @@
       <c r="A56" s="48"/>
       <c r="B56" s="68"/>
       <c r="C56" s="68"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="38"/>
+      <c r="D56" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>220</v>
+      </c>
       <c r="G56" s="4"/>
       <c r="H56" s="13"/>
       <c r="I56" s="4"/>
@@ -9974,13 +10588,13 @@
       <c r="B57" s="68"/>
       <c r="C57" s="68"/>
       <c r="D57" s="46" t="s">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="13"/>
@@ -9992,31 +10606,31 @@
       <c r="B58" s="68"/>
       <c r="C58" s="68"/>
       <c r="D58" s="46" t="s">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="13"/>
       <c r="I58" s="4"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="48"/>
       <c r="B59" s="68"/>
       <c r="C59" s="68"/>
       <c r="D59" s="46" t="s">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
@@ -10026,10 +10640,16 @@
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="48"/>
       <c r="B60" s="68"/>
-      <c r="C60" s="69"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="38"/>
+      <c r="C60" s="68"/>
+      <c r="D60" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>240</v>
+      </c>
       <c r="G60" s="4"/>
       <c r="H60" s="13"/>
       <c r="I60" s="4"/>
@@ -10038,35 +10658,27 @@
     <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="48"/>
       <c r="B61" s="68"/>
-      <c r="C61" s="72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="F61" s="38" t="s">
-        <v>232</v>
-      </c>
+      <c r="C61" s="68"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="38"/>
       <c r="G61" s="4"/>
       <c r="H61" s="13"/>
       <c r="I61" s="4"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" ht="33" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="48"/>
       <c r="B62" s="68"/>
       <c r="C62" s="68"/>
       <c r="D62" s="46" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="F62" s="38" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="13"/>
@@ -10077,21 +10689,33 @@
       <c r="A63" s="48"/>
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
-      <c r="D63" s="47"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="38"/>
+      <c r="D63" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>232</v>
+      </c>
       <c r="G63" s="4"/>
       <c r="H63" s="13"/>
       <c r="I63" s="4"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="48"/>
       <c r="B64" s="68"/>
       <c r="C64" s="68"/>
-      <c r="D64" s="47"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="38"/>
+      <c r="D64" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="G64" s="4"/>
       <c r="H64" s="13"/>
       <c r="I64" s="4"/>
@@ -10100,7 +10724,7 @@
     <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="48"/>
       <c r="B65" s="68"/>
-      <c r="C65" s="68"/>
+      <c r="C65" s="69"/>
       <c r="D65" s="47"/>
       <c r="E65" s="17"/>
       <c r="F65" s="38"/>
@@ -10112,22 +10736,36 @@
     <row r="66" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="48"/>
       <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="38"/>
+      <c r="C66" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>232</v>
+      </c>
       <c r="G66" s="4"/>
       <c r="H66" s="13"/>
       <c r="I66" s="4"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" ht="33" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="48"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="38"/>
+      <c r="D67" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="G67" s="4"/>
       <c r="H67" s="13"/>
       <c r="I67" s="4"/>
@@ -10162,34 +10800,34 @@
       <c r="B70" s="68"/>
       <c r="C70" s="68"/>
       <c r="D70" s="47"/>
-      <c r="E70" s="14"/>
+      <c r="E70" s="17"/>
       <c r="F70" s="38"/>
       <c r="G70" s="4"/>
-      <c r="H70" s="5"/>
+      <c r="H70" s="13"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
+      <c r="J70" s="12"/>
     </row>
     <row r="71" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="48"/>
       <c r="B71" s="68"/>
       <c r="C71" s="68"/>
       <c r="D71" s="47"/>
-      <c r="E71" s="14"/>
+      <c r="E71" s="17"/>
       <c r="F71" s="38"/>
       <c r="G71" s="4"/>
-      <c r="H71" s="5"/>
+      <c r="H71" s="13"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="12"/>
     </row>
     <row r="72" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="48"/>
       <c r="B72" s="68"/>
       <c r="C72" s="68"/>
       <c r="D72" s="47"/>
-      <c r="E72" s="14"/>
+      <c r="E72" s="17"/>
       <c r="F72" s="38"/>
       <c r="G72" s="4"/>
-      <c r="H72" s="44"/>
+      <c r="H72" s="13"/>
       <c r="I72" s="4"/>
       <c r="J72" s="12"/>
     </row>
@@ -10198,24 +10836,24 @@
       <c r="B73" s="68"/>
       <c r="C73" s="68"/>
       <c r="D73" s="47"/>
-      <c r="E73" s="14"/>
+      <c r="E73" s="17"/>
       <c r="F73" s="38"/>
       <c r="G73" s="4"/>
-      <c r="H73" s="5"/>
+      <c r="H73" s="13"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
+      <c r="J73" s="12"/>
     </row>
     <row r="74" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="48"/>
       <c r="B74" s="68"/>
       <c r="C74" s="68"/>
       <c r="D74" s="47"/>
-      <c r="E74" s="14"/>
+      <c r="E74" s="17"/>
       <c r="F74" s="38"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="5"/>
+      <c r="H74" s="13"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
+      <c r="J74" s="12"/>
     </row>
     <row r="75" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="48"/>
@@ -10243,25 +10881,85 @@
     </row>
     <row r="77" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="48"/>
-      <c r="B77" s="69"/>
-      <c r="C77" s="69"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="68"/>
       <c r="D77" s="47"/>
       <c r="E77" s="14"/>
       <c r="F77" s="38"/>
       <c r="G77" s="4"/>
-      <c r="H77" s="5"/>
+      <c r="H77" s="44"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="J77" s="12"/>
+    </row>
+    <row r="78" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="48"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="68"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="48"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="47"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="48"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="47"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="48"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="68"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="48"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B77"/>
-    <mergeCell ref="C3:C17"/>
-    <mergeCell ref="C18:C60"/>
-    <mergeCell ref="C61:C77"/>
+    <mergeCell ref="B3:B82"/>
+    <mergeCell ref="C3:C22"/>
+    <mergeCell ref="C23:C65"/>
+    <mergeCell ref="C66:C82"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F30A8E-4AA6-4F85-9797-61C7906D7CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74ED28D1-9B32-4D00-9E8E-A64310104801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="275">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -3000,22 +3000,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>前画面にて「登録する」を押下</t>
-    <rPh sb="0" eb="1">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「登録する」ボタン</t>
     <rPh sb="1" eb="3">
       <t>トウロク</t>
@@ -3779,6 +3763,156 @@
     </rPh>
     <rPh sb="53" eb="55">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面にて「登録する」を押下後、本画面にて「登録完了しました」と表示あり</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ホンガメン</t>
+    </rPh>
+    <rPh sb="30" eb="34">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「family_name」カラムへ入力した内容が登録されている</t>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「last_name」カラムへ入力した内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「family_name_kana」カラムへ入力した内容が登録されている</t>
+    <rPh sb="28" eb="30">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「last_name_kana」カラムへ入力した内容が登録されている</t>
+    <rPh sb="26" eb="28">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「mail」カラムへ入力した内容が登録されている</t>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「password」カラムへ入力した内容が登録されている</t>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムへ"男"を選択したならば”０”、”女”を選択したならば”１”が登録されている</t>
+    <rPh sb="19" eb="20">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「postal_code」カラムへ入力した内容が登録されている</t>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「prefecture」カラムへ入力した内容が登録されている</t>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「address_1」カラムへ入力した内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「address_２」カラムへ入力した内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムへ入力した内容が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9571,7 +9705,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9635,10 +9769,10 @@
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
@@ -9653,10 +9787,10 @@
         <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
@@ -9671,10 +9805,10 @@
         <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
@@ -9689,10 +9823,10 @@
         <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
@@ -9707,10 +9841,10 @@
         <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
@@ -9725,10 +9859,10 @@
         <v>197</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
@@ -9743,10 +9877,10 @@
         <v>200</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
@@ -9761,10 +9895,10 @@
         <v>45</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
@@ -9779,10 +9913,10 @@
         <v>45</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
@@ -9797,10 +9931,10 @@
         <v>199</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
@@ -9815,7 +9949,7 @@
         <v>198</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>209</v>
@@ -9833,10 +9967,10 @@
         <v>201</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -9851,10 +9985,10 @@
         <v>211</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
@@ -9869,10 +10003,10 @@
         <v>213</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
@@ -9887,10 +10021,10 @@
         <v>82</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
@@ -9905,10 +10039,10 @@
         <v>82</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
@@ -10429,10 +10563,10 @@
         <v>45</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -10450,7 +10584,7 @@
         <v>217</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
@@ -10630,7 +10764,7 @@
         <v>217</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
@@ -10648,7 +10782,7 @@
         <v>217</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="13"/>
@@ -10690,13 +10824,13 @@
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
       <c r="D63" s="46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="13"/>
@@ -10708,13 +10842,13 @@
       <c r="B64" s="68"/>
       <c r="C64" s="68"/>
       <c r="D64" s="46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="13"/>
@@ -10740,176 +10874,248 @@
         <v>216</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="13"/>
       <c r="I66" s="4"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" ht="33" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="48"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
       <c r="D67" s="46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="13"/>
       <c r="I67" s="4"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="48"/>
       <c r="B68" s="68"/>
       <c r="C68" s="68"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="38"/>
+      <c r="D68" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>263</v>
+      </c>
       <c r="G68" s="4"/>
       <c r="H68" s="13"/>
       <c r="I68" s="4"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="48"/>
       <c r="B69" s="68"/>
       <c r="C69" s="68"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="38"/>
+      <c r="D69" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>264</v>
+      </c>
       <c r="G69" s="4"/>
       <c r="H69" s="13"/>
       <c r="I69" s="4"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="48"/>
       <c r="B70" s="68"/>
       <c r="C70" s="68"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="38"/>
+      <c r="D70" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>265</v>
+      </c>
       <c r="G70" s="4"/>
       <c r="H70" s="13"/>
       <c r="I70" s="4"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="48"/>
       <c r="B71" s="68"/>
       <c r="C71" s="68"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="38"/>
+      <c r="D71" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>266</v>
+      </c>
       <c r="G71" s="4"/>
       <c r="H71" s="13"/>
       <c r="I71" s="4"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="48"/>
       <c r="B72" s="68"/>
       <c r="C72" s="68"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="38"/>
+      <c r="D72" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>267</v>
+      </c>
       <c r="G72" s="4"/>
       <c r="H72" s="13"/>
       <c r="I72" s="4"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="73" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="48"/>
       <c r="B73" s="68"/>
       <c r="C73" s="68"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="38"/>
+      <c r="D73" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>268</v>
+      </c>
       <c r="G73" s="4"/>
       <c r="H73" s="13"/>
       <c r="I73" s="4"/>
       <c r="J73" s="12"/>
     </row>
-    <row r="74" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="48"/>
       <c r="B74" s="68"/>
       <c r="C74" s="68"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="38"/>
+      <c r="D74" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>269</v>
+      </c>
       <c r="G74" s="4"/>
       <c r="H74" s="13"/>
       <c r="I74" s="4"/>
       <c r="J74" s="12"/>
     </row>
-    <row r="75" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="48"/>
       <c r="B75" s="68"/>
       <c r="C75" s="68"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="38"/>
+      <c r="D75" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>270</v>
+      </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="5"/>
+      <c r="H75" s="13"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="48"/>
       <c r="B76" s="68"/>
       <c r="C76" s="68"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="38"/>
+      <c r="D76" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>271</v>
+      </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="13"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="48"/>
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
-      <c r="D77" s="47"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="38"/>
+      <c r="D77" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>272</v>
+      </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="44"/>
+      <c r="H77" s="13"/>
       <c r="I77" s="4"/>
       <c r="J77" s="12"/>
     </row>
-    <row r="78" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="48"/>
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="38"/>
+      <c r="D78" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>273</v>
+      </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="13"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J78" s="12"/>
+    </row>
+    <row r="79" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="48"/>
       <c r="B79" s="68"/>
       <c r="C79" s="68"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="38"/>
+      <c r="D79" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>274</v>
+      </c>
       <c r="G79" s="4"/>
       <c r="H79" s="5"/>
       <c r="I79" s="4"/>
@@ -10920,7 +11126,7 @@
       <c r="B80" s="68"/>
       <c r="C80" s="68"/>
       <c r="D80" s="47"/>
-      <c r="E80" s="14"/>
+      <c r="E80" s="17"/>
       <c r="F80" s="38"/>
       <c r="G80" s="4"/>
       <c r="H80" s="5"/>
@@ -10935,14 +11141,14 @@
       <c r="E81" s="14"/>
       <c r="F81" s="38"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="5"/>
+      <c r="H81" s="44"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
+      <c r="J81" s="12"/>
     </row>
     <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="48"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="69"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="68"/>
       <c r="D82" s="47"/>
       <c r="E82" s="14"/>
       <c r="F82" s="38"/>
@@ -10951,15 +11157,63 @@
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="48"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="48"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68"/>
+      <c r="D84" s="47"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="48"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="68"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="38"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="48"/>
+      <c r="B86" s="69"/>
+      <c r="C86" s="69"/>
+      <c r="D86" s="47"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B82"/>
+    <mergeCell ref="B3:B86"/>
     <mergeCell ref="C3:C22"/>
     <mergeCell ref="C23:C65"/>
-    <mergeCell ref="C66:C82"/>
+    <mergeCell ref="C66:C86"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74ED28D1-9B32-4D00-9E8E-A64310104801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426CC59F-F3A4-4BCC-B183-DC9D5CDC47E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="278">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2863,16 +2863,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録完了画面</t>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>カンリョウガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>表示内容確認後、「登録する」を押下</t>
     <rPh sb="0" eb="7">
       <t>ヒョウジナイヨウカクニンゴ</t>
@@ -2950,16 +2940,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「password」カラムへ内容が登録されている</t>
-    <rPh sb="20" eb="22">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データベース「postal_code」カラムへ内容が登録されている</t>
     <rPh sb="23" eb="25">
       <t>ナイヨウ</t>
@@ -3046,44 +3026,6 @@
       <t>トウロク</t>
     </rPh>
     <rPh sb="52" eb="54">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録に不備のある場合「エラーが発生したためアカウント登録できません。」表示</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録完了or登録エラー表示</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -3805,25 +3747,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録確認画面にて「登録する」を押下</t>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データベース「family_name」カラムへ入力した内容が登録されている</t>
     <rPh sb="23" eb="25">
       <t>ニュウリョク</t>
@@ -3859,13 +3782,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「password」カラムへ入力した内容が登録されている</t>
-    <rPh sb="20" eb="22">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データベース「gender」カラムへ"男"を選択したならば”０”、”女”を選択したならば”１”が登録されている</t>
     <rPh sb="19" eb="20">
       <t>オトコ</t>
@@ -3913,6 +3829,135 @@
     <t>データベース「authority」カラムへ入力した内容が登録されている</t>
     <rPh sb="21" eb="23">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「password」カラムへ入力した内容がハッシュ化された文字列となり登録されている</t>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>モジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「password」カラムへ内容がハッシュ化された文字列となり登録されている</t>
+    <rPh sb="20" eb="22">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「registered_time」カラムへ登録した日時が表示されている</t>
+    <rPh sb="27" eb="29">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了表示</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した内容がデータベース「account」テーブル内にすべて格納されている</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「登録完了しました」と画面中央に表示</t>
+    <rPh sb="1" eb="5">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ガメンチュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した内容がデータベースへ格納できず不備がある</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>フビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録エラー表示</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「エラーが発生したためアカウント登録できません。」と画面中央に赤字表示</t>
+    <rPh sb="5" eb="7">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ガメンチュウオウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>アカジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9705,7 +9750,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9769,10 +9814,10 @@
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="49" t="s">
         <v>240</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>244</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
@@ -9787,10 +9832,10 @@
         <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
@@ -9805,10 +9850,10 @@
         <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
@@ -9823,10 +9868,10 @@
         <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
@@ -9841,10 +9886,10 @@
         <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
@@ -9859,10 +9904,10 @@
         <v>197</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
@@ -9877,10 +9922,10 @@
         <v>200</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
@@ -9895,10 +9940,10 @@
         <v>45</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
@@ -9913,10 +9958,10 @@
         <v>45</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
@@ -9931,10 +9976,10 @@
         <v>199</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
@@ -9949,7 +9994,7 @@
         <v>198</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>209</v>
@@ -9967,10 +10012,10 @@
         <v>201</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -9985,10 +10030,10 @@
         <v>211</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
@@ -10003,10 +10048,10 @@
         <v>213</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
@@ -10021,10 +10066,10 @@
         <v>82</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
@@ -10039,10 +10084,10 @@
         <v>82</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
@@ -10329,10 +10374,10 @@
         <v>192</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
@@ -10347,10 +10392,10 @@
         <v>192</v>
       </c>
       <c r="E36" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F36" s="38" t="s">
         <v>217</v>
-      </c>
-      <c r="F36" s="38" t="s">
-        <v>218</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
@@ -10365,10 +10410,10 @@
         <v>194</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
@@ -10383,10 +10428,10 @@
         <v>194</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
@@ -10398,13 +10443,13 @@
       <c r="B39" s="68"/>
       <c r="C39" s="68"/>
       <c r="D39" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
@@ -10416,13 +10461,13 @@
       <c r="B40" s="68"/>
       <c r="C40" s="68"/>
       <c r="D40" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" s="38" t="s">
         <v>222</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>223</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="13"/>
@@ -10437,10 +10482,10 @@
         <v>195</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="13"/>
@@ -10455,10 +10500,10 @@
         <v>195</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="13"/>
@@ -10473,10 +10518,10 @@
         <v>24</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="13"/>
@@ -10491,10 +10536,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="13"/>
@@ -10509,10 +10554,10 @@
         <v>29</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="13"/>
@@ -10527,10 +10572,10 @@
         <v>29</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="13"/>
@@ -10545,10 +10590,10 @@
         <v>45</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="13"/>
@@ -10563,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -10581,10 +10626,10 @@
         <v>45</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
@@ -10599,10 +10644,10 @@
         <v>54</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
@@ -10617,10 +10662,10 @@
         <v>54</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="13"/>
@@ -10635,10 +10680,10 @@
         <v>53</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -10653,10 +10698,10 @@
         <v>53</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="13"/>
@@ -10671,10 +10716,10 @@
         <v>201</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="13"/>
@@ -10689,10 +10734,10 @@
         <v>201</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="13"/>
@@ -10707,10 +10752,10 @@
         <v>70</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="13"/>
@@ -10725,10 +10770,10 @@
         <v>70</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="13"/>
@@ -10743,10 +10788,10 @@
         <v>82</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="13"/>
@@ -10761,10 +10806,10 @@
         <v>82</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
@@ -10779,10 +10824,10 @@
         <v>82</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="13"/>
@@ -10824,13 +10869,13 @@
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
       <c r="D63" s="46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="13"/>
@@ -10842,13 +10887,13 @@
       <c r="B64" s="68"/>
       <c r="C64" s="68"/>
       <c r="D64" s="46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="13"/>
@@ -10867,38 +10912,36 @@
       <c r="I65" s="4"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="48"/>
       <c r="B66" s="68"/>
-      <c r="C66" s="72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D66" s="46" t="s">
-        <v>234</v>
+      <c r="C66" s="68"/>
+      <c r="D66" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="13"/>
       <c r="I66" s="4"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="48"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
-      <c r="D67" s="46" t="s">
-        <v>234</v>
+      <c r="D67" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="13"/>
@@ -10910,13 +10953,13 @@
       <c r="B68" s="68"/>
       <c r="C68" s="68"/>
       <c r="D68" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F68" s="38" t="s">
         <v>260</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>263</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="13"/>
@@ -10928,13 +10971,13 @@
       <c r="B69" s="68"/>
       <c r="C69" s="68"/>
       <c r="D69" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E69" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F69" s="38" t="s">
         <v>261</v>
-      </c>
-      <c r="F69" s="38" t="s">
-        <v>264</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="13"/>
@@ -10946,13 +10989,13 @@
       <c r="B70" s="68"/>
       <c r="C70" s="68"/>
       <c r="D70" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="13"/>
@@ -10964,13 +11007,13 @@
       <c r="B71" s="68"/>
       <c r="C71" s="68"/>
       <c r="D71" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="13"/>
@@ -10982,13 +11025,13 @@
       <c r="B72" s="68"/>
       <c r="C72" s="68"/>
       <c r="D72" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="13"/>
@@ -11000,13 +11043,13 @@
       <c r="B73" s="68"/>
       <c r="C73" s="68"/>
       <c r="D73" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="13"/>
@@ -11018,13 +11061,13 @@
       <c r="B74" s="68"/>
       <c r="C74" s="68"/>
       <c r="D74" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="13"/>
@@ -11036,13 +11079,13 @@
       <c r="B75" s="68"/>
       <c r="C75" s="68"/>
       <c r="D75" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="13"/>
@@ -11054,13 +11097,13 @@
       <c r="B76" s="68"/>
       <c r="C76" s="68"/>
       <c r="D76" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="13"/>
@@ -11072,62 +11115,68 @@
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
       <c r="D77" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="13"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="12"/>
+      <c r="J77" s="4"/>
     </row>
     <row r="78" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="48"/>
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
       <c r="D78" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="13"/>
+      <c r="H78" s="5"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="12"/>
-    </row>
-    <row r="79" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="48"/>
       <c r="B79" s="68"/>
       <c r="C79" s="68"/>
-      <c r="D79" s="47" t="s">
-        <v>260</v>
+      <c r="D79" s="46" t="s">
+        <v>272</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>274</v>
       </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="5"/>
+      <c r="H79" s="44"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
+      <c r="J79" s="12"/>
     </row>
     <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="48"/>
       <c r="B80" s="68"/>
       <c r="C80" s="68"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="38"/>
+      <c r="D80" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>277</v>
+      </c>
       <c r="G80" s="4"/>
       <c r="H80" s="5"/>
       <c r="I80" s="4"/>
@@ -11141,9 +11190,9 @@
       <c r="E81" s="14"/>
       <c r="F81" s="38"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="44"/>
+      <c r="H81" s="5"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="12"/>
+      <c r="J81" s="4"/>
     </row>
     <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="48"/>
@@ -11171,8 +11220,8 @@
     </row>
     <row r="84" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="48"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="69"/>
       <c r="D84" s="47"/>
       <c r="E84" s="14"/>
       <c r="F84" s="38"/>
@@ -11181,39 +11230,15 @@
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="48"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="68"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="48"/>
-      <c r="B86" s="69"/>
-      <c r="C86" s="69"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="85" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B86"/>
+    <mergeCell ref="B3:B84"/>
     <mergeCell ref="C3:C22"/>
     <mergeCell ref="C23:C65"/>
-    <mergeCell ref="C66:C86"/>
+    <mergeCell ref="C66:C84"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426CC59F-F3A4-4BCC-B183-DC9D5CDC47E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8243FCEE-DF37-4AC2-B7D6-BD2E8F7959A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="単体テスト（訂正前あり）" sheetId="1" r:id="rId1"/>
+    <sheet name="単体テスト（訂正前）" sheetId="1" r:id="rId1"/>
     <sheet name="単体テスト (新)" sheetId="4" r:id="rId2"/>
-    <sheet name="結合テスト" sheetId="6" r:id="rId3"/>
-    <sheet name="総合テスト" sheetId="5" r:id="rId4"/>
+    <sheet name="結合テスト（訂正前・バラ）" sheetId="6" r:id="rId3"/>
+    <sheet name="結合テスト（新）" sheetId="7" r:id="rId4"/>
+    <sheet name="総合テスト" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="292">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -3747,6 +3748,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>アカウント登録確認画面にて「登録する」を押下</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>データベース「family_name」カラムへ入力した内容が登録されている</t>
     <rPh sb="23" eb="25">
       <t>ニュウリョク</t>
@@ -3958,6 +3978,235 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面ーアカウント登録確認画面</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>トウロクカクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1－3結合</t>
+    <rPh sb="3" eb="5">
+      <t>ケツゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面ーアカウント登録完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面にてすべて入力後、「確認する」を押下</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面
+「確認する」ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面「前に戻る」ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示された入力内容を維持したまま「アカウント登録画面」に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録確認画面
+「登録する」ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての入力値を確認後、XAMMPの「MySQL」がSTARTしてることを確認し、「登録する」押下</t>
+    <rPh sb="4" eb="7">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての入力値を確認後、XAMMPの「MySQL」をSTARTせず「登録する」押下</t>
+    <rPh sb="4" eb="7">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面へ遷移し、「エラーが発生したためアカウント登録できません。」と表示</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面ー
+アカウント登録完了画面</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4065,7 +4314,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4081,6 +4330,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4271,7 +4526,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4493,6 +4748,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9750,7 +10020,1510 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:L84"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" style="42" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+    </row>
+    <row r="2" spans="1:12" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="48"/>
+      <c r="B3" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="48"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="48"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="48"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="48"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="48"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="48"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="48"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>238</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="12"/>
+      <c r="L10" s="74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="48"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="77" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="12"/>
+      <c r="L11" s="74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="48"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="48"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="48"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="12"/>
+    </row>
+    <row r="15" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="48"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="12"/>
+    </row>
+    <row r="16" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="48"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="48"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="12"/>
+      <c r="L17" s="74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="48"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>251</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="12"/>
+      <c r="L18" s="74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="48"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="48"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="48"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="12"/>
+    </row>
+    <row r="22" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="48"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="48"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="48"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="48"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="48"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="48"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="48"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="48"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="48"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="48"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="48"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="48"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="48"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="48"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="48"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="12"/>
+    </row>
+    <row r="37" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="48"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="48"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="48"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="12"/>
+    </row>
+    <row r="40" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="48"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="48"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="48"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="48"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="48"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="48"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="12"/>
+    </row>
+    <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="48"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="48"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="48"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="48"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="48"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="48"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="12"/>
+    </row>
+    <row r="52" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="48"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="48"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="68"/>
+      <c r="D53" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="12"/>
+    </row>
+    <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="48"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="48"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="48"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="48"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="12"/>
+    </row>
+    <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="48"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="48"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="68"/>
+      <c r="D59" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="12"/>
+    </row>
+    <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="48"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="68"/>
+      <c r="D60" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="48"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="48"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="48"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="48"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="12"/>
+    </row>
+    <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="48"/>
+      <c r="B65" s="68"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="12"/>
+    </row>
+    <row r="66" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="48"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="G66" s="4"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="12"/>
+    </row>
+    <row r="67" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="48"/>
+      <c r="B67" s="68"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="G67" s="4"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="48"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="68"/>
+      <c r="D68" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="G68" s="4"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="48"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="48"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="G70" s="4"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="48"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+      <c r="D71" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="48"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="68"/>
+      <c r="D72" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="48"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="68"/>
+      <c r="D73" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="48"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="68"/>
+      <c r="D74" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="G74" s="4"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="12"/>
+    </row>
+    <row r="75" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="48"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="68"/>
+      <c r="D75" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="48"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="48"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="68"/>
+      <c r="D77" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="48"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="68"/>
+      <c r="D78" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="G78" s="4"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="48"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="12"/>
+    </row>
+    <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="48"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="48"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="68"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="48"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="68"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="48"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:B83"/>
+    <mergeCell ref="C3:C22"/>
+    <mergeCell ref="C23:C65"/>
+    <mergeCell ref="C66:C83"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D411216B-B5B7-4B48-B0D3-CF2BB4857B38}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9808,13 +11581,13 @@
         <v>66</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F3" s="49" t="s">
         <v>240</v>
@@ -9832,7 +11605,7 @@
         <v>194</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>241</v>
@@ -9850,7 +11623,7 @@
         <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>242</v>
@@ -9868,7 +11641,7 @@
         <v>195</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>243</v>
@@ -9883,10 +11656,10 @@
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
       <c r="D7" s="45" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>244</v>
@@ -9901,10 +11674,10 @@
       <c r="B8" s="68"/>
       <c r="C8" s="68"/>
       <c r="D8" s="45" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>245</v>
@@ -9919,10 +11692,10 @@
       <c r="B9" s="68"/>
       <c r="C9" s="68"/>
       <c r="D9" s="45" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>246</v>
@@ -9932,36 +11705,36 @@
       <c r="I9" s="4"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
       <c r="B10" s="68"/>
       <c r="C10" s="68"/>
       <c r="D10" s="45" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
       <c r="B11" s="68"/>
       <c r="C11" s="68"/>
       <c r="D11" s="45" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
@@ -9973,13 +11746,13 @@
       <c r="B12" s="68"/>
       <c r="C12" s="68"/>
       <c r="D12" s="45" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
@@ -9991,13 +11764,13 @@
       <c r="B13" s="68"/>
       <c r="C13" s="68"/>
       <c r="D13" s="45" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
@@ -10009,13 +11782,13 @@
       <c r="B14" s="68"/>
       <c r="C14" s="68"/>
       <c r="D14" s="45" t="s">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -10026,15 +11799,9 @@
       <c r="A15" s="48"/>
       <c r="B15" s="68"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>249</v>
-      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="38"/>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
       <c r="I15" s="4"/>
@@ -10045,50 +11812,44 @@
       <c r="B16" s="68"/>
       <c r="C16" s="68"/>
       <c r="D16" s="45" t="s">
-        <v>213</v>
+        <v>284</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
       <c r="I16" s="4"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
       <c r="B17" s="68"/>
       <c r="C17" s="68"/>
-      <c r="D17" s="45" t="s">
-        <v>82</v>
+      <c r="D17" s="46" t="s">
+        <v>285</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="4"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
       <c r="B18" s="68"/>
       <c r="C18" s="68"/>
-      <c r="D18" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>251</v>
-      </c>
+      <c r="D18" s="45"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="38"/>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
       <c r="I18" s="4"/>
@@ -10097,7 +11858,7 @@
     <row r="19" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="48"/>
       <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
+      <c r="C19" s="69"/>
       <c r="D19" s="45"/>
       <c r="E19" s="17"/>
       <c r="F19" s="38"/>
@@ -10106,224 +11867,236 @@
       <c r="I19" s="4"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="48"/>
       <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
-      <c r="D20" s="45" t="s">
-        <v>148</v>
+      <c r="C20" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="13"/>
       <c r="I20" s="4"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="48"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="38"/>
+      <c r="D21" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>260</v>
+      </c>
       <c r="G21" s="4"/>
       <c r="H21" s="13"/>
       <c r="I21" s="4"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
       <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="38"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>261</v>
+      </c>
       <c r="G22" s="4"/>
       <c r="H22" s="13"/>
       <c r="I22" s="4"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
       <c r="B23" s="68"/>
-      <c r="C23" s="72" t="s">
-        <v>215</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>192</v>
+      <c r="C23" s="68"/>
+      <c r="D23" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="13"/>
       <c r="I23" s="4"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="48"/>
       <c r="B24" s="68"/>
       <c r="C24" s="68"/>
-      <c r="D24" s="45" t="s">
-        <v>194</v>
+      <c r="D24" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="13"/>
       <c r="I24" s="4"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="48"/>
       <c r="B25" s="68"/>
       <c r="C25" s="68"/>
-      <c r="D25" s="45" t="s">
-        <v>195</v>
+      <c r="D25" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="13"/>
       <c r="I25" s="4"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="48"/>
       <c r="B26" s="68"/>
       <c r="C26" s="68"/>
-      <c r="D26" s="45" t="s">
-        <v>195</v>
+      <c r="D26" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
       <c r="I26" s="4"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="48"/>
       <c r="B27" s="68"/>
       <c r="C27" s="68"/>
-      <c r="D27" s="46" t="s">
-        <v>196</v>
+      <c r="D27" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="13"/>
       <c r="I27" s="4"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="48"/>
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
-      <c r="D28" s="46" t="s">
-        <v>197</v>
+      <c r="D28" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="13"/>
       <c r="I28" s="4"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="48"/>
       <c r="B29" s="68"/>
       <c r="C29" s="68"/>
-      <c r="D29" s="46" t="s">
-        <v>200</v>
+      <c r="D29" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="13"/>
       <c r="I29" s="4"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="48"/>
       <c r="B30" s="68"/>
       <c r="C30" s="68"/>
-      <c r="D30" s="46" t="s">
-        <v>199</v>
+      <c r="D30" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="13"/>
       <c r="I30" s="4"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="48"/>
       <c r="B31" s="68"/>
       <c r="C31" s="68"/>
-      <c r="D31" s="46" t="s">
-        <v>198</v>
+      <c r="D31" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
       <c r="I31" s="4"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="48"/>
       <c r="B32" s="68"/>
       <c r="C32" s="68"/>
-      <c r="D32" s="46" t="s">
-        <v>201</v>
+      <c r="D32" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="13"/>
@@ -10334,50 +12107,44 @@
       <c r="A33" s="48"/>
       <c r="B33" s="68"/>
       <c r="C33" s="68"/>
-      <c r="D33" s="46" t="s">
-        <v>211</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>212</v>
-      </c>
+      <c r="D33" s="47"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="38"/>
       <c r="G33" s="4"/>
       <c r="H33" s="13"/>
       <c r="I33" s="4"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="48"/>
       <c r="B34" s="68"/>
       <c r="C34" s="68"/>
       <c r="D34" s="46" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="13"/>
       <c r="I34" s="4"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="48"/>
       <c r="B35" s="68"/>
       <c r="C35" s="68"/>
       <c r="D35" s="46" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
@@ -10388,15 +12155,9 @@
       <c r="A36" s="48"/>
       <c r="B36" s="68"/>
       <c r="C36" s="68"/>
-      <c r="D36" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F36" s="38" t="s">
-        <v>217</v>
-      </c>
+      <c r="D36" s="46"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="38"/>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
       <c r="I36" s="4"/>
@@ -10406,15 +12167,9 @@
       <c r="A37" s="48"/>
       <c r="B37" s="68"/>
       <c r="C37" s="68"/>
-      <c r="D37" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="D37" s="46"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="38"/>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
       <c r="I37" s="4"/>
@@ -10424,15 +12179,9 @@
       <c r="A38" s="48"/>
       <c r="B38" s="68"/>
       <c r="C38" s="68"/>
-      <c r="D38" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>218</v>
-      </c>
+      <c r="D38" s="46"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="38"/>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
       <c r="I38" s="4"/>
@@ -10441,16 +12190,10 @@
     <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="48"/>
       <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F39" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="C39" s="69"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="38"/>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
       <c r="I39" s="4"/>
@@ -10459,18 +12202,14 @@
     <row r="40" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="48"/>
       <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>222</v>
-      </c>
+      <c r="C40" s="78" t="s">
+        <v>291</v>
+      </c>
+      <c r="D40" s="46"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="38"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="13"/>
+      <c r="H40" s="44"/>
       <c r="I40" s="4"/>
       <c r="J40" s="12"/>
     </row>
@@ -10478,767 +12217,131 @@
       <c r="A41" s="48"/>
       <c r="B41" s="68"/>
       <c r="C41" s="68"/>
-      <c r="D41" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="D41" s="46"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="38"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="13"/>
+      <c r="H41" s="5"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="12"/>
+      <c r="J41" s="4"/>
     </row>
     <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
-      <c r="D42" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="38" t="s">
-        <v>220</v>
-      </c>
+      <c r="D42" s="47"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="38"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="13"/>
+      <c r="H42" s="5"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="12"/>
+      <c r="J42" s="4"/>
     </row>
     <row r="43" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
       <c r="B43" s="68"/>
       <c r="C43" s="68"/>
-      <c r="D43" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="D43" s="47"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="38"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="13"/>
+      <c r="H43" s="5"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="12"/>
+      <c r="J43" s="4"/>
     </row>
     <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
       <c r="B44" s="68"/>
       <c r="C44" s="68"/>
-      <c r="D44" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F44" s="38" t="s">
-        <v>223</v>
-      </c>
+      <c r="D44" s="47"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="38"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="13"/>
+      <c r="H44" s="5"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="12"/>
+      <c r="J44" s="4"/>
     </row>
     <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
       <c r="B45" s="68"/>
       <c r="C45" s="68"/>
-      <c r="D45" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="D45" s="47"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="38"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="13"/>
+      <c r="H45" s="5"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="12"/>
+      <c r="J45" s="4"/>
     </row>
     <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>
       <c r="B46" s="68"/>
       <c r="C46" s="68"/>
-      <c r="D46" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F46" s="38" t="s">
-        <v>270</v>
-      </c>
+      <c r="D46" s="47"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="38"/>
       <c r="G46" s="4"/>
-      <c r="H46" s="13"/>
+      <c r="H46" s="5"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="12"/>
+      <c r="J46" s="4"/>
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="48"/>
       <c r="B47" s="68"/>
       <c r="C47" s="68"/>
-      <c r="D47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="D47" s="47"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="38"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="13"/>
+      <c r="H47" s="5"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="12"/>
+      <c r="J47" s="4"/>
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
       <c r="B48" s="68"/>
       <c r="C48" s="68"/>
-      <c r="D48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>232</v>
-      </c>
+      <c r="D48" s="47"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="38"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="13"/>
+      <c r="H48" s="5"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="12"/>
+      <c r="J48" s="4"/>
     </row>
     <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="48"/>
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
-      <c r="D49" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>233</v>
-      </c>
+      <c r="D49" s="47"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="38"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="13"/>
+      <c r="H49" s="5"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="12"/>
+      <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="48"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="68"/>
-      <c r="D50" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>219</v>
-      </c>
+      <c r="B50" s="69"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="38"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="13"/>
+      <c r="H50" s="5"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="12"/>
-    </row>
-    <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="48"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="68"/>
-      <c r="D51" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="12"/>
-    </row>
-    <row r="52" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="48"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
-      <c r="D52" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F52" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="48"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="68"/>
-      <c r="D53" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F53" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="12"/>
-    </row>
-    <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="48"/>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F54" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="48"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F55" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="48"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F56" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="48"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F57" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="12"/>
-    </row>
-    <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="48"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F58" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="48"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F59" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="12"/>
-    </row>
-    <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="48"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F60" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="12"/>
-    </row>
-    <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="48"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="12"/>
-    </row>
-    <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="48"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F62" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="12"/>
-    </row>
-    <row r="63" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="48"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F63" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="12"/>
-    </row>
-    <row r="64" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="48"/>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F64" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="12"/>
-    </row>
-    <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="48"/>
-      <c r="B65" s="68"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="12"/>
-    </row>
-    <row r="66" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="48"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F66" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G66" s="4"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="12"/>
-    </row>
-    <row r="67" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="48"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F67" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="12"/>
-    </row>
-    <row r="68" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="48"/>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
-      <c r="D68" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="G68" s="4"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="12"/>
-    </row>
-    <row r="69" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="48"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-      <c r="D69" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F69" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="G69" s="4"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="12"/>
-    </row>
-    <row r="70" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="48"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F70" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="12"/>
-    </row>
-    <row r="71" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="48"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="68"/>
-      <c r="D71" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F71" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="12"/>
-    </row>
-    <row r="72" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="48"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
-      <c r="D72" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F72" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="12"/>
-    </row>
-    <row r="73" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="48"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="68"/>
-      <c r="D73" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F73" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="G73" s="4"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="12"/>
-    </row>
-    <row r="74" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="48"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="68"/>
-      <c r="D74" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F74" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="G74" s="4"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="12"/>
-    </row>
-    <row r="75" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="48"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="68"/>
-      <c r="D75" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F75" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="12"/>
-    </row>
-    <row r="76" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="48"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
-      <c r="D76" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F76" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="G76" s="4"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="12"/>
-    </row>
-    <row r="77" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="48"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
-      <c r="D77" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F77" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="G77" s="4"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="48"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
-      <c r="D78" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F78" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="G78" s="4"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="48"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="E79" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="F79" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="G79" s="4"/>
-      <c r="H79" s="44"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="12"/>
-    </row>
-    <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="48"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68"/>
-      <c r="D80" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="F80" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="G80" s="4"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="48"/>
-      <c r="B81" s="68"/>
-      <c r="C81" s="68"/>
-      <c r="D81" s="47"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="48"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="68"/>
-      <c r="D82" s="47"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="48"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="48"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="69"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B84"/>
-    <mergeCell ref="C3:C22"/>
-    <mergeCell ref="C23:C65"/>
-    <mergeCell ref="C66:C84"/>
+    <mergeCell ref="B3:B50"/>
+    <mergeCell ref="C3:C19"/>
+    <mergeCell ref="C20:C39"/>
+    <mergeCell ref="C40:C50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11246,7 +12349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31F6E48-2FF7-40BE-9951-33BCA157813A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8243FCEE-DF37-4AC2-B7D6-BD2E8F7959A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F507BB-2B29-42ED-9858-13BF77D9FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="301">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -4207,6 +4207,123 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了（性別）</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムへ情報が登録されている</t>
+    <rPh sb="18" eb="20">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"男"を選択したならば”０”、”女”を選択したならば”１”がデータベース「gender」カラムに登録されている</t>
+    <rPh sb="1" eb="2">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムへ情報が登録されている</t>
+    <rPh sb="21" eb="23">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了
+（アカウント権限）</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"一般"を選択したならば”０”、”管理者”を選択したならば”１”がデータベース「authority」カラムに登録されている</t>
+    <rPh sb="1" eb="3">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面にてすべて入力後、アカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面
+「TOPページへ戻る」
+　　　　　　　　ボタン</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面にて「TOPページへ戻る」押下</t>
+    <rPh sb="5" eb="11">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4677,6 +4794,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -4746,23 +4875,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5096,24 +5213,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
     </row>
     <row r="2" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -5134,10 +5251,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="54" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -5155,8 +5272,8 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="55"/>
-      <c r="C4" s="50"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="54"/>
       <c r="D4" s="19" t="s">
         <v>20</v>
       </c>
@@ -5183,8 +5300,8 @@
       </c>
     </row>
     <row r="5" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="55"/>
-      <c r="C5" s="50"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="19" t="s">
         <v>20</v>
       </c>
@@ -5211,8 +5328,8 @@
       </c>
     </row>
     <row r="6" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="55"/>
-      <c r="C6" s="50"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="19" t="s">
         <v>20</v>
       </c>
@@ -5239,8 +5356,8 @@
       </c>
     </row>
     <row r="7" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="55"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
@@ -5267,8 +5384,8 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="55"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
@@ -5284,8 +5401,8 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="55"/>
-      <c r="C9" s="50"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
@@ -5301,8 +5418,8 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="55"/>
-      <c r="C10" s="50"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="8" t="s">
         <v>20</v>
       </c>
@@ -5318,8 +5435,8 @@
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="55"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
@@ -5335,8 +5452,8 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="55"/>
-      <c r="C12" s="50"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="54"/>
       <c r="D12" s="8" t="s">
         <v>20</v>
       </c>
@@ -5352,8 +5469,8 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="55"/>
-      <c r="C13" s="50"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
@@ -5369,8 +5486,8 @@
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="55"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
@@ -5386,8 +5503,8 @@
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="55"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
@@ -5403,8 +5520,8 @@
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="55"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="28" t="s">
         <v>21</v>
       </c>
@@ -5431,8 +5548,8 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="55"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="28" t="s">
         <v>21</v>
       </c>
@@ -5459,8 +5576,8 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="55"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="28" t="s">
         <v>21</v>
       </c>
@@ -5487,8 +5604,8 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="55"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="28" t="s">
         <v>21</v>
       </c>
@@ -5515,8 +5632,8 @@
       </c>
     </row>
     <row r="20" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="55"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="6" t="s">
         <v>21</v>
       </c>
@@ -5532,8 +5649,8 @@
       <c r="J20" s="12"/>
     </row>
     <row r="21" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="55"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="6" t="s">
         <v>21</v>
       </c>
@@ -5549,8 +5666,8 @@
       <c r="J21" s="12"/>
     </row>
     <row r="22" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="55"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="6" t="s">
         <v>21</v>
       </c>
@@ -5566,8 +5683,8 @@
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="55"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
@@ -5583,8 +5700,8 @@
       <c r="J23" s="12"/>
     </row>
     <row r="24" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="55"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="54"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
@@ -5600,8 +5717,8 @@
       <c r="J24" s="12"/>
     </row>
     <row r="25" spans="2:11" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="55"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
@@ -5617,8 +5734,8 @@
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="55"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
@@ -5634,8 +5751,8 @@
       <c r="J26" s="12"/>
     </row>
     <row r="27" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="55"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="6" t="s">
         <v>22</v>
       </c>
@@ -5651,8 +5768,8 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="55"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="28" t="s">
         <v>22</v>
       </c>
@@ -5671,8 +5788,8 @@
       </c>
     </row>
     <row r="29" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="55"/>
-      <c r="C29" s="50"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="28" t="s">
         <v>22</v>
       </c>
@@ -5691,8 +5808,8 @@
       </c>
     </row>
     <row r="30" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="55"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="54"/>
       <c r="D30" s="28" t="s">
         <v>22</v>
       </c>
@@ -5711,8 +5828,8 @@
       </c>
     </row>
     <row r="31" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="55"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="54"/>
       <c r="D31" s="28" t="s">
         <v>22</v>
       </c>
@@ -5731,8 +5848,8 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="55"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="54"/>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
@@ -5748,8 +5865,8 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="55"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="54"/>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
@@ -5765,8 +5882,8 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="55"/>
-      <c r="C34" s="50"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="54"/>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
@@ -5782,8 +5899,8 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="55"/>
-      <c r="C35" s="50"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="54"/>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
@@ -5799,8 +5916,8 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="55"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="54"/>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
@@ -5816,8 +5933,8 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="55"/>
-      <c r="C37" s="50"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="54"/>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
@@ -5833,8 +5950,8 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="55"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="54"/>
       <c r="D38" s="6" t="s">
         <v>22</v>
       </c>
@@ -5850,8 +5967,8 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="55"/>
-      <c r="C39" s="50"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="54"/>
       <c r="D39" s="6" t="s">
         <v>23</v>
       </c>
@@ -5867,8 +5984,8 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="55"/>
-      <c r="C40" s="50"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="54"/>
       <c r="D40" s="28" t="s">
         <v>23</v>
       </c>
@@ -5887,8 +6004,8 @@
       </c>
     </row>
     <row r="41" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="55"/>
-      <c r="C41" s="50"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="54"/>
       <c r="D41" s="28" t="s">
         <v>23</v>
       </c>
@@ -5907,8 +6024,8 @@
       </c>
     </row>
     <row r="42" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="55"/>
-      <c r="C42" s="50"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="54"/>
       <c r="D42" s="28" t="s">
         <v>23</v>
       </c>
@@ -5927,8 +6044,8 @@
       </c>
     </row>
     <row r="43" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="55"/>
-      <c r="C43" s="50"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="54"/>
       <c r="D43" s="28" t="s">
         <v>23</v>
       </c>
@@ -5947,8 +6064,8 @@
       </c>
     </row>
     <row r="44" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="55"/>
-      <c r="C44" s="50"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="54"/>
       <c r="D44" s="6" t="s">
         <v>23</v>
       </c>
@@ -5964,8 +6081,8 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="55"/>
-      <c r="C45" s="50"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="6" t="s">
         <v>23</v>
       </c>
@@ -5981,8 +6098,8 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="55"/>
-      <c r="C46" s="50"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="54"/>
       <c r="D46" s="6" t="s">
         <v>23</v>
       </c>
@@ -5998,8 +6115,8 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="55"/>
-      <c r="C47" s="50"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="54"/>
       <c r="D47" s="6" t="s">
         <v>23</v>
       </c>
@@ -6015,8 +6132,8 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="55"/>
-      <c r="C48" s="50"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="54"/>
       <c r="D48" s="6" t="s">
         <v>23</v>
       </c>
@@ -6032,8 +6149,8 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="55"/>
-      <c r="C49" s="50"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="54"/>
       <c r="D49" s="6" t="s">
         <v>23</v>
       </c>
@@ -6049,8 +6166,8 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="55"/>
-      <c r="C50" s="50"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="54"/>
       <c r="D50" s="6" t="s">
         <v>23</v>
       </c>
@@ -6066,8 +6183,8 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="55"/>
-      <c r="C51" s="50"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="54"/>
       <c r="D51" s="7" t="s">
         <v>24</v>
       </c>
@@ -6083,8 +6200,8 @@
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="55"/>
-      <c r="C52" s="50"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="54"/>
       <c r="D52" s="30" t="s">
         <v>24</v>
       </c>
@@ -6100,8 +6217,8 @@
       <c r="J52" s="31"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="55"/>
-      <c r="C53" s="50"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="30" t="s">
         <v>24</v>
       </c>
@@ -6117,8 +6234,8 @@
       <c r="J53" s="31"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="55"/>
-      <c r="C54" s="50"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="30" t="s">
         <v>24</v>
       </c>
@@ -6134,8 +6251,8 @@
       <c r="J54" s="31"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="55"/>
-      <c r="C55" s="50"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="54"/>
       <c r="D55" s="30" t="s">
         <v>24</v>
       </c>
@@ -6151,8 +6268,8 @@
       <c r="J55" s="31"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="55"/>
-      <c r="C56" s="50"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="54"/>
       <c r="D56" s="30" t="s">
         <v>24</v>
       </c>
@@ -6168,8 +6285,8 @@
       <c r="J56" s="31"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="55"/>
-      <c r="C57" s="50"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="54"/>
       <c r="D57" s="30" t="s">
         <v>24</v>
       </c>
@@ -6185,8 +6302,8 @@
       <c r="J57" s="31"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="55"/>
-      <c r="C58" s="50"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="54"/>
       <c r="D58" s="30" t="s">
         <v>24</v>
       </c>
@@ -6202,8 +6319,8 @@
       <c r="J58" s="31"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="55"/>
-      <c r="C59" s="50"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="54"/>
       <c r="D59" s="30" t="s">
         <v>24</v>
       </c>
@@ -6219,8 +6336,8 @@
       <c r="J59" s="31"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="55"/>
-      <c r="C60" s="50"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="54"/>
       <c r="D60" s="7" t="s">
         <v>24</v>
       </c>
@@ -6236,8 +6353,8 @@
       <c r="J60" s="4"/>
     </row>
     <row r="61" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="55"/>
-      <c r="C61" s="50"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="54"/>
       <c r="D61" s="7" t="s">
         <v>24</v>
       </c>
@@ -6253,8 +6370,8 @@
       <c r="J61" s="4"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="55"/>
-      <c r="C62" s="50"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="54"/>
       <c r="D62" s="7" t="s">
         <v>24</v>
       </c>
@@ -6270,8 +6387,8 @@
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="55"/>
-      <c r="C63" s="50"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="54"/>
       <c r="D63" s="7" t="s">
         <v>24</v>
       </c>
@@ -6287,8 +6404,8 @@
       <c r="J63" s="4"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="55"/>
-      <c r="C64" s="50"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="54"/>
       <c r="D64" s="7" t="s">
         <v>24</v>
       </c>
@@ -6304,8 +6421,8 @@
       <c r="J64" s="4"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="55"/>
-      <c r="C65" s="50"/>
+      <c r="B65" s="59"/>
+      <c r="C65" s="54"/>
       <c r="D65" s="7" t="s">
         <v>24</v>
       </c>
@@ -6321,8 +6438,8 @@
       <c r="J65" s="4"/>
     </row>
     <row r="66" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="55"/>
-      <c r="C66" s="50"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="54"/>
       <c r="D66" s="7" t="s">
         <v>24</v>
       </c>
@@ -6338,8 +6455,8 @@
       <c r="J66" s="4"/>
     </row>
     <row r="67" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="55"/>
-      <c r="C67" s="50"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="54"/>
       <c r="D67" s="7" t="s">
         <v>24</v>
       </c>
@@ -6355,8 +6472,8 @@
       <c r="J67" s="4"/>
     </row>
     <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="55"/>
-      <c r="C68" s="50"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="54"/>
       <c r="D68" s="7" t="s">
         <v>24</v>
       </c>
@@ -6372,8 +6489,8 @@
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="55"/>
-      <c r="C69" s="50"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="54"/>
       <c r="D69" s="7" t="s">
         <v>29</v>
       </c>
@@ -6389,8 +6506,8 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="55"/>
-      <c r="C70" s="50"/>
+      <c r="B70" s="59"/>
+      <c r="C70" s="54"/>
       <c r="D70" s="30" t="s">
         <v>29</v>
       </c>
@@ -6406,8 +6523,8 @@
       <c r="J70" s="31"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="55"/>
-      <c r="C71" s="50"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="54"/>
       <c r="D71" s="30" t="s">
         <v>29</v>
       </c>
@@ -6423,8 +6540,8 @@
       <c r="J71" s="31"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="55"/>
-      <c r="C72" s="50"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="54"/>
       <c r="D72" s="30" t="s">
         <v>29</v>
       </c>
@@ -6440,8 +6557,8 @@
       <c r="J72" s="31"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="55"/>
-      <c r="C73" s="50"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="54"/>
       <c r="D73" s="30" t="s">
         <v>29</v>
       </c>
@@ -6457,8 +6574,8 @@
       <c r="J73" s="31"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="55"/>
-      <c r="C74" s="50"/>
+      <c r="B74" s="59"/>
+      <c r="C74" s="54"/>
       <c r="D74" s="30" t="s">
         <v>29</v>
       </c>
@@ -6474,8 +6591,8 @@
       <c r="J74" s="31"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="55"/>
-      <c r="C75" s="50"/>
+      <c r="B75" s="59"/>
+      <c r="C75" s="54"/>
       <c r="D75" s="30" t="s">
         <v>29</v>
       </c>
@@ -6491,8 +6608,8 @@
       <c r="J75" s="31"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="55"/>
-      <c r="C76" s="50"/>
+      <c r="B76" s="59"/>
+      <c r="C76" s="54"/>
       <c r="D76" s="30" t="s">
         <v>29</v>
       </c>
@@ -6508,8 +6625,8 @@
       <c r="J76" s="31"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="55"/>
-      <c r="C77" s="50"/>
+      <c r="B77" s="59"/>
+      <c r="C77" s="54"/>
       <c r="D77" s="7" t="s">
         <v>29</v>
       </c>
@@ -6525,8 +6642,8 @@
       <c r="J77" s="4"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="55"/>
-      <c r="C78" s="50"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="54"/>
       <c r="D78" s="7" t="s">
         <v>29</v>
       </c>
@@ -6542,8 +6659,8 @@
       <c r="J78" s="4"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="55"/>
-      <c r="C79" s="50"/>
+      <c r="B79" s="59"/>
+      <c r="C79" s="54"/>
       <c r="D79" s="7" t="s">
         <v>29</v>
       </c>
@@ -6559,8 +6676,8 @@
       <c r="J79" s="4"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="55"/>
-      <c r="C80" s="50"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="54"/>
       <c r="D80" s="7" t="s">
         <v>29</v>
       </c>
@@ -6576,8 +6693,8 @@
       <c r="J80" s="4"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="55"/>
-      <c r="C81" s="50"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="54"/>
       <c r="D81" s="7" t="s">
         <v>29</v>
       </c>
@@ -6593,8 +6710,8 @@
       <c r="J81" s="4"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="55"/>
-      <c r="C82" s="50"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="54"/>
       <c r="D82" s="7" t="s">
         <v>29</v>
       </c>
@@ -6610,8 +6727,8 @@
       <c r="J82" s="4"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="55"/>
-      <c r="C83" s="50"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="54"/>
       <c r="D83" s="7" t="s">
         <v>29</v>
       </c>
@@ -6627,8 +6744,8 @@
       <c r="J83" s="4"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="55"/>
-      <c r="C84" s="50"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="54"/>
       <c r="D84" s="7" t="s">
         <v>45</v>
       </c>
@@ -6644,8 +6761,8 @@
       <c r="J84" s="4"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="55"/>
-      <c r="C85" s="50"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="54"/>
       <c r="D85" s="7" t="s">
         <v>45</v>
       </c>
@@ -6661,8 +6778,8 @@
       <c r="J85" s="4"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="55"/>
-      <c r="C86" s="50"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="54"/>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
@@ -6678,8 +6795,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="55"/>
-      <c r="C87" s="50"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="54"/>
       <c r="D87" s="30" t="s">
         <v>54</v>
       </c>
@@ -6695,8 +6812,8 @@
       <c r="J87" s="31"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="55"/>
-      <c r="C88" s="50"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="54"/>
       <c r="D88" s="30" t="s">
         <v>54</v>
       </c>
@@ -6712,8 +6829,8 @@
       <c r="J88" s="31"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="55"/>
-      <c r="C89" s="50"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="54"/>
       <c r="D89" s="30" t="s">
         <v>54</v>
       </c>
@@ -6729,8 +6846,8 @@
       <c r="J89" s="31"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="55"/>
-      <c r="C90" s="50"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="54"/>
       <c r="D90" s="30" t="s">
         <v>54</v>
       </c>
@@ -6746,8 +6863,8 @@
       <c r="J90" s="31"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="55"/>
-      <c r="C91" s="50"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="54"/>
       <c r="D91" s="7" t="s">
         <v>54</v>
       </c>
@@ -6763,8 +6880,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="55"/>
-      <c r="C92" s="50"/>
+      <c r="B92" s="59"/>
+      <c r="C92" s="54"/>
       <c r="D92" s="7" t="s">
         <v>54</v>
       </c>
@@ -6780,8 +6897,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="55"/>
-      <c r="C93" s="50"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="54"/>
       <c r="D93" s="7" t="s">
         <v>54</v>
       </c>
@@ -6797,8 +6914,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="55"/>
-      <c r="C94" s="50"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="54"/>
       <c r="D94" s="7" t="s">
         <v>54</v>
       </c>
@@ -6814,8 +6931,8 @@
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="55"/>
-      <c r="C95" s="50"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="54"/>
       <c r="D95" s="7" t="s">
         <v>54</v>
       </c>
@@ -6831,8 +6948,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="55"/>
-      <c r="C96" s="50"/>
+      <c r="B96" s="59"/>
+      <c r="C96" s="54"/>
       <c r="D96" s="7" t="s">
         <v>54</v>
       </c>
@@ -6848,8 +6965,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="55"/>
-      <c r="C97" s="50"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="54"/>
       <c r="D97" s="7" t="s">
         <v>54</v>
       </c>
@@ -6865,8 +6982,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="55"/>
-      <c r="C98" s="50"/>
+      <c r="B98" s="59"/>
+      <c r="C98" s="54"/>
       <c r="D98" s="30" t="s">
         <v>53</v>
       </c>
@@ -6882,8 +6999,8 @@
       <c r="J98" s="31"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="55"/>
-      <c r="C99" s="50"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="54"/>
       <c r="D99" s="30" t="s">
         <v>53</v>
       </c>
@@ -6899,8 +7016,8 @@
       <c r="J99" s="31"/>
     </row>
     <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="55"/>
-      <c r="C100" s="50"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="54"/>
       <c r="D100" s="30" t="s">
         <v>53</v>
       </c>
@@ -6916,8 +7033,8 @@
       <c r="J100" s="31"/>
     </row>
     <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="55"/>
-      <c r="C101" s="50"/>
+      <c r="B101" s="59"/>
+      <c r="C101" s="54"/>
       <c r="D101" s="7" t="s">
         <v>53</v>
       </c>
@@ -6933,8 +7050,8 @@
       <c r="J101" s="4"/>
     </row>
     <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="55"/>
-      <c r="C102" s="50"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="54"/>
       <c r="D102" s="7" t="s">
         <v>53</v>
       </c>
@@ -6950,8 +7067,8 @@
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="55"/>
-      <c r="C103" s="50"/>
+      <c r="B103" s="59"/>
+      <c r="C103" s="54"/>
       <c r="D103" s="7" t="s">
         <v>59</v>
       </c>
@@ -6967,8 +7084,8 @@
       <c r="J103" s="4"/>
     </row>
     <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="55"/>
-      <c r="C104" s="50"/>
+      <c r="B104" s="59"/>
+      <c r="C104" s="54"/>
       <c r="D104" s="30" t="s">
         <v>59</v>
       </c>
@@ -6984,8 +7101,8 @@
       <c r="J104" s="31"/>
     </row>
     <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="55"/>
-      <c r="C105" s="50"/>
+      <c r="B105" s="59"/>
+      <c r="C105" s="54"/>
       <c r="D105" s="30" t="s">
         <v>59</v>
       </c>
@@ -7001,8 +7118,8 @@
       <c r="J105" s="31"/>
     </row>
     <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="55"/>
-      <c r="C106" s="50"/>
+      <c r="B106" s="59"/>
+      <c r="C106" s="54"/>
       <c r="D106" s="30" t="s">
         <v>59</v>
       </c>
@@ -7018,8 +7135,8 @@
       <c r="J106" s="31"/>
     </row>
     <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="55"/>
-      <c r="C107" s="50"/>
+      <c r="B107" s="59"/>
+      <c r="C107" s="54"/>
       <c r="D107" s="30" t="s">
         <v>59</v>
       </c>
@@ -7035,8 +7152,8 @@
       <c r="J107" s="31"/>
     </row>
     <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="55"/>
-      <c r="C108" s="50"/>
+      <c r="B108" s="59"/>
+      <c r="C108" s="54"/>
       <c r="D108" s="30" t="s">
         <v>59</v>
       </c>
@@ -7052,8 +7169,8 @@
       <c r="J108" s="31"/>
     </row>
     <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="55"/>
-      <c r="C109" s="50"/>
+      <c r="B109" s="59"/>
+      <c r="C109" s="54"/>
       <c r="D109" s="30" t="s">
         <v>59</v>
       </c>
@@ -7069,8 +7186,8 @@
       <c r="J109" s="31"/>
     </row>
     <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="55"/>
-      <c r="C110" s="50"/>
+      <c r="B110" s="59"/>
+      <c r="C110" s="54"/>
       <c r="D110" s="30" t="s">
         <v>59</v>
       </c>
@@ -7086,8 +7203,8 @@
       <c r="J110" s="31"/>
     </row>
     <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="55"/>
-      <c r="C111" s="50"/>
+      <c r="B111" s="59"/>
+      <c r="C111" s="54"/>
       <c r="D111" s="30" t="s">
         <v>59</v>
       </c>
@@ -7103,8 +7220,8 @@
       <c r="J111" s="31"/>
     </row>
     <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="55"/>
-      <c r="C112" s="50"/>
+      <c r="B112" s="59"/>
+      <c r="C112" s="54"/>
       <c r="D112" s="7" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +7237,8 @@
       <c r="J112" s="4"/>
     </row>
     <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="55"/>
-      <c r="C113" s="50"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="54"/>
       <c r="D113" s="7" t="s">
         <v>59</v>
       </c>
@@ -7137,8 +7254,8 @@
       <c r="J113" s="4"/>
     </row>
     <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="55"/>
-      <c r="C114" s="50"/>
+      <c r="B114" s="59"/>
+      <c r="C114" s="54"/>
       <c r="D114" s="7" t="s">
         <v>59</v>
       </c>
@@ -7154,8 +7271,8 @@
       <c r="J114" s="4"/>
     </row>
     <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="55"/>
-      <c r="C115" s="50"/>
+      <c r="B115" s="59"/>
+      <c r="C115" s="54"/>
       <c r="D115" s="7" t="s">
         <v>59</v>
       </c>
@@ -7171,8 +7288,8 @@
       <c r="J115" s="4"/>
     </row>
     <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="55"/>
-      <c r="C116" s="50"/>
+      <c r="B116" s="59"/>
+      <c r="C116" s="54"/>
       <c r="D116" s="7" t="s">
         <v>59</v>
       </c>
@@ -7188,8 +7305,8 @@
       <c r="J116" s="4"/>
     </row>
     <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="55"/>
-      <c r="C117" s="50"/>
+      <c r="B117" s="59"/>
+      <c r="C117" s="54"/>
       <c r="D117" s="7" t="s">
         <v>59</v>
       </c>
@@ -7205,8 +7322,8 @@
       <c r="J117" s="4"/>
     </row>
     <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="55"/>
-      <c r="C118" s="50"/>
+      <c r="B118" s="59"/>
+      <c r="C118" s="54"/>
       <c r="D118" s="7" t="s">
         <v>59</v>
       </c>
@@ -7222,8 +7339,8 @@
       <c r="J118" s="4"/>
     </row>
     <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="55"/>
-      <c r="C119" s="50"/>
+      <c r="B119" s="59"/>
+      <c r="C119" s="54"/>
       <c r="D119" s="7" t="s">
         <v>59</v>
       </c>
@@ -7239,8 +7356,8 @@
       <c r="J119" s="4"/>
     </row>
     <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="55"/>
-      <c r="C120" s="50"/>
+      <c r="B120" s="59"/>
+      <c r="C120" s="54"/>
       <c r="D120" s="7" t="s">
         <v>70</v>
       </c>
@@ -7256,8 +7373,8 @@
       <c r="J120" s="4"/>
     </row>
     <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="55"/>
-      <c r="C121" s="50"/>
+      <c r="B121" s="59"/>
+      <c r="C121" s="54"/>
       <c r="D121" s="7" t="s">
         <v>70</v>
       </c>
@@ -7273,8 +7390,8 @@
       <c r="J121" s="4"/>
     </row>
     <row r="122" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="55"/>
-      <c r="C122" s="50"/>
+      <c r="B122" s="59"/>
+      <c r="C122" s="54"/>
       <c r="D122" s="7" t="s">
         <v>70</v>
       </c>
@@ -7290,8 +7407,8 @@
       <c r="J122" s="4"/>
     </row>
     <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="55"/>
-      <c r="C123" s="50"/>
+      <c r="B123" s="59"/>
+      <c r="C123" s="54"/>
       <c r="D123" s="7" t="s">
         <v>70</v>
       </c>
@@ -7307,8 +7424,8 @@
       <c r="J123" s="4"/>
     </row>
     <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="55"/>
-      <c r="C124" s="50"/>
+      <c r="B124" s="59"/>
+      <c r="C124" s="54"/>
       <c r="D124" s="7" t="s">
         <v>70</v>
       </c>
@@ -7324,8 +7441,8 @@
       <c r="J124" s="4"/>
     </row>
     <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="55"/>
-      <c r="C125" s="50"/>
+      <c r="B125" s="59"/>
+      <c r="C125" s="54"/>
       <c r="D125" s="7" t="s">
         <v>70</v>
       </c>
@@ -7341,8 +7458,8 @@
       <c r="J125" s="4"/>
     </row>
     <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="55"/>
-      <c r="C126" s="50"/>
+      <c r="B126" s="59"/>
+      <c r="C126" s="54"/>
       <c r="D126" s="7" t="s">
         <v>70</v>
       </c>
@@ -7358,8 +7475,8 @@
       <c r="J126" s="4"/>
     </row>
     <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="55"/>
-      <c r="C127" s="50"/>
+      <c r="B127" s="59"/>
+      <c r="C127" s="54"/>
       <c r="D127" s="7" t="s">
         <v>70</v>
       </c>
@@ -7375,8 +7492,8 @@
       <c r="J127" s="4"/>
     </row>
     <row r="128" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="55"/>
-      <c r="C128" s="50"/>
+      <c r="B128" s="59"/>
+      <c r="C128" s="54"/>
       <c r="D128" s="7" t="s">
         <v>70</v>
       </c>
@@ -7392,8 +7509,8 @@
       <c r="J128" s="4"/>
     </row>
     <row r="129" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B129" s="55"/>
-      <c r="C129" s="50"/>
+      <c r="B129" s="59"/>
+      <c r="C129" s="54"/>
       <c r="D129" s="7" t="s">
         <v>70</v>
       </c>
@@ -7409,8 +7526,8 @@
       <c r="J129" s="4"/>
     </row>
     <row r="130" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="55"/>
-      <c r="C130" s="50"/>
+      <c r="B130" s="59"/>
+      <c r="C130" s="54"/>
       <c r="D130" s="7" t="s">
         <v>70</v>
       </c>
@@ -7426,8 +7543,8 @@
       <c r="J130" s="4"/>
     </row>
     <row r="131" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B131" s="55"/>
-      <c r="C131" s="50"/>
+      <c r="B131" s="59"/>
+      <c r="C131" s="54"/>
       <c r="D131" s="7" t="s">
         <v>82</v>
       </c>
@@ -7443,8 +7560,8 @@
       <c r="J131" s="4"/>
     </row>
     <row r="132" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B132" s="55"/>
-      <c r="C132" s="50"/>
+      <c r="B132" s="59"/>
+      <c r="C132" s="54"/>
       <c r="D132" s="7" t="s">
         <v>82</v>
       </c>
@@ -7460,8 +7577,8 @@
       <c r="J132" s="4"/>
     </row>
     <row r="133" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="55"/>
-      <c r="C133" s="51"/>
+      <c r="B133" s="59"/>
+      <c r="C133" s="55"/>
       <c r="D133" s="7"/>
       <c r="E133" s="14"/>
       <c r="F133" s="7"/>
@@ -7471,8 +7588,8 @@
       <c r="J133" s="4"/>
     </row>
     <row r="134" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="55"/>
-      <c r="C134" s="58"/>
+      <c r="B134" s="59"/>
+      <c r="C134" s="62"/>
       <c r="D134" s="7"/>
       <c r="E134" s="14"/>
       <c r="F134" s="7"/>
@@ -7482,8 +7599,8 @@
       <c r="J134" s="4"/>
     </row>
     <row r="135" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="55"/>
-      <c r="C135" s="59"/>
+      <c r="B135" s="59"/>
+      <c r="C135" s="63"/>
       <c r="D135" s="7"/>
       <c r="E135" s="14"/>
       <c r="F135" s="7"/>
@@ -7493,8 +7610,8 @@
       <c r="J135" s="4"/>
     </row>
     <row r="136" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="55"/>
-      <c r="C136" s="59"/>
+      <c r="B136" s="59"/>
+      <c r="C136" s="63"/>
       <c r="D136" s="7"/>
       <c r="E136" s="14"/>
       <c r="F136" s="7"/>
@@ -7504,8 +7621,8 @@
       <c r="J136" s="4"/>
     </row>
     <row r="137" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="55"/>
-      <c r="C137" s="59"/>
+      <c r="B137" s="59"/>
+      <c r="C137" s="63"/>
       <c r="D137" s="7"/>
       <c r="E137" s="14"/>
       <c r="F137" s="7"/>
@@ -7515,8 +7632,8 @@
       <c r="J137" s="4"/>
     </row>
     <row r="138" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="55"/>
-      <c r="C138" s="59"/>
+      <c r="B138" s="59"/>
+      <c r="C138" s="63"/>
       <c r="D138" s="7"/>
       <c r="E138" s="14"/>
       <c r="F138" s="7"/>
@@ -7526,8 +7643,8 @@
       <c r="J138" s="4"/>
     </row>
     <row r="139" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B139" s="55"/>
-      <c r="C139" s="59"/>
+      <c r="B139" s="59"/>
+      <c r="C139" s="63"/>
       <c r="D139" s="7"/>
       <c r="E139" s="14"/>
       <c r="F139" s="7"/>
@@ -7537,8 +7654,8 @@
       <c r="J139" s="4"/>
     </row>
     <row r="140" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="55"/>
-      <c r="C140" s="59"/>
+      <c r="B140" s="59"/>
+      <c r="C140" s="63"/>
       <c r="D140" s="7"/>
       <c r="E140" s="14"/>
       <c r="F140" s="7"/>
@@ -7548,8 +7665,8 @@
       <c r="J140" s="4"/>
     </row>
     <row r="141" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="55"/>
-      <c r="C141" s="59"/>
+      <c r="B141" s="59"/>
+      <c r="C141" s="63"/>
       <c r="D141" s="7"/>
       <c r="E141" s="14"/>
       <c r="F141" s="7"/>
@@ -7559,8 +7676,8 @@
       <c r="J141" s="4"/>
     </row>
     <row r="142" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B142" s="55"/>
-      <c r="C142" s="59"/>
+      <c r="B142" s="59"/>
+      <c r="C142" s="63"/>
       <c r="D142" s="7"/>
       <c r="E142" s="14"/>
       <c r="F142" s="7"/>
@@ -7570,8 +7687,8 @@
       <c r="J142" s="4"/>
     </row>
     <row r="143" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B143" s="55"/>
-      <c r="C143" s="59"/>
+      <c r="B143" s="59"/>
+      <c r="C143" s="63"/>
       <c r="D143" s="7"/>
       <c r="E143" s="14"/>
       <c r="F143" s="7"/>
@@ -7581,8 +7698,8 @@
       <c r="J143" s="4"/>
     </row>
     <row r="144" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B144" s="55"/>
-      <c r="C144" s="59"/>
+      <c r="B144" s="59"/>
+      <c r="C144" s="63"/>
       <c r="D144" s="7"/>
       <c r="E144" s="14"/>
       <c r="F144" s="7"/>
@@ -7592,8 +7709,8 @@
       <c r="J144" s="4"/>
     </row>
     <row r="145" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="55"/>
-      <c r="C145" s="59"/>
+      <c r="B145" s="59"/>
+      <c r="C145" s="63"/>
       <c r="D145" s="7"/>
       <c r="E145" s="14"/>
       <c r="F145" s="7"/>
@@ -7603,8 +7720,8 @@
       <c r="J145" s="4"/>
     </row>
     <row r="146" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B146" s="55"/>
-      <c r="C146" s="59"/>
+      <c r="B146" s="59"/>
+      <c r="C146" s="63"/>
       <c r="D146" s="7"/>
       <c r="E146" s="14"/>
       <c r="F146" s="7"/>
@@ -7614,8 +7731,8 @@
       <c r="J146" s="4"/>
     </row>
     <row r="147" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B147" s="55"/>
-      <c r="C147" s="59"/>
+      <c r="B147" s="59"/>
+      <c r="C147" s="63"/>
       <c r="D147" s="7"/>
       <c r="E147" s="14"/>
       <c r="F147" s="7"/>
@@ -7625,8 +7742,8 @@
       <c r="J147" s="4"/>
     </row>
     <row r="148" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B148" s="55"/>
-      <c r="C148" s="59"/>
+      <c r="B148" s="59"/>
+      <c r="C148" s="63"/>
       <c r="D148" s="7"/>
       <c r="E148" s="14"/>
       <c r="F148" s="7"/>
@@ -7636,8 +7753,8 @@
       <c r="J148" s="4"/>
     </row>
     <row r="149" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B149" s="56"/>
-      <c r="C149" s="60"/>
+      <c r="B149" s="60"/>
+      <c r="C149" s="64"/>
       <c r="D149" s="7"/>
       <c r="E149" s="14"/>
       <c r="F149" s="7"/>
@@ -7684,24 +7801,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -7722,10 +7839,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="66" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -7751,8 +7868,8 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="68"/>
-      <c r="C4" s="62"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="66"/>
       <c r="D4" s="45" t="s">
         <v>20</v>
       </c>
@@ -7776,8 +7893,8 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="68"/>
-      <c r="C5" s="62"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="45" t="s">
         <v>20</v>
       </c>
@@ -7801,8 +7918,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="68"/>
-      <c r="C6" s="62"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="45" t="s">
         <v>20</v>
       </c>
@@ -7826,8 +7943,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="68"/>
-      <c r="C7" s="62"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="45" t="s">
         <v>20</v>
       </c>
@@ -7851,8 +7968,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="68"/>
-      <c r="C8" s="62"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
@@ -7876,8 +7993,8 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="68"/>
-      <c r="C9" s="62"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
@@ -7901,8 +8018,8 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="68"/>
-      <c r="C10" s="62"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="45" t="s">
         <v>20</v>
       </c>
@@ -7926,8 +8043,8 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="68"/>
-      <c r="C11" s="62"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="46" t="s">
         <v>21</v>
       </c>
@@ -7951,8 +8068,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="68"/>
-      <c r="C12" s="62"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="46" t="s">
         <v>21</v>
       </c>
@@ -7976,8 +8093,8 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="68"/>
-      <c r="C13" s="62"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="46" t="s">
         <v>21</v>
       </c>
@@ -8001,8 +8118,8 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="68"/>
-      <c r="C14" s="62"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="66"/>
       <c r="D14" s="46" t="s">
         <v>21</v>
       </c>
@@ -8026,8 +8143,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="68"/>
-      <c r="C15" s="62"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="66"/>
       <c r="D15" s="46" t="s">
         <v>21</v>
       </c>
@@ -8051,8 +8168,8 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="68"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="46" t="s">
         <v>21</v>
       </c>
@@ -8076,8 +8193,8 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="68"/>
-      <c r="C17" s="62"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="66"/>
       <c r="D17" s="46" t="s">
         <v>21</v>
       </c>
@@ -8101,8 +8218,8 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="68"/>
-      <c r="C18" s="62"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="66"/>
       <c r="D18" s="46" t="s">
         <v>22</v>
       </c>
@@ -8126,8 +8243,8 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="68"/>
-      <c r="C19" s="62"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="46" t="s">
         <v>22</v>
       </c>
@@ -8151,8 +8268,8 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="68"/>
-      <c r="C20" s="62"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="66"/>
       <c r="D20" s="46" t="s">
         <v>22</v>
       </c>
@@ -8176,8 +8293,8 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="68"/>
-      <c r="C21" s="62"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="46" t="s">
         <v>22</v>
       </c>
@@ -8201,8 +8318,8 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="68"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="66"/>
       <c r="D22" s="46" t="s">
         <v>22</v>
       </c>
@@ -8226,8 +8343,8 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="68"/>
-      <c r="C23" s="62"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="66"/>
       <c r="D23" s="46" t="s">
         <v>22</v>
       </c>
@@ -8251,8 +8368,8 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="68"/>
-      <c r="C24" s="62"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="66"/>
       <c r="D24" s="46" t="s">
         <v>22</v>
       </c>
@@ -8276,8 +8393,8 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="68"/>
-      <c r="C25" s="62"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="66"/>
       <c r="D25" s="46" t="s">
         <v>23</v>
       </c>
@@ -8301,8 +8418,8 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="68"/>
-      <c r="C26" s="62"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="66"/>
       <c r="D26" s="46" t="s">
         <v>23</v>
       </c>
@@ -8326,8 +8443,8 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="68"/>
-      <c r="C27" s="62"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="46" t="s">
         <v>23</v>
       </c>
@@ -8351,8 +8468,8 @@
       </c>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="68"/>
-      <c r="C28" s="62"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="66"/>
       <c r="D28" s="46" t="s">
         <v>23</v>
       </c>
@@ -8376,8 +8493,8 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="68"/>
-      <c r="C29" s="62"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="66"/>
       <c r="D29" s="46" t="s">
         <v>23</v>
       </c>
@@ -8401,8 +8518,8 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="68"/>
-      <c r="C30" s="62"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="66"/>
       <c r="D30" s="46" t="s">
         <v>23</v>
       </c>
@@ -8426,8 +8543,8 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="68"/>
-      <c r="C31" s="62"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="66"/>
       <c r="D31" s="46" t="s">
         <v>23</v>
       </c>
@@ -8451,8 +8568,8 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="68"/>
-      <c r="C32" s="62"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="66"/>
       <c r="D32" s="47" t="s">
         <v>24</v>
       </c>
@@ -8476,8 +8593,8 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="68"/>
-      <c r="C33" s="62"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="66"/>
       <c r="D33" s="47" t="s">
         <v>24</v>
       </c>
@@ -8501,8 +8618,8 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="68"/>
-      <c r="C34" s="62"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="66"/>
       <c r="D34" s="47" t="s">
         <v>24</v>
       </c>
@@ -8526,8 +8643,8 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="68"/>
-      <c r="C35" s="62"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="66"/>
       <c r="D35" s="47" t="s">
         <v>24</v>
       </c>
@@ -8551,8 +8668,8 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="68"/>
-      <c r="C36" s="62"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="66"/>
       <c r="D36" s="47" t="s">
         <v>24</v>
       </c>
@@ -8576,8 +8693,8 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="68"/>
-      <c r="C37" s="62"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="66"/>
       <c r="D37" s="47" t="s">
         <v>24</v>
       </c>
@@ -8601,8 +8718,8 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="68"/>
-      <c r="C38" s="62"/>
+      <c r="B38" s="72"/>
+      <c r="C38" s="66"/>
       <c r="D38" s="47" t="s">
         <v>24</v>
       </c>
@@ -8626,8 +8743,8 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="68"/>
-      <c r="C39" s="62"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="66"/>
       <c r="D39" s="47" t="s">
         <v>24</v>
       </c>
@@ -8651,8 +8768,8 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="68"/>
-      <c r="C40" s="62"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="66"/>
       <c r="D40" s="47" t="s">
         <v>24</v>
       </c>
@@ -8676,8 +8793,8 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="68"/>
-      <c r="C41" s="62"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="66"/>
       <c r="D41" s="47" t="s">
         <v>24</v>
       </c>
@@ -8701,8 +8818,8 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="68"/>
-      <c r="C42" s="62"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="66"/>
       <c r="D42" s="47" t="s">
         <v>24</v>
       </c>
@@ -8726,8 +8843,8 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="68"/>
-      <c r="C43" s="62"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="66"/>
       <c r="D43" s="47" t="s">
         <v>29</v>
       </c>
@@ -8751,8 +8868,8 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="68"/>
-      <c r="C44" s="62"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="66"/>
       <c r="D44" s="47" t="s">
         <v>29</v>
       </c>
@@ -8776,8 +8893,8 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="68"/>
-      <c r="C45" s="62"/>
+      <c r="B45" s="72"/>
+      <c r="C45" s="66"/>
       <c r="D45" s="47" t="s">
         <v>29</v>
       </c>
@@ -8801,8 +8918,8 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="68"/>
-      <c r="C46" s="62"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="66"/>
       <c r="D46" s="47" t="s">
         <v>29</v>
       </c>
@@ -8826,8 +8943,8 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="68"/>
-      <c r="C47" s="62"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="66"/>
       <c r="D47" s="47" t="s">
         <v>29</v>
       </c>
@@ -8851,8 +8968,8 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="68"/>
-      <c r="C48" s="62"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="66"/>
       <c r="D48" s="47" t="s">
         <v>29</v>
       </c>
@@ -8876,8 +8993,8 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="68"/>
-      <c r="C49" s="62"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="66"/>
       <c r="D49" s="47" t="s">
         <v>29</v>
       </c>
@@ -8901,8 +9018,8 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="68"/>
-      <c r="C50" s="62"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="66"/>
       <c r="D50" s="47" t="s">
         <v>29</v>
       </c>
@@ -8926,8 +9043,8 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="68"/>
-      <c r="C51" s="62"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="66"/>
       <c r="D51" s="47" t="s">
         <v>29</v>
       </c>
@@ -8951,8 +9068,8 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="68"/>
-      <c r="C52" s="62"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="66"/>
       <c r="D52" s="47" t="s">
         <v>45</v>
       </c>
@@ -8976,8 +9093,8 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="68"/>
-      <c r="C53" s="62"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="66"/>
       <c r="D53" s="47" t="s">
         <v>45</v>
       </c>
@@ -9001,8 +9118,8 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="68"/>
-      <c r="C54" s="62"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="66"/>
       <c r="D54" s="47" t="s">
         <v>45</v>
       </c>
@@ -9026,8 +9143,8 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="68"/>
-      <c r="C55" s="62"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="66"/>
       <c r="D55" s="47" t="s">
         <v>54</v>
       </c>
@@ -9051,8 +9168,8 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="68"/>
-      <c r="C56" s="62"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="66"/>
       <c r="D56" s="47" t="s">
         <v>54</v>
       </c>
@@ -9076,8 +9193,8 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="68"/>
-      <c r="C57" s="62"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="66"/>
       <c r="D57" s="47" t="s">
         <v>54</v>
       </c>
@@ -9101,8 +9218,8 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="68"/>
-      <c r="C58" s="62"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="66"/>
       <c r="D58" s="47" t="s">
         <v>54</v>
       </c>
@@ -9126,8 +9243,8 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="68"/>
-      <c r="C59" s="62"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="66"/>
       <c r="D59" s="47" t="s">
         <v>54</v>
       </c>
@@ -9151,8 +9268,8 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="68"/>
-      <c r="C60" s="62"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="66"/>
       <c r="D60" s="47" t="s">
         <v>54</v>
       </c>
@@ -9176,8 +9293,8 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="68"/>
-      <c r="C61" s="62"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="66"/>
       <c r="D61" s="47" t="s">
         <v>54</v>
       </c>
@@ -9201,8 +9318,8 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="68"/>
-      <c r="C62" s="62"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="66"/>
       <c r="D62" s="47" t="s">
         <v>53</v>
       </c>
@@ -9226,8 +9343,8 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="68"/>
-      <c r="C63" s="62"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="66"/>
       <c r="D63" s="47" t="s">
         <v>53</v>
       </c>
@@ -9251,8 +9368,8 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="68"/>
-      <c r="C64" s="62"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="66"/>
       <c r="D64" s="47" t="s">
         <v>59</v>
       </c>
@@ -9276,8 +9393,8 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="68"/>
-      <c r="C65" s="62"/>
+      <c r="B65" s="72"/>
+      <c r="C65" s="66"/>
       <c r="D65" s="47" t="s">
         <v>59</v>
       </c>
@@ -9301,8 +9418,8 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="68"/>
-      <c r="C66" s="62"/>
+      <c r="B66" s="72"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="47" t="s">
         <v>59</v>
       </c>
@@ -9326,8 +9443,8 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="68"/>
-      <c r="C67" s="62"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="66"/>
       <c r="D67" s="47" t="s">
         <v>59</v>
       </c>
@@ -9351,8 +9468,8 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="68"/>
-      <c r="C68" s="62"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="66"/>
       <c r="D68" s="47" t="s">
         <v>59</v>
       </c>
@@ -9376,8 +9493,8 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="68"/>
-      <c r="C69" s="62"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="66"/>
       <c r="D69" s="47" t="s">
         <v>59</v>
       </c>
@@ -9401,8 +9518,8 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="68"/>
-      <c r="C70" s="62"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="66"/>
       <c r="D70" s="47" t="s">
         <v>59</v>
       </c>
@@ -9426,8 +9543,8 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="68"/>
-      <c r="C71" s="62"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="66"/>
       <c r="D71" s="47" t="s">
         <v>59</v>
       </c>
@@ -9451,8 +9568,8 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="68"/>
-      <c r="C72" s="62"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="66"/>
       <c r="D72" s="47" t="s">
         <v>59</v>
       </c>
@@ -9476,8 +9593,8 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="68"/>
-      <c r="C73" s="62"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="66"/>
       <c r="D73" s="47" t="s">
         <v>70</v>
       </c>
@@ -9501,8 +9618,8 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="68"/>
-      <c r="C74" s="62"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="66"/>
       <c r="D74" s="47" t="s">
         <v>70</v>
       </c>
@@ -9526,8 +9643,8 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="68"/>
-      <c r="C75" s="62"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="66"/>
       <c r="D75" s="47" t="s">
         <v>70</v>
       </c>
@@ -9551,8 +9668,8 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="68"/>
-      <c r="C76" s="62"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="66"/>
       <c r="D76" s="47" t="s">
         <v>70</v>
       </c>
@@ -9576,8 +9693,8 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="68"/>
-      <c r="C77" s="62"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="66"/>
       <c r="D77" s="47" t="s">
         <v>70</v>
       </c>
@@ -9601,8 +9718,8 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="68"/>
-      <c r="C78" s="62"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="66"/>
       <c r="D78" s="47" t="s">
         <v>70</v>
       </c>
@@ -9626,8 +9743,8 @@
       </c>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="68"/>
-      <c r="C79" s="62"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="66"/>
       <c r="D79" s="47" t="s">
         <v>70</v>
       </c>
@@ -9651,8 +9768,8 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="68"/>
-      <c r="C80" s="62"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="66"/>
       <c r="D80" s="47" t="s">
         <v>70</v>
       </c>
@@ -9676,8 +9793,8 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="68"/>
-      <c r="C81" s="62"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="66"/>
       <c r="D81" s="47" t="s">
         <v>70</v>
       </c>
@@ -9701,8 +9818,8 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="68"/>
-      <c r="C82" s="62"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="66"/>
       <c r="D82" s="47" t="s">
         <v>82</v>
       </c>
@@ -9726,8 +9843,8 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="68"/>
-      <c r="C83" s="62"/>
+      <c r="B83" s="72"/>
+      <c r="C83" s="66"/>
       <c r="D83" s="47" t="s">
         <v>82</v>
       </c>
@@ -9751,8 +9868,8 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="68"/>
-      <c r="C84" s="62"/>
+      <c r="B84" s="72"/>
+      <c r="C84" s="66"/>
       <c r="D84" s="47" t="s">
         <v>148</v>
       </c>
@@ -9776,8 +9893,8 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="68"/>
-      <c r="C85" s="62"/>
+      <c r="B85" s="72"/>
+      <c r="C85" s="66"/>
       <c r="D85" s="47" t="s">
         <v>148</v>
       </c>
@@ -9801,8 +9918,8 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="68"/>
-      <c r="C86" s="63"/>
+      <c r="B86" s="72"/>
+      <c r="C86" s="67"/>
       <c r="D86" s="47"/>
       <c r="E86" s="17"/>
       <c r="F86" s="7"/>
@@ -9812,8 +9929,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="68"/>
-      <c r="C87" s="64" t="s">
+      <c r="B87" s="72"/>
+      <c r="C87" s="68" t="s">
         <v>153</v>
       </c>
       <c r="D87" s="47" t="s">
@@ -9839,8 +9956,8 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="68"/>
-      <c r="C88" s="65"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="69"/>
       <c r="D88" s="47" t="s">
         <v>157</v>
       </c>
@@ -9864,8 +9981,8 @@
       </c>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="68"/>
-      <c r="C89" s="65"/>
+      <c r="B89" s="72"/>
+      <c r="C89" s="69"/>
       <c r="D89" s="47"/>
       <c r="E89" s="14"/>
       <c r="F89" s="38"/>
@@ -9875,8 +9992,8 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="68"/>
-      <c r="C90" s="65"/>
+      <c r="B90" s="72"/>
+      <c r="C90" s="69"/>
       <c r="D90" s="47"/>
       <c r="E90" s="14"/>
       <c r="F90" s="38"/>
@@ -9886,8 +10003,8 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="68"/>
-      <c r="C91" s="65"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="69"/>
       <c r="D91" s="47"/>
       <c r="E91" s="14"/>
       <c r="F91" s="7"/>
@@ -9897,8 +10014,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="68"/>
-      <c r="C92" s="65"/>
+      <c r="B92" s="72"/>
+      <c r="C92" s="69"/>
       <c r="D92" s="47"/>
       <c r="E92" s="14"/>
       <c r="F92" s="7"/>
@@ -9908,8 +10025,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="68"/>
-      <c r="C93" s="66"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="70"/>
       <c r="D93" s="47"/>
       <c r="E93" s="14"/>
       <c r="F93" s="7"/>
@@ -9919,8 +10036,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="68"/>
-      <c r="C94" s="70" t="s">
+      <c r="B94" s="72"/>
+      <c r="C94" s="74" t="s">
         <v>162</v>
       </c>
       <c r="D94" s="47" t="s">
@@ -9946,8 +10063,8 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="68"/>
-      <c r="C95" s="55"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="59"/>
       <c r="D95" s="47"/>
       <c r="E95" s="14"/>
       <c r="F95" s="7"/>
@@ -9957,8 +10074,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="68"/>
-      <c r="C96" s="55"/>
+      <c r="B96" s="72"/>
+      <c r="C96" s="59"/>
       <c r="D96" s="7"/>
       <c r="E96" s="14"/>
       <c r="F96" s="7"/>
@@ -9968,8 +10085,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="68"/>
-      <c r="C97" s="55"/>
+      <c r="B97" s="72"/>
+      <c r="C97" s="59"/>
       <c r="D97" s="7"/>
       <c r="E97" s="14"/>
       <c r="F97" s="7"/>
@@ -9979,8 +10096,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="68"/>
-      <c r="C98" s="55"/>
+      <c r="B98" s="72"/>
+      <c r="C98" s="59"/>
       <c r="D98" s="7"/>
       <c r="E98" s="14"/>
       <c r="F98" s="7"/>
@@ -9990,8 +10107,8 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="69"/>
-      <c r="C99" s="56"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="60"/>
       <c r="D99" s="7"/>
       <c r="E99" s="14"/>
       <c r="F99" s="7"/>
@@ -10035,24 +10152,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="1:12" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10074,10 +10191,10 @@
     </row>
     <row r="3" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="48"/>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="75" t="s">
         <v>191</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -10096,8 +10213,8 @@
     </row>
     <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="48"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="45" t="s">
         <v>194</v>
       </c>
@@ -10114,8 +10231,8 @@
     </row>
     <row r="5" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="48"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="45" t="s">
         <v>195</v>
       </c>
@@ -10132,8 +10249,8 @@
     </row>
     <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="48"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="45" t="s">
         <v>195</v>
       </c>
@@ -10150,8 +10267,8 @@
     </row>
     <row r="7" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="45" t="s">
         <v>196</v>
       </c>
@@ -10168,8 +10285,8 @@
     </row>
     <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="48"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="45" t="s">
         <v>197</v>
       </c>
@@ -10186,8 +10303,8 @@
     </row>
     <row r="9" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="48"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="45" t="s">
         <v>200</v>
       </c>
@@ -10204,50 +10321,50 @@
     </row>
     <row r="10" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="75" t="s">
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="53" t="s">
         <v>238</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
       <c r="J10" s="12"/>
-      <c r="L10" s="74" t="s">
+      <c r="L10" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="75" t="s">
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="53" t="s">
         <v>237</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
       <c r="I11" s="4"/>
       <c r="J11" s="12"/>
-      <c r="L11" s="74" t="s">
+      <c r="L11" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="48"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="45" t="s">
         <v>199</v>
       </c>
@@ -10264,8 +10381,8 @@
     </row>
     <row r="13" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="48"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="45" t="s">
         <v>198</v>
       </c>
@@ -10282,8 +10399,8 @@
     </row>
     <row r="14" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="48"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="45" t="s">
         <v>201</v>
       </c>
@@ -10300,8 +10417,8 @@
     </row>
     <row r="15" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="48"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
       <c r="D15" s="45" t="s">
         <v>211</v>
       </c>
@@ -10318,8 +10435,8 @@
     </row>
     <row r="16" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="48"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
       <c r="D16" s="45" t="s">
         <v>213</v>
       </c>
@@ -10336,50 +10453,50 @@
     </row>
     <row r="17" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="75" t="s">
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="F17" s="77" t="s">
+      <c r="F17" s="53" t="s">
         <v>231</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="4"/>
       <c r="J17" s="12"/>
-      <c r="L17" s="74" t="s">
+      <c r="L17" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="75" t="s">
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="F18" s="77" t="s">
+      <c r="F18" s="53" t="s">
         <v>251</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
       <c r="I18" s="4"/>
       <c r="J18" s="12"/>
-      <c r="L18" s="74" t="s">
+      <c r="L18" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="48"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
       <c r="D19" s="45"/>
       <c r="E19" s="17"/>
       <c r="F19" s="38"/>
@@ -10390,8 +10507,8 @@
     </row>
     <row r="20" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="48"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
       <c r="D20" s="45" t="s">
         <v>148</v>
       </c>
@@ -10408,8 +10525,8 @@
     </row>
     <row r="21" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="48"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
       <c r="D21" s="45"/>
       <c r="E21" s="17"/>
       <c r="F21" s="38"/>
@@ -10420,8 +10537,8 @@
     </row>
     <row r="22" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="73"/>
       <c r="D22" s="45"/>
       <c r="E22" s="17"/>
       <c r="F22" s="38"/>
@@ -10432,8 +10549,8 @@
     </row>
     <row r="23" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="72" t="s">
+      <c r="B23" s="72"/>
+      <c r="C23" s="76" t="s">
         <v>215</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -10452,8 +10569,8 @@
     </row>
     <row r="24" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="48"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
       <c r="D24" s="45" t="s">
         <v>194</v>
       </c>
@@ -10470,8 +10587,8 @@
     </row>
     <row r="25" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="48"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
       <c r="D25" s="45" t="s">
         <v>195</v>
       </c>
@@ -10488,8 +10605,8 @@
     </row>
     <row r="26" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="48"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
       <c r="D26" s="45" t="s">
         <v>195</v>
       </c>
@@ -10506,8 +10623,8 @@
     </row>
     <row r="27" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="48"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="46" t="s">
         <v>196</v>
       </c>
@@ -10524,8 +10641,8 @@
     </row>
     <row r="28" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="48"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
       <c r="D28" s="46" t="s">
         <v>197</v>
       </c>
@@ -10542,8 +10659,8 @@
     </row>
     <row r="29" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="48"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="46" t="s">
         <v>200</v>
       </c>
@@ -10560,8 +10677,8 @@
     </row>
     <row r="30" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="48"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
       <c r="D30" s="46" t="s">
         <v>199</v>
       </c>
@@ -10578,8 +10695,8 @@
     </row>
     <row r="31" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="48"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
       <c r="D31" s="46" t="s">
         <v>198</v>
       </c>
@@ -10596,8 +10713,8 @@
     </row>
     <row r="32" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="48"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
       <c r="D32" s="46" t="s">
         <v>201</v>
       </c>
@@ -10614,8 +10731,8 @@
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="48"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="68"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
       <c r="D33" s="46" t="s">
         <v>211</v>
       </c>
@@ -10632,8 +10749,8 @@
     </row>
     <row r="34" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="48"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
       <c r="D34" s="46" t="s">
         <v>213</v>
       </c>
@@ -10650,8 +10767,8 @@
     </row>
     <row r="35" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="48"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
       <c r="D35" s="46" t="s">
         <v>192</v>
       </c>
@@ -10668,8 +10785,8 @@
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="48"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
       <c r="D36" s="46" t="s">
         <v>192</v>
       </c>
@@ -10686,8 +10803,8 @@
     </row>
     <row r="37" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="48"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
       <c r="D37" s="46" t="s">
         <v>194</v>
       </c>
@@ -10704,8 +10821,8 @@
     </row>
     <row r="38" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="48"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
+      <c r="B38" s="72"/>
+      <c r="C38" s="72"/>
       <c r="D38" s="46" t="s">
         <v>194</v>
       </c>
@@ -10722,8 +10839,8 @@
     </row>
     <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="48"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
       <c r="D39" s="46" t="s">
         <v>221</v>
       </c>
@@ -10740,8 +10857,8 @@
     </row>
     <row r="40" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="48"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
       <c r="D40" s="46" t="s">
         <v>221</v>
       </c>
@@ -10758,8 +10875,8 @@
     </row>
     <row r="41" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="48"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
       <c r="D41" s="46" t="s">
         <v>195</v>
       </c>
@@ -10776,8 +10893,8 @@
     </row>
     <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
       <c r="D42" s="46" t="s">
         <v>195</v>
       </c>
@@ -10794,8 +10911,8 @@
     </row>
     <row r="43" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
       <c r="D43" s="46" t="s">
         <v>24</v>
       </c>
@@ -10812,8 +10929,8 @@
     </row>
     <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="72"/>
       <c r="D44" s="46" t="s">
         <v>24</v>
       </c>
@@ -10830,8 +10947,8 @@
     </row>
     <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="68"/>
+      <c r="B45" s="72"/>
+      <c r="C45" s="72"/>
       <c r="D45" s="46" t="s">
         <v>29</v>
       </c>
@@ -10848,8 +10965,8 @@
     </row>
     <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
       <c r="D46" s="46" t="s">
         <v>29</v>
       </c>
@@ -10866,8 +10983,8 @@
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="48"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
       <c r="D47" s="46" t="s">
         <v>45</v>
       </c>
@@ -10884,8 +11001,8 @@
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="68"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
       <c r="D48" s="46" t="s">
         <v>45</v>
       </c>
@@ -10902,8 +11019,8 @@
     </row>
     <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="48"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="68"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
       <c r="D49" s="46" t="s">
         <v>45</v>
       </c>
@@ -10920,8 +11037,8 @@
     </row>
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="48"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="68"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
       <c r="D50" s="46" t="s">
         <v>54</v>
       </c>
@@ -10938,8 +11055,8 @@
     </row>
     <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="48"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="68"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
       <c r="D51" s="46" t="s">
         <v>54</v>
       </c>
@@ -10956,8 +11073,8 @@
     </row>
     <row r="52" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="48"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="72"/>
       <c r="D52" s="46" t="s">
         <v>53</v>
       </c>
@@ -10974,8 +11091,8 @@
     </row>
     <row r="53" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="48"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="68"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
       <c r="D53" s="46" t="s">
         <v>53</v>
       </c>
@@ -10992,8 +11109,8 @@
     </row>
     <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="48"/>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
       <c r="D54" s="46" t="s">
         <v>201</v>
       </c>
@@ -11010,8 +11127,8 @@
     </row>
     <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="48"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="72"/>
       <c r="D55" s="46" t="s">
         <v>201</v>
       </c>
@@ -11028,8 +11145,8 @@
     </row>
     <row r="56" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="48"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="72"/>
       <c r="D56" s="46" t="s">
         <v>70</v>
       </c>
@@ -11046,8 +11163,8 @@
     </row>
     <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="48"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
       <c r="D57" s="46" t="s">
         <v>70</v>
       </c>
@@ -11064,8 +11181,8 @@
     </row>
     <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="48"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
       <c r="D58" s="46" t="s">
         <v>82</v>
       </c>
@@ -11082,8 +11199,8 @@
     </row>
     <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="48"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="72"/>
       <c r="D59" s="46" t="s">
         <v>82</v>
       </c>
@@ -11100,8 +11217,8 @@
     </row>
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="48"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="72"/>
       <c r="D60" s="46" t="s">
         <v>82</v>
       </c>
@@ -11118,8 +11235,8 @@
     </row>
     <row r="61" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="48"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
       <c r="D61" s="46"/>
       <c r="E61" s="17"/>
       <c r="F61" s="38"/>
@@ -11130,8 +11247,8 @@
     </row>
     <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="48"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
       <c r="D62" s="46" t="s">
         <v>156</v>
       </c>
@@ -11148,8 +11265,8 @@
     </row>
     <row r="63" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="48"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="72"/>
       <c r="D63" s="46" t="s">
         <v>228</v>
       </c>
@@ -11166,8 +11283,8 @@
     </row>
     <row r="64" spans="1:10" ht="49.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="48"/>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="72"/>
       <c r="D64" s="46" t="s">
         <v>228</v>
       </c>
@@ -11184,8 +11301,8 @@
     </row>
     <row r="65" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="48"/>
-      <c r="B65" s="68"/>
-      <c r="C65" s="69"/>
+      <c r="B65" s="72"/>
+      <c r="C65" s="73"/>
       <c r="D65" s="47"/>
       <c r="E65" s="17"/>
       <c r="F65" s="38"/>
@@ -11196,8 +11313,8 @@
     </row>
     <row r="66" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="48"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="B66" s="72"/>
+      <c r="C66" s="72" t="s">
         <v>282</v>
       </c>
       <c r="D66" s="47" t="s">
@@ -11216,8 +11333,8 @@
     </row>
     <row r="67" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="48"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="72"/>
       <c r="D67" s="47" t="s">
         <v>256</v>
       </c>
@@ -11234,8 +11351,8 @@
     </row>
     <row r="68" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="48"/>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
       <c r="D68" s="47" t="s">
         <v>256</v>
       </c>
@@ -11252,8 +11369,8 @@
     </row>
     <row r="69" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="48"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
       <c r="D69" s="47" t="s">
         <v>256</v>
       </c>
@@ -11270,8 +11387,8 @@
     </row>
     <row r="70" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="48"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="72"/>
       <c r="D70" s="47" t="s">
         <v>256</v>
       </c>
@@ -11288,8 +11405,8 @@
     </row>
     <row r="71" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="48"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="68"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="72"/>
       <c r="D71" s="47" t="s">
         <v>256</v>
       </c>
@@ -11306,8 +11423,8 @@
     </row>
     <row r="72" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="48"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="72"/>
       <c r="D72" s="47" t="s">
         <v>256</v>
       </c>
@@ -11324,8 +11441,8 @@
     </row>
     <row r="73" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="48"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="68"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="72"/>
       <c r="D73" s="47" t="s">
         <v>256</v>
       </c>
@@ -11342,8 +11459,8 @@
     </row>
     <row r="74" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="48"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="68"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="72"/>
       <c r="D74" s="47" t="s">
         <v>256</v>
       </c>
@@ -11360,8 +11477,8 @@
     </row>
     <row r="75" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="48"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="68"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="72"/>
       <c r="D75" s="47" t="s">
         <v>256</v>
       </c>
@@ -11378,8 +11495,8 @@
     </row>
     <row r="76" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="48"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="72"/>
       <c r="D76" s="47" t="s">
         <v>256</v>
       </c>
@@ -11396,8 +11513,8 @@
     </row>
     <row r="77" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="48"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="72"/>
       <c r="D77" s="47" t="s">
         <v>256</v>
       </c>
@@ -11414,8 +11531,8 @@
     </row>
     <row r="78" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="48"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="72"/>
       <c r="D78" s="47" t="s">
         <v>256</v>
       </c>
@@ -11432,8 +11549,8 @@
     </row>
     <row r="79" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="48"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
       <c r="D79" s="46" t="s">
         <v>273</v>
       </c>
@@ -11450,8 +11567,8 @@
     </row>
     <row r="80" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="48"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
       <c r="D80" s="46" t="s">
         <v>277</v>
       </c>
@@ -11468,8 +11585,8 @@
     </row>
     <row r="81" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="48"/>
-      <c r="B81" s="68"/>
-      <c r="C81" s="68"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="72"/>
       <c r="D81" s="47"/>
       <c r="E81" s="14"/>
       <c r="F81" s="38"/>
@@ -11480,8 +11597,8 @@
     </row>
     <row r="82" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="48"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="68"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="72"/>
       <c r="D82" s="47"/>
       <c r="E82" s="14"/>
       <c r="F82" s="38"/>
@@ -11492,8 +11609,8 @@
     </row>
     <row r="83" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="48"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68"/>
+      <c r="B83" s="72"/>
+      <c r="C83" s="72"/>
       <c r="D83" s="47"/>
       <c r="E83" s="14"/>
       <c r="F83" s="38"/>
@@ -11538,24 +11655,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -11577,10 +11694,10 @@
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="48"/>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="75" t="s">
         <v>279</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -11599,8 +11716,8 @@
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="48"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="45" t="s">
         <v>194</v>
       </c>
@@ -11617,8 +11734,8 @@
     </row>
     <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="48"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="45" t="s">
         <v>195</v>
       </c>
@@ -11635,8 +11752,8 @@
     </row>
     <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="48"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="45" t="s">
         <v>195</v>
       </c>
@@ -11653,8 +11770,8 @@
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="45" t="s">
         <v>24</v>
       </c>
@@ -11671,8 +11788,8 @@
     </row>
     <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="48"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="45" t="s">
         <v>29</v>
       </c>
@@ -11689,8 +11806,8 @@
     </row>
     <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="48"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="45" t="s">
         <v>45</v>
       </c>
@@ -11707,8 +11824,8 @@
     </row>
     <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
       <c r="D10" s="45" t="s">
         <v>54</v>
       </c>
@@ -11725,8 +11842,8 @@
     </row>
     <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="45" t="s">
         <v>53</v>
       </c>
@@ -11743,8 +11860,8 @@
     </row>
     <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="48"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="45" t="s">
         <v>201</v>
       </c>
@@ -11761,8 +11878,8 @@
     </row>
     <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="48"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="45" t="s">
         <v>70</v>
       </c>
@@ -11779,8 +11896,8 @@
     </row>
     <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="48"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="45" t="s">
         <v>82</v>
       </c>
@@ -11797,8 +11914,8 @@
     </row>
     <row r="15" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="48"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
       <c r="D15" s="45"/>
       <c r="E15" s="17"/>
       <c r="F15" s="38"/>
@@ -11809,8 +11926,8 @@
     </row>
     <row r="16" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="48"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
       <c r="D16" s="45" t="s">
         <v>284</v>
       </c>
@@ -11827,8 +11944,8 @@
     </row>
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
       <c r="D17" s="46" t="s">
         <v>285</v>
       </c>
@@ -11845,8 +11962,8 @@
     </row>
     <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="45"/>
       <c r="E18" s="17"/>
       <c r="F18" s="38"/>
@@ -11857,8 +11974,8 @@
     </row>
     <row r="19" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="48"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="73"/>
       <c r="D19" s="45"/>
       <c r="E19" s="17"/>
       <c r="F19" s="38"/>
@@ -11869,8 +11986,8 @@
     </row>
     <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="48"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="72" t="s">
+      <c r="B20" s="72"/>
+      <c r="C20" s="76" t="s">
         <v>281</v>
       </c>
       <c r="D20" s="47" t="s">
@@ -11889,8 +12006,8 @@
     </row>
     <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="48"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
       <c r="D21" s="47" t="s">
         <v>256</v>
       </c>
@@ -11907,8 +12024,8 @@
     </row>
     <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
       <c r="D22" s="47" t="s">
         <v>256</v>
       </c>
@@ -11925,8 +12042,8 @@
     </row>
     <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
       <c r="D23" s="47" t="s">
         <v>256</v>
       </c>
@@ -11943,8 +12060,8 @@
     </row>
     <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="48"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
       <c r="D24" s="47" t="s">
         <v>256</v>
       </c>
@@ -11961,8 +12078,8 @@
     </row>
     <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="48"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
       <c r="D25" s="47" t="s">
         <v>256</v>
       </c>
@@ -11979,8 +12096,8 @@
     </row>
     <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="48"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
       <c r="D26" s="47" t="s">
         <v>256</v>
       </c>
@@ -11988,7 +12105,7 @@
         <v>258</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
@@ -11997,8 +12114,8 @@
     </row>
     <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="48"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="47" t="s">
         <v>256</v>
       </c>
@@ -12015,8 +12132,8 @@
     </row>
     <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="48"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
       <c r="D28" s="47" t="s">
         <v>256</v>
       </c>
@@ -12033,8 +12150,8 @@
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="48"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="47" t="s">
         <v>256</v>
       </c>
@@ -12051,8 +12168,8 @@
     </row>
     <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="48"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
       <c r="D30" s="47" t="s">
         <v>256</v>
       </c>
@@ -12069,8 +12186,8 @@
     </row>
     <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="48"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
       <c r="D31" s="47" t="s">
         <v>256</v>
       </c>
@@ -12078,7 +12195,7 @@
         <v>258</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
@@ -12087,8 +12204,8 @@
     </row>
     <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="48"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
       <c r="D32" s="47" t="s">
         <v>256</v>
       </c>
@@ -12105,8 +12222,8 @@
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="48"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="68"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
       <c r="D33" s="47"/>
       <c r="E33" s="17"/>
       <c r="F33" s="38"/>
@@ -12117,8 +12234,8 @@
     </row>
     <row r="34" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="48"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
       <c r="D34" s="46" t="s">
         <v>287</v>
       </c>
@@ -12135,8 +12252,8 @@
     </row>
     <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="48"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
       <c r="D35" s="46" t="s">
         <v>287</v>
       </c>
@@ -12153,8 +12270,8 @@
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="48"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
       <c r="D36" s="46"/>
       <c r="E36" s="17"/>
       <c r="F36" s="38"/>
@@ -12165,8 +12282,8 @@
     </row>
     <row r="37" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="48"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
       <c r="D37" s="46"/>
       <c r="E37" s="17"/>
       <c r="F37" s="38"/>
@@ -12177,8 +12294,8 @@
     </row>
     <row r="38" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="48"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
+      <c r="B38" s="72"/>
+      <c r="C38" s="72"/>
       <c r="D38" s="46"/>
       <c r="E38" s="17"/>
       <c r="F38" s="38"/>
@@ -12189,8 +12306,8 @@
     </row>
     <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="48"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="69"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="73"/>
       <c r="D39" s="47"/>
       <c r="E39" s="17"/>
       <c r="F39" s="38"/>
@@ -12199,27 +12316,39 @@
       <c r="I39" s="4"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="48"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="78" t="s">
+      <c r="B40" s="72"/>
+      <c r="C40" s="77" t="s">
         <v>291</v>
       </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="38"/>
+      <c r="D40" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>294</v>
+      </c>
       <c r="G40" s="4"/>
       <c r="H40" s="44"/>
       <c r="I40" s="4"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="48"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="38"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>297</v>
+      </c>
       <c r="G41" s="4"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
@@ -12227,8 +12356,8 @@
     </row>
     <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
       <c r="D42" s="47"/>
       <c r="E42" s="14"/>
       <c r="F42" s="38"/>
@@ -12237,12 +12366,16 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="14"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>300</v>
+      </c>
       <c r="F43" s="38"/>
       <c r="G43" s="4"/>
       <c r="H43" s="5"/>
@@ -12251,8 +12384,8 @@
     </row>
     <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="72"/>
       <c r="D44" s="47"/>
       <c r="E44" s="14"/>
       <c r="F44" s="38"/>
@@ -12263,8 +12396,8 @@
     </row>
     <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="68"/>
+      <c r="B45" s="72"/>
+      <c r="C45" s="72"/>
       <c r="D45" s="47"/>
       <c r="E45" s="14"/>
       <c r="F45" s="38"/>
@@ -12275,8 +12408,8 @@
     </row>
     <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
       <c r="D46" s="47"/>
       <c r="E46" s="14"/>
       <c r="F46" s="38"/>
@@ -12287,8 +12420,8 @@
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="48"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
       <c r="D47" s="47"/>
       <c r="E47" s="14"/>
       <c r="F47" s="38"/>
@@ -12299,8 +12432,8 @@
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="68"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
       <c r="D48" s="47"/>
       <c r="E48" s="14"/>
       <c r="F48" s="38"/>
@@ -12311,8 +12444,8 @@
     </row>
     <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="48"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="68"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
       <c r="D49" s="47"/>
       <c r="E49" s="14"/>
       <c r="F49" s="38"/>
@@ -12323,8 +12456,8 @@
     </row>
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="48"/>
-      <c r="B50" s="69"/>
-      <c r="C50" s="69"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="73"/>
       <c r="D50" s="47"/>
       <c r="E50" s="14"/>
       <c r="F50" s="38"/>
@@ -12369,24 +12502,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="39" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -12407,10 +12540,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="54" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -12428,8 +12561,8 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="55"/>
-      <c r="C4" s="50"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="54"/>
       <c r="D4" s="8" t="s">
         <v>20</v>
       </c>
@@ -12445,8 +12578,8 @@
       <c r="J4" s="12"/>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="55"/>
-      <c r="C5" s="50"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
@@ -12462,8 +12595,8 @@
       <c r="J5" s="12"/>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="55"/>
-      <c r="C6" s="50"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="8" t="s">
         <v>20</v>
       </c>
@@ -12479,8 +12612,8 @@
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="55"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
@@ -12496,8 +12629,8 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="55"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
@@ -12513,8 +12646,8 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="55"/>
-      <c r="C9" s="50"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
@@ -12530,8 +12663,8 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="55"/>
-      <c r="C10" s="50"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="8" t="s">
         <v>20</v>
       </c>
@@ -12547,8 +12680,8 @@
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="55"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
@@ -12564,8 +12697,8 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="55"/>
-      <c r="C12" s="50"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="54"/>
       <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
@@ -12581,8 +12714,8 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="55"/>
-      <c r="C13" s="50"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
@@ -12598,8 +12731,8 @@
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="55"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="6" t="s">
         <v>21</v>
       </c>
@@ -12615,8 +12748,8 @@
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="55"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
@@ -12632,8 +12765,8 @@
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="55"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -12649,8 +12782,8 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="55"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="6" t="s">
         <v>21</v>
       </c>
@@ -12666,8 +12799,8 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="55"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
@@ -12683,8 +12816,8 @@
       <c r="J18" s="12"/>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="55"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="6" t="s">
         <v>22</v>
       </c>
@@ -12700,8 +12833,8 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="55"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="6" t="s">
         <v>22</v>
       </c>
@@ -12717,8 +12850,8 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="55"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
@@ -12734,8 +12867,8 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="55"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
@@ -12751,8 +12884,8 @@
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="55"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
@@ -12768,8 +12901,8 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="55"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="54"/>
       <c r="D24" s="6" t="s">
         <v>22</v>
       </c>
@@ -12785,8 +12918,8 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="55"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="6" t="s">
         <v>23</v>
       </c>
@@ -12802,8 +12935,8 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="55"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="6" t="s">
         <v>23</v>
       </c>
@@ -12819,8 +12952,8 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="55"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="6" t="s">
         <v>23</v>
       </c>
@@ -12836,8 +12969,8 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="55"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="6" t="s">
         <v>23</v>
       </c>
@@ -12853,8 +12986,8 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="55"/>
-      <c r="C29" s="50"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="6" t="s">
         <v>23</v>
       </c>
@@ -12870,8 +13003,8 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="55"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="54"/>
       <c r="D30" s="6" t="s">
         <v>23</v>
       </c>
@@ -12887,8 +13020,8 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="55"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="54"/>
       <c r="D31" s="6" t="s">
         <v>23</v>
       </c>
@@ -12904,8 +13037,8 @@
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="55"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="54"/>
       <c r="D32" s="7" t="s">
         <v>24</v>
       </c>
@@ -12921,8 +13054,8 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="55"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="54"/>
       <c r="D33" s="7" t="s">
         <v>24</v>
       </c>
@@ -12938,8 +13071,8 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="55"/>
-      <c r="C34" s="50"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="54"/>
       <c r="D34" s="7" t="s">
         <v>24</v>
       </c>
@@ -12955,8 +13088,8 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="55"/>
-      <c r="C35" s="50"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="54"/>
       <c r="D35" s="7" t="s">
         <v>24</v>
       </c>
@@ -12972,8 +13105,8 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="55"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="54"/>
       <c r="D36" s="7" t="s">
         <v>24</v>
       </c>
@@ -12989,8 +13122,8 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="55"/>
-      <c r="C37" s="50"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="54"/>
       <c r="D37" s="7" t="s">
         <v>24</v>
       </c>
@@ -13006,8 +13139,8 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="55"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="54"/>
       <c r="D38" s="7" t="s">
         <v>24</v>
       </c>
@@ -13025,8 +13158,8 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="55"/>
-      <c r="C39" s="50"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="54"/>
       <c r="D39" s="7" t="s">
         <v>24</v>
       </c>
@@ -13042,8 +13175,8 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="55"/>
-      <c r="C40" s="50"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="54"/>
       <c r="D40" s="7" t="s">
         <v>24</v>
       </c>
@@ -13061,8 +13194,8 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="55"/>
-      <c r="C41" s="50"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="54"/>
       <c r="D41" s="7" t="s">
         <v>24</v>
       </c>
@@ -13078,8 +13211,8 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="55"/>
-      <c r="C42" s="50"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="54"/>
       <c r="D42" s="7" t="s">
         <v>24</v>
       </c>
@@ -13095,8 +13228,8 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="55"/>
-      <c r="C43" s="50"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="54"/>
       <c r="D43" s="7" t="s">
         <v>29</v>
       </c>
@@ -13112,8 +13245,8 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="55"/>
-      <c r="C44" s="50"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="54"/>
       <c r="D44" s="7" t="s">
         <v>29</v>
       </c>
@@ -13129,8 +13262,8 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="55"/>
-      <c r="C45" s="50"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="7" t="s">
         <v>29</v>
       </c>
@@ -13146,8 +13279,8 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="55"/>
-      <c r="C46" s="50"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="54"/>
       <c r="D46" s="7" t="s">
         <v>29</v>
       </c>
@@ -13163,8 +13296,8 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="55"/>
-      <c r="C47" s="50"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="54"/>
       <c r="D47" s="7" t="s">
         <v>29</v>
       </c>
@@ -13180,8 +13313,8 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="55"/>
-      <c r="C48" s="50"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="54"/>
       <c r="D48" s="7" t="s">
         <v>29</v>
       </c>
@@ -13197,8 +13330,8 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="55"/>
-      <c r="C49" s="50"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="54"/>
       <c r="D49" s="7" t="s">
         <v>29</v>
       </c>
@@ -13214,8 +13347,8 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="55"/>
-      <c r="C50" s="50"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="54"/>
       <c r="D50" s="7" t="s">
         <v>29</v>
       </c>
@@ -13231,8 +13364,8 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="55"/>
-      <c r="C51" s="50"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="54"/>
       <c r="D51" s="7" t="s">
         <v>29</v>
       </c>
@@ -13248,8 +13381,8 @@
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="55"/>
-      <c r="C52" s="50"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="54"/>
       <c r="D52" s="7" t="s">
         <v>45</v>
       </c>
@@ -13265,8 +13398,8 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="55"/>
-      <c r="C53" s="50"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="7" t="s">
         <v>45</v>
       </c>
@@ -13282,8 +13415,8 @@
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="55"/>
-      <c r="C54" s="50"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="7" t="s">
         <v>45</v>
       </c>
@@ -13299,8 +13432,8 @@
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="55"/>
-      <c r="C55" s="50"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="54"/>
       <c r="D55" s="7" t="s">
         <v>54</v>
       </c>
@@ -13316,8 +13449,8 @@
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="55"/>
-      <c r="C56" s="50"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="54"/>
       <c r="D56" s="7" t="s">
         <v>54</v>
       </c>
@@ -13333,8 +13466,8 @@
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="55"/>
-      <c r="C57" s="50"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="54"/>
       <c r="D57" s="7" t="s">
         <v>54</v>
       </c>
@@ -13350,8 +13483,8 @@
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="55"/>
-      <c r="C58" s="50"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="54"/>
       <c r="D58" s="7" t="s">
         <v>54</v>
       </c>
@@ -13367,8 +13500,8 @@
       <c r="J58" s="4"/>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="55"/>
-      <c r="C59" s="50"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="54"/>
       <c r="D59" s="7" t="s">
         <v>54</v>
       </c>
@@ -13384,8 +13517,8 @@
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="55"/>
-      <c r="C60" s="50"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="54"/>
       <c r="D60" s="7" t="s">
         <v>54</v>
       </c>
@@ -13401,8 +13534,8 @@
       <c r="J60" s="4"/>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="55"/>
-      <c r="C61" s="50"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="54"/>
       <c r="D61" s="7" t="s">
         <v>54</v>
       </c>
@@ -13418,8 +13551,8 @@
       <c r="J61" s="4"/>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="55"/>
-      <c r="C62" s="50"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="54"/>
       <c r="D62" s="7" t="s">
         <v>53</v>
       </c>
@@ -13435,8 +13568,8 @@
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="55"/>
-      <c r="C63" s="50"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="54"/>
       <c r="D63" s="7" t="s">
         <v>53</v>
       </c>
@@ -13452,8 +13585,8 @@
       <c r="J63" s="4"/>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="55"/>
-      <c r="C64" s="50"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="54"/>
       <c r="D64" s="7" t="s">
         <v>59</v>
       </c>
@@ -13469,8 +13602,8 @@
       <c r="J64" s="4"/>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="55"/>
-      <c r="C65" s="50"/>
+      <c r="B65" s="59"/>
+      <c r="C65" s="54"/>
       <c r="D65" s="7" t="s">
         <v>59</v>
       </c>
@@ -13488,8 +13621,8 @@
       <c r="J65" s="4"/>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="55"/>
-      <c r="C66" s="50"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="54"/>
       <c r="D66" s="7" t="s">
         <v>59</v>
       </c>
@@ -13505,8 +13638,8 @@
       <c r="J66" s="4"/>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="55"/>
-      <c r="C67" s="50"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="54"/>
       <c r="D67" s="7" t="s">
         <v>59</v>
       </c>
@@ -13524,8 +13657,8 @@
       <c r="J67" s="4"/>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="55"/>
-      <c r="C68" s="50"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="54"/>
       <c r="D68" s="7" t="s">
         <v>59</v>
       </c>
@@ -13543,8 +13676,8 @@
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="55"/>
-      <c r="C69" s="50"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="54"/>
       <c r="D69" s="7" t="s">
         <v>59</v>
       </c>
@@ -13562,8 +13695,8 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="55"/>
-      <c r="C70" s="50"/>
+      <c r="B70" s="59"/>
+      <c r="C70" s="54"/>
       <c r="D70" s="7" t="s">
         <v>59</v>
       </c>
@@ -13581,8 +13714,8 @@
       <c r="J70" s="4"/>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="55"/>
-      <c r="C71" s="50"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="54"/>
       <c r="D71" s="7" t="s">
         <v>59</v>
       </c>
@@ -13598,8 +13731,8 @@
       <c r="J71" s="4"/>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="55"/>
-      <c r="C72" s="50"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="54"/>
       <c r="D72" s="7" t="s">
         <v>59</v>
       </c>
@@ -13615,8 +13748,8 @@
       <c r="J72" s="4"/>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="55"/>
-      <c r="C73" s="50"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="54"/>
       <c r="D73" s="7" t="s">
         <v>70</v>
       </c>
@@ -13632,8 +13765,8 @@
       <c r="J73" s="4"/>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="55"/>
-      <c r="C74" s="50"/>
+      <c r="B74" s="59"/>
+      <c r="C74" s="54"/>
       <c r="D74" s="7" t="s">
         <v>70</v>
       </c>
@@ -13649,8 +13782,8 @@
       <c r="J74" s="4"/>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="55"/>
-      <c r="C75" s="50"/>
+      <c r="B75" s="59"/>
+      <c r="C75" s="54"/>
       <c r="D75" s="7" t="s">
         <v>70</v>
       </c>
@@ -13668,8 +13801,8 @@
       <c r="J75" s="4"/>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="55"/>
-      <c r="C76" s="50"/>
+      <c r="B76" s="59"/>
+      <c r="C76" s="54"/>
       <c r="D76" s="7" t="s">
         <v>70</v>
       </c>
@@ -13685,8 +13818,8 @@
       <c r="J76" s="4"/>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="55"/>
-      <c r="C77" s="50"/>
+      <c r="B77" s="59"/>
+      <c r="C77" s="54"/>
       <c r="D77" s="7" t="s">
         <v>70</v>
       </c>
@@ -13702,8 +13835,8 @@
       <c r="J77" s="4"/>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="55"/>
-      <c r="C78" s="50"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="54"/>
       <c r="D78" s="7" t="s">
         <v>70</v>
       </c>
@@ -13719,8 +13852,8 @@
       <c r="J78" s="4"/>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="55"/>
-      <c r="C79" s="50"/>
+      <c r="B79" s="59"/>
+      <c r="C79" s="54"/>
       <c r="D79" s="7" t="s">
         <v>70</v>
       </c>
@@ -13736,8 +13869,8 @@
       <c r="J79" s="4"/>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="55"/>
-      <c r="C80" s="50"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="54"/>
       <c r="D80" s="7" t="s">
         <v>70</v>
       </c>
@@ -13753,8 +13886,8 @@
       <c r="J80" s="4"/>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="55"/>
-      <c r="C81" s="50"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="54"/>
       <c r="D81" s="7" t="s">
         <v>70</v>
       </c>
@@ -13770,8 +13903,8 @@
       <c r="J81" s="4"/>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="55"/>
-      <c r="C82" s="50"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="54"/>
       <c r="D82" s="7" t="s">
         <v>82</v>
       </c>
@@ -13787,8 +13920,8 @@
       <c r="J82" s="4"/>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="55"/>
-      <c r="C83" s="50"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="54"/>
       <c r="D83" s="7" t="s">
         <v>82</v>
       </c>
@@ -13804,8 +13937,8 @@
       <c r="J83" s="4"/>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="55"/>
-      <c r="C84" s="50"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="54"/>
       <c r="D84" s="7" t="s">
         <v>148</v>
       </c>
@@ -13821,8 +13954,8 @@
       <c r="J84" s="4"/>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="55"/>
-      <c r="C85" s="50"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="54"/>
       <c r="D85" s="7" t="s">
         <v>148</v>
       </c>
@@ -13838,8 +13971,8 @@
       <c r="J85" s="4"/>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="55"/>
-      <c r="C86" s="51"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="55"/>
       <c r="D86" s="7"/>
       <c r="E86" s="17"/>
       <c r="F86" s="7"/>
@@ -13849,8 +13982,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="55"/>
-      <c r="C87" s="64" t="s">
+      <c r="B87" s="59"/>
+      <c r="C87" s="68" t="s">
         <v>153</v>
       </c>
       <c r="D87" s="7" t="s">
@@ -13868,8 +14001,8 @@
       <c r="J87" s="4"/>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="55"/>
-      <c r="C88" s="65"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="69"/>
       <c r="D88" s="7" t="s">
         <v>157</v>
       </c>
@@ -13885,8 +14018,8 @@
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="55"/>
-      <c r="C89" s="65"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="69"/>
       <c r="D89" s="7"/>
       <c r="E89" s="14"/>
       <c r="F89" s="38"/>
@@ -13896,8 +14029,8 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="55"/>
-      <c r="C90" s="65"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="69"/>
       <c r="D90" s="7"/>
       <c r="E90" s="14"/>
       <c r="F90" s="38"/>
@@ -13907,8 +14040,8 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="55"/>
-      <c r="C91" s="65"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="69"/>
       <c r="D91" s="7"/>
       <c r="E91" s="14"/>
       <c r="F91" s="7"/>
@@ -13918,8 +14051,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="55"/>
-      <c r="C92" s="65"/>
+      <c r="B92" s="59"/>
+      <c r="C92" s="69"/>
       <c r="D92" s="7"/>
       <c r="E92" s="14"/>
       <c r="F92" s="7"/>
@@ -13929,8 +14062,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="55"/>
-      <c r="C93" s="66"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="70"/>
       <c r="D93" s="7"/>
       <c r="E93" s="14"/>
       <c r="F93" s="7"/>
@@ -13940,8 +14073,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="55"/>
-      <c r="C94" s="70" t="s">
+      <c r="B94" s="59"/>
+      <c r="C94" s="74" t="s">
         <v>162</v>
       </c>
       <c r="D94" s="7" t="s">
@@ -13959,8 +14092,8 @@
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="55"/>
-      <c r="C95" s="55"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="59"/>
       <c r="D95" s="7"/>
       <c r="E95" s="14"/>
       <c r="F95" s="7"/>
@@ -13970,8 +14103,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="55"/>
-      <c r="C96" s="55"/>
+      <c r="B96" s="59"/>
+      <c r="C96" s="59"/>
       <c r="D96" s="7"/>
       <c r="E96" s="14"/>
       <c r="F96" s="7"/>
@@ -13981,8 +14114,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="55"/>
-      <c r="C97" s="55"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="59"/>
       <c r="D97" s="7"/>
       <c r="E97" s="14"/>
       <c r="F97" s="7"/>
@@ -13992,8 +14125,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="55"/>
-      <c r="C98" s="55"/>
+      <c r="B98" s="59"/>
+      <c r="C98" s="59"/>
       <c r="D98" s="7"/>
       <c r="E98" s="14"/>
       <c r="F98" s="7"/>
@@ -14003,8 +14136,8 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="56"/>
-      <c r="C99" s="56"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="60"/>
       <c r="D99" s="7"/>
       <c r="E99" s="14"/>
       <c r="F99" s="7"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F507BB-2B29-42ED-9858-13BF77D9FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4E75DC-E3C4-4F03-B7E2-3C9502B04CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="303">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -4324,6 +4324,23 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面へ遷移</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11709,7 +11726,9 @@
       <c r="F3" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="10" t="s">
+        <v>302</v>
+      </c>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -11727,7 +11746,9 @@
       <c r="F4" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H4" s="13"/>
       <c r="I4" s="4"/>
       <c r="J4" s="12"/>
@@ -11745,7 +11766,9 @@
       <c r="F5" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H5" s="13"/>
       <c r="I5" s="4"/>
       <c r="J5" s="12"/>
@@ -11763,7 +11786,9 @@
       <c r="F6" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H6" s="13"/>
       <c r="I6" s="4"/>
       <c r="J6" s="12"/>
@@ -11781,7 +11806,9 @@
       <c r="F7" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H7" s="13"/>
       <c r="I7" s="4"/>
       <c r="J7" s="12"/>
@@ -11799,7 +11826,9 @@
       <c r="F8" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H8" s="13"/>
       <c r="I8" s="4"/>
       <c r="J8" s="12"/>
@@ -11817,7 +11846,9 @@
       <c r="F9" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="4"/>
       <c r="J9" s="12"/>
@@ -11835,7 +11866,9 @@
       <c r="F10" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
       <c r="J10" s="12"/>
@@ -11853,7 +11886,9 @@
       <c r="F11" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H11" s="13"/>
       <c r="I11" s="4"/>
       <c r="J11" s="12"/>
@@ -11871,7 +11906,9 @@
       <c r="F12" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H12" s="13"/>
       <c r="I12" s="4"/>
       <c r="J12" s="12"/>
@@ -11889,7 +11926,9 @@
       <c r="F13" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H13" s="13"/>
       <c r="I13" s="4"/>
       <c r="J13" s="12"/>
@@ -11907,7 +11946,9 @@
       <c r="F14" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="H14" s="13"/>
       <c r="I14" s="4"/>
       <c r="J14" s="12"/>
@@ -12376,7 +12417,9 @@
       <c r="E43" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="F43" s="38"/>
+      <c r="F43" s="38" t="s">
+        <v>301</v>
+      </c>
       <c r="G43" s="4"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4E75DC-E3C4-4F03-B7E2-3C9502B04CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0833513E-F66B-4E3F-BDAA-153095D4FD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="309">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -4228,22 +4228,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>"男"を選択したならば”０”、”女”を選択したならば”１”がデータベース「gender」カラムに登録されている</t>
-    <rPh sb="1" eb="2">
-      <t>オトコ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>オンナ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データベース「authority」カラムへ情報が登録されている</t>
     <rPh sb="21" eb="23">
       <t>ジョウホウ</t>
@@ -4258,47 +4242,6 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>ケンゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"一般"を選択したならば”０”、”管理者”を選択したならば”１”がデータベース「authority」カラムに登録されている</t>
-    <rPh sb="1" eb="3">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面にてすべて入力後、アカウント登録確認画面にて「登録する」押下</t>
-    <rPh sb="5" eb="9">
-      <t>トウロクガメン</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>ニュウリョクゴ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4342,6 +4285,159 @@
     <rPh sb="0" eb="2">
       <t>ジシン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・性別欄にて”男を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムに”０”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・性別欄にて”女を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムに”１”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・アカウント権限欄にて”一般を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムに”０”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムに”１”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PC/chrome</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7881,7 +7977,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -11657,7 +11753,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -11727,11 +11823,17 @@
         <v>240</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
+        <v>299</v>
+      </c>
+      <c r="H3" s="11">
+        <v>45981</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="48"/>
@@ -11747,11 +11849,17 @@
         <v>241</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H4" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="48"/>
@@ -11767,11 +11875,17 @@
         <v>242</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H5" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="48"/>
@@ -11787,11 +11901,17 @@
         <v>243</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H6" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48"/>
@@ -11807,11 +11927,17 @@
         <v>244</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H7" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="48"/>
@@ -11827,11 +11953,17 @@
         <v>245</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H8" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="48"/>
@@ -11847,11 +11979,17 @@
         <v>246</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H9" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
@@ -11867,11 +12005,17 @@
         <v>247</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H10" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
@@ -11887,11 +12031,17 @@
         <v>209</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H11" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="48"/>
@@ -11907,11 +12057,17 @@
         <v>248</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H12" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="48"/>
@@ -11927,11 +12083,17 @@
         <v>249</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H13" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="48"/>
@@ -11947,11 +12109,17 @@
         <v>250</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="12"/>
+        <v>299</v>
+      </c>
+      <c r="H14" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="48"/>
@@ -11978,10 +12146,16 @@
       <c r="F16" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="13"/>
+      <c r="G16" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H16" s="13">
+        <v>45981</v>
+      </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="12"/>
+      <c r="J16" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
@@ -11996,10 +12170,16 @@
       <c r="F17" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="13"/>
+      <c r="G17" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H17" s="13">
+        <v>45981</v>
+      </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="12"/>
+      <c r="J17" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
@@ -12236,7 +12416,7 @@
         <v>258</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
@@ -12357,7 +12537,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="48"/>
       <c r="B40" s="72"/>
       <c r="C40" s="77" t="s">
@@ -12367,58 +12547,64 @@
         <v>292</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="44"/>
       <c r="I40" s="4"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="48"/>
       <c r="B41" s="72"/>
       <c r="C41" s="72"/>
-      <c r="D41" s="46" t="s">
-        <v>296</v>
+      <c r="D41" s="47" t="s">
+        <v>292</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
       <c r="B42" s="72"/>
       <c r="C42" s="72"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="38"/>
+      <c r="D42" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>305</v>
+      </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
       <c r="B43" s="72"/>
       <c r="C43" s="72"/>
       <c r="D43" s="46" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="5"/>
@@ -12429,21 +12615,27 @@
       <c r="A44" s="48"/>
       <c r="B44" s="72"/>
       <c r="C44" s="72"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="14"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="17"/>
       <c r="F44" s="38"/>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
       <c r="B45" s="72"/>
       <c r="C45" s="72"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="38"/>
+      <c r="D45" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>298</v>
+      </c>
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
       <c r="I45" s="4"/>
@@ -12475,8 +12667,8 @@
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
       <c r="D48" s="47"/>
       <c r="E48" s="14"/>
       <c r="F48" s="38"/>
@@ -12485,39 +12677,15 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="48"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="48"/>
-      <c r="B50" s="73"/>
-      <c r="C50" s="73"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="49" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B50"/>
+    <mergeCell ref="B3:B48"/>
     <mergeCell ref="C3:C19"/>
     <mergeCell ref="C20:C39"/>
-    <mergeCell ref="C40:C50"/>
+    <mergeCell ref="C40:C48"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0833513E-F66B-4E3F-BDAA-153095D4FD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EC1937-7F94-47DD-8A6E-6F30BE1A5223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="309">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -12220,10 +12220,18 @@
       <c r="F20" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="12"/>
+      <c r="G20" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H20" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="48"/>
@@ -12238,10 +12246,18 @@
       <c r="F21" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="12"/>
+      <c r="G21" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H21" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
@@ -12256,10 +12272,18 @@
       <c r="F22" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="12"/>
+      <c r="G22" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H22" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
@@ -12274,10 +12298,18 @@
       <c r="F23" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="12"/>
+      <c r="G23" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="48"/>
@@ -12292,10 +12324,18 @@
       <c r="F24" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="12"/>
+      <c r="G24" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H24" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="48"/>
@@ -12310,10 +12350,18 @@
       <c r="F25" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="12"/>
+      <c r="G25" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H25" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="48"/>
@@ -12328,10 +12376,18 @@
       <c r="F26" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="12"/>
+      <c r="G26" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H26" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="48"/>
@@ -12346,10 +12402,18 @@
       <c r="F27" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="12"/>
+      <c r="G27" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H27" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="48"/>
@@ -12364,10 +12428,18 @@
       <c r="F28" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="12"/>
+      <c r="G28" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="48"/>
@@ -12382,10 +12454,18 @@
       <c r="F29" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="12"/>
+      <c r="G29" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H29" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="48"/>
@@ -12400,10 +12480,18 @@
       <c r="F30" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="12"/>
+      <c r="G30" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H30" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="48"/>
@@ -12418,10 +12506,18 @@
       <c r="F31" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="12"/>
+      <c r="G31" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H31" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="48"/>
@@ -12436,10 +12532,18 @@
       <c r="F32" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="12"/>
+      <c r="G32" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H32" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="48"/>
@@ -12466,10 +12570,18 @@
       <c r="F34" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="12"/>
+      <c r="G34" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H34" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="48"/>
@@ -12484,10 +12596,18 @@
       <c r="F35" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="12"/>
+      <c r="G35" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H35" s="13">
+        <v>45981</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="48"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EC1937-7F94-47DD-8A6E-6F30BE1A5223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EFA52-AD3E-4D21-85FC-44336CF3CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="309">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -12672,10 +12672,18 @@
       <c r="F40" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="12"/>
+      <c r="G40" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H40" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="41" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="48"/>
@@ -12690,10 +12698,18 @@
       <c r="F41" s="38" t="s">
         <v>303</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H41" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
@@ -12708,10 +12724,18 @@
       <c r="F42" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H42" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
@@ -12726,10 +12750,18 @@
       <c r="F43" s="38" t="s">
         <v>306</v>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H43" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
@@ -12756,10 +12788,18 @@
       <c r="F45" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
+      <c r="G45" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H45" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EFA52-AD3E-4D21-85FC-44336CF3CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FCF4EE-B1E9-43B1-8050-538CEBA31EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="309">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -2243,19 +2243,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレスとしての正しい形式でなくても入力できてしまう</t>
-    <rPh sb="11" eb="12">
-      <t>タダ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>なし　（「これらのオプションから選択してください」）</t>
     <rPh sb="16" eb="18">
       <t>センタク</t>
@@ -2283,74 +2270,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>＠２回以上でも可能となってしまう</t>
-    <rPh sb="2" eb="5">
-      <t>カイイジョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>市区町村での数字の入力も可能となる
-（入力規制したほうがいいのでは）</t>
-    <rPh sb="0" eb="4">
-      <t>シクチョウソン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>スウジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>ニュウリョクキセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>なし　※総合テストに記載あり</t>
     <rPh sb="4" eb="6">
       <t>ソウゴウ</t>
     </rPh>
     <rPh sb="10" eb="12">
       <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>市区町村の入力においてハイフンは不要ではないか</t>
-    <rPh sb="0" eb="4">
-      <t>シクチョウソン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>フヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マンション名等で英字の入力が必要なケースもあるのではないか</t>
-    <rPh sb="5" eb="6">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>エイジ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4288,10 +4213,171 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アカウント登録画面・性別欄にて”男を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <t>データベース「gender」カラムに”０”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「gender」カラムに”１”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムに”０”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース「authority」カラムに”１”と登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PC/chrome</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録完了
+（郵便番号）</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面にて”０から始まる７桁”を入力し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・アカウント権限欄にて”一般”を選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・アカウント権限欄にて”管理者”を選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>ニュウリョクゴ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント登録画面・性別欄にて”女”を選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <rPh sb="5" eb="9">
+      <t>トウロクガメン</t>
+    </rPh>
     <rPh sb="10" eb="12">
       <t>セイベツ</t>
     </rPh>
@@ -4299,7 +4385,7 @@
       <t>ラン</t>
     </rPh>
     <rPh sb="16" eb="17">
-      <t>オトコ</t>
+      <t>オンナ</t>
     </rPh>
     <rPh sb="19" eb="21">
       <t>センタク</t>
@@ -4331,11 +4417,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「gender」カラムに”０”と登録されている</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面・性別欄にて”女を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
+    <t>アカウント登録画面・性別欄にて”男”を選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
     <rPh sb="5" eb="9">
       <t>トウロクガメン</t>
     </rPh>
@@ -4346,7 +4428,7 @@
       <t>ラン</t>
     </rPh>
     <rPh sb="16" eb="17">
-      <t>オンナ</t>
+      <t>オトコ</t>
     </rPh>
     <rPh sb="19" eb="21">
       <t>センタク</t>
@@ -4378,66 +4460,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データベース「gender」カラムに”１”と登録されている</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アカウント登録画面・アカウント権限欄にて”一般を”選択し、すべて入力後「確認する」押下、そしてアカウント登録確認画面にて「登録する」押下</t>
-    <rPh sb="5" eb="9">
-      <t>トウロクガメン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="32" eb="35">
-      <t>ニュウリョクゴ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データベース「authority」カラムに”０”と登録されている</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データベース「authority」カラムに”１”と登録されている</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>なし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PC/chrome</t>
+    <t>データベース「postal_code」カラムへ入力した内容が登録されている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あり
+（１桁目の０が表示されていない）</t>
+    <rPh sb="5" eb="7">
+      <t>ケタメ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4544,7 +4578,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4566,6 +4600,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4756,7 +4796,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4993,6 +5033,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7977,7 +8038,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8849,7 +8910,7 @@
         <v>45974</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>166</v>
@@ -8899,7 +8960,7 @@
         <v>45974</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>166</v>
@@ -9199,7 +9260,7 @@
         <v>45974</v>
       </c>
       <c r="I52" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>166</v>
@@ -9224,7 +9285,7 @@
         <v>45974</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>166</v>
@@ -9249,7 +9310,7 @@
         <v>45974</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>166</v>
@@ -9274,7 +9335,7 @@
         <v>45974</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>166</v>
@@ -9299,7 +9360,7 @@
         <v>45974</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J56" s="12" t="s">
         <v>166</v>
@@ -9324,7 +9385,7 @@
         <v>45974</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>166</v>
@@ -9349,7 +9410,7 @@
         <v>45974</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>166</v>
@@ -9374,7 +9435,7 @@
         <v>45974</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>166</v>
@@ -9399,7 +9460,7 @@
         <v>45974</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J60" s="12" t="s">
         <v>166</v>
@@ -9424,7 +9485,7 @@
         <v>45974</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J61" s="12" t="s">
         <v>166</v>
@@ -9449,7 +9510,7 @@
         <v>45974</v>
       </c>
       <c r="I62" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J62" s="12" t="s">
         <v>166</v>
@@ -9474,7 +9535,7 @@
         <v>45974</v>
       </c>
       <c r="I63" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>166</v>
@@ -9499,7 +9560,7 @@
         <v>45974</v>
       </c>
       <c r="I64" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J64" s="12" t="s">
         <v>166</v>
@@ -9524,7 +9585,7 @@
         <v>45974</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>166</v>
@@ -9549,7 +9610,7 @@
         <v>45974</v>
       </c>
       <c r="I66" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>166</v>
@@ -9574,7 +9635,7 @@
         <v>45974</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>166</v>
@@ -9599,7 +9660,7 @@
         <v>45974</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J68" s="12" t="s">
         <v>166</v>
@@ -9624,7 +9685,7 @@
         <v>45974</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J69" s="12" t="s">
         <v>166</v>
@@ -9649,7 +9710,7 @@
         <v>45974</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J70" s="12" t="s">
         <v>166</v>
@@ -9674,7 +9735,7 @@
         <v>45974</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>166</v>
@@ -9699,7 +9760,7 @@
         <v>45974</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J72" s="12" t="s">
         <v>166</v>
@@ -9724,7 +9785,7 @@
         <v>45974</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J73" s="12" t="s">
         <v>166</v>
@@ -9737,7 +9798,7 @@
         <v>70</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>9</v>
@@ -9749,7 +9810,7 @@
         <v>45974</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>166</v>
@@ -9762,7 +9823,7 @@
         <v>70</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>28</v>
@@ -9774,7 +9835,7 @@
         <v>45974</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J75" s="12" t="s">
         <v>166</v>
@@ -9787,7 +9848,7 @@
         <v>70</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>9</v>
@@ -9799,7 +9860,7 @@
         <v>45974</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J76" s="12" t="s">
         <v>166</v>
@@ -9812,7 +9873,7 @@
         <v>70</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>9</v>
@@ -9824,7 +9885,7 @@
         <v>45974</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>166</v>
@@ -9837,7 +9898,7 @@
         <v>70</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>9</v>
@@ -9849,7 +9910,7 @@
         <v>45974</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>166</v>
@@ -9862,7 +9923,7 @@
         <v>70</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>9</v>
@@ -9874,7 +9935,7 @@
         <v>45974</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>166</v>
@@ -9887,7 +9948,7 @@
         <v>70</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>28</v>
@@ -9899,7 +9960,7 @@
         <v>45974</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>166</v>
@@ -9912,7 +9973,7 @@
         <v>70</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>9</v>
@@ -9924,7 +9985,7 @@
         <v>45974</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>166</v>
@@ -9949,7 +10010,7 @@
         <v>45974</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J82" s="12" t="s">
         <v>166</v>
@@ -9974,7 +10035,7 @@
         <v>45974</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>166</v>
@@ -9999,7 +10060,7 @@
         <v>45974</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J84" s="12" t="s">
         <v>166</v>
@@ -10024,7 +10085,7 @@
         <v>45974</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J85" s="12" t="s">
         <v>166</v>
@@ -10062,7 +10123,7 @@
         <v>45974</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>166</v>
@@ -10087,7 +10148,7 @@
         <v>45974</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J88" s="12" t="s">
         <v>166</v>
@@ -10169,7 +10230,7 @@
         <v>45974</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J94" s="12" t="s">
         <v>166</v>
@@ -10308,16 +10369,16 @@
         <v>66</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
@@ -10329,13 +10390,13 @@
       <c r="B4" s="72"/>
       <c r="C4" s="72"/>
       <c r="D4" s="45" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E4" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>236</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>241</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
@@ -10347,13 +10408,13 @@
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
       <c r="D5" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
@@ -10365,13 +10426,13 @@
       <c r="B6" s="72"/>
       <c r="C6" s="72"/>
       <c r="D6" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
@@ -10383,13 +10444,13 @@
       <c r="B7" s="72"/>
       <c r="C7" s="72"/>
       <c r="D7" s="45" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
@@ -10401,13 +10462,13 @@
       <c r="B8" s="72"/>
       <c r="C8" s="72"/>
       <c r="D8" s="45" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
@@ -10419,13 +10480,13 @@
       <c r="B9" s="72"/>
       <c r="C9" s="72"/>
       <c r="D9" s="45" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
@@ -10440,17 +10501,17 @@
         <v>45</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4"/>
       <c r="J10" s="12"/>
       <c r="L10" s="50" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -10461,17 +10522,17 @@
         <v>45</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
       <c r="I11" s="4"/>
       <c r="J11" s="12"/>
       <c r="L11" s="50" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -10479,13 +10540,13 @@
       <c r="B12" s="72"/>
       <c r="C12" s="72"/>
       <c r="D12" s="45" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
@@ -10497,13 +10558,13 @@
       <c r="B13" s="72"/>
       <c r="C13" s="72"/>
       <c r="D13" s="45" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
@@ -10515,13 +10576,13 @@
       <c r="B14" s="72"/>
       <c r="C14" s="72"/>
       <c r="D14" s="45" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
@@ -10533,13 +10594,13 @@
       <c r="B15" s="72"/>
       <c r="C15" s="72"/>
       <c r="D15" s="45" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
@@ -10551,13 +10612,13 @@
       <c r="B16" s="72"/>
       <c r="C16" s="72"/>
       <c r="D16" s="45" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
@@ -10572,17 +10633,17 @@
         <v>82</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="4"/>
       <c r="J17" s="12"/>
       <c r="L17" s="50" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -10593,17 +10654,17 @@
         <v>82</v>
       </c>
       <c r="E18" s="52" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
       <c r="I18" s="4"/>
       <c r="J18" s="12"/>
       <c r="L18" s="50" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -10664,16 +10725,16 @@
       <c r="A23" s="48"/>
       <c r="B23" s="72"/>
       <c r="C23" s="76" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="13"/>
@@ -10685,13 +10746,13 @@
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
       <c r="D24" s="45" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="13"/>
@@ -10703,13 +10764,13 @@
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
       <c r="D25" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="13"/>
@@ -10721,13 +10782,13 @@
       <c r="B26" s="72"/>
       <c r="C26" s="72"/>
       <c r="D26" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
@@ -10739,13 +10800,13 @@
       <c r="B27" s="72"/>
       <c r="C27" s="72"/>
       <c r="D27" s="46" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="13"/>
@@ -10757,13 +10818,13 @@
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
       <c r="D28" s="46" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="13"/>
@@ -10775,13 +10836,13 @@
       <c r="B29" s="72"/>
       <c r="C29" s="72"/>
       <c r="D29" s="46" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="13"/>
@@ -10793,13 +10854,13 @@
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
       <c r="D30" s="46" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="13"/>
@@ -10811,13 +10872,13 @@
       <c r="B31" s="72"/>
       <c r="C31" s="72"/>
       <c r="D31" s="46" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
@@ -10829,13 +10890,13 @@
       <c r="B32" s="72"/>
       <c r="C32" s="72"/>
       <c r="D32" s="46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="13"/>
@@ -10847,13 +10908,13 @@
       <c r="B33" s="72"/>
       <c r="C33" s="72"/>
       <c r="D33" s="46" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="13"/>
@@ -10865,13 +10926,13 @@
       <c r="B34" s="72"/>
       <c r="C34" s="72"/>
       <c r="D34" s="46" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="13"/>
@@ -10883,13 +10944,13 @@
       <c r="B35" s="72"/>
       <c r="C35" s="72"/>
       <c r="D35" s="46" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
@@ -10901,13 +10962,13 @@
       <c r="B36" s="72"/>
       <c r="C36" s="72"/>
       <c r="D36" s="46" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
@@ -10919,13 +10980,13 @@
       <c r="B37" s="72"/>
       <c r="C37" s="72"/>
       <c r="D37" s="46" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
@@ -10937,13 +10998,13 @@
       <c r="B38" s="72"/>
       <c r="C38" s="72"/>
       <c r="D38" s="46" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
@@ -10955,13 +11016,13 @@
       <c r="B39" s="72"/>
       <c r="C39" s="72"/>
       <c r="D39" s="46" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
@@ -10973,13 +11034,13 @@
       <c r="B40" s="72"/>
       <c r="C40" s="72"/>
       <c r="D40" s="46" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="13"/>
@@ -10991,13 +11052,13 @@
       <c r="B41" s="72"/>
       <c r="C41" s="72"/>
       <c r="D41" s="46" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="13"/>
@@ -11009,13 +11070,13 @@
       <c r="B42" s="72"/>
       <c r="C42" s="72"/>
       <c r="D42" s="46" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="13"/>
@@ -11030,10 +11091,10 @@
         <v>24</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="13"/>
@@ -11048,10 +11109,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="13"/>
@@ -11066,10 +11127,10 @@
         <v>29</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="13"/>
@@ -11084,10 +11145,10 @@
         <v>29</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="13"/>
@@ -11102,10 +11163,10 @@
         <v>45</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="13"/>
@@ -11120,10 +11181,10 @@
         <v>45</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="13"/>
@@ -11138,10 +11199,10 @@
         <v>45</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="13"/>
@@ -11156,10 +11217,10 @@
         <v>54</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="13"/>
@@ -11174,10 +11235,10 @@
         <v>54</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="13"/>
@@ -11192,10 +11253,10 @@
         <v>53</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="13"/>
@@ -11210,10 +11271,10 @@
         <v>53</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="13"/>
@@ -11225,13 +11286,13 @@
       <c r="B54" s="72"/>
       <c r="C54" s="72"/>
       <c r="D54" s="46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="13"/>
@@ -11243,13 +11304,13 @@
       <c r="B55" s="72"/>
       <c r="C55" s="72"/>
       <c r="D55" s="46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="13"/>
@@ -11264,10 +11325,10 @@
         <v>70</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="13"/>
@@ -11282,10 +11343,10 @@
         <v>70</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="13"/>
@@ -11300,10 +11361,10 @@
         <v>82</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="13"/>
@@ -11318,10 +11379,10 @@
         <v>82</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="13"/>
@@ -11336,10 +11397,10 @@
         <v>82</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="13"/>
@@ -11381,13 +11442,13 @@
       <c r="B63" s="72"/>
       <c r="C63" s="72"/>
       <c r="D63" s="46" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="13"/>
@@ -11399,13 +11460,13 @@
       <c r="B64" s="72"/>
       <c r="C64" s="72"/>
       <c r="D64" s="46" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>159</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="13"/>
@@ -11428,16 +11489,16 @@
       <c r="A66" s="48"/>
       <c r="B66" s="72"/>
       <c r="C66" s="72" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D66" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="13"/>
@@ -11449,13 +11510,13 @@
       <c r="B67" s="72"/>
       <c r="C67" s="72"/>
       <c r="D67" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="13"/>
@@ -11467,13 +11528,13 @@
       <c r="B68" s="72"/>
       <c r="C68" s="72"/>
       <c r="D68" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="F68" s="38" t="s">
         <v>256</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>261</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="13"/>
@@ -11485,13 +11546,13 @@
       <c r="B69" s="72"/>
       <c r="C69" s="72"/>
       <c r="D69" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E69" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="F69" s="38" t="s">
         <v>257</v>
-      </c>
-      <c r="F69" s="38" t="s">
-        <v>262</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="13"/>
@@ -11503,13 +11564,13 @@
       <c r="B70" s="72"/>
       <c r="C70" s="72"/>
       <c r="D70" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="13"/>
@@ -11521,13 +11582,13 @@
       <c r="B71" s="72"/>
       <c r="C71" s="72"/>
       <c r="D71" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="13"/>
@@ -11539,13 +11600,13 @@
       <c r="B72" s="72"/>
       <c r="C72" s="72"/>
       <c r="D72" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="13"/>
@@ -11557,13 +11618,13 @@
       <c r="B73" s="72"/>
       <c r="C73" s="72"/>
       <c r="D73" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="13"/>
@@ -11575,13 +11636,13 @@
       <c r="B74" s="72"/>
       <c r="C74" s="72"/>
       <c r="D74" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="13"/>
@@ -11593,13 +11654,13 @@
       <c r="B75" s="72"/>
       <c r="C75" s="72"/>
       <c r="D75" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="13"/>
@@ -11611,13 +11672,13 @@
       <c r="B76" s="72"/>
       <c r="C76" s="72"/>
       <c r="D76" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="13"/>
@@ -11629,13 +11690,13 @@
       <c r="B77" s="72"/>
       <c r="C77" s="72"/>
       <c r="D77" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="5"/>
@@ -11647,13 +11708,13 @@
       <c r="B78" s="72"/>
       <c r="C78" s="72"/>
       <c r="D78" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F78" s="38" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="5"/>
@@ -11665,13 +11726,13 @@
       <c r="B79" s="72"/>
       <c r="C79" s="72"/>
       <c r="D79" s="46" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F79" s="38" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="44"/>
@@ -11683,13 +11744,13 @@
       <c r="B80" s="72"/>
       <c r="C80" s="72"/>
       <c r="D80" s="46" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F80" s="38" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="5"/>
@@ -11753,7 +11814,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -11811,28 +11872,28 @@
         <v>66</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H3" s="11">
         <v>45981</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -11840,25 +11901,25 @@
       <c r="B4" s="72"/>
       <c r="C4" s="72"/>
       <c r="D4" s="45" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H4" s="13">
         <v>45981</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -11866,25 +11927,25 @@
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
       <c r="D5" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H5" s="13">
         <v>45981</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -11892,25 +11953,25 @@
       <c r="B6" s="72"/>
       <c r="C6" s="72"/>
       <c r="D6" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H6" s="13">
         <v>45981</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -11921,22 +11982,22 @@
         <v>24</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H7" s="13">
         <v>45981</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -11947,22 +12008,22 @@
         <v>29</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H8" s="13">
         <v>45981</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -11973,22 +12034,22 @@
         <v>45</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H9" s="13">
         <v>45981</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -11999,22 +12060,22 @@
         <v>54</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H10" s="13">
         <v>45981</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12025,22 +12086,22 @@
         <v>53</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H11" s="13">
         <v>45981</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12048,25 +12109,25 @@
       <c r="B12" s="72"/>
       <c r="C12" s="72"/>
       <c r="D12" s="45" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H12" s="13">
         <v>45981</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12077,22 +12138,22 @@
         <v>70</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H13" s="13">
         <v>45981</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12103,22 +12164,22 @@
         <v>82</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H14" s="13">
         <v>45981</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12138,7 +12199,7 @@
       <c r="B16" s="72"/>
       <c r="C16" s="72"/>
       <c r="D16" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>150</v>
@@ -12147,14 +12208,14 @@
         <v>152</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H16" s="13">
         <v>45981</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12162,23 +12223,23 @@
       <c r="B17" s="72"/>
       <c r="C17" s="72"/>
       <c r="D17" s="46" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>158</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H17" s="13">
         <v>45981</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12209,28 +12270,28 @@
       <c r="A20" s="48"/>
       <c r="B20" s="72"/>
       <c r="C20" s="76" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H20" s="13">
         <v>45981</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12238,25 +12299,25 @@
       <c r="B21" s="72"/>
       <c r="C21" s="72"/>
       <c r="D21" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H21" s="13">
         <v>45981</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12264,25 +12325,25 @@
       <c r="B22" s="72"/>
       <c r="C22" s="72"/>
       <c r="D22" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>261</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H22" s="13">
         <v>45981</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12290,25 +12351,25 @@
       <c r="B23" s="72"/>
       <c r="C23" s="72"/>
       <c r="D23" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H23" s="13">
         <v>45981</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12316,25 +12377,25 @@
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
       <c r="D24" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E24" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="F24" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="F24" s="38" t="s">
-        <v>263</v>
-      </c>
       <c r="G24" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H24" s="13">
         <v>45981</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12342,25 +12403,25 @@
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
       <c r="D25" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H25" s="13">
         <v>45981</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12368,25 +12429,25 @@
       <c r="B26" s="72"/>
       <c r="C26" s="72"/>
       <c r="D26" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H26" s="13">
         <v>45981</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12394,25 +12455,25 @@
       <c r="B27" s="72"/>
       <c r="C27" s="72"/>
       <c r="D27" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H27" s="13">
         <v>45981</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12420,25 +12481,25 @@
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
       <c r="D28" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H28" s="13">
         <v>45981</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12446,25 +12507,25 @@
       <c r="B29" s="72"/>
       <c r="C29" s="72"/>
       <c r="D29" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H29" s="13">
         <v>45981</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12472,25 +12533,25 @@
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
       <c r="D30" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H30" s="13">
         <v>45981</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12498,25 +12559,25 @@
       <c r="B31" s="72"/>
       <c r="C31" s="72"/>
       <c r="D31" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F31" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="H31" s="13">
         <v>45981</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -12524,25 +12585,25 @@
       <c r="B32" s="72"/>
       <c r="C32" s="72"/>
       <c r="D32" s="47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H32" s="13">
         <v>45981</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12562,25 +12623,25 @@
       <c r="B34" s="72"/>
       <c r="C34" s="72"/>
       <c r="D34" s="46" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H34" s="13">
         <v>45981</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.55000000000000004">
@@ -12588,25 +12649,25 @@
       <c r="B35" s="72"/>
       <c r="C35" s="72"/>
       <c r="D35" s="46" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H35" s="13">
         <v>45981</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -12661,28 +12722,28 @@
       <c r="A40" s="48"/>
       <c r="B40" s="72"/>
       <c r="C40" s="77" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H40" s="44">
         <v>45981</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -12690,25 +12751,25 @@
       <c r="B41" s="72"/>
       <c r="C41" s="72"/>
       <c r="D41" s="47" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H41" s="44">
         <v>45981</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -12716,25 +12777,25 @@
       <c r="B42" s="72"/>
       <c r="C42" s="72"/>
       <c r="D42" s="46" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H42" s="44">
         <v>45981</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -12742,76 +12803,90 @@
       <c r="B43" s="72"/>
       <c r="C43" s="72"/>
       <c r="D43" s="46" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>304</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="H43" s="44">
         <v>45981</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
       <c r="B44" s="72"/>
       <c r="C44" s="72"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
+      <c r="D44" s="79" t="s">
+        <v>301</v>
+      </c>
+      <c r="E44" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="F44" s="81" t="s">
+        <v>307</v>
+      </c>
+      <c r="G44" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="83">
+        <v>45986</v>
+      </c>
+      <c r="I44" s="84" t="s">
+        <v>308</v>
+      </c>
+      <c r="J44" s="85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
       <c r="B45" s="72"/>
       <c r="C45" s="72"/>
-      <c r="D45" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="H45" s="44">
-        <v>45981</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D45" s="46"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>
       <c r="B46" s="72"/>
       <c r="C46" s="72"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
+      <c r="D46" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H46" s="44">
+        <v>45981</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="48"/>
@@ -12827,8 +12902,8 @@
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
       <c r="D48" s="47"/>
       <c r="E48" s="14"/>
       <c r="F48" s="38"/>
@@ -12837,15 +12912,27 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="48"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:B48"/>
+    <mergeCell ref="B3:B49"/>
     <mergeCell ref="C3:C19"/>
     <mergeCell ref="C20:C39"/>
-    <mergeCell ref="C40:C48"/>
+    <mergeCell ref="C40:C49"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12910,1438 +12997,922 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
       <c r="I3" s="16"/>
       <c r="J3" s="10"/>
     </row>
-    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="59"/>
       <c r="C4" s="54"/>
-      <c r="D4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="4"/>
       <c r="H4" s="13"/>
       <c r="I4" s="40"/>
       <c r="J4" s="12"/>
     </row>
-    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="59"/>
       <c r="C5" s="54"/>
-      <c r="D5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="13"/>
       <c r="I5" s="40"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="59"/>
       <c r="C6" s="54"/>
-      <c r="D6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="13"/>
       <c r="I6" s="40"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="59"/>
       <c r="C7" s="54"/>
-      <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
       <c r="I7" s="40"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="59"/>
       <c r="C8" s="54"/>
-      <c r="D8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
       <c r="I8" s="40"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="59"/>
       <c r="C9" s="54"/>
-      <c r="D9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
       <c r="I9" s="40"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="59"/>
       <c r="C10" s="54"/>
-      <c r="D10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="I10" s="40"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="59"/>
       <c r="C11" s="54"/>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="4"/>
       <c r="H11" s="13"/>
       <c r="I11" s="40"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="59"/>
       <c r="C12" s="54"/>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="4"/>
       <c r="H12" s="13"/>
       <c r="I12" s="40"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="59"/>
       <c r="C13" s="54"/>
-      <c r="D13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
       <c r="I13" s="40"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="59"/>
       <c r="C14" s="54"/>
-      <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="4"/>
       <c r="H14" s="13"/>
       <c r="I14" s="40"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="59"/>
       <c r="C15" s="54"/>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="4"/>
       <c r="H15" s="13"/>
       <c r="I15" s="40"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="59"/>
       <c r="C16" s="54"/>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="4"/>
       <c r="H16" s="13"/>
       <c r="I16" s="40"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="59"/>
       <c r="C17" s="54"/>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="4"/>
       <c r="H17" s="13"/>
       <c r="I17" s="40"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="59"/>
       <c r="C18" s="54"/>
-      <c r="D18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="4"/>
       <c r="H18" s="13"/>
       <c r="I18" s="40"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="59"/>
       <c r="C19" s="54"/>
-      <c r="D19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="4"/>
       <c r="H19" s="13"/>
       <c r="I19" s="40"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="59"/>
       <c r="C20" s="54"/>
-      <c r="D20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="4"/>
       <c r="H20" s="13"/>
       <c r="I20" s="40"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="59"/>
       <c r="C21" s="54"/>
-      <c r="D21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="4"/>
       <c r="H21" s="13"/>
       <c r="I21" s="40"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="59"/>
       <c r="C22" s="54"/>
-      <c r="D22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="4"/>
       <c r="H22" s="13"/>
       <c r="I22" s="40"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="59"/>
       <c r="C23" s="54"/>
-      <c r="D23" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="4"/>
       <c r="H23" s="13"/>
       <c r="I23" s="40"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="59"/>
       <c r="C24" s="54"/>
-      <c r="D24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="4"/>
       <c r="H24" s="13"/>
       <c r="I24" s="40"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="59"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="4"/>
       <c r="H25" s="13"/>
       <c r="I25" s="40"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="59"/>
       <c r="C26" s="54"/>
-      <c r="D26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="4"/>
       <c r="H26" s="13"/>
       <c r="I26" s="40"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="59"/>
       <c r="C27" s="54"/>
-      <c r="D27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="4"/>
       <c r="H27" s="13"/>
       <c r="I27" s="40"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="59"/>
       <c r="C28" s="54"/>
-      <c r="D28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="4"/>
       <c r="H28" s="13"/>
       <c r="I28" s="40"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="59"/>
       <c r="C29" s="54"/>
-      <c r="D29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="4"/>
       <c r="H29" s="13"/>
       <c r="I29" s="40"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="59"/>
       <c r="C30" s="54"/>
-      <c r="D30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="4"/>
       <c r="H30" s="13"/>
       <c r="I30" s="40"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="59"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="4"/>
       <c r="H31" s="13"/>
       <c r="I31" s="40"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="59"/>
       <c r="C32" s="54"/>
-      <c r="D32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="4"/>
       <c r="H32" s="13"/>
       <c r="I32" s="40"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="59"/>
       <c r="C33" s="54"/>
-      <c r="D33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>115</v>
-      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="4"/>
       <c r="H33" s="13"/>
       <c r="I33" s="40"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="59"/>
       <c r="C34" s="54"/>
-      <c r="D34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="4"/>
       <c r="H34" s="13"/>
       <c r="I34" s="40"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="59"/>
       <c r="C35" s="54"/>
-      <c r="D35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="4"/>
       <c r="H35" s="13"/>
       <c r="I35" s="40"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="59"/>
       <c r="C36" s="54"/>
-      <c r="D36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="4"/>
       <c r="H36" s="13"/>
       <c r="I36" s="40"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="59"/>
       <c r="C37" s="54"/>
-      <c r="D37" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="7"/>
       <c r="G37" s="4"/>
       <c r="H37" s="13"/>
       <c r="I37" s="40"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="59"/>
       <c r="C38" s="54"/>
-      <c r="D38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="4"/>
       <c r="H38" s="13"/>
-      <c r="I38" s="40" t="s">
-        <v>173</v>
-      </c>
+      <c r="I38" s="40"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="59"/>
       <c r="C39" s="54"/>
-      <c r="D39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="4"/>
       <c r="H39" s="13"/>
       <c r="I39" s="40"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="59"/>
       <c r="C40" s="54"/>
-      <c r="D40" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="7"/>
       <c r="G40" s="4"/>
       <c r="H40" s="13"/>
-      <c r="I40" s="43" t="s">
-        <v>178</v>
-      </c>
+      <c r="I40" s="43"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="59"/>
       <c r="C41" s="54"/>
-      <c r="D41" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="4"/>
       <c r="H41" s="13"/>
       <c r="I41" s="40"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="59"/>
       <c r="C42" s="54"/>
-      <c r="D42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="4"/>
       <c r="H42" s="13"/>
       <c r="I42" s="40"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="59"/>
       <c r="C43" s="54"/>
-      <c r="D43" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>128</v>
-      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="7"/>
       <c r="G43" s="4"/>
       <c r="H43" s="5"/>
       <c r="I43" s="40"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="59"/>
       <c r="C44" s="54"/>
-      <c r="D44" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="7"/>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
       <c r="I44" s="40"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="59"/>
       <c r="C45" s="54"/>
-      <c r="D45" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D45" s="7"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="7"/>
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
       <c r="I45" s="40"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="59"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D46" s="7"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="7"/>
       <c r="G46" s="4"/>
       <c r="H46" s="5"/>
       <c r="I46" s="40"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="59"/>
       <c r="C47" s="54"/>
-      <c r="D47" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="7"/>
       <c r="G47" s="4"/>
       <c r="H47" s="5"/>
       <c r="I47" s="40"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="59"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="7"/>
       <c r="G48" s="4"/>
       <c r="H48" s="5"/>
       <c r="I48" s="40"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="59"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="7"/>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
       <c r="I49" s="40"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="59"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="4"/>
       <c r="H50" s="5"/>
       <c r="I50" s="40"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="59"/>
       <c r="C51" s="54"/>
-      <c r="D51" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>154</v>
-      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="7"/>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
       <c r="I51" s="40"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="59"/>
       <c r="C52" s="54"/>
-      <c r="D52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="7"/>
       <c r="G52" s="4"/>
       <c r="H52" s="5"/>
       <c r="I52" s="40"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="59"/>
       <c r="C53" s="54"/>
-      <c r="D53" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="7"/>
       <c r="G53" s="4"/>
       <c r="H53" s="5"/>
       <c r="I53" s="40"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="59"/>
       <c r="C54" s="54"/>
-      <c r="D54" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="7"/>
       <c r="G54" s="4"/>
       <c r="H54" s="5"/>
       <c r="I54" s="40"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="59"/>
       <c r="C55" s="54"/>
-      <c r="D55" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>128</v>
-      </c>
+      <c r="D55" s="7"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="4"/>
       <c r="H55" s="5"/>
       <c r="I55" s="40"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="59"/>
       <c r="C56" s="54"/>
-      <c r="D56" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D56" s="7"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="7"/>
       <c r="G56" s="4"/>
       <c r="H56" s="5"/>
       <c r="I56" s="40"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="59"/>
       <c r="C57" s="54"/>
-      <c r="D57" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D57" s="7"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="7"/>
       <c r="G57" s="4"/>
       <c r="H57" s="5"/>
       <c r="I57" s="40"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="59"/>
       <c r="C58" s="54"/>
-      <c r="D58" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="7"/>
       <c r="G58" s="4"/>
       <c r="H58" s="5"/>
       <c r="I58" s="40"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="59"/>
       <c r="C59" s="54"/>
-      <c r="D59" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="7"/>
       <c r="G59" s="4"/>
       <c r="H59" s="5"/>
       <c r="I59" s="40"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="59"/>
       <c r="C60" s="54"/>
-      <c r="D60" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="7"/>
       <c r="G60" s="4"/>
       <c r="H60" s="5"/>
       <c r="I60" s="40"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="59"/>
       <c r="C61" s="54"/>
-      <c r="D61" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="7"/>
       <c r="G61" s="4"/>
       <c r="H61" s="5"/>
       <c r="I61" s="40"/>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="59"/>
       <c r="C62" s="54"/>
-      <c r="D62" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>137</v>
-      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="7"/>
       <c r="G62" s="4"/>
       <c r="H62" s="5"/>
       <c r="I62" s="40"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="59"/>
       <c r="C63" s="54"/>
-      <c r="D63" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="7"/>
       <c r="G63" s="4"/>
       <c r="H63" s="5"/>
       <c r="I63" s="40"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="59"/>
       <c r="C64" s="54"/>
-      <c r="D64" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="7"/>
       <c r="G64" s="4"/>
       <c r="H64" s="5"/>
       <c r="I64" s="40"/>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="59"/>
       <c r="C65" s="54"/>
-      <c r="D65" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="7"/>
       <c r="G65" s="4"/>
       <c r="H65" s="5"/>
-      <c r="I65" s="40" t="s">
-        <v>179</v>
-      </c>
+      <c r="I65" s="40"/>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="59"/>
       <c r="C66" s="54"/>
-      <c r="D66" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="7"/>
       <c r="G66" s="4"/>
       <c r="H66" s="5"/>
       <c r="I66" s="40"/>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="59"/>
       <c r="C67" s="54"/>
-      <c r="D67" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="4"/>
       <c r="H67" s="5"/>
-      <c r="I67" s="40" t="s">
-        <v>179</v>
-      </c>
+      <c r="I67" s="40"/>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="59"/>
       <c r="C68" s="54"/>
-      <c r="D68" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="4"/>
       <c r="H68" s="5"/>
-      <c r="I68" s="40" t="s">
-        <v>179</v>
-      </c>
+      <c r="I68" s="40"/>
       <c r="J68" s="4"/>
     </row>
-    <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="59"/>
       <c r="C69" s="54"/>
-      <c r="D69" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D69" s="7"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="4"/>
       <c r="H69" s="5"/>
-      <c r="I69" s="40" t="s">
-        <v>179</v>
-      </c>
+      <c r="I69" s="40"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="59"/>
       <c r="C70" s="54"/>
-      <c r="D70" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D70" s="7"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="4"/>
       <c r="H70" s="5"/>
-      <c r="I70" s="40" t="s">
-        <v>181</v>
-      </c>
+      <c r="I70" s="40"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="59"/>
       <c r="C71" s="54"/>
-      <c r="D71" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="4"/>
       <c r="H71" s="5"/>
       <c r="I71" s="40"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="59"/>
       <c r="C72" s="54"/>
-      <c r="D72" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D72" s="7"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="4"/>
       <c r="H72" s="5"/>
       <c r="I72" s="40"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="59"/>
       <c r="C73" s="54"/>
-      <c r="D73" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="D73" s="7"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="7"/>
       <c r="G73" s="4"/>
       <c r="H73" s="5"/>
       <c r="I73" s="40"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="59"/>
       <c r="C74" s="54"/>
-      <c r="D74" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D74" s="7"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="7"/>
       <c r="G74" s="4"/>
       <c r="H74" s="5"/>
       <c r="I74" s="40"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="59"/>
       <c r="C75" s="54"/>
-      <c r="D75" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D75" s="7"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="7"/>
       <c r="G75" s="4"/>
       <c r="H75" s="5"/>
-      <c r="I75" s="40" t="s">
-        <v>182</v>
-      </c>
+      <c r="I75" s="40"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="59"/>
       <c r="C76" s="54"/>
-      <c r="D76" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D76" s="7"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="7"/>
       <c r="G76" s="4"/>
       <c r="H76" s="5"/>
       <c r="I76" s="40"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="59"/>
       <c r="C77" s="54"/>
-      <c r="D77" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D77" s="7"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="7"/>
       <c r="G77" s="4"/>
       <c r="H77" s="5"/>
       <c r="I77" s="40"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="59"/>
       <c r="C78" s="54"/>
-      <c r="D78" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D78" s="7"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="7"/>
       <c r="G78" s="4"/>
       <c r="H78" s="5"/>
       <c r="I78" s="40"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="59"/>
       <c r="C79" s="54"/>
-      <c r="D79" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E79" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="7"/>
       <c r="G79" s="4"/>
       <c r="H79" s="5"/>
       <c r="I79" s="40"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="59"/>
       <c r="C80" s="54"/>
-      <c r="D80" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="7"/>
       <c r="G80" s="4"/>
       <c r="H80" s="5"/>
       <c r="I80" s="40"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="59"/>
       <c r="C81" s="54"/>
-      <c r="D81" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D81" s="7"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="7"/>
       <c r="G81" s="4"/>
       <c r="H81" s="5"/>
       <c r="I81" s="40"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="59"/>
       <c r="C82" s="54"/>
-      <c r="D82" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D82" s="7"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="7"/>
       <c r="G82" s="4"/>
       <c r="H82" s="5"/>
       <c r="I82" s="40"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="59"/>
       <c r="C83" s="54"/>
-      <c r="D83" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D83" s="7"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="7"/>
       <c r="G83" s="4"/>
       <c r="H83" s="5"/>
       <c r="I83" s="40"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="59"/>
       <c r="C84" s="54"/>
-      <c r="D84" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F84" s="38" t="s">
-        <v>149</v>
-      </c>
+      <c r="D84" s="7"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="38"/>
       <c r="G84" s="4"/>
       <c r="H84" s="5"/>
       <c r="I84" s="40"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="59"/>
       <c r="C85" s="54"/>
-      <c r="D85" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="F85" s="38" t="s">
-        <v>152</v>
-      </c>
+      <c r="D85" s="7"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="38"/>
       <c r="G85" s="4"/>
       <c r="H85" s="5"/>
       <c r="I85" s="40"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="59"/>
       <c r="C86" s="55"/>
       <c r="D86" s="7"/>
@@ -14352,43 +13923,29 @@
       <c r="I86" s="40"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="59"/>
-      <c r="C87" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F87" s="38" t="s">
-        <v>160</v>
-      </c>
+      <c r="C87" s="68"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="38"/>
       <c r="G87" s="4"/>
       <c r="H87" s="5"/>
       <c r="I87" s="40"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="59"/>
       <c r="C88" s="69"/>
-      <c r="D88" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="F88" s="38" t="s">
-        <v>161</v>
-      </c>
+      <c r="D88" s="7"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="38"/>
       <c r="G88" s="4"/>
       <c r="H88" s="5"/>
       <c r="I88" s="40"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="59"/>
       <c r="C89" s="69"/>
       <c r="D89" s="7"/>
@@ -14399,7 +13956,7 @@
       <c r="I89" s="40"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="59"/>
       <c r="C90" s="69"/>
       <c r="D90" s="7"/>
@@ -14410,7 +13967,7 @@
       <c r="I90" s="40"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="59"/>
       <c r="C91" s="69"/>
       <c r="D91" s="7"/>
@@ -14421,7 +13978,7 @@
       <c r="I91" s="40"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="59"/>
       <c r="C92" s="69"/>
       <c r="D92" s="7"/>
@@ -14432,7 +13989,7 @@
       <c r="I92" s="40"/>
       <c r="J92" s="4"/>
     </row>
-    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="59"/>
       <c r="C93" s="70"/>
       <c r="D93" s="7"/>
@@ -14443,26 +14000,18 @@
       <c r="I93" s="40"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="59"/>
-      <c r="C94" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>165</v>
-      </c>
+      <c r="C94" s="74"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="7"/>
       <c r="G94" s="4"/>
       <c r="H94" s="5"/>
       <c r="I94" s="40"/>
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="59"/>
       <c r="C95" s="59"/>
       <c r="D95" s="7"/>
@@ -14473,7 +14022,7 @@
       <c r="I95" s="40"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="59"/>
       <c r="C96" s="59"/>
       <c r="D96" s="7"/>
@@ -14484,7 +14033,7 @@
       <c r="I96" s="40"/>
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="59"/>
       <c r="C97" s="59"/>
       <c r="D97" s="7"/>
@@ -14495,7 +14044,7 @@
       <c r="I97" s="40"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="59"/>
       <c r="C98" s="59"/>
       <c r="D98" s="7"/>
@@ -14506,7 +14055,7 @@
       <c r="I98" s="40"/>
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="60"/>
       <c r="C99" s="60"/>
       <c r="D99" s="7"/>

--- a/テストケース.xlsx
+++ b/テストケース.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA669A7A-A607-4DB3-8D64-4C9E4C1056F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56469E86-C705-4DFE-8D83-5F39EEE27749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{AE792E3C-5D04-4135-A95C-F6BFEA0379B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="単体テスト (新)" sheetId="4" r:id="rId1"/>
-    <sheet name="結合テスト（新）" sheetId="7" r:id="rId2"/>
-    <sheet name="総合テスト" sheetId="5" r:id="rId3"/>
-    <sheet name="単体テスト（訂正前）" sheetId="1" r:id="rId4"/>
-    <sheet name="結合テスト（訂正前・バラ）" sheetId="6" r:id="rId5"/>
+    <sheet name="単体テスト (アカウント登録)" sheetId="4" r:id="rId1"/>
+    <sheet name="単体テスト (アカウント削除・更新)" sheetId="8" r:id="rId2"/>
+    <sheet name="結合テスト（アカウント登録）" sheetId="7" r:id="rId3"/>
+    <sheet name="結合テスト（アカウント削除・更新)" sheetId="9" r:id="rId4"/>
+    <sheet name="総合テスト" sheetId="5" r:id="rId5"/>
+    <sheet name="単体テスト（訂正前）" sheetId="1" r:id="rId6"/>
+    <sheet name="結合テスト（訂正前・バラ）" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="368">
   <si>
     <t>機能（どのシステム機能を）</t>
     <phoneticPr fontId="1"/>
@@ -4819,6 +4821,546 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除機能</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント一覧画面</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント更新機能</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント更新画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント更新確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント更新完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント一覧画面ーアカウント削除画面</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント一覧画面にて削除したいアカウントの「削除」ボタンを押下</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「名前（性）欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「名前（名）欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「カナ（性）欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「カナ（名）欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「メールアドレス欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「パスワード欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「性別 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「郵便番号 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「都道府県 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>トドウフケン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「市区町村 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>チョウソン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「番地 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バンチ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面に遷移し、データベースにて該当ID者の「アカウント権限 欄」の内容が表示されている</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウント削除画面
+「確認する」ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「確認する」押下</t>
+    <rPh sb="1" eb="3">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アカウント削除確認画面」へ遷移</t>
+    <rPh sb="6" eb="8">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4926,7 +5468,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4957,8 +5499,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -5138,13 +5686,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5328,6 +5904,24 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -5364,23 +5958,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -5394,19 +5985,76 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5724,6 +6372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A2056B-5BAF-4B6A-8EF5-CB29DB5A4449}">
   <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:J105"/>
@@ -5741,24 +6390,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
     </row>
     <row r="2" spans="2:10" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -5779,10 +6428,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="71" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -5808,8 +6457,8 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="71"/>
-      <c r="C4" s="65"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="45" t="s">
         <v>20</v>
       </c>
@@ -5833,8 +6482,8 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="71"/>
-      <c r="C5" s="65"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="71"/>
       <c r="D5" s="45" t="s">
         <v>20</v>
       </c>
@@ -5858,8 +6507,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="71"/>
-      <c r="C6" s="65"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="71"/>
       <c r="D6" s="45" t="s">
         <v>20</v>
       </c>
@@ -5883,8 +6532,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="71"/>
-      <c r="C7" s="65"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="71"/>
       <c r="D7" s="45" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6557,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="71"/>
-      <c r="C8" s="65"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="71"/>
       <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
@@ -5933,8 +6582,8 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="71"/>
-      <c r="C9" s="65"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="71"/>
       <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
@@ -5958,8 +6607,8 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="71"/>
-      <c r="C10" s="65"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="71"/>
       <c r="D10" s="45" t="s">
         <v>20</v>
       </c>
@@ -5983,8 +6632,8 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="71"/>
-      <c r="C11" s="65"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="71"/>
       <c r="D11" s="46" t="s">
         <v>21</v>
       </c>
@@ -6008,8 +6657,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="71"/>
-      <c r="C12" s="65"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="71"/>
       <c r="D12" s="46" t="s">
         <v>21</v>
       </c>
@@ -6033,8 +6682,8 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="71"/>
-      <c r="C13" s="65"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="71"/>
       <c r="D13" s="46" t="s">
         <v>21</v>
       </c>
@@ -6058,8 +6707,8 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="71"/>
-      <c r="C14" s="65"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="71"/>
       <c r="D14" s="46" t="s">
         <v>21</v>
       </c>
@@ -6083,8 +6732,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="71"/>
-      <c r="C15" s="65"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="71"/>
       <c r="D15" s="46" t="s">
         <v>21</v>
       </c>
@@ -6108,8 +6757,8 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="71"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="71"/>
       <c r="D16" s="46" t="s">
         <v>21</v>
       </c>
@@ -6133,8 +6782,8 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="71"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="71"/>
       <c r="D17" s="46" t="s">
         <v>21</v>
       </c>
@@ -6158,8 +6807,8 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="71"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="46" t="s">
         <v>22</v>
       </c>
@@ -6183,8 +6832,8 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="71"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="46" t="s">
         <v>22</v>
       </c>
@@ -6208,8 +6857,8 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="71"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="71"/>
       <c r="D20" s="46" t="s">
         <v>22</v>
       </c>
@@ -6233,8 +6882,8 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="71"/>
-      <c r="C21" s="65"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="71"/>
       <c r="D21" s="46" t="s">
         <v>22</v>
       </c>
@@ -6258,8 +6907,8 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="71"/>
-      <c r="C22" s="65"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="71"/>
       <c r="D22" s="46" t="s">
         <v>22</v>
       </c>
@@ -6283,8 +6932,8 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="71"/>
-      <c r="C23" s="65"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="71"/>
       <c r="D23" s="46" t="s">
         <v>22</v>
       </c>
@@ -6308,8 +6957,8 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="71"/>
-      <c r="C24" s="65"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="46" t="s">
         <v>22</v>
       </c>
@@ -6333,8 +6982,8 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="71"/>
-      <c r="C25" s="65"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="46" t="s">
         <v>23</v>
       </c>
@@ -6358,8 +7007,8 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="71"/>
-      <c r="C26" s="65"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="46" t="s">
         <v>23</v>
       </c>
@@ -6383,8 +7032,8 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="71"/>
-      <c r="C27" s="65"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="46" t="s">
         <v>23</v>
       </c>
@@ -6408,8 +7057,8 @@
       </c>
     </row>
     <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="71"/>
-      <c r="C28" s="65"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="46" t="s">
         <v>23</v>
       </c>
@@ -6433,8 +7082,8 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="71"/>
-      <c r="C29" s="65"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="71"/>
       <c r="D29" s="46" t="s">
         <v>23</v>
       </c>
@@ -6458,8 +7107,8 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="71"/>
-      <c r="C30" s="65"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="71"/>
       <c r="D30" s="46" t="s">
         <v>23</v>
       </c>
@@ -6483,8 +7132,8 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="71"/>
-      <c r="C31" s="65"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="71"/>
       <c r="D31" s="46" t="s">
         <v>23</v>
       </c>
@@ -6508,8 +7157,8 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="71"/>
-      <c r="C32" s="65"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="71"/>
       <c r="D32" s="47" t="s">
         <v>24</v>
       </c>
@@ -6533,8 +7182,8 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="71"/>
-      <c r="C33" s="65"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="71"/>
       <c r="D33" s="47" t="s">
         <v>24</v>
       </c>
@@ -6558,8 +7207,8 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="71"/>
-      <c r="C34" s="65"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="71"/>
       <c r="D34" s="47" t="s">
         <v>24</v>
       </c>
@@ -6583,8 +7232,8 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="71"/>
-      <c r="C35" s="65"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="71"/>
       <c r="D35" s="47" t="s">
         <v>24</v>
       </c>
@@ -6608,8 +7257,8 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="71"/>
-      <c r="C36" s="65"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="71"/>
       <c r="D36" s="47" t="s">
         <v>24</v>
       </c>
@@ -6633,8 +7282,8 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="71"/>
-      <c r="C37" s="65"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="71"/>
       <c r="D37" s="47" t="s">
         <v>24</v>
       </c>
@@ -6658,8 +7307,8 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="71"/>
-      <c r="C38" s="65"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="71"/>
       <c r="D38" s="47" t="s">
         <v>24</v>
       </c>
@@ -6683,8 +7332,8 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="71"/>
-      <c r="C39" s="65"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="71"/>
       <c r="D39" s="47" t="s">
         <v>24</v>
       </c>
@@ -6708,8 +7357,8 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="71"/>
-      <c r="C40" s="65"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="71"/>
       <c r="D40" s="47" t="s">
         <v>24</v>
       </c>
@@ -6733,8 +7382,8 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="71"/>
-      <c r="C41" s="65"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="71"/>
       <c r="D41" s="47" t="s">
         <v>24</v>
       </c>
@@ -6758,8 +7407,8 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="71"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="71"/>
       <c r="D42" s="47" t="s">
         <v>24</v>
       </c>
@@ -6783,8 +7432,8 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="71"/>
-      <c r="C43" s="65"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="71"/>
       <c r="D43" s="47" t="s">
         <v>29</v>
       </c>
@@ -6808,8 +7457,8 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="71"/>
-      <c r="C44" s="65"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="71"/>
       <c r="D44" s="47" t="s">
         <v>29</v>
       </c>
@@ -6833,8 +7482,8 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="71"/>
-      <c r="C45" s="65"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="71"/>
       <c r="D45" s="47" t="s">
         <v>29</v>
       </c>
@@ -6858,8 +7507,8 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="71"/>
-      <c r="C46" s="65"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="71"/>
       <c r="D46" s="47" t="s">
         <v>29</v>
       </c>
@@ -6883,8 +7532,8 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="71"/>
-      <c r="C47" s="65"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="71"/>
       <c r="D47" s="47" t="s">
         <v>29</v>
       </c>
@@ -6908,8 +7557,8 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="71"/>
-      <c r="C48" s="65"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="71"/>
       <c r="D48" s="47" t="s">
         <v>29</v>
       </c>
@@ -6933,8 +7582,8 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="71"/>
-      <c r="C49" s="65"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="71"/>
       <c r="D49" s="47" t="s">
         <v>29</v>
       </c>
@@ -6958,8 +7607,8 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="71"/>
-      <c r="C50" s="65"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="71"/>
       <c r="D50" s="47" t="s">
         <v>29</v>
       </c>
@@ -6983,8 +7632,8 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="71"/>
-      <c r="C51" s="65"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="71"/>
       <c r="D51" s="47" t="s">
         <v>29</v>
       </c>
@@ -7008,8 +7657,8 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="71"/>
-      <c r="C52" s="65"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="71"/>
       <c r="D52" s="47" t="s">
         <v>45</v>
       </c>
@@ -7033,8 +7682,8 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="71"/>
-      <c r="C53" s="65"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="71"/>
       <c r="D53" s="47" t="s">
         <v>45</v>
       </c>
@@ -7058,8 +7707,8 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="71"/>
-      <c r="C54" s="65"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="71"/>
       <c r="D54" s="47" t="s">
         <v>45</v>
       </c>
@@ -7083,8 +7732,8 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="71"/>
-      <c r="C55" s="65"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="71"/>
       <c r="D55" s="47" t="s">
         <v>54</v>
       </c>
@@ -7108,8 +7757,8 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="71"/>
-      <c r="C56" s="65"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="71"/>
       <c r="D56" s="47" t="s">
         <v>54</v>
       </c>
@@ -7133,8 +7782,8 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="71"/>
-      <c r="C57" s="65"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="71"/>
       <c r="D57" s="47" t="s">
         <v>54</v>
       </c>
@@ -7158,8 +7807,8 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="71"/>
-      <c r="C58" s="65"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="71"/>
       <c r="D58" s="47" t="s">
         <v>54</v>
       </c>
@@ -7183,8 +7832,8 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="71"/>
-      <c r="C59" s="65"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="71"/>
       <c r="D59" s="47" t="s">
         <v>54</v>
       </c>
@@ -7208,8 +7857,8 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="71"/>
-      <c r="C60" s="65"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="71"/>
       <c r="D60" s="47" t="s">
         <v>54</v>
       </c>
@@ -7233,8 +7882,8 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="71"/>
-      <c r="C61" s="65"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="71"/>
       <c r="D61" s="47" t="s">
         <v>54</v>
       </c>
@@ -7258,8 +7907,8 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="71"/>
-      <c r="C62" s="65"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="71"/>
       <c r="D62" s="47" t="s">
         <v>53</v>
       </c>
@@ -7283,8 +7932,8 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="71"/>
-      <c r="C63" s="65"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="71"/>
       <c r="D63" s="47" t="s">
         <v>53</v>
       </c>
@@ -7308,8 +7957,8 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="71"/>
-      <c r="C64" s="65"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="71"/>
       <c r="D64" s="47" t="s">
         <v>59</v>
       </c>
@@ -7333,8 +7982,8 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="71"/>
-      <c r="C65" s="65"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="71"/>
       <c r="D65" s="47" t="s">
         <v>59</v>
       </c>
@@ -7358,8 +8007,8 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="71"/>
-      <c r="C66" s="65"/>
+      <c r="B66" s="77"/>
+      <c r="C66" s="71"/>
       <c r="D66" s="47" t="s">
         <v>59</v>
       </c>
@@ -7383,8 +8032,8 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="71"/>
-      <c r="C67" s="65"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="71"/>
       <c r="D67" s="47" t="s">
         <v>59</v>
       </c>
@@ -7408,8 +8057,8 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="71"/>
-      <c r="C68" s="65"/>
+      <c r="B68" s="77"/>
+      <c r="C68" s="71"/>
       <c r="D68" s="47" t="s">
         <v>59</v>
       </c>
@@ -7433,8 +8082,8 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="71"/>
-      <c r="C69" s="65"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="71"/>
       <c r="D69" s="47" t="s">
         <v>59</v>
       </c>
@@ -7458,8 +8107,8 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="71"/>
-      <c r="C70" s="65"/>
+      <c r="B70" s="77"/>
+      <c r="C70" s="71"/>
       <c r="D70" s="47" t="s">
         <v>59</v>
       </c>
@@ -7483,8 +8132,8 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="71"/>
-      <c r="C71" s="65"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="71"/>
       <c r="D71" s="47" t="s">
         <v>59</v>
       </c>
@@ -7508,8 +8157,8 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="71"/>
-      <c r="C72" s="65"/>
+      <c r="B72" s="77"/>
+      <c r="C72" s="71"/>
       <c r="D72" s="47" t="s">
         <v>59</v>
       </c>
@@ -7533,8 +8182,8 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="71"/>
-      <c r="C73" s="65"/>
+      <c r="B73" s="77"/>
+      <c r="C73" s="71"/>
       <c r="D73" s="47" t="s">
         <v>70</v>
       </c>
@@ -7558,8 +8207,8 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="71"/>
-      <c r="C74" s="65"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="71"/>
       <c r="D74" s="47" t="s">
         <v>70</v>
       </c>
@@ -7583,8 +8232,8 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="71"/>
-      <c r="C75" s="65"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="71"/>
       <c r="D75" s="47" t="s">
         <v>70</v>
       </c>
@@ -7608,8 +8257,8 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="71"/>
-      <c r="C76" s="65"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="71"/>
       <c r="D76" s="47" t="s">
         <v>70</v>
       </c>
@@ -7633,8 +8282,8 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="71"/>
-      <c r="C77" s="65"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="71"/>
       <c r="D77" s="47" t="s">
         <v>70</v>
       </c>
@@ -7658,8 +8307,8 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="71"/>
-      <c r="C78" s="65"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="71"/>
       <c r="D78" s="47" t="s">
         <v>70</v>
       </c>
@@ -7683,8 +8332,8 @@
       </c>
     </row>
     <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="71"/>
-      <c r="C79" s="65"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="71"/>
       <c r="D79" s="47" t="s">
         <v>70</v>
       </c>
@@ -7708,8 +8357,8 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="71"/>
-      <c r="C80" s="65"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="71"/>
       <c r="D80" s="47" t="s">
         <v>70</v>
       </c>
@@ -7733,8 +8382,8 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="71"/>
-      <c r="C81" s="65"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="71"/>
       <c r="D81" s="47" t="s">
         <v>70</v>
       </c>
@@ -7758,8 +8407,8 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="71"/>
-      <c r="C82" s="65"/>
+      <c r="B82" s="77"/>
+      <c r="C82" s="71"/>
       <c r="D82" s="47" t="s">
         <v>82</v>
       </c>
@@ -7783,8 +8432,8 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="71"/>
-      <c r="C83" s="65"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="71"/>
       <c r="D83" s="47" t="s">
         <v>82</v>
       </c>
@@ -7808,8 +8457,8 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="71"/>
-      <c r="C84" s="65"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="71"/>
       <c r="D84" s="47" t="s">
         <v>148</v>
       </c>
@@ -7833,8 +8482,8 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="71"/>
-      <c r="C85" s="65"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="71"/>
       <c r="D85" s="47" t="s">
         <v>148</v>
       </c>
@@ -7858,8 +8507,8 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="71"/>
-      <c r="C86" s="66"/>
+      <c r="B86" s="77"/>
+      <c r="C86" s="72"/>
       <c r="D86" s="47"/>
       <c r="E86" s="17"/>
       <c r="F86" s="7"/>
@@ -7869,8 +8518,8 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="71"/>
-      <c r="C87" s="67" t="s">
+      <c r="B87" s="77"/>
+      <c r="C87" s="73" t="s">
         <v>153</v>
       </c>
       <c r="D87" s="47" t="s">
@@ -7896,8 +8545,8 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="71"/>
-      <c r="C88" s="68"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="74"/>
       <c r="D88" s="47" t="s">
         <v>157</v>
       </c>
@@ -7921,8 +8570,8 @@
       </c>
     </row>
     <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="71"/>
-      <c r="C89" s="68"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="74"/>
       <c r="D89" s="47"/>
       <c r="E89" s="14"/>
       <c r="F89" s="38"/>
@@ -7932,8 +8581,8 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="71"/>
-      <c r="C90" s="68"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="74"/>
       <c r="D90" s="47"/>
       <c r="E90" s="14"/>
       <c r="F90" s="38"/>
@@ -7943,8 +8592,8 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="71"/>
-      <c r="C91" s="68"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="74"/>
       <c r="D91" s="47"/>
       <c r="E91" s="14"/>
       <c r="F91" s="7"/>
@@ -7954,8 +8603,8 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="71"/>
-      <c r="C92" s="68"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="74"/>
       <c r="D92" s="47"/>
       <c r="E92" s="14"/>
       <c r="F92" s="7"/>
@@ -7965,8 +8614,8 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="71"/>
-      <c r="C93" s="69"/>
+      <c r="B93" s="77"/>
+      <c r="C93" s="75"/>
       <c r="D93" s="47"/>
       <c r="E93" s="14"/>
       <c r="F93" s="7"/>
@@ -7976,8 +8625,8 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="2:10" ht="40" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="71"/>
-      <c r="C94" s="73" t="s">
+      <c r="B94" s="77"/>
+      <c r="C94" s="61" t="s">
         <v>162</v>
       </c>
       <c r="D94" s="46" t="s">
@@ -8003,8 +8652,8 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="71"/>
-      <c r="C95" s="74"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="62"/>
       <c r="D95" s="47"/>
       <c r="E95" s="14"/>
       <c r="F95" s="7"/>
@@ -8014,8 +8663,8 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="71"/>
-      <c r="C96" s="74"/>
+      <c r="B96" s="77"/>
+      <c r="C96" s="62"/>
       <c r="D96" s="7"/>
       <c r="E96" s="14"/>
       <c r="F96" s="7"/>
@@ -8025,8 +8674,8 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="71"/>
-      <c r="C97" s="74"/>
+      <c r="B97" s="77"/>
+      <c r="C97" s="62"/>
       <c r="D97" s="7"/>
       <c r="E97" s="14"/>
       <c r="F97" s="7"/>
@@ -8036,8 +8685,8 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="71"/>
-      <c r="C98" s="74"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="62"/>
       <c r="D98" s="7"/>
       <c r="E98" s="14"/>
       <c r="F98" s="7"/>
@@ -8047,8 +8696,8 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="72"/>
-      <c r="C99" s="75"/>
+      <c r="B99" s="78"/>
+      <c r="C99" s="63"/>
       <c r="D99" s="7"/>
       <c r="E99" s="14"/>
       <c r="F99" s="7"/>
@@ -8058,9 +8707,9 @@
       <c r="J99" s="4"/>
     </row>
     <row r="100" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="83"/>
-      <c r="C100" s="73" t="s">
-        <v>162</v>
+      <c r="B100" s="64"/>
+      <c r="C100" s="61" t="s">
+        <v>346</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>308</v>
@@ -8085,8 +8734,8 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="84"/>
-      <c r="C101" s="74"/>
+      <c r="B101" s="65"/>
+      <c r="C101" s="62"/>
       <c r="D101" s="4" t="s">
         <v>338</v>
       </c>
@@ -8100,8 +8749,8 @@
       <c r="J101" s="4"/>
     </row>
     <row r="102" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="84"/>
-      <c r="C102" s="74"/>
+      <c r="B102" s="65"/>
+      <c r="C102" s="62"/>
       <c r="D102" s="4" t="s">
         <v>339</v>
       </c>
@@ -8115,8 +8764,8 @@
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="84"/>
-      <c r="C103" s="74"/>
+      <c r="B103" s="65"/>
+      <c r="C103" s="62"/>
       <c r="D103" s="4"/>
       <c r="E103" s="14"/>
       <c r="F103" s="4"/>
@@ -8126,8 +8775,8 @@
       <c r="J103" s="4"/>
     </row>
     <row r="104" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="84"/>
-      <c r="C104" s="74"/>
+      <c r="B104" s="65"/>
+      <c r="C104" s="62"/>
       <c r="D104" s="4"/>
       <c r="E104" s="14"/>
       <c r="F104" s="4"/>
@@ -8137,8 +8786,8 @@
       <c r="J104" s="4"/>
     </row>
     <row r="105" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="85"/>
-      <c r="C105" s="75"/>
+      <c r="B105" s="66"/>
+      <c r="C105" s="63"/>
       <c r="D105" s="4"/>
       <c r="E105" s="14"/>
       <c r="F105" s="4"/>
@@ -8165,8 +8814,1993 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D536F01-19A2-4466-A85C-1946BB0ACB53}">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:J127"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+    </row>
+    <row r="2" spans="2:10" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="76" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="77"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="77"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="77"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="77"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="77"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="77"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="77"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="77"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="77"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="77"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="77"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="12"/>
+    </row>
+    <row r="15" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="77"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="12"/>
+    </row>
+    <row r="16" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="77"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="77"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="77"/>
+      <c r="C18" s="73" t="s">
+        <v>344</v>
+      </c>
+      <c r="D18" s="47"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="77"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="77"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="77"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="77"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="77"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="77"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="77"/>
+      <c r="C25" s="61" t="s">
+        <v>345</v>
+      </c>
+      <c r="D25" s="46"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="77"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="77"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="77"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="77"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B30" s="78"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="71" t="s">
+        <v>348</v>
+      </c>
+      <c r="D31" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="77"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="93" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="77"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="77"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="93" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="77"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="77"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="93" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="12"/>
+    </row>
+    <row r="37" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="77"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="93" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="77"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="93" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="39" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="77"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="12"/>
+    </row>
+    <row r="40" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="77"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="77"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="93" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="77"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="77"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="77"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="77"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="12"/>
+    </row>
+    <row r="46" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="77"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="77"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="77"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="77"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="77"/>
+      <c r="C50" s="71"/>
+      <c r="D50" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="77"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="F51" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="12"/>
+    </row>
+    <row r="52" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="77"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="93" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="77"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="12"/>
+    </row>
+    <row r="54" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="77"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="77"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="77"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="77"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="F57" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="12"/>
+    </row>
+    <row r="58" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="77"/>
+      <c r="C58" s="71"/>
+      <c r="D58" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="F58" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="77"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="93" t="s">
+        <v>105</v>
+      </c>
+      <c r="F59" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="12"/>
+    </row>
+    <row r="60" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="77"/>
+      <c r="C60" s="71"/>
+      <c r="D60" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="77"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="77"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="93" t="s">
+        <v>110</v>
+      </c>
+      <c r="F62" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="77"/>
+      <c r="C63" s="71"/>
+      <c r="D63" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="93" t="s">
+        <v>111</v>
+      </c>
+      <c r="F63" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" spans="2:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="77"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="F64" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="12"/>
+    </row>
+    <row r="65" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="77"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="F65" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" s="4"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="12"/>
+    </row>
+    <row r="66" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="77"/>
+      <c r="C66" s="71"/>
+      <c r="D66" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="93" t="s">
+        <v>168</v>
+      </c>
+      <c r="F66" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="4"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="12"/>
+    </row>
+    <row r="67" spans="2:10" ht="54.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="77"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="93" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="4"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="77"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="93" t="s">
+        <v>170</v>
+      </c>
+      <c r="F68" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="4"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="77"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="F69" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" spans="2:10" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="77"/>
+      <c r="C70" s="71"/>
+      <c r="D70" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="93" t="s">
+        <v>124</v>
+      </c>
+      <c r="F70" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="4"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="77"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="77"/>
+      <c r="C72" s="71"/>
+      <c r="D72" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="93" t="s">
+        <v>118</v>
+      </c>
+      <c r="F72" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="77"/>
+      <c r="C73" s="71"/>
+      <c r="D73" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="F73" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="77"/>
+      <c r="C74" s="71"/>
+      <c r="D74" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="F74" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" s="4"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="12"/>
+    </row>
+    <row r="75" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="77"/>
+      <c r="C75" s="71"/>
+      <c r="D75" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="77"/>
+      <c r="C76" s="71"/>
+      <c r="D76" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="F76" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="77"/>
+      <c r="C77" s="71"/>
+      <c r="D77" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="93" t="s">
+        <v>121</v>
+      </c>
+      <c r="F77" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="12"/>
+    </row>
+    <row r="78" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="77"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="F78" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" s="4"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="12"/>
+    </row>
+    <row r="79" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="77"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="F79" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="12"/>
+    </row>
+    <row r="80" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="77"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="97" t="s">
+        <v>135</v>
+      </c>
+      <c r="F80" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="12"/>
+    </row>
+    <row r="81" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="77"/>
+      <c r="C81" s="71"/>
+      <c r="D81" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="12"/>
+    </row>
+    <row r="82" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="77"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" s="93" t="s">
+        <v>47</v>
+      </c>
+      <c r="F82" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="12"/>
+    </row>
+    <row r="83" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="77"/>
+      <c r="C83" s="71"/>
+      <c r="D83" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="12"/>
+    </row>
+    <row r="84" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="77"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E84" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="12"/>
+    </row>
+    <row r="85" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="77"/>
+      <c r="C85" s="71"/>
+      <c r="D85" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" s="93" t="s">
+        <v>131</v>
+      </c>
+      <c r="F85" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="77"/>
+      <c r="C86" s="71"/>
+      <c r="D86" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E86" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="F86" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="77"/>
+      <c r="C87" s="71"/>
+      <c r="D87" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E87" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="F87" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="12"/>
+    </row>
+    <row r="88" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="77"/>
+      <c r="C88" s="71"/>
+      <c r="D88" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E88" s="93" t="s">
+        <v>133</v>
+      </c>
+      <c r="F88" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="12"/>
+    </row>
+    <row r="89" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="77"/>
+      <c r="C89" s="71"/>
+      <c r="D89" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E89" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="F89" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="12"/>
+    </row>
+    <row r="90" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="77"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="F90" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="40"/>
+      <c r="J90" s="12"/>
+    </row>
+    <row r="91" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="77"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="93" t="s">
+        <v>138</v>
+      </c>
+      <c r="F91" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="40"/>
+      <c r="J91" s="12"/>
+    </row>
+    <row r="92" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="77"/>
+      <c r="C92" s="71"/>
+      <c r="D92" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E92" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="40"/>
+      <c r="J92" s="12"/>
+    </row>
+    <row r="93" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="77"/>
+      <c r="C93" s="71"/>
+      <c r="D93" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E93" s="93" t="s">
+        <v>139</v>
+      </c>
+      <c r="F93" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" s="4"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="12"/>
+    </row>
+    <row r="94" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="77"/>
+      <c r="C94" s="71"/>
+      <c r="D94" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E94" s="93" t="s">
+        <v>144</v>
+      </c>
+      <c r="F94" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="40"/>
+      <c r="J94" s="12"/>
+    </row>
+    <row r="95" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="77"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E95" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="F95" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="12"/>
+    </row>
+    <row r="96" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="77"/>
+      <c r="C96" s="71"/>
+      <c r="D96" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E96" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="F96" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="12"/>
+    </row>
+    <row r="97" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="77"/>
+      <c r="C97" s="71"/>
+      <c r="D97" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" s="93" t="s">
+        <v>142</v>
+      </c>
+      <c r="F97" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="12"/>
+    </row>
+    <row r="98" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="77"/>
+      <c r="C98" s="71"/>
+      <c r="D98" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E98" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="F98" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="12"/>
+    </row>
+    <row r="99" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="77"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E99" s="93" t="s">
+        <v>145</v>
+      </c>
+      <c r="F99" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="12"/>
+    </row>
+    <row r="100" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="77"/>
+      <c r="C100" s="71"/>
+      <c r="D100" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E100" s="93" t="s">
+        <v>146</v>
+      </c>
+      <c r="F100" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G100" s="4"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="12"/>
+    </row>
+    <row r="101" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="77"/>
+      <c r="C101" s="71"/>
+      <c r="D101" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E101" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="4"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="12"/>
+    </row>
+    <row r="102" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="77"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E102" s="93" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="12"/>
+    </row>
+    <row r="103" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="77"/>
+      <c r="C103" s="71"/>
+      <c r="D103" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E103" s="93" t="s">
+        <v>178</v>
+      </c>
+      <c r="F103" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="12"/>
+    </row>
+    <row r="104" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="77"/>
+      <c r="C104" s="71"/>
+      <c r="D104" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E104" s="93" t="s">
+        <v>179</v>
+      </c>
+      <c r="F104" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G104" s="4"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="12"/>
+    </row>
+    <row r="105" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="77"/>
+      <c r="C105" s="71"/>
+      <c r="D105" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E105" s="93" t="s">
+        <v>180</v>
+      </c>
+      <c r="F105" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105" s="4"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="12"/>
+    </row>
+    <row r="106" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="77"/>
+      <c r="C106" s="71"/>
+      <c r="D106" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E106" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="F106" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G106" s="4"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="12"/>
+    </row>
+    <row r="107" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="77"/>
+      <c r="C107" s="71"/>
+      <c r="D107" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E107" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="F107" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G107" s="4"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="12"/>
+    </row>
+    <row r="108" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="77"/>
+      <c r="C108" s="71"/>
+      <c r="D108" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E108" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="F108" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="12"/>
+    </row>
+    <row r="109" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="77"/>
+      <c r="C109" s="71"/>
+      <c r="D109" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E109" s="93" t="s">
+        <v>184</v>
+      </c>
+      <c r="F109" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="12"/>
+    </row>
+    <row r="110" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="77"/>
+      <c r="C110" s="71"/>
+      <c r="D110" s="96" t="s">
+        <v>82</v>
+      </c>
+      <c r="E110" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="F110" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="12"/>
+    </row>
+    <row r="111" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="77"/>
+      <c r="C111" s="71"/>
+      <c r="D111" s="96" t="s">
+        <v>82</v>
+      </c>
+      <c r="E111" s="93" t="s">
+        <v>84</v>
+      </c>
+      <c r="F111" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G111" s="4"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="12"/>
+    </row>
+    <row r="112" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="77"/>
+      <c r="C112" s="71"/>
+      <c r="D112" s="96" t="s">
+        <v>148</v>
+      </c>
+      <c r="E112" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F112" s="98" t="s">
+        <v>149</v>
+      </c>
+      <c r="G112" s="4"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="12"/>
+    </row>
+    <row r="113" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="77"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="96" t="s">
+        <v>148</v>
+      </c>
+      <c r="E113" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="F113" s="98" t="s">
+        <v>152</v>
+      </c>
+      <c r="G113" s="4"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="12"/>
+    </row>
+    <row r="114" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="77"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="96"/>
+      <c r="E114" s="93"/>
+      <c r="F114" s="94"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+    </row>
+    <row r="115" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="77"/>
+      <c r="C115" s="73" t="s">
+        <v>349</v>
+      </c>
+      <c r="D115" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="F115" s="98" t="s">
+        <v>160</v>
+      </c>
+      <c r="G115" s="4"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="12"/>
+    </row>
+    <row r="116" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="77"/>
+      <c r="C116" s="74"/>
+      <c r="D116" s="96" t="s">
+        <v>157</v>
+      </c>
+      <c r="E116" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="F116" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="G116" s="4"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="12"/>
+    </row>
+    <row r="117" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="77"/>
+      <c r="C117" s="74"/>
+      <c r="D117" s="96"/>
+      <c r="E117" s="97"/>
+      <c r="F117" s="98"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+    </row>
+    <row r="118" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="77"/>
+      <c r="C118" s="74"/>
+      <c r="D118" s="96"/>
+      <c r="E118" s="97"/>
+      <c r="F118" s="98"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+    </row>
+    <row r="119" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="77"/>
+      <c r="C119" s="74"/>
+      <c r="D119" s="96"/>
+      <c r="E119" s="97"/>
+      <c r="F119" s="94"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+    </row>
+    <row r="120" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="77"/>
+      <c r="C120" s="74"/>
+      <c r="D120" s="96"/>
+      <c r="E120" s="97"/>
+      <c r="F120" s="94"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+    </row>
+    <row r="121" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="77"/>
+      <c r="C121" s="75"/>
+      <c r="D121" s="96"/>
+      <c r="E121" s="97"/>
+      <c r="F121" s="94"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+    </row>
+    <row r="122" spans="2:10" ht="40" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="77"/>
+      <c r="C122" s="61" t="s">
+        <v>350</v>
+      </c>
+      <c r="D122" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="E122" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="F122" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="G122" s="4"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="12"/>
+    </row>
+    <row r="123" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="77"/>
+      <c r="C123" s="62"/>
+      <c r="D123" s="47"/>
+      <c r="E123" s="14"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+    </row>
+    <row r="124" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="77"/>
+      <c r="C124" s="62"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="14"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+    </row>
+    <row r="125" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="77"/>
+      <c r="C125" s="62"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="14"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="77"/>
+      <c r="C126" s="62"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="14"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" spans="2:10" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="78"/>
+      <c r="C127" s="63"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="14"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B31:B127"/>
+    <mergeCell ref="C31:C114"/>
+    <mergeCell ref="C115:C121"/>
+    <mergeCell ref="C122:C127"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:B30"/>
+    <mergeCell ref="C3:C17"/>
+    <mergeCell ref="C18:C24"/>
+    <mergeCell ref="C25:C30"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D411216B-B5B7-4B48-B0D3-CF2BB4857B38}">
   <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J62"/>
@@ -8184,24 +10818,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="15" t="s">
         <v>1</v>
       </c>
@@ -8223,10 +10857,10 @@
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="48"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="82" t="s">
         <v>273</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -8253,8 +10887,8 @@
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="48"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
       <c r="D4" s="45" t="s">
         <v>188</v>
       </c>
@@ -8279,8 +10913,8 @@
     </row>
     <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="48"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
       <c r="D5" s="45" t="s">
         <v>189</v>
       </c>
@@ -8305,8 +10939,8 @@
     </row>
     <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="48"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
       <c r="D6" s="45" t="s">
         <v>189</v>
       </c>
@@ -8331,8 +10965,8 @@
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48"/>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
       <c r="D7" s="45" t="s">
         <v>24</v>
       </c>
@@ -8357,8 +10991,8 @@
     </row>
     <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="48"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
       <c r="D8" s="45" t="s">
         <v>29</v>
       </c>
@@ -8383,8 +11017,8 @@
     </row>
     <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="48"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
       <c r="D9" s="45" t="s">
         <v>45</v>
       </c>
@@ -8409,8 +11043,8 @@
     </row>
     <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="48"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
       <c r="D10" s="45" t="s">
         <v>54</v>
       </c>
@@ -8435,8 +11069,8 @@
     </row>
     <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="48"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="45" t="s">
         <v>53</v>
       </c>
@@ -8461,8 +11095,8 @@
     </row>
     <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="48"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
       <c r="D12" s="45" t="s">
         <v>195</v>
       </c>
@@ -8487,8 +11121,8 @@
     </row>
     <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="48"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
       <c r="D13" s="45" t="s">
         <v>70</v>
       </c>
@@ -8513,8 +11147,8 @@
     </row>
     <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="48"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="45" t="s">
         <v>82</v>
       </c>
@@ -8539,8 +11173,8 @@
     </row>
     <row r="15" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="48"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="45"/>
       <c r="E15" s="17"/>
       <c r="F15" s="38"/>
@@ -8551,8 +11185,8 @@
     </row>
     <row r="16" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="48"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="45" t="s">
         <v>278</v>
       </c>
@@ -8575,8 +11209,8 @@
     </row>
     <row r="17" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="48"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
       <c r="D17" s="46" t="s">
         <v>279</v>
       </c>
@@ -8599,8 +11233,8 @@
     </row>
     <row r="18" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="48"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
       <c r="D18" s="45"/>
       <c r="E18" s="17"/>
       <c r="F18" s="38"/>
@@ -8611,8 +11245,8 @@
     </row>
     <row r="19" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="48"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="45"/>
       <c r="E19" s="17"/>
       <c r="F19" s="38"/>
@@ -8623,8 +11257,8 @@
     </row>
     <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="48"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="77" t="s">
+      <c r="B20" s="77"/>
+      <c r="C20" s="83" t="s">
         <v>275</v>
       </c>
       <c r="D20" s="47" t="s">
@@ -8651,8 +11285,8 @@
     </row>
     <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="48"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
       <c r="D21" s="47" t="s">
         <v>250</v>
       </c>
@@ -8677,8 +11311,8 @@
     </row>
     <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="48"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
       <c r="D22" s="47" t="s">
         <v>250</v>
       </c>
@@ -8703,8 +11337,8 @@
     </row>
     <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="48"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="47" t="s">
         <v>250</v>
       </c>
@@ -8729,8 +11363,8 @@
     </row>
     <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="48"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
       <c r="D24" s="47" t="s">
         <v>250</v>
       </c>
@@ -8755,8 +11389,8 @@
     </row>
     <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="48"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
       <c r="D25" s="47" t="s">
         <v>250</v>
       </c>
@@ -8781,8 +11415,8 @@
     </row>
     <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="48"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
       <c r="D26" s="47" t="s">
         <v>250</v>
       </c>
@@ -8807,8 +11441,8 @@
     </row>
     <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="48"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
       <c r="D27" s="47" t="s">
         <v>250</v>
       </c>
@@ -8833,8 +11467,8 @@
     </row>
     <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="48"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
       <c r="D28" s="47" t="s">
         <v>250</v>
       </c>
@@ -8859,8 +11493,8 @@
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="48"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
       <c r="D29" s="47" t="s">
         <v>250</v>
       </c>
@@ -8885,8 +11519,8 @@
     </row>
     <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="48"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
       <c r="D30" s="47" t="s">
         <v>250</v>
       </c>
@@ -8911,8 +11545,8 @@
     </row>
     <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="48"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
       <c r="D31" s="47" t="s">
         <v>250</v>
       </c>
@@ -8937,8 +11571,8 @@
     </row>
     <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="48"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
       <c r="D32" s="47" t="s">
         <v>250</v>
       </c>
@@ -8963,8 +11597,8 @@
     </row>
     <row r="33" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="48"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
       <c r="D33" s="47"/>
       <c r="E33" s="17"/>
       <c r="F33" s="38"/>
@@ -8975,8 +11609,8 @@
     </row>
     <row r="34" spans="1:10" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="48"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
       <c r="D34" s="46" t="s">
         <v>281</v>
       </c>
@@ -9001,8 +11635,8 @@
     </row>
     <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="48"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
       <c r="D35" s="46" t="s">
         <v>281</v>
       </c>
@@ -9027,8 +11661,8 @@
     </row>
     <row r="36" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="48"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
       <c r="D36" s="46"/>
       <c r="E36" s="17"/>
       <c r="F36" s="38"/>
@@ -9039,8 +11673,8 @@
     </row>
     <row r="37" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="48"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
       <c r="D37" s="46"/>
       <c r="E37" s="17"/>
       <c r="F37" s="38"/>
@@ -9051,8 +11685,8 @@
     </row>
     <row r="38" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="48"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
       <c r="D38" s="46"/>
       <c r="E38" s="17"/>
       <c r="F38" s="38"/>
@@ -9063,8 +11697,8 @@
     </row>
     <row r="39" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="48"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="72"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="78"/>
       <c r="D39" s="47"/>
       <c r="E39" s="17"/>
       <c r="F39" s="38"/>
@@ -9075,8 +11709,8 @@
     </row>
     <row r="40" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="48"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="78" t="s">
+      <c r="B40" s="77"/>
+      <c r="C40" s="79" t="s">
         <v>285</v>
       </c>
       <c r="D40" s="47" t="s">
@@ -9103,8 +11737,8 @@
     </row>
     <row r="41" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="48"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
       <c r="D41" s="47" t="s">
         <v>286</v>
       </c>
@@ -9129,8 +11763,8 @@
     </row>
     <row r="42" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="48"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
       <c r="D42" s="46" t="s">
         <v>289</v>
       </c>
@@ -9155,8 +11789,8 @@
     </row>
     <row r="43" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="48"/>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
       <c r="D43" s="46" t="s">
         <v>289</v>
       </c>
@@ -9181,8 +11815,8 @@
     </row>
     <row r="44" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="48"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
       <c r="D44" s="54" t="s">
         <v>300</v>
       </c>
@@ -9207,8 +11841,8 @@
     </row>
     <row r="45" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="48"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
       <c r="D45" s="46"/>
       <c r="E45" s="17"/>
       <c r="F45" s="38"/>
@@ -9219,8 +11853,8 @@
     </row>
     <row r="46" spans="1:10" ht="60" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="48"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
       <c r="D46" s="46" t="s">
         <v>290</v>
       </c>
@@ -9245,8 +11879,8 @@
     </row>
     <row r="47" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="48"/>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
       <c r="D47" s="47"/>
       <c r="E47" s="14"/>
       <c r="F47" s="38"/>
@@ -9257,8 +11891,8 @@
     </row>
     <row r="48" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="48"/>
-      <c r="B48" s="71"/>
-      <c r="C48" s="71"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
       <c r="D48" s="47"/>
       <c r="E48" s="14"/>
       <c r="F48" s="38"/>
@@ -9269,8 +11903,8 @@
     </row>
     <row r="49" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="48"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="78"/>
       <c r="D49" s="47"/>
       <c r="E49" s="14"/>
       <c r="F49" s="38"/>
@@ -9280,10 +11914,10 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="61" t="s">
         <v>330</v>
       </c>
-      <c r="C50" s="78" t="s">
+      <c r="C50" s="79" t="s">
         <v>312</v>
       </c>
       <c r="D50" s="47" t="s">
@@ -9307,8 +11941,8 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="74"/>
-      <c r="C51" s="86"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="80"/>
       <c r="D51" s="47" t="s">
         <v>318</v>
       </c>
@@ -9330,8 +11964,8 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="74"/>
-      <c r="C52" s="86"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="80"/>
       <c r="D52" s="47" t="s">
         <v>319</v>
       </c>
@@ -9353,8 +11987,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="74"/>
-      <c r="C53" s="86"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="80"/>
       <c r="D53" s="47" t="s">
         <v>320</v>
       </c>
@@ -9376,8 +12010,8 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="74"/>
-      <c r="C54" s="86"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="80"/>
       <c r="D54" s="47" t="s">
         <v>24</v>
       </c>
@@ -9399,8 +12033,8 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="74"/>
-      <c r="C55" s="86"/>
+      <c r="B55" s="62"/>
+      <c r="C55" s="80"/>
       <c r="D55" s="47" t="s">
         <v>322</v>
       </c>
@@ -9422,8 +12056,8 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="74"/>
-      <c r="C56" s="86"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="80"/>
       <c r="D56" s="47" t="s">
         <v>322</v>
       </c>
@@ -9445,8 +12079,8 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="74"/>
-      <c r="C57" s="86"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="80"/>
       <c r="D57" s="47" t="s">
         <v>325</v>
       </c>
@@ -9468,8 +12102,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="74"/>
-      <c r="C58" s="86"/>
+      <c r="B58" s="62"/>
+      <c r="C58" s="80"/>
       <c r="D58" s="47" t="s">
         <v>325</v>
       </c>
@@ -9491,8 +12125,8 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="74"/>
-      <c r="C59" s="86"/>
+      <c r="B59" s="62"/>
+      <c r="C59" s="80"/>
       <c r="D59" s="47" t="s">
         <v>331</v>
       </c>
@@ -9514,8 +12148,8 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="74"/>
-      <c r="C60" s="86"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="80"/>
       <c r="D60" s="47" t="s">
         <v>331</v>
       </c>
@@ -9537,8 +12171,8 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="74"/>
-      <c r="C61" s="86"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="80"/>
       <c r="D61" s="47" t="s">
         <v>332</v>
       </c>
@@ -9562,8 +12196,8 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="75"/>
-      <c r="C62" s="87"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="81"/>
       <c r="D62" s="47" t="s">
         <v>334</v>
       </c>
@@ -9601,7 +12235,1072 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23C7BF2-6BED-42A4-83C3-6FD9F1E11BB8}">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K61"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" style="42" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.58203125" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+    </row>
+    <row r="2" spans="1:10" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="48"/>
+      <c r="B3" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="48"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="48"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="48"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="48"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="48"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="48"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="48"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="48"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="48"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="48"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="48"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="G14" s="4"/>
+      